--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>##var</t>
   </si>
@@ -116,7 +116,16 @@
     <t>demo.Reward</t>
   </si>
   <si>
-    <t>reward.xlsx</t>
+    <t>1@reward.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbMapAreaInfo</t>
+  </si>
+  <si>
+    <t>demo.MapAreaInfo</t>
+  </si>
+  <si>
+    <t>area_info@map.xlsx</t>
   </si>
 </sst>
 </file>
@@ -732,11 +741,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="22">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1058,8 +1073,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3"/>
+  <dimension ref="A1:K5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
@@ -1169,11 +1184,29 @@
       <c r="D4" t="b">
         <v>1</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="2" t="s">
         <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="B5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E4" r:id="rId1" display="1@reward.xlsx"/>
+    <hyperlink ref="E5" r:id="rId2" display="area_info@map.xlsx" tooltip="mailto:area_info@map.xlsx"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
   <si>
     <t>##var</t>
   </si>
@@ -126,6 +126,24 @@
   </si>
   <si>
     <t>area_info@map.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbDropBundle</t>
+  </si>
+  <si>
+    <t>demo.DropBundle</t>
+  </si>
+  <si>
+    <t>drop_bundle@drop.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbDropItem</t>
+  </si>
+  <si>
+    <t>demo.DropItem</t>
+  </si>
+  <si>
+    <t>drop_item@drop.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1073,8 +1091,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:K7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
@@ -1202,10 +1220,40 @@
         <v>32</v>
       </c>
     </row>
+    <row r="6" spans="1:11">
+      <c r="B6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="B7" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="1@reward.xlsx"/>
     <hyperlink ref="E5" r:id="rId2" display="area_info@map.xlsx" tooltip="mailto:area_info@map.xlsx"/>
+    <hyperlink ref="E6" r:id="rId3" display="drop_bundle@drop.xlsx"/>
+    <hyperlink ref="E7" r:id="rId4" display="drop_item@drop.xlsx" tooltip="mailto:drop_item@drop.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
   <si>
     <t>##var</t>
   </si>
@@ -144,6 +144,15 @@
   </si>
   <si>
     <t>drop_item@drop.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbFixedFacility</t>
+  </si>
+  <si>
+    <t>demo.FixedFacility</t>
+  </si>
+  <si>
+    <t>fixed_facility@home_facility.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1091,8 +1100,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="6"/>
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
@@ -1248,12 +1257,27 @@
         <v>38</v>
       </c>
     </row>
+    <row r="8" spans="1:11">
+      <c r="B8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="1@reward.xlsx"/>
     <hyperlink ref="E5" r:id="rId2" display="area_info@map.xlsx" tooltip="mailto:area_info@map.xlsx"/>
     <hyperlink ref="E6" r:id="rId3" display="drop_bundle@drop.xlsx"/>
     <hyperlink ref="E7" r:id="rId4" display="drop_item@drop.xlsx" tooltip="mailto:drop_item@drop.xlsx"/>
+    <hyperlink ref="E8" r:id="rId5" display="fixed_facility@home_facility.xlsx" tooltip="mailto:fixed_facility@home_facility.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
   <si>
     <t>##var</t>
   </si>
@@ -153,6 +153,33 @@
   </si>
   <si>
     <t>fixed_facility@home_facility.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbBornPoint</t>
+  </si>
+  <si>
+    <t>demo.BornPoint</t>
+  </si>
+  <si>
+    <t>born_points@born_points.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbUnitNpc</t>
+  </si>
+  <si>
+    <t>demo.UnitNpc</t>
+  </si>
+  <si>
+    <t>unit_npc@unit_npc.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbUnitNpcAttr</t>
+  </si>
+  <si>
+    <t>demo.UnitNpcAttr</t>
+  </si>
+  <si>
+    <t>unit_npc_attribute@unit_npc.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1100,8 +1127,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="7"/>
+  <dimension ref="A1:K11"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
     <col min="3" max="3" width="15.625" customWidth="1"/>
@@ -1271,6 +1298,48 @@
         <v>41</v>
       </c>
     </row>
+    <row r="9" spans="1:11">
+      <c r="B9" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="B10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="B11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="1@reward.xlsx"/>
@@ -1278,6 +1347,9 @@
     <hyperlink ref="E6" r:id="rId3" display="drop_bundle@drop.xlsx"/>
     <hyperlink ref="E7" r:id="rId4" display="drop_item@drop.xlsx" tooltip="mailto:drop_item@drop.xlsx"/>
     <hyperlink ref="E8" r:id="rId5" display="fixed_facility@home_facility.xlsx" tooltip="mailto:fixed_facility@home_facility.xlsx"/>
+    <hyperlink ref="E9" r:id="rId6" display="born_points@born_points.xlsx" tooltip="mailto:born_points@born_points.xlsx"/>
+    <hyperlink ref="E10" r:id="rId7" display="unit_npc@unit_npc.xlsx" tooltip="mailto:unit_npc@unit_npc.xlsx"/>
+    <hyperlink ref="E11" r:id="rId8" display="unit_npc_attribute@unit_npc.xlsx" tooltip="mailto:unit_npc_attribute@unit_npc.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
   <si>
     <t>##var</t>
   </si>
@@ -180,6 +180,42 @@
   </si>
   <si>
     <t>unit_npc_attribute@unit_npc.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbQuestData</t>
+  </si>
+  <si>
+    <t>demo.QuestData</t>
+  </si>
+  <si>
+    <t>quest_data@quests.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbQuestStepData</t>
+  </si>
+  <si>
+    <t>demo.QuestStepData</t>
+  </si>
+  <si>
+    <t>quest_step_data@quests.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbQuestStepOutcome</t>
+  </si>
+  <si>
+    <t>demo.QuestStepOutcome</t>
+  </si>
+  <si>
+    <t>quest_step_outcome@quests.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbQuestStepObjective</t>
+  </si>
+  <si>
+    <t>demo.QuestStepObjective</t>
+  </si>
+  <si>
+    <t>quest_step_objective@quests.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1127,7 +1163,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -1340,6 +1376,62 @@
         <v>50</v>
       </c>
     </row>
+    <row r="12" spans="1:11">
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="s">
+        <v>55</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="B14" t="s">
+        <v>57</v>
+      </c>
+      <c r="C14" t="s">
+        <v>58</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15" t="s">
+        <v>61</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E4" r:id="rId1" display="1@reward.xlsx"/>
@@ -1350,6 +1442,10 @@
     <hyperlink ref="E9" r:id="rId6" display="born_points@born_points.xlsx" tooltip="mailto:born_points@born_points.xlsx"/>
     <hyperlink ref="E10" r:id="rId7" display="unit_npc@unit_npc.xlsx" tooltip="mailto:unit_npc@unit_npc.xlsx"/>
     <hyperlink ref="E11" r:id="rId8" display="unit_npc_attribute@unit_npc.xlsx" tooltip="mailto:unit_npc_attribute@unit_npc.xlsx"/>
+    <hyperlink ref="E12" r:id="rId9" display="quest_data@quests.xlsx" tooltip="mailto:quest_data@quests.xlsx"/>
+    <hyperlink ref="E13" r:id="rId10" display="quest_step_data@quests.xlsx" tooltip="mailto:quest_step_data@quests.xlsx"/>
+    <hyperlink ref="E14" r:id="rId11" display="quest_step_outcome@quests.xlsx" tooltip="mailto:quest_step_outcome@quests.xlsx"/>
+    <hyperlink ref="E15" r:id="rId12" display="quest_step_objective@quests.xlsx" tooltip="mailto:quest_step_objective@quests.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
   <si>
     <t>##var</t>
   </si>
@@ -216,6 +216,15 @@
   </si>
   <si>
     <t>quest_step_objective@quests.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbDialogMetaInfo</t>
+  </si>
+  <si>
+    <t>demo.DialogMetaInfo</t>
+  </si>
+  <si>
+    <t>dialog_meta_info@dialog.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1163,7 +1172,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K15"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -1430,6 +1439,20 @@
       </c>
       <c r="E15" s="3" t="s">
         <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="B16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1446,6 +1469,7 @@
     <hyperlink ref="E13" r:id="rId10" display="quest_step_data@quests.xlsx" tooltip="mailto:quest_step_data@quests.xlsx"/>
     <hyperlink ref="E14" r:id="rId11" display="quest_step_outcome@quests.xlsx" tooltip="mailto:quest_step_outcome@quests.xlsx"/>
     <hyperlink ref="E15" r:id="rId12" display="quest_step_objective@quests.xlsx" tooltip="mailto:quest_step_objective@quests.xlsx"/>
+    <hyperlink ref="E16" r:id="rId13" display="dialog_meta_info@dialog.xlsx" tooltip="mailto:dialog_meta_info@dialog.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="69">
   <si>
     <t>##var</t>
   </si>
@@ -225,6 +225,15 @@
   </si>
   <si>
     <t>dialog_meta_info@dialog.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbItemData</t>
+  </si>
+  <si>
+    <t>demo.ItemData</t>
+  </si>
+  <si>
+    <t>item@item.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1181,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.375" customWidth="1"/>
@@ -1453,6 +1462,20 @@
       </c>
       <c r="E16" s="3" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5">
+      <c r="B17" t="s">
+        <v>66</v>
+      </c>
+      <c r="C17" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
@@ -1470,6 +1493,7 @@
     <hyperlink ref="E14" r:id="rId11" display="quest_step_outcome@quests.xlsx" tooltip="mailto:quest_step_outcome@quests.xlsx"/>
     <hyperlink ref="E15" r:id="rId12" display="quest_step_objective@quests.xlsx" tooltip="mailto:quest_step_objective@quests.xlsx"/>
     <hyperlink ref="E16" r:id="rId13" display="dialog_meta_info@dialog.xlsx" tooltip="mailto:dialog_meta_info@dialog.xlsx"/>
+    <hyperlink ref="E17" r:id="rId14" display="item@item.xlsx" tooltip="mailto:item@item.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K19"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="4" min="2" max="2"/>
@@ -1456,42 +1456,62 @@
       </c>
     </row>
     <row r="18">
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="0" t="inlineStr">
         <is>
           <t>demo.TbShop</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>demo.Shop</t>
         </is>
       </c>
-      <c r="D18" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" t="inlineStr">
+      <c r="D18" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="0" t="inlineStr">
         <is>
           <t>shop@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="0" t="inlineStr">
         <is>
           <t>demo.TbShopGoods</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>demo.ShopGoods</t>
         </is>
       </c>
-      <c r="D19" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" t="inlineStr">
+      <c r="D19" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
         <is>
           <t>shop_goods@shop.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>demo.TbItemUse</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>demo.ItemUse</t>
+        </is>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>item_use@item_use.xlsx</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1496,22 +1496,22 @@
       </c>
     </row>
     <row r="20">
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="0" t="inlineStr">
         <is>
           <t>demo.TbItemUse</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>demo.ItemUse</t>
         </is>
       </c>
-      <c r="D20" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>item_use@item_use.xlsx</t>
+      <c r="D20" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="0" t="inlineStr">
+        <is>
+          <t>item_use@item.xlsx</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="4" min="2" max="2"/>
@@ -1512,6 +1512,26 @@
       <c r="E20" s="0" t="inlineStr">
         <is>
           <t>item_use@item.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>demo.TbNpcDialogInfo</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>demo.NpcDialogInfo</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>npc_dialog_info@dialog.xlsx</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="4" min="2" max="2"/>
@@ -1516,22 +1516,92 @@
       </c>
     </row>
     <row r="21">
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="0" t="inlineStr">
         <is>
           <t>demo.TbNpcDialogInfo</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>demo.NpcDialogInfo</t>
         </is>
       </c>
-      <c r="D21" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="D21" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="0" t="inlineStr">
         <is>
           <t>npc_dialog_info@dialog.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>demo.TbWorldMapArea</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>demo.WorldMapArea</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>world_map_area@map.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>demo.TbWorldMapRoomRule</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>demo.WorldMapRoomRule</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>world_map_room_rule@map.xlsx</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>demo.TbWorldMapSettings</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>demo.WorldMapSettings</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>world_map_settings@map.xlsx</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>one</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K24"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="4" min="2" max="2"/>
@@ -1536,72 +1536,52 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>demo.TbWorldMapArea</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>demo.WorldMapArea</t>
-        </is>
-      </c>
-      <c r="D22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>world_map_area@map.xlsx</t>
+      <c r="B22" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbWorldMapGlobal</t>
+        </is>
+      </c>
+      <c r="C22" s="0" t="inlineStr">
+        <is>
+          <t>demo.WorldMapGlobal</t>
+        </is>
+      </c>
+      <c r="D22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
+        <is>
+          <t>world_map_global@map.xlsx</t>
+        </is>
+      </c>
+      <c r="G22" s="0" t="inlineStr">
+        <is>
+          <t>one</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>demo.TbWorldMapRoomRule</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>demo.WorldMapRoomRule</t>
-        </is>
-      </c>
-      <c r="D23" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>world_map_room_rule@map.xlsx</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbWorldMapBigMapLayer</t>
+        </is>
+      </c>
+      <c r="C23" s="0" t="inlineStr">
+        <is>
+          <t>demo.WorldMapBigMapLayer</t>
+        </is>
+      </c>
+      <c r="D23" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="0" t="inlineStr">
+        <is>
+          <t>world_map_big_map@map.xlsx</t>
+        </is>
+      </c>
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>list</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>demo.TbWorldMapSettings</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>demo.WorldMapSettings</t>
-        </is>
-      </c>
-      <c r="D24" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>world_map_settings@map.xlsx</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>one</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1018,7 +1018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="4" min="2" max="2"/>
@@ -1582,6 +1582,26 @@
       <c r="G23" s="0" t="inlineStr">
         <is>
           <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbDreamInfiltrationSpot</t>
+        </is>
+      </c>
+      <c r="C24" s="0" t="inlineStr">
+        <is>
+          <t>demo.DreamInfiltrationSpot</t>
+        </is>
+      </c>
+      <c r="D24" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="E24" s="0" t="inlineStr">
+        <is>
+          <t>dream_infiltration@dream_infiltration.xlsx</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
   <si>
     <t>##var</t>
   </si>
@@ -321,6 +321,15 @@
   </si>
   <si>
     <t>fishing_spot_fish@fishing_spot.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbPlayerDesireLevel</t>
+  </si>
+  <si>
+    <t>demo.PlayerDesireLevel</t>
+  </si>
+  <si>
+    <t>player_desire_level@player_status.xlsx</t>
   </si>
 </sst>
 </file>
@@ -936,7 +945,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -951,6 +960,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1272,7 +1284,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K26"/>
+  <dimension ref="A1:K27"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.375" style="2" customWidth="1"/>
@@ -1699,6 +1711,20 @@
       </c>
       <c r="E26" s="5" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7">
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" t="s">
+        <v>99</v>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1719,6 +1745,7 @@
     <hyperlink ref="E17" r:id="rId14" display="item@item.xlsx" tooltip="mailto:item@item.xlsx"/>
     <hyperlink ref="E25" r:id="rId15" display="fishing_spot@fishing_spot.xlsx"/>
     <hyperlink ref="E26" r:id="rId16" display="fishing_spot_fish@fishing_spot.xlsx"/>
+    <hyperlink ref="E27" r:id="rId17" display="player_desire_level@player_status.xlsx" tooltip="mailto:player_desire_level@player_status.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="107">
   <si>
     <t>##var</t>
   </si>
@@ -330,6 +330,24 @@
   </si>
   <si>
     <t>player_desire_level@player_status.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbWantedLevelInfo</t>
+  </si>
+  <si>
+    <t>demo.WantedLevelInfo</t>
+  </si>
+  <si>
+    <t>wanted_level_info@wanted.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbWantedBehaveInfo</t>
+  </si>
+  <si>
+    <t>demo.WantedBehaveInfo</t>
+  </si>
+  <si>
+    <t>wanted_behave_info@wanted.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1284,7 +1302,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K27"/>
+  <dimension ref="A1:K29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="20.375" style="2" customWidth="1"/>
@@ -1725,6 +1743,34 @@
       </c>
       <c r="E27" s="6" t="s">
         <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7">
+      <c r="B28" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" t="s">
+        <v>102</v>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7">
+      <c r="B29" t="s">
+        <v>104</v>
+      </c>
+      <c r="C29" t="s">
+        <v>105</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1746,6 +1792,8 @@
     <hyperlink ref="E25" r:id="rId15" display="fishing_spot@fishing_spot.xlsx"/>
     <hyperlink ref="E26" r:id="rId16" display="fishing_spot_fish@fishing_spot.xlsx"/>
     <hyperlink ref="E27" r:id="rId17" display="player_desire_level@player_status.xlsx" tooltip="mailto:player_desire_level@player_status.xlsx"/>
+    <hyperlink ref="E28" r:id="rId18" display="wanted_level_info@wanted.xlsx" tooltip="mailto:wanted_level_info@wanted.xlsx"/>
+    <hyperlink ref="E29" r:id="rId19" display="wanted_behave_info@wanted.xlsx" tooltip="mailto:wanted_behave_info@wanted.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1024,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:K34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -1732,22 +1732,82 @@
       </c>
     </row>
     <row r="31">
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="0" t="inlineStr">
         <is>
           <t>demo.TbWantedGuardSpawnTier</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="0" t="inlineStr">
         <is>
           <t>demo.WantedGuardSpawnTier</t>
         </is>
       </c>
-      <c r="D31" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="D31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
         <is>
           <t>wanted_guard_spawn@wanted.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbEntitySkillData</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="inlineStr">
+        <is>
+          <t>demo.EntitySkillData</t>
+        </is>
+      </c>
+      <c r="D32" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="0" t="inlineStr">
+        <is>
+          <t>entity_skill@skill.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbSkillSchool</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>demo.SkillSchool</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>skill_school@skill.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbSkillLearnEntry</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>demo.SkillLearnEntry</t>
+        </is>
+      </c>
+      <c r="D34" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>skill_learn@skill.xlsx</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1024,7 +1024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K34"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="20.375" customWidth="1" style="2" min="2" max="2"/>
@@ -1808,6 +1808,86 @@
       <c r="E34" s="0" t="inlineStr">
         <is>
           <t>skill_learn@skill.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbDesireCrystalDef</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="inlineStr">
+        <is>
+          <t>demo.DesireCrystalDef</t>
+        </is>
+      </c>
+      <c r="D35" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="0" t="inlineStr">
+        <is>
+          <t>desire_crystal_def@desire_crystal.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbMapDesireCrystalBudget</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>demo.MapDesireCrystalBudget</t>
+        </is>
+      </c>
+      <c r="D36" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbMapWalkerDesireCrystalQuota</t>
+        </is>
+      </c>
+      <c r="C37" s="0" t="inlineStr">
+        <is>
+          <t>demo.MapWalkerDesireCrystalQuota</t>
+        </is>
+      </c>
+      <c r="D37" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="0" t="inlineStr">
+        <is>
+          <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbNamedNpcDesireCrystal</t>
+        </is>
+      </c>
+      <c r="C38" s="0" t="inlineStr">
+        <is>
+          <t>demo.NamedNpcDesireCrystal</t>
+        </is>
+      </c>
+      <c r="D38" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="0" t="inlineStr">
+        <is>
+          <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="155">
   <si>
     <t>##var</t>
   </si>
@@ -350,6 +350,15 @@
     <t>player_san_corrupt_level@player_status.xlsx</t>
   </si>
   <si>
+    <t>demo.TbPlayerClothesExposeInfo</t>
+  </si>
+  <si>
+    <t>demo.PlayerClothesExposeInfo</t>
+  </si>
+  <si>
+    <t>player_clothes_expose_info@player_status.xlsx</t>
+  </si>
+  <si>
     <t>demo.TbWantedLevelInfo</t>
   </si>
   <si>
@@ -474,6 +483,15 @@
   </si>
   <si>
     <t>container_stack_tag_rule@container_stack.xlsx</t>
+  </si>
+  <si>
+    <t>demo.TbMapAreaEffect</t>
+  </si>
+  <si>
+    <t>demo.MapAreaEffect</t>
+  </si>
+  <si>
+    <t>map_area_effect@map_area_effect.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1089,7 +1107,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1101,6 +1119,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1422,7 +1443,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:K47"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="2" max="2" width="67.75" style="2" customWidth="1"/>
@@ -1900,24 +1921,24 @@
       </c>
     </row>
     <row r="31" spans="2:7">
-      <c r="B31"/>
-      <c r="C31"/>
-      <c r="D31"/>
-      <c r="E31" s="4"/>
+      <c r="B31" t="s">
+        <v>107</v>
+      </c>
+      <c r="C31" t="s">
+        <v>108</v>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>109</v>
+      </c>
     </row>
     <row r="32" spans="2:7">
-      <c r="B32" t="s">
-        <v>107</v>
-      </c>
-      <c r="C32" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="4" t="s">
-        <v>109</v>
-      </c>
+      <c r="B32"/>
+      <c r="C32"/>
+      <c r="D32"/>
+      <c r="E32" s="4"/>
     </row>
     <row r="33" spans="2:5">
       <c r="B33" t="s">
@@ -1943,7 +1964,7 @@
       <c r="D34" t="b">
         <v>1</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E34" s="4" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2099,6 +2120,34 @@
       </c>
       <c r="E45" t="s">
         <v>148</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5">
+      <c r="B46" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" t="s">
+        <v>150</v>
+      </c>
+      <c r="D46" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5">
+      <c r="B47" t="s">
+        <v>152</v>
+      </c>
+      <c r="C47" t="s">
+        <v>153</v>
+      </c>
+      <c r="D47" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" t="s">
+        <v>154</v>
       </c>
     </row>
   </sheetData>
@@ -2120,10 +2169,11 @@
     <hyperlink ref="E25" r:id="rId15" display="fishing_spot@fishing_spot.xlsx"/>
     <hyperlink ref="E26" r:id="rId16" display="fishing_spot_fish@fishing_spot.xlsx"/>
     <hyperlink ref="E28" r:id="rId17" display="player_desire_level@player_status.xlsx" tooltip="mailto:player_desire_level@player_status.xlsx"/>
-    <hyperlink ref="E32" r:id="rId18" display="wanted_level_info@wanted.xlsx" tooltip="mailto:wanted_level_info@wanted.xlsx"/>
-    <hyperlink ref="E33" r:id="rId19" display="wanted_behave_info@wanted.xlsx" tooltip="mailto:wanted_behave_info@wanted.xlsx"/>
-    <hyperlink ref="E29" r:id="rId20" display="player_jingyu_level@player_status.xlsx" tooltip="mailto:player_jingyu_level@player_status.xlsx"/>
-    <hyperlink ref="E30" r:id="rId21" display="player_san_corrupt_level@player_status.xlsx" tooltip="mailto:player_san_corrupt_level@player_status.xlsx"/>
+    <hyperlink ref="E29" r:id="rId18" display="player_jingyu_level@player_status.xlsx" tooltip="mailto:player_jingyu_level@player_status.xlsx"/>
+    <hyperlink ref="E30" r:id="rId19" display="player_san_corrupt_level@player_status.xlsx" tooltip="mailto:player_san_corrupt_level@player_status.xlsx"/>
+    <hyperlink ref="E33" r:id="rId20" display="wanted_level_info@wanted.xlsx" tooltip="mailto:wanted_level_info@wanted.xlsx"/>
+    <hyperlink ref="E34" r:id="rId21" display="wanted_behave_info@wanted.xlsx" tooltip="mailto:wanted_behave_info@wanted.xlsx"/>
+    <hyperlink ref="E31" r:id="rId22" display="player_clothes_expose_info@player_status.xlsx"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K65"/>
+  <dimension ref="A1:K66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -2324,6 +2324,26 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>demo.TbSavePoint</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>demo.SavePoint</t>
+        </is>
+      </c>
+      <c r="D66" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>save_point@save_point.xlsx</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -619,7 +619,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -627,12 +627,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
@@ -1021,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K66"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -1332,7 +1326,7 @@
       <c r="D11" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="0" t="inlineStr">
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>unit_npc_attribute@unit_npc.xlsx</t>
         </is>
@@ -1341,52 +1335,38 @@
     <row r="12">
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>demo.TbQuestData</t>
+          <t>demo.TbDesireDensityInfo</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>demo.QuestData</t>
+          <t>demo.DesireDensityInfo</t>
         </is>
       </c>
       <c r="D12" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="0" t="inlineStr">
-        <is>
-          <t>quest_data@quests.xlsx</t>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>desire_density_info@unit_npc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbQuestStepData</t>
-        </is>
-      </c>
-      <c r="C13" s="0" t="inlineStr">
-        <is>
-          <t>demo.QuestStepData</t>
-        </is>
-      </c>
-      <c r="D13" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="0" t="inlineStr">
-        <is>
-          <t>quest_step_data@quests.xlsx</t>
-        </is>
-      </c>
+      <c r="B13" s="0" t="n"/>
+      <c r="C13" s="0" t="n"/>
+      <c r="D13" s="0" t="n"/>
+      <c r="E13" s="0" t="n"/>
     </row>
     <row r="14">
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>demo.TbQuestStepOutcome</t>
+          <t>demo.TbQuestData</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>demo.QuestStepOutcome</t>
+          <t>demo.QuestData</t>
         </is>
       </c>
       <c r="D14" s="0" t="b">
@@ -1394,19 +1374,19 @@
       </c>
       <c r="E14" s="0" t="inlineStr">
         <is>
-          <t>quest_step_outcome@quests.xlsx</t>
+          <t>quest_data@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>demo.TbQuestStepObjective</t>
+          <t>demo.TbQuestStepData</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>demo.QuestStepObjective</t>
+          <t>demo.QuestStepData</t>
         </is>
       </c>
       <c r="D15" s="0" t="b">
@@ -1414,19 +1394,19 @@
       </c>
       <c r="E15" s="0" t="inlineStr">
         <is>
-          <t>quest_step_objective@quests.xlsx</t>
+          <t>quest_step_data@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="0" t="inlineStr">
         <is>
-          <t>demo.TbDialogMetaInfo</t>
+          <t>demo.TbQuestStepOutcome</t>
         </is>
       </c>
       <c r="C16" s="0" t="inlineStr">
         <is>
-          <t>demo.DialogMetaInfo</t>
+          <t>demo.QuestStepOutcome</t>
         </is>
       </c>
       <c r="D16" s="0" t="b">
@@ -1434,19 +1414,19 @@
       </c>
       <c r="E16" s="0" t="inlineStr">
         <is>
-          <t>dialog_meta_info@dialog.xlsx</t>
+          <t>quest_step_outcome@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>demo.TbItemData</t>
+          <t>demo.TbQuestStepObjective</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>demo.ItemData</t>
+          <t>demo.QuestStepObjective</t>
         </is>
       </c>
       <c r="D17" s="0" t="b">
@@ -1454,19 +1434,19 @@
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>item@item.xlsx</t>
+          <t>quest_step_objective@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>demo.TbShop</t>
+          <t>demo.TbDialogMetaInfo</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>demo.Shop</t>
+          <t>demo.DialogMetaInfo</t>
         </is>
       </c>
       <c r="D18" s="0" t="b">
@@ -1474,19 +1454,19 @@
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t>shop@shop.xlsx</t>
+          <t>dialog_meta_info@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>demo.TbShopGoods</t>
+          <t>demo.TbItemData</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>demo.ShopGoods</t>
+          <t>demo.ItemData</t>
         </is>
       </c>
       <c r="D19" s="0" t="b">
@@ -1494,19 +1474,19 @@
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>shop_goods@shop.xlsx</t>
+          <t>item@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>demo.TbItemUse</t>
+          <t>demo.TbShop</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>demo.ItemUse</t>
+          <t>demo.Shop</t>
         </is>
       </c>
       <c r="D20" s="0" t="b">
@@ -1514,19 +1494,19 @@
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>item_use@item.xlsx</t>
+          <t>shop@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>demo.TbNpcDialogInfo</t>
+          <t>demo.TbShopGoods</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>demo.NpcDialogInfo</t>
+          <t>demo.ShopGoods</t>
         </is>
       </c>
       <c r="D21" s="0" t="b">
@@ -1534,19 +1514,19 @@
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>npc_dialog_info@dialog.xlsx</t>
+          <t>shop_goods@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>demo.TbWorldMapGlobal</t>
+          <t>demo.TbItemUse</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>demo.WorldMapGlobal</t>
+          <t>demo.ItemUse</t>
         </is>
       </c>
       <c r="D22" s="0" t="b">
@@ -1554,24 +1534,19 @@
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>world_map_global@map.xlsx</t>
-        </is>
-      </c>
-      <c r="G22" s="0" t="inlineStr">
-        <is>
-          <t>one</t>
+          <t>item_use@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>demo.TbWorldMapBigMapLayer</t>
+          <t>demo.TbNpcDialogInfo</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>demo.WorldMapBigMapLayer</t>
+          <t>demo.NpcDialogInfo</t>
         </is>
       </c>
       <c r="D23" s="0" t="b">
@@ -1579,24 +1554,19 @@
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>world_map_big_map@map.xlsx</t>
-        </is>
-      </c>
-      <c r="G23" s="0" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>npc_dialog_info@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>demo.TbDreamInfiltrationSpot</t>
+          <t>demo.TbWorldMapGlobal</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>demo.DreamInfiltrationSpot</t>
+          <t>demo.WorldMapGlobal</t>
         </is>
       </c>
       <c r="D24" s="0" t="b">
@@ -1604,19 +1574,24 @@
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>dream_infiltration@dream_infiltration.xlsx</t>
+          <t>world_map_global@map.xlsx</t>
+        </is>
+      </c>
+      <c r="G24" s="0" t="inlineStr">
+        <is>
+          <t>one</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>demo.TbCharDreamEntryInfo</t>
+          <t>demo.TbWorldMapBigMapLayer</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>demo.CharDreamEntryInfo</t>
+          <t>demo.WorldMapBigMapLayer</t>
         </is>
       </c>
       <c r="D25" s="0" t="b">
@@ -1624,19 +1599,24 @@
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t>char_dream_entry@dream_infiltration.xlsx</t>
+          <t>world_map_big_map@map.xlsx</t>
+        </is>
+      </c>
+      <c r="G25" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>demo.TbFishingSpot</t>
+          <t>demo.TbDreamInfiltrationSpot</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>demo.FishingSpot</t>
+          <t>demo.DreamInfiltrationSpot</t>
         </is>
       </c>
       <c r="D26" s="0" t="b">
@@ -1644,19 +1624,19 @@
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t>fishing_spot@fishing_spot.xlsx</t>
+          <t>dream_infiltration@dream_infiltration.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>demo.TbFishingSpotFish</t>
+          <t>demo.TbCharDreamEntryInfo</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>demo.FishingSpotFish</t>
+          <t>demo.CharDreamEntryInfo</t>
         </is>
       </c>
       <c r="D27" s="0" t="b">
@@ -1664,20 +1644,39 @@
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>fishing_spot_fish@fishing_spot.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="28"/>
+          <t>char_dream_entry@dream_infiltration.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbFishingSpot</t>
+        </is>
+      </c>
+      <c r="C28" s="0" t="inlineStr">
+        <is>
+          <t>demo.FishingSpot</t>
+        </is>
+      </c>
+      <c r="D28" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="0" t="inlineStr">
+        <is>
+          <t>fishing_spot@fishing_spot.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="29">
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>demo.TbPlayerDesireLevel</t>
+          <t>demo.TbFishingSpotFish</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>demo.PlayerDesireLevel</t>
+          <t>demo.FishingSpotFish</t>
         </is>
       </c>
       <c r="D29" s="0" t="b">
@@ -1685,39 +1684,20 @@
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>player_desire_level@player_status.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbPlayerJingYuLevel</t>
-        </is>
-      </c>
-      <c r="C30" s="0" t="inlineStr">
-        <is>
-          <t>demo.PlayerJingYuLevel</t>
-        </is>
-      </c>
-      <c r="D30" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="0" t="inlineStr">
-        <is>
-          <t>player_jingyu_level@player_status.xlsx</t>
-        </is>
-      </c>
-    </row>
+          <t>fishing_spot_fish@fishing_spot.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="30"/>
     <row r="31">
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>demo.TbPlayerSanCorruptLevel</t>
+          <t>demo.TbPlayerDesireLevel</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>demo.PlayerSanCorruptLevel</t>
+          <t>demo.PlayerDesireLevel</t>
         </is>
       </c>
       <c r="D31" s="0" t="b">
@@ -1725,19 +1705,19 @@
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>player_san_corrupt_level@player_status.xlsx</t>
+          <t>player_desire_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>demo.TbPlayerClothesExposeInfo</t>
+          <t>demo.TbPlayerJingYuLevel</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>demo.PlayerClothesExposeInfo</t>
+          <t>demo.PlayerJingYuLevel</t>
         </is>
       </c>
       <c r="D32" s="0" t="b">
@@ -1745,20 +1725,39 @@
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>player_clothes_expose_info@player_status.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="33"/>
+          <t>player_jingyu_level@player_status.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbPlayerSanCorruptLevel</t>
+        </is>
+      </c>
+      <c r="C33" s="0" t="inlineStr">
+        <is>
+          <t>demo.PlayerSanCorruptLevel</t>
+        </is>
+      </c>
+      <c r="D33" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="0" t="inlineStr">
+        <is>
+          <t>player_san_corrupt_level@player_status.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="34">
       <c r="B34" s="0" t="inlineStr">
         <is>
-          <t>demo.TbWantedLevelInfo</t>
+          <t>demo.TbPlayerClothesExposeInfo</t>
         </is>
       </c>
       <c r="C34" s="0" t="inlineStr">
         <is>
-          <t>demo.WantedLevelInfo</t>
+          <t>demo.PlayerClothesExposeInfo</t>
         </is>
       </c>
       <c r="D34" s="0" t="b">
@@ -1766,39 +1765,20 @@
       </c>
       <c r="E34" s="0" t="inlineStr">
         <is>
-          <t>wanted_level_info@wanted.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbWantedBehaveInfo</t>
-        </is>
-      </c>
-      <c r="C35" s="0" t="inlineStr">
-        <is>
-          <t>demo.WantedBehaveInfo</t>
-        </is>
-      </c>
-      <c r="D35" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="0" t="inlineStr">
-        <is>
-          <t>wanted_behave_info@wanted.xlsx</t>
-        </is>
-      </c>
-    </row>
+          <t>player_clothes_expose_info@player_status.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="B36" s="0" t="inlineStr">
         <is>
-          <t>demo.TbTalentNode</t>
+          <t>demo.TbWantedLevelInfo</t>
         </is>
       </c>
       <c r="C36" s="0" t="inlineStr">
         <is>
-          <t>demo.TalentNode</t>
+          <t>demo.WantedLevelInfo</t>
         </is>
       </c>
       <c r="D36" s="0" t="b">
@@ -1806,19 +1786,19 @@
       </c>
       <c r="E36" s="0" t="inlineStr">
         <is>
-          <t>talent@talent.xlsx</t>
+          <t>wanted_level_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>demo.TbWantedGuardSpawnTier</t>
+          <t>demo.TbWantedBehaveInfo</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>demo.WantedGuardSpawnTier</t>
+          <t>demo.WantedBehaveInfo</t>
         </is>
       </c>
       <c r="D37" s="0" t="b">
@@ -1826,19 +1806,19 @@
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>wanted_guard_spawn@wanted.xlsx</t>
+          <t>wanted_behave_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>demo.TbEntitySkillData</t>
+          <t>demo.TbTalentNode</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>demo.EntitySkillData</t>
+          <t>demo.TalentNode</t>
         </is>
       </c>
       <c r="D38" s="0" t="b">
@@ -1846,19 +1826,19 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>entity_skill@skill.xlsx</t>
+          <t>talent@talent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="0" t="inlineStr">
         <is>
-          <t>demo.TbSkillSchool</t>
+          <t>demo.TbWantedGuardSpawnTier</t>
         </is>
       </c>
       <c r="C39" s="0" t="inlineStr">
         <is>
-          <t>demo.SkillSchool</t>
+          <t>demo.WantedGuardSpawnTier</t>
         </is>
       </c>
       <c r="D39" s="0" t="b">
@@ -1866,19 +1846,19 @@
       </c>
       <c r="E39" s="0" t="inlineStr">
         <is>
-          <t>skill_school@skill.xlsx</t>
+          <t>wanted_guard_spawn@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>demo.TbSkillLearnEntry</t>
+          <t>demo.TbEntitySkillData</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>demo.SkillLearnEntry</t>
+          <t>demo.EntitySkillData</t>
         </is>
       </c>
       <c r="D40" s="0" t="b">
@@ -1886,19 +1866,19 @@
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t>skill_learn@skill.xlsx</t>
+          <t>entity_skill@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>demo.TbDesireCrystalDef</t>
+          <t>demo.TbSkillSchool</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>demo.DesireCrystalDef</t>
+          <t>demo.SkillSchool</t>
         </is>
       </c>
       <c r="D41" s="0" t="b">
@@ -1906,19 +1886,19 @@
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
-          <t>desire_crystal_def@desire_crystal.xlsx</t>
+          <t>skill_school@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMapDesireCrystalBudget</t>
+          <t>demo.TbSkillLearnEntry</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>demo.MapDesireCrystalBudget</t>
+          <t>demo.SkillLearnEntry</t>
         </is>
       </c>
       <c r="D42" s="0" t="b">
@@ -1926,19 +1906,19 @@
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
-          <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
+          <t>skill_learn@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMapWalkerDesireCrystalQuota</t>
+          <t>demo.TbDesireCrystalDef</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>demo.MapWalkerDesireCrystalQuota</t>
+          <t>demo.DesireCrystalDef</t>
         </is>
       </c>
       <c r="D43" s="0" t="b">
@@ -1946,19 +1926,19 @@
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
-          <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
+          <t>desire_crystal_def@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>demo.TbNamedNpcDesireCrystal</t>
+          <t>demo.TbMapDesireCrystalBudget</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>demo.NamedNpcDesireCrystal</t>
+          <t>demo.MapDesireCrystalBudget</t>
         </is>
       </c>
       <c r="D44" s="0" t="b">
@@ -1966,19 +1946,19 @@
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
-          <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
+          <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>demo.TbSpiritMonsterTypeBudget</t>
+          <t>demo.TbMapWalkerDesireCrystalQuota</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>demo.SpiritMonsterTypeBudget</t>
+          <t>demo.MapWalkerDesireCrystalQuota</t>
         </is>
       </c>
       <c r="D45" s="0" t="b">
@@ -1986,19 +1966,19 @@
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
-          <t>spirit_monster_budget@player_status.xlsx</t>
+          <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>demo.TbContainerItemStackOverride</t>
+          <t>demo.TbNamedNpcDesireCrystal</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>demo.ContainerItemStackOverride</t>
+          <t>demo.NamedNpcDesireCrystal</t>
         </is>
       </c>
       <c r="D46" s="0" t="b">
@@ -2006,19 +1986,19 @@
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
-          <t>container_item_stack_override@container_stack.xlsx</t>
+          <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>demo.TbContainerStackTagRule</t>
+          <t>demo.TbSpiritMonsterTypeBudget</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>demo.ContainerStackTagRule</t>
+          <t>demo.SpiritMonsterTypeBudget</t>
         </is>
       </c>
       <c r="D47" s="0" t="b">
@@ -2026,19 +2006,19 @@
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
-          <t>container_stack_tag_rule@container_stack.xlsx</t>
+          <t>spirit_monster_budget@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMapAreaEffect</t>
+          <t>demo.TbContainerItemStackOverride</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>demo.MapAreaEffect</t>
+          <t>demo.ContainerItemStackOverride</t>
         </is>
       </c>
       <c r="D48" s="0" t="b">
@@ -2046,20 +2026,39 @@
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
-          <t>map_area_effect@map_area_effect.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="49"/>
+          <t>container_item_stack_override@container_stack.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="B49" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbContainerStackTagRule</t>
+        </is>
+      </c>
+      <c r="C49" s="0" t="inlineStr">
+        <is>
+          <t>demo.ContainerStackTagRule</t>
+        </is>
+      </c>
+      <c r="D49" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="0" t="inlineStr">
+        <is>
+          <t>container_stack_tag_rule@container_stack.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="50">
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>demo.TbFallenAmountProgressInfo</t>
+          <t>demo.TbMapAreaEffect</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>demo.FallenAmountProgressInfo</t>
+          <t>demo.MapAreaEffect</t>
         </is>
       </c>
       <c r="D50" s="0" t="b">
@@ -2067,39 +2066,20 @@
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>fallen_amount_progress_info@fallen_amount_progress_info.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbRumorIntel</t>
-        </is>
-      </c>
-      <c r="C51" s="0" t="inlineStr">
-        <is>
-          <t>demo.RumorIntel</t>
-        </is>
-      </c>
-      <c r="D51" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="0" t="inlineStr">
-        <is>
-          <t>rumor_intel@rumor_tables.xlsx</t>
-        </is>
-      </c>
-    </row>
+          <t>map_area_effect@map_area_effect.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="51"/>
     <row r="52">
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>demo.TbRumorRandomPool</t>
+          <t>demo.TbFallenAmountProgressInfo</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>demo.RumorRandomPool</t>
+          <t>demo.FallenAmountProgressInfo</t>
         </is>
       </c>
       <c r="D52" s="0" t="b">
@@ -2107,19 +2087,19 @@
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
-          <t>rumor_random_pool@rumor_tables.xlsx</t>
+          <t>fallen_amount_progress_info@fallen_amount_progress_info.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>demo.TbRumorGlobal</t>
+          <t>demo.TbRumorIntel</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>demo.RumorGlobal</t>
+          <t>demo.RumorIntel</t>
         </is>
       </c>
       <c r="D53" s="0" t="b">
@@ -2127,20 +2107,39 @@
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
-          <t>rumor_global@rumor_tables.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="54"/>
+          <t>rumor_intel@rumor_tables.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="B54" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbRumorRandomPool</t>
+        </is>
+      </c>
+      <c r="C54" s="0" t="inlineStr">
+        <is>
+          <t>demo.RumorRandomPool</t>
+        </is>
+      </c>
+      <c r="D54" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="0" t="inlineStr">
+        <is>
+          <t>rumor_random_pool@rumor_tables.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="55">
       <c r="B55" s="0" t="inlineStr">
         <is>
-          <t>demo.TbCharacterInfo</t>
+          <t>demo.TbRumorGlobal</t>
         </is>
       </c>
       <c r="C55" s="0" t="inlineStr">
         <is>
-          <t>demo.CharacterInfo</t>
+          <t>demo.RumorGlobal</t>
         </is>
       </c>
       <c r="D55" s="0" t="b">
@@ -2148,39 +2147,20 @@
       </c>
       <c r="E55" s="0" t="inlineStr">
         <is>
-          <t>character_info@character.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbCharacterFavorInfo</t>
-        </is>
-      </c>
-      <c r="C56" s="0" t="inlineStr">
-        <is>
-          <t>demo.CharacterFavorInfo</t>
-        </is>
-      </c>
-      <c r="D56" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" s="0" t="inlineStr">
-        <is>
-          <t>character_favor_info@character.xlsx</t>
-        </is>
-      </c>
-    </row>
+          <t>rumor_global@rumor_tables.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56"/>
     <row r="57">
       <c r="B57" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMicroPlotDef</t>
+          <t>demo.TbCharacterInfo</t>
         </is>
       </c>
       <c r="C57" s="0" t="inlineStr">
         <is>
-          <t>demo.MicroPlotDef</t>
+          <t>demo.CharacterInfo</t>
         </is>
       </c>
       <c r="D57" s="0" t="b">
@@ -2188,19 +2168,19 @@
       </c>
       <c r="E57" s="0" t="inlineStr">
         <is>
-          <t>micro_plot_def@micro_plot.xlsx</t>
+          <t>character_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMapMicroPlotTrigger</t>
+          <t>demo.TbCharacterFavorInfo</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>demo.MapMicroPlotTrigger</t>
+          <t>demo.CharacterFavorInfo</t>
         </is>
       </c>
       <c r="D58" s="0" t="b">
@@ -2208,19 +2188,19 @@
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
-          <t>map_micro_plot_trigger@micro_plot.xlsx</t>
+          <t>character_favor_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMicroPlotTimelineEvent</t>
+          <t>demo.TbMicroPlotDef</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>demo.MicroPlotTimelineEvent</t>
+          <t>demo.MicroPlotDef</t>
         </is>
       </c>
       <c r="D59" s="0" t="b">
@@ -2228,123 +2208,212 @@
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
-          <t>micro_plot_timeline_event@micro_plot.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="60"/>
+          <t>micro_plot_def@micro_plot.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbMapMicroPlotTrigger</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>demo.MapMicroPlotTrigger</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>map_micro_plot_trigger@micro_plot.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="61">
       <c r="B61" s="0" t="inlineStr">
         <is>
+          <t>demo.TbMicroPlotTimelineEvent</t>
+        </is>
+      </c>
+      <c r="C61" s="0" t="inlineStr">
+        <is>
+          <t>demo.MicroPlotTimelineEvent</t>
+        </is>
+      </c>
+      <c r="D61" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="0" t="inlineStr">
+        <is>
+          <t>micro_plot_timeline_event@micro_plot.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
+    <row r="63">
+      <c r="B63" s="0" t="inlineStr">
+        <is>
           <t>demo.TbTrapSpec</t>
         </is>
       </c>
-      <c r="C61" s="0" t="inlineStr">
+      <c r="C63" s="0" t="inlineStr">
         <is>
           <t>demo.TrapSpec</t>
         </is>
       </c>
-      <c r="D61" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="0" t="inlineStr">
+      <c r="D63" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
         <is>
           <t>trap_spec@trap_spec.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbForgeRecipe</t>
-        </is>
-      </c>
-      <c r="C62" s="0" t="inlineStr">
-        <is>
-          <t>demo.ForgeRecipe</t>
-        </is>
-      </c>
-      <c r="D62" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E62" s="0" t="inlineStr">
-        <is>
-          <t>forge_recipe@forge_recipe.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="63"/>
     <row r="64">
       <c r="B64" s="0" t="inlineStr">
         <is>
+          <t>demo.TbForgeRecipe</t>
+        </is>
+      </c>
+      <c r="C64" s="0" t="inlineStr">
+        <is>
+          <t>demo.ForgeRecipe</t>
+        </is>
+      </c>
+      <c r="D64" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="0" t="inlineStr">
+        <is>
+          <t>forge_recipe@forge_recipe.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="65"/>
+    <row r="66">
+      <c r="B66" s="0" t="inlineStr">
+        <is>
           <t>demo.TbHActInfo</t>
         </is>
       </c>
-      <c r="C64" s="0" t="inlineStr">
+      <c r="C66" s="0" t="inlineStr">
         <is>
           <t>demo.HActInfo</t>
         </is>
       </c>
-      <c r="D64" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" s="0" t="inlineStr">
+      <c r="D66" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
         <is>
           <t>h_act_info@h_act_info.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="B65" s="0" t="inlineStr">
+    <row r="67">
+      <c r="B67" s="0" t="inlineStr">
         <is>
           <t>demo.TbTalentNodeLevel</t>
         </is>
       </c>
-      <c r="C65" s="0" t="inlineStr">
+      <c r="C67" s="0" t="inlineStr">
         <is>
           <t>demo.TalentNodeLevel</t>
         </is>
       </c>
-      <c r="D65" s="0" t="b">
+      <c r="D67" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="E65" s="0" t="inlineStr">
+      <c r="E67" s="0" t="inlineStr">
         <is>
           <t>talent_level@talent.xlsx</t>
         </is>
       </c>
-      <c r="F65" s="0" t="inlineStr">
+      <c r="F67" s="0" t="inlineStr">
         <is>
           <t>node_id+level</t>
         </is>
       </c>
-      <c r="G65" s="0" t="inlineStr">
+      <c r="G67" s="0" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="B66" t="inlineStr">
+    <row r="68">
+      <c r="B68" s="0" t="inlineStr">
         <is>
           <t>demo.TbSavePoint</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C68" s="0" t="inlineStr">
         <is>
           <t>demo.SavePoint</t>
         </is>
       </c>
-      <c r="D66" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" t="inlineStr">
+      <c r="D68" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" s="0" t="inlineStr">
         <is>
           <t>save_point@save_point.xlsx</t>
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbDesireDensityTier</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>demo.DesireDensityTier</t>
+        </is>
+      </c>
+      <c r="D69" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
+        <is>
+          <t>desire_density_tier@desire_density_tier.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbMindFragmentPoolEntry</t>
+        </is>
+      </c>
+      <c r="C70" s="0" t="inlineStr">
+        <is>
+          <t>demo.MindFragmentPoolEntry</t>
+        </is>
+      </c>
+      <c r="D70" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" s="0" t="inlineStr">
+        <is>
+          <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" display="unit_npc_attribute@unit_npc.xlsx" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" display="desire_density_info@unit_npc.xlsx" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -2403,9 +2403,34 @@
           <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="G70" s="0" t="inlineStr">
         <is>
           <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>demo.TbSecretBaseFacility</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>demo.SecretBaseFacility</t>
+        </is>
+      </c>
+      <c r="D71" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>secret_base_facility@secret_base_facility.xlsx</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>据点固定设施</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -2326,7 +2326,7 @@
         </is>
       </c>
       <c r="D67" s="0" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
@@ -2410,25 +2410,25 @@
       </c>
     </row>
     <row r="71">
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="0" t="inlineStr">
         <is>
           <t>demo.TbSecretBaseFacility</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="0" t="inlineStr">
         <is>
           <t>demo.SecretBaseFacility</t>
         </is>
       </c>
-      <c r="D71" t="b">
-        <v>1</v>
-      </c>
-      <c r="E71" t="inlineStr">
+      <c r="D71" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" s="0" t="inlineStr">
         <is>
           <t>secret_base_facility@secret_base_facility.xlsx</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I71" s="0" t="inlineStr">
         <is>
           <t>据点固定设施</t>
         </is>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -619,7 +619,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -627,6 +627,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
       <alignment vertical="center"/>
     </xf>
@@ -1015,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K73"/>
+  <dimension ref="A1:K79"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -1195,92 +1201,78 @@
     <row r="5">
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMapAreaInfo</t>
+          <t>demo.TbLogicAreaInfo</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>demo.MapAreaInfo</t>
+          <t>demo.LogicAreaInfo</t>
         </is>
       </c>
       <c r="D5" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="0" t="inlineStr">
-        <is>
-          <t>area_info@map.xlsx</t>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>logic_area_info@map.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>demo.TbDropBundle</t>
+          <t>demo.TbAreaVariantInfo</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>demo.DropBundle</t>
+          <t>demo.AreaVariantInfo</t>
         </is>
       </c>
       <c r="D6" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="0" t="inlineStr">
-        <is>
-          <t>drop_bundle@drop.xlsx</t>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>area_variant_info@map.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>demo.TbDropItem</t>
+          <t>demo.TbAreaOverlayStateInfo</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>demo.DropItem</t>
+          <t>demo.AreaOverlayStateInfo</t>
         </is>
       </c>
       <c r="D7" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="0" t="inlineStr">
-        <is>
-          <t>drop_item@drop.xlsx</t>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>area_overlay_state_info@map.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbFixedFacility</t>
-        </is>
-      </c>
-      <c r="C8" s="0" t="inlineStr">
-        <is>
-          <t>demo.FixedFacility</t>
-        </is>
-      </c>
-      <c r="D8" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="0" t="inlineStr">
-        <is>
-          <t>fixed_facility@home_facility.xlsx</t>
-        </is>
-      </c>
+      <c r="B8" s="0" t="n"/>
+      <c r="C8" s="0" t="n"/>
+      <c r="D8" s="0" t="n"/>
+      <c r="E8" s="0" t="n"/>
     </row>
     <row r="9">
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>demo.TbBornPoint</t>
+          <t>demo.TbDropBundle</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>demo.BornPoint</t>
+          <t>demo.DropBundle</t>
         </is>
       </c>
       <c r="D9" s="0" t="b">
@@ -1288,19 +1280,19 @@
       </c>
       <c r="E9" s="0" t="inlineStr">
         <is>
-          <t>born_points@born_points.xlsx</t>
+          <t>drop_bundle@drop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>demo.TbUnitNpc</t>
+          <t>demo.TbDropItem</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>demo.UnitNpc</t>
+          <t>demo.DropItem</t>
         </is>
       </c>
       <c r="D10" s="0" t="b">
@@ -1308,125 +1300,125 @@
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t>unit_npc@unit_npc.xlsx</t>
+          <t>drop_item@drop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>demo.TbUnitNpcAttr</t>
+          <t>demo.TbFixedFacility</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>demo.UnitNpcAttr</t>
+          <t>demo.FixedFacility</t>
         </is>
       </c>
       <c r="D11" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>unit_npc_attribute@unit_npc.xlsx</t>
+      <c r="E11" s="0" t="inlineStr">
+        <is>
+          <t>fixed_facility@home_facility.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>demo.TbDesireDensityInfo</t>
+          <t>demo.TbBornPoint</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>demo.DesireDensityInfo</t>
+          <t>demo.BornPoint</t>
         </is>
       </c>
       <c r="D12" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>desire_density_info@unit_npc.xlsx</t>
+      <c r="E12" s="0" t="inlineStr">
+        <is>
+          <t>born_points@born_points.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="0" t="n"/>
-      <c r="C13" s="0" t="n"/>
-      <c r="D13" s="0" t="n"/>
-      <c r="E13" s="0" t="n"/>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbUnitNpc</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>demo.UnitNpc</t>
+        </is>
+      </c>
+      <c r="D13" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="0" t="inlineStr">
+        <is>
+          <t>unit_npc@unit_npc.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>demo.TbQuestData</t>
+          <t>demo.TbUnitNpcAttr</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>demo.QuestData</t>
+          <t>demo.UnitNpcAttr</t>
         </is>
       </c>
       <c r="D14" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="0" t="inlineStr">
-        <is>
-          <t>quest_data@quests.xlsx</t>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>unit_npc_attribute@unit_npc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="inlineStr">
         <is>
-          <t>demo.TbQuestStepData</t>
+          <t>demo.TbDesireDensityInfo</t>
         </is>
       </c>
       <c r="C15" s="0" t="inlineStr">
         <is>
-          <t>demo.QuestStepData</t>
+          <t>demo.DesireDensityInfo</t>
         </is>
       </c>
       <c r="D15" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="0" t="inlineStr">
-        <is>
-          <t>quest_step_data@quests.xlsx</t>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>desire_density_info@unit_npc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbQuestStepOutcome</t>
-        </is>
-      </c>
-      <c r="C16" s="0" t="inlineStr">
-        <is>
-          <t>demo.QuestStepOutcome</t>
-        </is>
-      </c>
-      <c r="D16" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="0" t="inlineStr">
-        <is>
-          <t>quest_step_outcome@quests.xlsx</t>
-        </is>
-      </c>
+      <c r="B16" s="0" t="n"/>
+      <c r="C16" s="0" t="n"/>
+      <c r="D16" s="0" t="n"/>
+      <c r="E16" s="0" t="n"/>
     </row>
     <row r="17">
       <c r="B17" s="0" t="inlineStr">
         <is>
-          <t>demo.TbQuestStepObjective</t>
+          <t>demo.TbQuestData</t>
         </is>
       </c>
       <c r="C17" s="0" t="inlineStr">
         <is>
-          <t>demo.QuestStepObjective</t>
+          <t>demo.QuestData</t>
         </is>
       </c>
       <c r="D17" s="0" t="b">
@@ -1434,19 +1426,19 @@
       </c>
       <c r="E17" s="0" t="inlineStr">
         <is>
-          <t>quest_step_objective@quests.xlsx</t>
+          <t>quest_data@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>demo.TbDialogMetaInfo</t>
+          <t>demo.TbQuestStepData</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>demo.DialogMetaInfo</t>
+          <t>demo.QuestStepData</t>
         </is>
       </c>
       <c r="D18" s="0" t="b">
@@ -1454,19 +1446,19 @@
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t>dialog_meta_info@dialog.xlsx</t>
+          <t>quest_step_data@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>demo.TbItemData</t>
+          <t>demo.TbQuestStepOutcome</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>demo.ItemData</t>
+          <t>demo.QuestStepOutcome</t>
         </is>
       </c>
       <c r="D19" s="0" t="b">
@@ -1474,19 +1466,19 @@
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>item@item.xlsx</t>
+          <t>quest_step_outcome@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>demo.TbShop</t>
+          <t>demo.TbQuestStepObjective</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>demo.Shop</t>
+          <t>demo.QuestStepObjective</t>
         </is>
       </c>
       <c r="D20" s="0" t="b">
@@ -1494,19 +1486,19 @@
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>shop@shop.xlsx</t>
+          <t>quest_step_objective@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>demo.TbShopGoods</t>
+          <t>demo.TbDialogMetaInfo</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>demo.ShopGoods</t>
+          <t>demo.DialogMetaInfo</t>
         </is>
       </c>
       <c r="D21" s="0" t="b">
@@ -1514,19 +1506,19 @@
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>shop_goods@shop.xlsx</t>
+          <t>dialog_meta_info@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="0" t="inlineStr">
         <is>
-          <t>demo.TbItemUse</t>
+          <t>demo.TbItemData</t>
         </is>
       </c>
       <c r="C22" s="0" t="inlineStr">
         <is>
-          <t>demo.ItemUse</t>
+          <t>demo.ItemData</t>
         </is>
       </c>
       <c r="D22" s="0" t="b">
@@ -1534,19 +1526,19 @@
       </c>
       <c r="E22" s="0" t="inlineStr">
         <is>
-          <t>item_use@item.xlsx</t>
+          <t>item@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>demo.TbItemGift</t>
+          <t>demo.TbShop</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>demo.ItemGift</t>
+          <t>demo.Shop</t>
         </is>
       </c>
       <c r="D23" s="0" t="b">
@@ -1554,29 +1546,19 @@
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>item_gift@item.xlsx</t>
-        </is>
-      </c>
-      <c r="F23" s="0" t="inlineStr">
-        <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G23" s="0" t="inlineStr">
-        <is>
-          <t>map</t>
+          <t>shop@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>demo.TbNpcDialogInfo</t>
+          <t>demo.TbShopGoods</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>demo.NpcDialogInfo</t>
+          <t>demo.ShopGoods</t>
         </is>
       </c>
       <c r="D24" s="0" t="b">
@@ -1584,19 +1566,19 @@
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>npc_dialog_info@dialog.xlsx</t>
+          <t>shop_goods@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>demo.TbWorldMapGlobal</t>
+          <t>demo.TbItemUse</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>demo.WorldMapGlobal</t>
+          <t>demo.ItemUse</t>
         </is>
       </c>
       <c r="D25" s="0" t="b">
@@ -1604,24 +1586,19 @@
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t>world_map_global@map.xlsx</t>
-        </is>
-      </c>
-      <c r="G25" s="0" t="inlineStr">
-        <is>
-          <t>one</t>
+          <t>item_use@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>demo.TbWorldMapBigMapLayer</t>
+          <t>demo.TbItemGift</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>demo.WorldMapBigMapLayer</t>
+          <t>demo.ItemGift</t>
         </is>
       </c>
       <c r="D26" s="0" t="b">
@@ -1629,24 +1606,29 @@
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t>world_map_big_map@map.xlsx</t>
+          <t>item_gift@item.xlsx</t>
+        </is>
+      </c>
+      <c r="F26" s="0" t="inlineStr">
+        <is>
+          <t>item_id</t>
         </is>
       </c>
       <c r="G26" s="0" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>map</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>demo.TbDreamInfiltrationSpot</t>
+          <t>demo.TbNpcDialogInfo</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>demo.DreamInfiltrationSpot</t>
+          <t>demo.NpcDialogInfo</t>
         </is>
       </c>
       <c r="D27" s="0" t="b">
@@ -1654,19 +1636,19 @@
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>dream_infiltration@dream_infiltration.xlsx</t>
+          <t>npc_dialog_info@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>demo.TbCharDreamEntryInfo</t>
+          <t>demo.TbWorldMapGlobal</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>demo.CharDreamEntryInfo</t>
+          <t>demo.WorldMapGlobal</t>
         </is>
       </c>
       <c r="D28" s="0" t="b">
@@ -1674,19 +1656,24 @@
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>char_dream_entry@dream_infiltration.xlsx</t>
+          <t>world_map_global@map.xlsx</t>
+        </is>
+      </c>
+      <c r="G28" s="0" t="inlineStr">
+        <is>
+          <t>one</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>demo.TbFishingSpot</t>
+          <t>demo.TbWorldMapBigMapLayer</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>demo.FishingSpot</t>
+          <t>demo.WorldMapBigMapLayer</t>
         </is>
       </c>
       <c r="D29" s="0" t="b">
@@ -1694,19 +1681,24 @@
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>fishing_spot@fishing_spot.xlsx</t>
+          <t>world_map_big_map@map.xlsx</t>
+        </is>
+      </c>
+      <c r="G29" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>demo.TbFishingSpotFish</t>
+          <t>demo.TbDreamInfiltrationSpot</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>demo.FishingSpotFish</t>
+          <t>demo.DreamInfiltrationSpot</t>
         </is>
       </c>
       <c r="D30" s="0" t="b">
@@ -1714,19 +1706,39 @@
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>fishing_spot_fish@fishing_spot.xlsx</t>
+          <t>dream_infiltration@dream_infiltration.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbCharDreamEntryInfo</t>
+        </is>
+      </c>
+      <c r="C31" s="0" t="inlineStr">
+        <is>
+          <t>demo.CharDreamEntryInfo</t>
+        </is>
+      </c>
+      <c r="D31" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="0" t="inlineStr">
+        <is>
+          <t>char_dream_entry@dream_infiltration.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>demo.TbPlayerDesireLevel</t>
+          <t>demo.TbFishingSpot</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>demo.PlayerDesireLevel</t>
+          <t>demo.FishingSpot</t>
         </is>
       </c>
       <c r="D32" s="0" t="b">
@@ -1734,19 +1746,19 @@
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>player_desire_level@player_status.xlsx</t>
+          <t>fishing_spot@fishing_spot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>demo.TbPlayerJingYuLevel</t>
+          <t>demo.TbFishingSpotFish</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>demo.PlayerJingYuLevel</t>
+          <t>demo.FishingSpotFish</t>
         </is>
       </c>
       <c r="D33" s="0" t="b">
@@ -1754,39 +1766,20 @@
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>player_jingyu_level@player_status.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="B34" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbPlayerSanCorruptLevel</t>
-        </is>
-      </c>
-      <c r="C34" s="0" t="inlineStr">
-        <is>
-          <t>demo.PlayerSanCorruptLevel</t>
-        </is>
-      </c>
-      <c r="D34" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="0" t="inlineStr">
-        <is>
-          <t>player_san_corrupt_level@player_status.xlsx</t>
-        </is>
-      </c>
-    </row>
+          <t>fishing_spot_fish@fishing_spot.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
     <row r="35">
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>demo.TbPlayerClothesExposeInfo</t>
+          <t>demo.TbPlayerDesireLevel</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>demo.PlayerClothesExposeInfo</t>
+          <t>demo.PlayerDesireLevel</t>
         </is>
       </c>
       <c r="D35" s="0" t="b">
@@ -1794,19 +1787,39 @@
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>player_clothes_expose_info@player_status.xlsx</t>
+          <t>player_desire_level@player_status.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbPlayerJingYuLevel</t>
+        </is>
+      </c>
+      <c r="C36" s="0" t="inlineStr">
+        <is>
+          <t>demo.PlayerJingYuLevel</t>
+        </is>
+      </c>
+      <c r="D36" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="0" t="inlineStr">
+        <is>
+          <t>player_jingyu_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>demo.TbWantedLevelInfo</t>
+          <t>demo.TbPlayerSanCorruptLevel</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>demo.WantedLevelInfo</t>
+          <t>demo.PlayerSanCorruptLevel</t>
         </is>
       </c>
       <c r="D37" s="0" t="b">
@@ -1814,19 +1827,19 @@
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>wanted_level_info@wanted.xlsx</t>
+          <t>player_san_corrupt_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>demo.TbWantedBehaveInfo</t>
+          <t>demo.TbPlayerClothesExposeInfo</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>demo.WantedBehaveInfo</t>
+          <t>demo.PlayerClothesExposeInfo</t>
         </is>
       </c>
       <c r="D38" s="0" t="b">
@@ -1834,39 +1847,20 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>wanted_behave_info@wanted.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbTalentNode</t>
-        </is>
-      </c>
-      <c r="C39" s="0" t="inlineStr">
-        <is>
-          <t>demo.TalentNode</t>
-        </is>
-      </c>
-      <c r="D39" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="0" t="inlineStr">
-        <is>
-          <t>talent@talent.xlsx</t>
-        </is>
-      </c>
-    </row>
+          <t>player_clothes_expose_info@player_status.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
     <row r="40">
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>demo.TbWantedGuardSpawnTier</t>
+          <t>demo.TbWantedLevelInfo</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>demo.WantedGuardSpawnTier</t>
+          <t>demo.WantedLevelInfo</t>
         </is>
       </c>
       <c r="D40" s="0" t="b">
@@ -1874,19 +1868,19 @@
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t>wanted_guard_spawn@wanted.xlsx</t>
+          <t>wanted_level_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="0" t="inlineStr">
         <is>
-          <t>demo.TbEntitySkillData</t>
+          <t>demo.TbWantedBehaveInfo</t>
         </is>
       </c>
       <c r="C41" s="0" t="inlineStr">
         <is>
-          <t>demo.EntitySkillData</t>
+          <t>demo.WantedBehaveInfo</t>
         </is>
       </c>
       <c r="D41" s="0" t="b">
@@ -1894,19 +1888,19 @@
       </c>
       <c r="E41" s="0" t="inlineStr">
         <is>
-          <t>entity_skill@skill.xlsx</t>
+          <t>wanted_behave_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>demo.TbSkillSchool</t>
+          <t>demo.TbTalentNode</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>demo.SkillSchool</t>
+          <t>demo.TalentNode</t>
         </is>
       </c>
       <c r="D42" s="0" t="b">
@@ -1914,19 +1908,19 @@
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
-          <t>skill_school@skill.xlsx</t>
+          <t>talent@talent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>demo.TbSkillLearnEntry</t>
+          <t>demo.TbWantedGuardSpawnTier</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>demo.SkillLearnEntry</t>
+          <t>demo.WantedGuardSpawnTier</t>
         </is>
       </c>
       <c r="D43" s="0" t="b">
@@ -1934,19 +1928,19 @@
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
-          <t>skill_learn@skill.xlsx</t>
+          <t>wanted_guard_spawn@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>demo.TbDesireCrystalDef</t>
+          <t>demo.TbEntitySkillData</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>demo.DesireCrystalDef</t>
+          <t>demo.EntitySkillData</t>
         </is>
       </c>
       <c r="D44" s="0" t="b">
@@ -1954,19 +1948,19 @@
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
-          <t>desire_crystal_def@desire_crystal.xlsx</t>
+          <t>entity_skill@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMapDesireCrystalBudget</t>
+          <t>demo.TbSkillSchool</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>demo.MapDesireCrystalBudget</t>
+          <t>demo.SkillSchool</t>
         </is>
       </c>
       <c r="D45" s="0" t="b">
@@ -1974,19 +1968,19 @@
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
-          <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
+          <t>skill_school@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMapWalkerDesireCrystalQuota</t>
+          <t>demo.TbSkillLearnEntry</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>demo.MapWalkerDesireCrystalQuota</t>
+          <t>demo.SkillLearnEntry</t>
         </is>
       </c>
       <c r="D46" s="0" t="b">
@@ -1994,19 +1988,19 @@
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
-          <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
+          <t>skill_learn@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>demo.TbNamedNpcDesireCrystal</t>
+          <t>demo.TbDesireCrystalDef</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>demo.NamedNpcDesireCrystal</t>
+          <t>demo.DesireCrystalDef</t>
         </is>
       </c>
       <c r="D47" s="0" t="b">
@@ -2014,19 +2008,19 @@
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
-          <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
+          <t>desire_crystal_def@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>demo.TbSpiritMonsterTypeBudget</t>
+          <t>demo.TbMapDesireCrystalBudget</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>demo.SpiritMonsterTypeBudget</t>
+          <t>demo.MapDesireCrystalBudget</t>
         </is>
       </c>
       <c r="D48" s="0" t="b">
@@ -2034,19 +2028,19 @@
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
-          <t>spirit_monster_budget@player_status.xlsx</t>
+          <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>demo.TbContainerItemStackOverride</t>
+          <t>demo.TbMapWalkerDesireCrystalQuota</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>demo.ContainerItemStackOverride</t>
+          <t>demo.MapWalkerDesireCrystalQuota</t>
         </is>
       </c>
       <c r="D49" s="0" t="b">
@@ -2054,19 +2048,19 @@
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>container_item_stack_override@container_stack.xlsx</t>
+          <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>demo.TbContainerStackTagRule</t>
+          <t>demo.TbNamedNpcDesireCrystal</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>demo.ContainerStackTagRule</t>
+          <t>demo.NamedNpcDesireCrystal</t>
         </is>
       </c>
       <c r="D50" s="0" t="b">
@@ -2074,19 +2068,19 @@
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>container_stack_tag_rule@container_stack.xlsx</t>
+          <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMapAreaEffect</t>
+          <t>demo.TbSpiritMonsterTypeBudget</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>demo.MapAreaEffect</t>
+          <t>demo.SpiritMonsterTypeBudget</t>
         </is>
       </c>
       <c r="D51" s="0" t="b">
@@ -2094,19 +2088,39 @@
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
-          <t>map_area_effect@map_area_effect.xlsx</t>
+          <t>spirit_monster_budget@player_status.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="B52" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbContainerItemStackOverride</t>
+        </is>
+      </c>
+      <c r="C52" s="0" t="inlineStr">
+        <is>
+          <t>demo.ContainerItemStackOverride</t>
+        </is>
+      </c>
+      <c r="D52" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" s="0" t="inlineStr">
+        <is>
+          <t>container_item_stack_override@container_stack.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>demo.TbFallenAmountProgressInfo</t>
+          <t>demo.TbContainerStackTagRule</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>demo.FallenAmountProgressInfo</t>
+          <t>demo.ContainerStackTagRule</t>
         </is>
       </c>
       <c r="D53" s="0" t="b">
@@ -2114,19 +2128,19 @@
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
-          <t>fallen_amount_progress_info@fallen_amount_progress_info.xlsx</t>
+          <t>container_stack_tag_rule@container_stack.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>demo.TbRumorIntel</t>
+          <t>demo.TbMapAreaEffect</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>demo.RumorIntel</t>
+          <t>demo.MapAreaEffect</t>
         </is>
       </c>
       <c r="D54" s="0" t="b">
@@ -2134,39 +2148,20 @@
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
-          <t>rumor_intel@rumor_tables.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbRumorRandomPool</t>
-        </is>
-      </c>
-      <c r="C55" s="0" t="inlineStr">
-        <is>
-          <t>demo.RumorRandomPool</t>
-        </is>
-      </c>
-      <c r="D55" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="0" t="inlineStr">
-        <is>
-          <t>rumor_random_pool@rumor_tables.xlsx</t>
-        </is>
-      </c>
-    </row>
+          <t>map_area_effect@map_area_effect.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55"/>
     <row r="56">
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>demo.TbRumorGlobal</t>
+          <t>demo.TbFallenAmountProgressInfo</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>demo.RumorGlobal</t>
+          <t>demo.FallenAmountProgressInfo</t>
         </is>
       </c>
       <c r="D56" s="0" t="b">
@@ -2174,19 +2169,39 @@
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
-          <t>rumor_global@rumor_tables.xlsx</t>
+          <t>fallen_amount_progress_info@fallen_amount_progress_info.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="B57" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbRumorIntel</t>
+        </is>
+      </c>
+      <c r="C57" s="0" t="inlineStr">
+        <is>
+          <t>demo.RumorIntel</t>
+        </is>
+      </c>
+      <c r="D57" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="0" t="inlineStr">
+        <is>
+          <t>rumor_intel@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>demo.TbCharacterInfo</t>
+          <t>demo.TbRumorRandomPool</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>demo.CharacterInfo</t>
+          <t>demo.RumorRandomPool</t>
         </is>
       </c>
       <c r="D58" s="0" t="b">
@@ -2194,19 +2209,19 @@
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
-          <t>character_info@character.xlsx</t>
+          <t>rumor_random_pool@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>demo.TbCharacterFavorInfo</t>
+          <t>demo.TbRumorGlobal</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>demo.CharacterFavorInfo</t>
+          <t>demo.RumorGlobal</t>
         </is>
       </c>
       <c r="D59" s="0" t="b">
@@ -2214,39 +2229,20 @@
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
-          <t>character_favor_info@character.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbMicroPlotDef</t>
-        </is>
-      </c>
-      <c r="C60" s="0" t="inlineStr">
-        <is>
-          <t>demo.MicroPlotDef</t>
-        </is>
-      </c>
-      <c r="D60" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="0" t="inlineStr">
-        <is>
-          <t>micro_plot_def@micro_plot.xlsx</t>
-        </is>
-      </c>
-    </row>
+          <t>rumor_global@rumor_tables.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60"/>
     <row r="61">
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMapMicroPlotTrigger</t>
+          <t>demo.TbCharacterInfo</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>demo.MapMicroPlotTrigger</t>
+          <t>demo.CharacterInfo</t>
         </is>
       </c>
       <c r="D61" s="0" t="b">
@@ -2254,19 +2250,19 @@
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
-          <t>map_micro_plot_trigger@micro_plot.xlsx</t>
+          <t>character_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMicroPlotTimelineEvent</t>
+          <t>demo.TbCharacterFavorInfo</t>
         </is>
       </c>
       <c r="C62" s="0" t="inlineStr">
         <is>
-          <t>demo.MicroPlotTimelineEvent</t>
+          <t>demo.CharacterFavorInfo</t>
         </is>
       </c>
       <c r="D62" s="0" t="b">
@@ -2274,19 +2270,39 @@
       </c>
       <c r="E62" s="0" t="inlineStr">
         <is>
-          <t>micro_plot_timeline_event@micro_plot.xlsx</t>
+          <t>character_favor_info@character.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="B63" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbMicroPlotDef</t>
+        </is>
+      </c>
+      <c r="C63" s="0" t="inlineStr">
+        <is>
+          <t>demo.MicroPlotDef</t>
+        </is>
+      </c>
+      <c r="D63" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="0" t="inlineStr">
+        <is>
+          <t>micro_plot_def@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>demo.TbTrapSpec</t>
+          <t>demo.TbMapMicroPlotTrigger</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>demo.TrapSpec</t>
+          <t>demo.MapMicroPlotTrigger</t>
         </is>
       </c>
       <c r="D64" s="0" t="b">
@@ -2294,19 +2310,19 @@
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
-          <t>trap_spec@trap_spec.xlsx</t>
+          <t>map_micro_plot_trigger@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>demo.TbForgeRecipe</t>
+          <t>demo.TbMicroPlotTimelineEvent</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>demo.ForgeRecipe</t>
+          <t>demo.MicroPlotTimelineEvent</t>
         </is>
       </c>
       <c r="D65" s="0" t="b">
@@ -2314,19 +2330,20 @@
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
-          <t>forge_recipe@forge_recipe.xlsx</t>
-        </is>
-      </c>
-    </row>
+          <t>micro_plot_timeline_event@micro_plot.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66"/>
     <row r="67">
       <c r="B67" s="0" t="inlineStr">
         <is>
-          <t>demo.TbHActInfo</t>
+          <t>demo.TbTrapSpec</t>
         </is>
       </c>
       <c r="C67" s="0" t="inlineStr">
         <is>
-          <t>demo.HActInfo</t>
+          <t>demo.TrapSpec</t>
         </is>
       </c>
       <c r="D67" s="0" t="b">
@@ -2334,19 +2351,19 @@
       </c>
       <c r="E67" s="0" t="inlineStr">
         <is>
-          <t>h_act_info@h_act_info.xlsx</t>
+          <t>trap_spec@trap_spec.xlsx</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="0" t="inlineStr">
         <is>
-          <t>demo.TbTalentNodeLevel</t>
+          <t>demo.TbForgeRecipe</t>
         </is>
       </c>
       <c r="C68" s="0" t="inlineStr">
         <is>
-          <t>demo.TalentNodeLevel</t>
+          <t>demo.ForgeRecipe</t>
         </is>
       </c>
       <c r="D68" s="0" t="b">
@@ -2354,49 +2371,20 @@
       </c>
       <c r="E68" s="0" t="inlineStr">
         <is>
-          <t>talent_level@talent.xlsx</t>
-        </is>
-      </c>
-      <c r="F68" s="0" t="inlineStr">
-        <is>
-          <t>node_id+level</t>
-        </is>
-      </c>
-      <c r="G68" s="0" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="B69" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbSavePoint</t>
-        </is>
-      </c>
-      <c r="C69" s="0" t="inlineStr">
-        <is>
-          <t>demo.SavePoint</t>
-        </is>
-      </c>
-      <c r="D69" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E69" s="0" t="inlineStr">
-        <is>
-          <t>save_point@save_point.xlsx</t>
-        </is>
-      </c>
-    </row>
+          <t>forge_recipe@forge_recipe.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="69"/>
     <row r="70">
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>demo.TbDesireDensityTier</t>
+          <t>demo.TbHActInfo</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>demo.DesireDensityTier</t>
+          <t>demo.HActInfo</t>
         </is>
       </c>
       <c r="D70" s="0" t="b">
@@ -2404,19 +2392,19 @@
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
-          <t>desire_density_tier@desire_density_tier.xlsx</t>
+          <t>h_act_info@h_act_info.xlsx</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMindFragmentPoolEntry</t>
+          <t>demo.TbTalentNodeLevel</t>
         </is>
       </c>
       <c r="C71" s="0" t="inlineStr">
         <is>
-          <t>demo.MindFragmentPoolEntry</t>
+          <t>demo.TalentNodeLevel</t>
         </is>
       </c>
       <c r="D71" s="0" t="b">
@@ -2424,7 +2412,12 @@
       </c>
       <c r="E71" s="0" t="inlineStr">
         <is>
-          <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
+          <t>talent_level@talent.xlsx</t>
+        </is>
+      </c>
+      <c r="F71" s="0" t="inlineStr">
+        <is>
+          <t>node_id+level</t>
         </is>
       </c>
       <c r="G71" s="0" t="inlineStr">
@@ -2436,67 +2429,206 @@
     <row r="72">
       <c r="B72" s="0" t="inlineStr">
         <is>
+          <t>demo.TbSavePoint</t>
+        </is>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>demo.SavePoint</t>
+        </is>
+      </c>
+      <c r="D72" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" s="0" t="inlineStr">
+        <is>
+          <t>save_point@save_point.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbDesireDensityTier</t>
+        </is>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>demo.DesireDensityTier</t>
+        </is>
+      </c>
+      <c r="D73" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
+        <is>
+          <t>desire_density_tier@desire_density_tier.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="B74" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbMindFragmentPoolEntry</t>
+        </is>
+      </c>
+      <c r="C74" s="0" t="inlineStr">
+        <is>
+          <t>demo.MindFragmentPoolEntry</t>
+        </is>
+      </c>
+      <c r="D74" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" s="0" t="inlineStr">
+        <is>
+          <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
+        </is>
+      </c>
+      <c r="G74" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="B75" s="0" t="inlineStr">
+        <is>
           <t>demo.TbSecretBaseFacility</t>
         </is>
       </c>
-      <c r="C72" s="0" t="inlineStr">
+      <c r="C75" s="0" t="inlineStr">
         <is>
           <t>demo.SecretBaseFacility</t>
         </is>
       </c>
-      <c r="D72" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E72" s="0" t="inlineStr">
+      <c r="D75" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" s="0" t="inlineStr">
         <is>
           <t>secret_base_facility@secret_base_facility.xlsx</t>
         </is>
       </c>
-      <c r="I72" s="0" t="inlineStr">
+      <c r="I75" s="0" t="inlineStr">
         <is>
           <t>据点固定设施</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="0" t="inlineStr">
         <is>
           <t>demo.TbSecretBaseBuildLevel</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
+      <c r="C76" s="0" t="inlineStr">
         <is>
           <t>demo.SecretBaseBuildLevel</t>
         </is>
       </c>
-      <c r="D73" t="b">
-        <v>1</v>
-      </c>
-      <c r="E73" t="inlineStr">
+      <c r="D76" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E76" s="0" t="inlineStr">
         <is>
           <t>secret_base_build_level@secret_base_build_level.xlsx</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F76" s="0" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="G76" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr">
+      <c r="I76" s="0" t="inlineStr">
         <is>
           <t>据点建设等级卷轴边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78">
+      <c r="B78" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbSecretBaseCharacter</t>
+        </is>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>demo.SecretBaseCharacter</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t>secret_base_character@secret_base_character.xlsx</t>
+        </is>
+      </c>
+      <c r="F78" s="0" t="inlineStr">
+        <is>
+          <t>slot_id</t>
+        </is>
+      </c>
+      <c r="G78" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I78" s="0" t="inlineStr">
+        <is>
+          <t>秘密据点角色</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>demo.TbHumanWeapon</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>demo.HumanWeapon</t>
+        </is>
+      </c>
+      <c r="D79" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>human_weapon@human_weapon.xlsx</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>human_weapon</t>
         </is>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E11" display="unit_npc_attribute@unit_npc.xlsx" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E12" display="desire_density_info@unit_npc.xlsx" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" display="logic_area_info@map.xlsx" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" display="area_variant_info@map.xlsx" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" tooltip="mailto:area_overlay_state_info@map.xlsx" display="area_overlay_state_info@map.xlsx" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" display="unit_npc_attribute@unit_npc.xlsx" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" display="desire_density_info@unit_npc.xlsx" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K79"/>
+  <dimension ref="A1:K80"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -2588,37 +2588,57 @@
       </c>
     </row>
     <row r="79">
-      <c r="B79" t="inlineStr">
+      <c r="B79" s="0" t="inlineStr">
         <is>
           <t>demo.TbHumanWeapon</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C79" s="0" t="inlineStr">
         <is>
           <t>demo.HumanWeapon</t>
         </is>
       </c>
-      <c r="D79" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" t="inlineStr">
+      <c r="D79" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
         <is>
           <t>human_weapon@human_weapon.xlsx</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="0" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="G79" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr">
+      <c r="I79" s="0" t="inlineStr">
         <is>
           <t>human_weapon</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>demo.TbRuneData</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>demo.RuneData</t>
+        </is>
+      </c>
+      <c r="D80" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>rune_data@rune.xlsx</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K80"/>
+  <dimension ref="A1:K83"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -2623,22 +2623,92 @@
       </c>
     </row>
     <row r="80">
-      <c r="B80" t="inlineStr">
+      <c r="B80" s="0" t="inlineStr">
         <is>
           <t>demo.TbRuneData</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C80" s="0" t="inlineStr">
         <is>
           <t>demo.RuneData</t>
         </is>
       </c>
-      <c r="D80" t="b">
-        <v>1</v>
-      </c>
-      <c r="E80" t="inlineStr">
+      <c r="D80" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" s="0" t="inlineStr">
         <is>
           <t>rune_data@rune.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="B81" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbBodyPartDef</t>
+        </is>
+      </c>
+      <c r="C81" s="0" t="inlineStr">
+        <is>
+          <t>demo.BodyPartDef</t>
+        </is>
+      </c>
+      <c r="D81" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" s="0" t="inlineStr">
+        <is>
+          <t>body_part_def@body_part.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="B82" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbBodyPartLevel</t>
+        </is>
+      </c>
+      <c r="C82" s="0" t="inlineStr">
+        <is>
+          <t>demo.BodyPartLevel</t>
+        </is>
+      </c>
+      <c r="D82" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t>body_part_level@body_part.xlsx</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>part_id+level</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="B83" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbPartLocalAttrDef</t>
+        </is>
+      </c>
+      <c r="C83" s="0" t="inlineStr">
+        <is>
+          <t>demo.PartLocalAttrDef</t>
+        </is>
+      </c>
+      <c r="D83" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t>part_local_attr_def@body_part.xlsx</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K84"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -2681,12 +2681,12 @@
           <t>body_part_level@body_part.xlsx</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" s="0" t="inlineStr">
         <is>
           <t>part_id+level</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="G82" s="0" t="inlineStr">
         <is>
           <t>list</t>
         </is>
@@ -2709,6 +2709,36 @@
       <c r="E83" s="0" t="inlineStr">
         <is>
           <t>part_local_attr_def@body_part.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>demo.TbPartGear</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>demo.PartGear</t>
+        </is>
+      </c>
+      <c r="D84" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>partgear@partgear.xlsx</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K85"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -2713,32 +2713,62 @@
       </c>
     </row>
     <row r="84">
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="0" t="inlineStr">
         <is>
           <t>demo.TbPartGear</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C84" s="0" t="inlineStr">
         <is>
           <t>demo.PartGear</t>
         </is>
       </c>
-      <c r="D84" t="b">
-        <v>1</v>
-      </c>
-      <c r="E84" t="inlineStr">
+      <c r="D84" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" s="0" t="inlineStr">
         <is>
           <t>partgear@partgear.xlsx</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" s="0" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="G84" s="0" t="inlineStr">
         <is>
           <t>map</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>demo.TbRuneUpgradeInfo</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>demo.RuneUpgradeInfo</t>
+        </is>
+      </c>
+      <c r="D85" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>rune_upgrade_info@rune.xlsx</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>upgrade_id</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>符文升级项</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K87"/>
+  <dimension ref="A1:K88"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -2795,32 +2795,62 @@
       </c>
     </row>
     <row r="87">
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="0" t="inlineStr">
         <is>
           <t>demo.TbRuneEquipSlot</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C87" s="0" t="inlineStr">
         <is>
           <t>demo.RuneEquipSlotInfo</t>
         </is>
       </c>
-      <c r="D87" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" t="inlineStr">
+      <c r="D87" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
         <is>
           <t>rune_equip_slot@rune.xlsx</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" s="0" t="inlineStr">
         <is>
           <t>equip_slot</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr">
+      <c r="J87" s="0" t="inlineStr">
         <is>
           <t>符文装配槽</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>demo.TbEntitySkillLevel</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>demo.EntitySkillLevel</t>
+        </is>
+      </c>
+      <c r="D88" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>skill_level@skill.xlsx</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>skill_id+level</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K88"/>
+  <dimension ref="A1:K90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -1221,78 +1221,78 @@
     <row r="6">
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>demo.TbAreaVariantInfo</t>
+          <t>demo.TbLogicAreaHomesteadReq</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>demo.AreaVariantInfo</t>
+          <t>demo.LogicAreaHomesteadReq</t>
         </is>
       </c>
       <c r="D6" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>area_variant_info@map.xlsx</t>
+      <c r="E6" s="0" t="inlineStr">
+        <is>
+          <t>logic_area_homestead_req@map_homestead.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="0" t="inlineStr">
         <is>
+          <t>demo.TbAreaVariantInfo</t>
+        </is>
+      </c>
+      <c r="C7" s="0" t="inlineStr">
+        <is>
+          <t>demo.AreaVariantInfo</t>
+        </is>
+      </c>
+      <c r="D7" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>area_variant_info@map.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0" t="inlineStr">
+        <is>
           <t>demo.TbAreaOverlayStateInfo</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C8" s="0" t="inlineStr">
         <is>
           <t>demo.AreaOverlayStateInfo</t>
         </is>
       </c>
-      <c r="D7" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
+      <c r="D8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
         <is>
           <t>area_overlay_state_info@map.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" s="0" t="n"/>
-      <c r="C8" s="0" t="n"/>
-      <c r="D8" s="0" t="n"/>
-      <c r="E8" s="0" t="n"/>
-    </row>
     <row r="9">
-      <c r="B9" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbDropBundle</t>
-        </is>
-      </c>
-      <c r="C9" s="0" t="inlineStr">
-        <is>
-          <t>demo.DropBundle</t>
-        </is>
-      </c>
-      <c r="D9" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="0" t="inlineStr">
-        <is>
-          <t>drop_bundle@drop.xlsx</t>
-        </is>
-      </c>
+      <c r="B9" s="0" t="n"/>
+      <c r="C9" s="0" t="n"/>
+      <c r="D9" s="0" t="n"/>
+      <c r="E9" s="0" t="n"/>
     </row>
     <row r="10">
       <c r="B10" s="0" t="inlineStr">
         <is>
-          <t>demo.TbDropItem</t>
+          <t>demo.TbDropBundle</t>
         </is>
       </c>
       <c r="C10" s="0" t="inlineStr">
         <is>
-          <t>demo.DropItem</t>
+          <t>demo.DropBundle</t>
         </is>
       </c>
       <c r="D10" s="0" t="b">
@@ -1300,19 +1300,19 @@
       </c>
       <c r="E10" s="0" t="inlineStr">
         <is>
-          <t>drop_item@drop.xlsx</t>
+          <t>drop_bundle@drop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="0" t="inlineStr">
         <is>
-          <t>demo.TbFixedFacility</t>
+          <t>demo.TbDropItem</t>
         </is>
       </c>
       <c r="C11" s="0" t="inlineStr">
         <is>
-          <t>demo.FixedFacility</t>
+          <t>demo.DropItem</t>
         </is>
       </c>
       <c r="D11" s="0" t="b">
@@ -1320,19 +1320,19 @@
       </c>
       <c r="E11" s="0" t="inlineStr">
         <is>
-          <t>fixed_facility@home_facility.xlsx</t>
+          <t>drop_item@drop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="0" t="inlineStr">
         <is>
-          <t>demo.TbBornPoint</t>
+          <t>demo.TbFixedFacility</t>
         </is>
       </c>
       <c r="C12" s="0" t="inlineStr">
         <is>
-          <t>demo.BornPoint</t>
+          <t>demo.FixedFacility</t>
         </is>
       </c>
       <c r="D12" s="0" t="b">
@@ -1340,19 +1340,19 @@
       </c>
       <c r="E12" s="0" t="inlineStr">
         <is>
-          <t>born_points@born_points.xlsx</t>
+          <t>fixed_facility@home_facility.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="0" t="inlineStr">
         <is>
-          <t>demo.TbUnitNpc</t>
+          <t>demo.TbBornPoint</t>
         </is>
       </c>
       <c r="C13" s="0" t="inlineStr">
         <is>
-          <t>demo.UnitNpc</t>
+          <t>demo.BornPoint</t>
         </is>
       </c>
       <c r="D13" s="0" t="b">
@@ -1360,85 +1360,85 @@
       </c>
       <c r="E13" s="0" t="inlineStr">
         <is>
-          <t>unit_npc@unit_npc.xlsx</t>
+          <t>born_points@born_points.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="0" t="inlineStr">
         <is>
-          <t>demo.TbUnitNpcAttr</t>
+          <t>demo.TbUnitNpc</t>
         </is>
       </c>
       <c r="C14" s="0" t="inlineStr">
         <is>
-          <t>demo.UnitNpcAttr</t>
+          <t>demo.UnitNpc</t>
         </is>
       </c>
       <c r="D14" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>unit_npc_attribute@unit_npc.xlsx</t>
+      <c r="E14" s="0" t="inlineStr">
+        <is>
+          <t>unit_npc@unit_npc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="0" t="inlineStr">
         <is>
+          <t>demo.TbUnitNpcAttr</t>
+        </is>
+      </c>
+      <c r="C15" s="0" t="inlineStr">
+        <is>
+          <t>demo.UnitNpcAttr</t>
+        </is>
+      </c>
+      <c r="D15" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>unit_npc_attribute@unit_npc.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="0" t="inlineStr">
+        <is>
           <t>demo.TbDesireDensityInfo</t>
         </is>
       </c>
-      <c r="C15" s="0" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>demo.DesireDensityInfo</t>
         </is>
       </c>
-      <c r="D15" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="D16" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>desire_density_info@unit_npc.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="0" t="n"/>
-      <c r="C16" s="0" t="n"/>
-      <c r="D16" s="0" t="n"/>
-      <c r="E16" s="0" t="n"/>
-    </row>
     <row r="17">
-      <c r="B17" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbQuestData</t>
-        </is>
-      </c>
-      <c r="C17" s="0" t="inlineStr">
-        <is>
-          <t>demo.QuestData</t>
-        </is>
-      </c>
-      <c r="D17" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="0" t="inlineStr">
-        <is>
-          <t>quest_data@quests.xlsx</t>
-        </is>
-      </c>
+      <c r="B17" s="0" t="n"/>
+      <c r="C17" s="0" t="n"/>
+      <c r="D17" s="0" t="n"/>
+      <c r="E17" s="0" t="n"/>
     </row>
     <row r="18">
       <c r="B18" s="0" t="inlineStr">
         <is>
-          <t>demo.TbQuestStepData</t>
+          <t>demo.TbQuestData</t>
         </is>
       </c>
       <c r="C18" s="0" t="inlineStr">
         <is>
-          <t>demo.QuestStepData</t>
+          <t>demo.QuestData</t>
         </is>
       </c>
       <c r="D18" s="0" t="b">
@@ -1446,19 +1446,19 @@
       </c>
       <c r="E18" s="0" t="inlineStr">
         <is>
-          <t>quest_step_data@quests.xlsx</t>
+          <t>quest_data@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="0" t="inlineStr">
         <is>
-          <t>demo.TbQuestStepOutcome</t>
+          <t>demo.TbQuestStepData</t>
         </is>
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>demo.QuestStepOutcome</t>
+          <t>demo.QuestStepData</t>
         </is>
       </c>
       <c r="D19" s="0" t="b">
@@ -1466,19 +1466,19 @@
       </c>
       <c r="E19" s="0" t="inlineStr">
         <is>
-          <t>quest_step_outcome@quests.xlsx</t>
+          <t>quest_step_data@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="0" t="inlineStr">
         <is>
-          <t>demo.TbQuestStepObjective</t>
+          <t>demo.TbQuestStepOutcome</t>
         </is>
       </c>
       <c r="C20" s="0" t="inlineStr">
         <is>
-          <t>demo.QuestStepObjective</t>
+          <t>demo.QuestStepOutcome</t>
         </is>
       </c>
       <c r="D20" s="0" t="b">
@@ -1486,19 +1486,19 @@
       </c>
       <c r="E20" s="0" t="inlineStr">
         <is>
-          <t>quest_step_objective@quests.xlsx</t>
+          <t>quest_step_outcome@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="0" t="inlineStr">
         <is>
-          <t>demo.TbDialogMetaInfo</t>
+          <t>demo.TbQuestStepObjective</t>
         </is>
       </c>
       <c r="C21" s="0" t="inlineStr">
         <is>
-          <t>demo.DialogMetaInfo</t>
+          <t>demo.QuestStepObjective</t>
         </is>
       </c>
       <c r="D21" s="0" t="b">
@@ -1506,39 +1506,39 @@
       </c>
       <c r="E21" s="0" t="inlineStr">
         <is>
-          <t>dialog_meta_info@dialog.xlsx</t>
+          <t>quest_step_objective@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbItemData</t>
-        </is>
-      </c>
-      <c r="C22" s="0" t="inlineStr">
-        <is>
-          <t>demo.ItemData</t>
-        </is>
-      </c>
-      <c r="D22" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
-        <is>
-          <t>item@item.xlsx</t>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>demo.TbQuestInteractDialog</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>demo.QuestInteractDialogData</t>
+        </is>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>quest_interact_dialog@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="0" t="inlineStr">
         <is>
-          <t>demo.TbShop</t>
+          <t>demo.TbDialogMetaInfo</t>
         </is>
       </c>
       <c r="C23" s="0" t="inlineStr">
         <is>
-          <t>demo.Shop</t>
+          <t>demo.DialogMetaInfo</t>
         </is>
       </c>
       <c r="D23" s="0" t="b">
@@ -1546,19 +1546,19 @@
       </c>
       <c r="E23" s="0" t="inlineStr">
         <is>
-          <t>shop@shop.xlsx</t>
+          <t>dialog_meta_info@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="0" t="inlineStr">
         <is>
-          <t>demo.TbShopGoods</t>
+          <t>demo.TbItemData</t>
         </is>
       </c>
       <c r="C24" s="0" t="inlineStr">
         <is>
-          <t>demo.ShopGoods</t>
+          <t>demo.ItemData</t>
         </is>
       </c>
       <c r="D24" s="0" t="b">
@@ -1566,19 +1566,19 @@
       </c>
       <c r="E24" s="0" t="inlineStr">
         <is>
-          <t>shop_goods@shop.xlsx</t>
+          <t>item@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="0" t="inlineStr">
         <is>
-          <t>demo.TbItemUse</t>
+          <t>demo.TbShop</t>
         </is>
       </c>
       <c r="C25" s="0" t="inlineStr">
         <is>
-          <t>demo.ItemUse</t>
+          <t>demo.Shop</t>
         </is>
       </c>
       <c r="D25" s="0" t="b">
@@ -1586,19 +1586,19 @@
       </c>
       <c r="E25" s="0" t="inlineStr">
         <is>
-          <t>item_use@item.xlsx</t>
+          <t>shop@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="0" t="inlineStr">
         <is>
-          <t>demo.TbItemGift</t>
+          <t>demo.TbShopGoods</t>
         </is>
       </c>
       <c r="C26" s="0" t="inlineStr">
         <is>
-          <t>demo.ItemGift</t>
+          <t>demo.ShopGoods</t>
         </is>
       </c>
       <c r="D26" s="0" t="b">
@@ -1606,29 +1606,19 @@
       </c>
       <c r="E26" s="0" t="inlineStr">
         <is>
-          <t>item_gift@item.xlsx</t>
-        </is>
-      </c>
-      <c r="F26" s="0" t="inlineStr">
-        <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G26" s="0" t="inlineStr">
-        <is>
-          <t>map</t>
+          <t>shop_goods@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="0" t="inlineStr">
         <is>
-          <t>demo.TbNpcDialogInfo</t>
+          <t>demo.TbItemUse</t>
         </is>
       </c>
       <c r="C27" s="0" t="inlineStr">
         <is>
-          <t>demo.NpcDialogInfo</t>
+          <t>demo.ItemUse</t>
         </is>
       </c>
       <c r="D27" s="0" t="b">
@@ -1636,19 +1626,19 @@
       </c>
       <c r="E27" s="0" t="inlineStr">
         <is>
-          <t>npc_dialog_info@dialog.xlsx</t>
+          <t>item_use@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="0" t="inlineStr">
         <is>
-          <t>demo.TbWorldMapGlobal</t>
+          <t>demo.TbItemGift</t>
         </is>
       </c>
       <c r="C28" s="0" t="inlineStr">
         <is>
-          <t>demo.WorldMapGlobal</t>
+          <t>demo.ItemGift</t>
         </is>
       </c>
       <c r="D28" s="0" t="b">
@@ -1656,24 +1646,29 @@
       </c>
       <c r="E28" s="0" t="inlineStr">
         <is>
-          <t>world_map_global@map.xlsx</t>
+          <t>item_gift@item.xlsx</t>
+        </is>
+      </c>
+      <c r="F28" s="0" t="inlineStr">
+        <is>
+          <t>item_id</t>
         </is>
       </c>
       <c r="G28" s="0" t="inlineStr">
         <is>
-          <t>one</t>
+          <t>map</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="0" t="inlineStr">
         <is>
-          <t>demo.TbWorldMapBigMapLayer</t>
+          <t>demo.TbNpcDialogInfo</t>
         </is>
       </c>
       <c r="C29" s="0" t="inlineStr">
         <is>
-          <t>demo.WorldMapBigMapLayer</t>
+          <t>demo.NpcDialogInfo</t>
         </is>
       </c>
       <c r="D29" s="0" t="b">
@@ -1681,24 +1676,19 @@
       </c>
       <c r="E29" s="0" t="inlineStr">
         <is>
-          <t>world_map_big_map@map.xlsx</t>
-        </is>
-      </c>
-      <c r="G29" s="0" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>npc_dialog_info@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="0" t="inlineStr">
         <is>
-          <t>demo.TbDreamInfiltrationSpot</t>
+          <t>demo.TbWorldMapGlobal</t>
         </is>
       </c>
       <c r="C30" s="0" t="inlineStr">
         <is>
-          <t>demo.DreamInfiltrationSpot</t>
+          <t>demo.WorldMapGlobal</t>
         </is>
       </c>
       <c r="D30" s="0" t="b">
@@ -1706,19 +1696,24 @@
       </c>
       <c r="E30" s="0" t="inlineStr">
         <is>
-          <t>dream_infiltration@dream_infiltration.xlsx</t>
+          <t>world_map_global@map.xlsx</t>
+        </is>
+      </c>
+      <c r="G30" s="0" t="inlineStr">
+        <is>
+          <t>one</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="0" t="inlineStr">
         <is>
-          <t>demo.TbCharDreamEntryInfo</t>
+          <t>demo.TbWorldMapBigMapLayer</t>
         </is>
       </c>
       <c r="C31" s="0" t="inlineStr">
         <is>
-          <t>demo.CharDreamEntryInfo</t>
+          <t>demo.WorldMapBigMapLayer</t>
         </is>
       </c>
       <c r="D31" s="0" t="b">
@@ -1726,19 +1721,24 @@
       </c>
       <c r="E31" s="0" t="inlineStr">
         <is>
-          <t>char_dream_entry@dream_infiltration.xlsx</t>
+          <t>world_map_big_map@map.xlsx</t>
+        </is>
+      </c>
+      <c r="G31" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="0" t="inlineStr">
         <is>
-          <t>demo.TbFishingSpot</t>
+          <t>demo.TbDreamInfiltrationSpot</t>
         </is>
       </c>
       <c r="C32" s="0" t="inlineStr">
         <is>
-          <t>demo.FishingSpot</t>
+          <t>demo.DreamInfiltrationSpot</t>
         </is>
       </c>
       <c r="D32" s="0" t="b">
@@ -1746,19 +1746,19 @@
       </c>
       <c r="E32" s="0" t="inlineStr">
         <is>
-          <t>fishing_spot@fishing_spot.xlsx</t>
+          <t>dream_infiltration@dream_infiltration.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="0" t="inlineStr">
         <is>
-          <t>demo.TbFishingSpotFish</t>
+          <t>demo.TbCharDreamEntryInfo</t>
         </is>
       </c>
       <c r="C33" s="0" t="inlineStr">
         <is>
-          <t>demo.FishingSpotFish</t>
+          <t>demo.CharDreamEntryInfo</t>
         </is>
       </c>
       <c r="D33" s="0" t="b">
@@ -1766,20 +1766,39 @@
       </c>
       <c r="E33" s="0" t="inlineStr">
         <is>
-          <t>fishing_spot_fish@fishing_spot.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="34"/>
+          <t>char_dream_entry@dream_infiltration.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbFishingSpot</t>
+        </is>
+      </c>
+      <c r="C34" s="0" t="inlineStr">
+        <is>
+          <t>demo.FishingSpot</t>
+        </is>
+      </c>
+      <c r="D34" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="0" t="inlineStr">
+        <is>
+          <t>fishing_spot@fishing_spot.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="35">
       <c r="B35" s="0" t="inlineStr">
         <is>
-          <t>demo.TbPlayerDesireLevel</t>
+          <t>demo.TbFishingSpotFish</t>
         </is>
       </c>
       <c r="C35" s="0" t="inlineStr">
         <is>
-          <t>demo.PlayerDesireLevel</t>
+          <t>demo.FishingSpotFish</t>
         </is>
       </c>
       <c r="D35" s="0" t="b">
@@ -1787,39 +1806,20 @@
       </c>
       <c r="E35" s="0" t="inlineStr">
         <is>
-          <t>player_desire_level@player_status.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbPlayerJingYuLevel</t>
-        </is>
-      </c>
-      <c r="C36" s="0" t="inlineStr">
-        <is>
-          <t>demo.PlayerJingYuLevel</t>
-        </is>
-      </c>
-      <c r="D36" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" s="0" t="inlineStr">
-        <is>
-          <t>player_jingyu_level@player_status.xlsx</t>
-        </is>
-      </c>
-    </row>
+          <t>fishing_spot_fish@fishing_spot.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
     <row r="37">
       <c r="B37" s="0" t="inlineStr">
         <is>
-          <t>demo.TbPlayerSanCorruptLevel</t>
+          <t>demo.TbPlayerDesireLevel</t>
         </is>
       </c>
       <c r="C37" s="0" t="inlineStr">
         <is>
-          <t>demo.PlayerSanCorruptLevel</t>
+          <t>demo.PlayerDesireLevel</t>
         </is>
       </c>
       <c r="D37" s="0" t="b">
@@ -1827,19 +1827,19 @@
       </c>
       <c r="E37" s="0" t="inlineStr">
         <is>
-          <t>player_san_corrupt_level@player_status.xlsx</t>
+          <t>player_desire_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="0" t="inlineStr">
         <is>
-          <t>demo.TbPlayerClothesExposeInfo</t>
+          <t>demo.TbPlayerJingYuLevel</t>
         </is>
       </c>
       <c r="C38" s="0" t="inlineStr">
         <is>
-          <t>demo.PlayerClothesExposeInfo</t>
+          <t>demo.PlayerJingYuLevel</t>
         </is>
       </c>
       <c r="D38" s="0" t="b">
@@ -1847,20 +1847,39 @@
       </c>
       <c r="E38" s="0" t="inlineStr">
         <is>
-          <t>player_clothes_expose_info@player_status.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="39"/>
+          <t>player_jingyu_level@player_status.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbPlayerSanCorruptLevel</t>
+        </is>
+      </c>
+      <c r="C39" s="0" t="inlineStr">
+        <is>
+          <t>demo.PlayerSanCorruptLevel</t>
+        </is>
+      </c>
+      <c r="D39" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="0" t="inlineStr">
+        <is>
+          <t>player_san_corrupt_level@player_status.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="40">
       <c r="B40" s="0" t="inlineStr">
         <is>
-          <t>demo.TbWantedLevelInfo</t>
+          <t>demo.TbPlayerClothesExposeInfo</t>
         </is>
       </c>
       <c r="C40" s="0" t="inlineStr">
         <is>
-          <t>demo.WantedLevelInfo</t>
+          <t>demo.PlayerClothesExposeInfo</t>
         </is>
       </c>
       <c r="D40" s="0" t="b">
@@ -1868,39 +1887,20 @@
       </c>
       <c r="E40" s="0" t="inlineStr">
         <is>
-          <t>wanted_level_info@wanted.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="B41" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbWantedBehaveInfo</t>
-        </is>
-      </c>
-      <c r="C41" s="0" t="inlineStr">
-        <is>
-          <t>demo.WantedBehaveInfo</t>
-        </is>
-      </c>
-      <c r="D41" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="0" t="inlineStr">
-        <is>
-          <t>wanted_behave_info@wanted.xlsx</t>
-        </is>
-      </c>
-    </row>
+          <t>player_clothes_expose_info@player_status.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
     <row r="42">
       <c r="B42" s="0" t="inlineStr">
         <is>
-          <t>demo.TbTalentNode</t>
+          <t>demo.TbWantedLevelInfo</t>
         </is>
       </c>
       <c r="C42" s="0" t="inlineStr">
         <is>
-          <t>demo.TalentNode</t>
+          <t>demo.WantedLevelInfo</t>
         </is>
       </c>
       <c r="D42" s="0" t="b">
@@ -1908,19 +1908,19 @@
       </c>
       <c r="E42" s="0" t="inlineStr">
         <is>
-          <t>talent@talent.xlsx</t>
+          <t>wanted_level_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="0" t="inlineStr">
         <is>
-          <t>demo.TbWantedGuardSpawnTier</t>
+          <t>demo.TbWantedBehaveInfo</t>
         </is>
       </c>
       <c r="C43" s="0" t="inlineStr">
         <is>
-          <t>demo.WantedGuardSpawnTier</t>
+          <t>demo.WantedBehaveInfo</t>
         </is>
       </c>
       <c r="D43" s="0" t="b">
@@ -1928,19 +1928,19 @@
       </c>
       <c r="E43" s="0" t="inlineStr">
         <is>
-          <t>wanted_guard_spawn@wanted.xlsx</t>
+          <t>wanted_behave_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="0" t="inlineStr">
         <is>
-          <t>demo.TbEntitySkillData</t>
+          <t>demo.TbTalentNode</t>
         </is>
       </c>
       <c r="C44" s="0" t="inlineStr">
         <is>
-          <t>demo.EntitySkillData</t>
+          <t>demo.TalentNode</t>
         </is>
       </c>
       <c r="D44" s="0" t="b">
@@ -1948,19 +1948,19 @@
       </c>
       <c r="E44" s="0" t="inlineStr">
         <is>
-          <t>entity_skill@skill.xlsx</t>
+          <t>talent@talent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="0" t="inlineStr">
         <is>
-          <t>demo.TbSkillSchool</t>
+          <t>demo.TbWantedGuardSpawnTier</t>
         </is>
       </c>
       <c r="C45" s="0" t="inlineStr">
         <is>
-          <t>demo.SkillSchool</t>
+          <t>demo.WantedGuardSpawnTier</t>
         </is>
       </c>
       <c r="D45" s="0" t="b">
@@ -1968,19 +1968,19 @@
       </c>
       <c r="E45" s="0" t="inlineStr">
         <is>
-          <t>skill_school@skill.xlsx</t>
+          <t>wanted_guard_spawn@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="0" t="inlineStr">
         <is>
-          <t>demo.TbSkillLearnEntry</t>
+          <t>demo.TbEntitySkillData</t>
         </is>
       </c>
       <c r="C46" s="0" t="inlineStr">
         <is>
-          <t>demo.SkillLearnEntry</t>
+          <t>demo.EntitySkillData</t>
         </is>
       </c>
       <c r="D46" s="0" t="b">
@@ -1988,19 +1988,19 @@
       </c>
       <c r="E46" s="0" t="inlineStr">
         <is>
-          <t>skill_learn@skill.xlsx</t>
+          <t>entity_skill@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="0" t="inlineStr">
         <is>
-          <t>demo.TbDesireCrystalDef</t>
+          <t>demo.TbSkillSchool</t>
         </is>
       </c>
       <c r="C47" s="0" t="inlineStr">
         <is>
-          <t>demo.DesireCrystalDef</t>
+          <t>demo.SkillSchool</t>
         </is>
       </c>
       <c r="D47" s="0" t="b">
@@ -2008,19 +2008,19 @@
       </c>
       <c r="E47" s="0" t="inlineStr">
         <is>
-          <t>desire_crystal_def@desire_crystal.xlsx</t>
+          <t>skill_school@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMapDesireCrystalBudget</t>
+          <t>demo.TbSkillLearnEntry</t>
         </is>
       </c>
       <c r="C48" s="0" t="inlineStr">
         <is>
-          <t>demo.MapDesireCrystalBudget</t>
+          <t>demo.SkillLearnEntry</t>
         </is>
       </c>
       <c r="D48" s="0" t="b">
@@ -2028,19 +2028,19 @@
       </c>
       <c r="E48" s="0" t="inlineStr">
         <is>
-          <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
+          <t>skill_learn@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMapWalkerDesireCrystalQuota</t>
+          <t>demo.TbDesireCrystalDef</t>
         </is>
       </c>
       <c r="C49" s="0" t="inlineStr">
         <is>
-          <t>demo.MapWalkerDesireCrystalQuota</t>
+          <t>demo.DesireCrystalDef</t>
         </is>
       </c>
       <c r="D49" s="0" t="b">
@@ -2048,19 +2048,19 @@
       </c>
       <c r="E49" s="0" t="inlineStr">
         <is>
-          <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
+          <t>desire_crystal_def@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="0" t="inlineStr">
         <is>
-          <t>demo.TbNamedNpcDesireCrystal</t>
+          <t>demo.TbMapDesireCrystalBudget</t>
         </is>
       </c>
       <c r="C50" s="0" t="inlineStr">
         <is>
-          <t>demo.NamedNpcDesireCrystal</t>
+          <t>demo.MapDesireCrystalBudget</t>
         </is>
       </c>
       <c r="D50" s="0" t="b">
@@ -2068,19 +2068,19 @@
       </c>
       <c r="E50" s="0" t="inlineStr">
         <is>
-          <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
+          <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="0" t="inlineStr">
         <is>
-          <t>demo.TbSpiritMonsterTypeBudget</t>
+          <t>demo.TbMapWalkerDesireCrystalQuota</t>
         </is>
       </c>
       <c r="C51" s="0" t="inlineStr">
         <is>
-          <t>demo.SpiritMonsterTypeBudget</t>
+          <t>demo.MapWalkerDesireCrystalQuota</t>
         </is>
       </c>
       <c r="D51" s="0" t="b">
@@ -2088,19 +2088,19 @@
       </c>
       <c r="E51" s="0" t="inlineStr">
         <is>
-          <t>spirit_monster_budget@player_status.xlsx</t>
+          <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="0" t="inlineStr">
         <is>
-          <t>demo.TbContainerItemStackOverride</t>
+          <t>demo.TbNamedNpcDesireCrystal</t>
         </is>
       </c>
       <c r="C52" s="0" t="inlineStr">
         <is>
-          <t>demo.ContainerItemStackOverride</t>
+          <t>demo.NamedNpcDesireCrystal</t>
         </is>
       </c>
       <c r="D52" s="0" t="b">
@@ -2108,19 +2108,19 @@
       </c>
       <c r="E52" s="0" t="inlineStr">
         <is>
-          <t>container_item_stack_override@container_stack.xlsx</t>
+          <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="0" t="inlineStr">
         <is>
-          <t>demo.TbContainerStackTagRule</t>
+          <t>demo.TbSpiritMonsterTypeBudget</t>
         </is>
       </c>
       <c r="C53" s="0" t="inlineStr">
         <is>
-          <t>demo.ContainerStackTagRule</t>
+          <t>demo.SpiritMonsterTypeBudget</t>
         </is>
       </c>
       <c r="D53" s="0" t="b">
@@ -2128,19 +2128,19 @@
       </c>
       <c r="E53" s="0" t="inlineStr">
         <is>
-          <t>container_stack_tag_rule@container_stack.xlsx</t>
+          <t>spirit_monster_budget@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMapAreaEffect</t>
+          <t>demo.TbContainerItemStackOverride</t>
         </is>
       </c>
       <c r="C54" s="0" t="inlineStr">
         <is>
-          <t>demo.MapAreaEffect</t>
+          <t>demo.ContainerItemStackOverride</t>
         </is>
       </c>
       <c r="D54" s="0" t="b">
@@ -2148,20 +2148,39 @@
       </c>
       <c r="E54" s="0" t="inlineStr">
         <is>
-          <t>map_area_effect@map_area_effect.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="55"/>
+          <t>container_item_stack_override@container_stack.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbContainerStackTagRule</t>
+        </is>
+      </c>
+      <c r="C55" s="0" t="inlineStr">
+        <is>
+          <t>demo.ContainerStackTagRule</t>
+        </is>
+      </c>
+      <c r="D55" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="0" t="inlineStr">
+        <is>
+          <t>container_stack_tag_rule@container_stack.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="56">
       <c r="B56" s="0" t="inlineStr">
         <is>
-          <t>demo.TbFallenAmountProgressInfo</t>
+          <t>demo.TbMapAreaEffect</t>
         </is>
       </c>
       <c r="C56" s="0" t="inlineStr">
         <is>
-          <t>demo.FallenAmountProgressInfo</t>
+          <t>demo.MapAreaEffect</t>
         </is>
       </c>
       <c r="D56" s="0" t="b">
@@ -2169,39 +2188,20 @@
       </c>
       <c r="E56" s="0" t="inlineStr">
         <is>
-          <t>fallen_amount_progress_info@fallen_amount_progress_info.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbRumorIntel</t>
-        </is>
-      </c>
-      <c r="C57" s="0" t="inlineStr">
-        <is>
-          <t>demo.RumorIntel</t>
-        </is>
-      </c>
-      <c r="D57" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E57" s="0" t="inlineStr">
-        <is>
-          <t>rumor_intel@rumor_tables.xlsx</t>
-        </is>
-      </c>
-    </row>
+          <t>map_area_effect@map_area_effect.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="57"/>
     <row r="58">
       <c r="B58" s="0" t="inlineStr">
         <is>
-          <t>demo.TbRumorRandomPool</t>
+          <t>demo.TbFallenAmountProgressInfo</t>
         </is>
       </c>
       <c r="C58" s="0" t="inlineStr">
         <is>
-          <t>demo.RumorRandomPool</t>
+          <t>demo.FallenAmountProgressInfo</t>
         </is>
       </c>
       <c r="D58" s="0" t="b">
@@ -2209,19 +2209,19 @@
       </c>
       <c r="E58" s="0" t="inlineStr">
         <is>
-          <t>rumor_random_pool@rumor_tables.xlsx</t>
+          <t>fallen_amount_progress_info@fallen_amount_progress_info.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="0" t="inlineStr">
         <is>
-          <t>demo.TbRumorGlobal</t>
+          <t>demo.TbRumorIntel</t>
         </is>
       </c>
       <c r="C59" s="0" t="inlineStr">
         <is>
-          <t>demo.RumorGlobal</t>
+          <t>demo.RumorIntel</t>
         </is>
       </c>
       <c r="D59" s="0" t="b">
@@ -2229,20 +2229,39 @@
       </c>
       <c r="E59" s="0" t="inlineStr">
         <is>
-          <t>rumor_global@rumor_tables.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="60"/>
+          <t>rumor_intel@rumor_tables.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="B60" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbRumorRandomPool</t>
+        </is>
+      </c>
+      <c r="C60" s="0" t="inlineStr">
+        <is>
+          <t>demo.RumorRandomPool</t>
+        </is>
+      </c>
+      <c r="D60" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="0" t="inlineStr">
+        <is>
+          <t>rumor_random_pool@rumor_tables.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="61">
       <c r="B61" s="0" t="inlineStr">
         <is>
-          <t>demo.TbCharacterInfo</t>
+          <t>demo.TbRumorGlobal</t>
         </is>
       </c>
       <c r="C61" s="0" t="inlineStr">
         <is>
-          <t>demo.CharacterInfo</t>
+          <t>demo.RumorGlobal</t>
         </is>
       </c>
       <c r="D61" s="0" t="b">
@@ -2250,39 +2269,20 @@
       </c>
       <c r="E61" s="0" t="inlineStr">
         <is>
-          <t>character_info@character.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbCharacterFavorInfo</t>
-        </is>
-      </c>
-      <c r="C62" s="0" t="inlineStr">
-        <is>
-          <t>demo.CharacterFavorInfo</t>
-        </is>
-      </c>
-      <c r="D62" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E62" s="0" t="inlineStr">
-        <is>
-          <t>character_favor_info@character.xlsx</t>
-        </is>
-      </c>
-    </row>
+          <t>rumor_global@rumor_tables.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="62"/>
     <row r="63">
       <c r="B63" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMicroPlotDef</t>
+          <t>demo.TbCharacterInfo</t>
         </is>
       </c>
       <c r="C63" s="0" t="inlineStr">
         <is>
-          <t>demo.MicroPlotDef</t>
+          <t>demo.CharacterInfo</t>
         </is>
       </c>
       <c r="D63" s="0" t="b">
@@ -2290,19 +2290,19 @@
       </c>
       <c r="E63" s="0" t="inlineStr">
         <is>
-          <t>micro_plot_def@micro_plot.xlsx</t>
+          <t>character_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMapMicroPlotTrigger</t>
+          <t>demo.TbCharacterFavorInfo</t>
         </is>
       </c>
       <c r="C64" s="0" t="inlineStr">
         <is>
-          <t>demo.MapMicroPlotTrigger</t>
+          <t>demo.CharacterFavorInfo</t>
         </is>
       </c>
       <c r="D64" s="0" t="b">
@@ -2310,19 +2310,19 @@
       </c>
       <c r="E64" s="0" t="inlineStr">
         <is>
-          <t>map_micro_plot_trigger@micro_plot.xlsx</t>
+          <t>character_favor_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMicroPlotTimelineEvent</t>
+          <t>demo.TbMicroPlotDef</t>
         </is>
       </c>
       <c r="C65" s="0" t="inlineStr">
         <is>
-          <t>demo.MicroPlotTimelineEvent</t>
+          <t>demo.MicroPlotDef</t>
         </is>
       </c>
       <c r="D65" s="0" t="b">
@@ -2330,61 +2330,80 @@
       </c>
       <c r="E65" s="0" t="inlineStr">
         <is>
-          <t>micro_plot_timeline_event@micro_plot.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="66"/>
+          <t>micro_plot_def@micro_plot.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbMapMicroPlotTrigger</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>demo.MapMicroPlotTrigger</t>
+        </is>
+      </c>
+      <c r="D66" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="0" t="inlineStr">
+        <is>
+          <t>map_micro_plot_trigger@micro_plot.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="67">
       <c r="B67" s="0" t="inlineStr">
         <is>
+          <t>demo.TbMicroPlotTimelineEvent</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>demo.MicroPlotTimelineEvent</t>
+        </is>
+      </c>
+      <c r="D67" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="0" t="inlineStr">
+        <is>
+          <t>micro_plot_timeline_event@micro_plot.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="68"/>
+    <row r="69">
+      <c r="B69" s="0" t="inlineStr">
+        <is>
           <t>demo.TbTrapSpec</t>
         </is>
       </c>
-      <c r="C67" s="0" t="inlineStr">
+      <c r="C69" s="0" t="inlineStr">
         <is>
           <t>demo.TrapSpec</t>
         </is>
       </c>
-      <c r="D67" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="0" t="inlineStr">
+      <c r="D69" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" s="0" t="inlineStr">
         <is>
           <t>trap_spec@trap_spec.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="B68" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbForgeRecipe</t>
-        </is>
-      </c>
-      <c r="C68" s="0" t="inlineStr">
-        <is>
-          <t>demo.ForgeRecipe</t>
-        </is>
-      </c>
-      <c r="D68" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E68" s="0" t="inlineStr">
-        <is>
-          <t>forge_recipe@forge_recipe.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="69"/>
     <row r="70">
       <c r="B70" s="0" t="inlineStr">
         <is>
-          <t>demo.TbHActInfo</t>
+          <t>demo.TbForgeRecipe</t>
         </is>
       </c>
       <c r="C70" s="0" t="inlineStr">
         <is>
-          <t>demo.HActInfo</t>
+          <t>demo.ForgeRecipe</t>
         </is>
       </c>
       <c r="D70" s="0" t="b">
@@ -2392,49 +2411,20 @@
       </c>
       <c r="E70" s="0" t="inlineStr">
         <is>
-          <t>h_act_info@h_act_info.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="B71" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbTalentNodeLevel</t>
-        </is>
-      </c>
-      <c r="C71" s="0" t="inlineStr">
-        <is>
-          <t>demo.TalentNodeLevel</t>
-        </is>
-      </c>
-      <c r="D71" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E71" s="0" t="inlineStr">
-        <is>
-          <t>talent_level@talent.xlsx</t>
-        </is>
-      </c>
-      <c r="F71" s="0" t="inlineStr">
-        <is>
-          <t>node_id+level</t>
-        </is>
-      </c>
-      <c r="G71" s="0" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
-    </row>
+          <t>forge_recipe@forge_recipe.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="71"/>
     <row r="72">
       <c r="B72" s="0" t="inlineStr">
         <is>
-          <t>demo.TbSavePoint</t>
+          <t>demo.TbHActInfo</t>
         </is>
       </c>
       <c r="C72" s="0" t="inlineStr">
         <is>
-          <t>demo.SavePoint</t>
+          <t>demo.HActInfo</t>
         </is>
       </c>
       <c r="D72" s="0" t="b">
@@ -2442,19 +2432,19 @@
       </c>
       <c r="E72" s="0" t="inlineStr">
         <is>
-          <t>save_point@save_point.xlsx</t>
+          <t>h_act_info@h_act_info.xlsx</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="0" t="inlineStr">
         <is>
-          <t>demo.TbDesireDensityTier</t>
+          <t>demo.TbTalentNodeLevel</t>
         </is>
       </c>
       <c r="C73" s="0" t="inlineStr">
         <is>
-          <t>demo.DesireDensityTier</t>
+          <t>demo.TalentNodeLevel</t>
         </is>
       </c>
       <c r="D73" s="0" t="b">
@@ -2462,19 +2452,29 @@
       </c>
       <c r="E73" s="0" t="inlineStr">
         <is>
-          <t>desire_density_tier@desire_density_tier.xlsx</t>
+          <t>talent_level@talent.xlsx</t>
+        </is>
+      </c>
+      <c r="F73" s="0" t="inlineStr">
+        <is>
+          <t>node_id+level</t>
+        </is>
+      </c>
+      <c r="G73" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMindFragmentPoolEntry</t>
+          <t>demo.TbSavePoint</t>
         </is>
       </c>
       <c r="C74" s="0" t="inlineStr">
         <is>
-          <t>demo.MindFragmentPoolEntry</t>
+          <t>demo.SavePoint</t>
         </is>
       </c>
       <c r="D74" s="0" t="b">
@@ -2482,24 +2482,19 @@
       </c>
       <c r="E74" s="0" t="inlineStr">
         <is>
-          <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
-        </is>
-      </c>
-      <c r="G74" s="0" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>save_point@save_point.xlsx</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="0" t="inlineStr">
         <is>
-          <t>demo.TbSecretBaseFacility</t>
+          <t>demo.TbDesireDensityTier</t>
         </is>
       </c>
       <c r="C75" s="0" t="inlineStr">
         <is>
-          <t>demo.SecretBaseFacility</t>
+          <t>demo.DesireDensityTier</t>
         </is>
       </c>
       <c r="D75" s="0" t="b">
@@ -2507,24 +2502,19 @@
       </c>
       <c r="E75" s="0" t="inlineStr">
         <is>
-          <t>secret_base_facility@secret_base_facility.xlsx</t>
-        </is>
-      </c>
-      <c r="I75" s="0" t="inlineStr">
-        <is>
-          <t>据点固定设施</t>
+          <t>desire_density_tier@desire_density_tier.xlsx</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>demo.TbSecretBaseBuildLevel</t>
+          <t>demo.TbMindFragmentPoolEntry</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>demo.SecretBaseBuildLevel</t>
+          <t>demo.MindFragmentPoolEntry</t>
         </is>
       </c>
       <c r="D76" s="0" t="b">
@@ -2532,35 +2522,49 @@
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
-          <t>secret_base_build_level@secret_base_build_level.xlsx</t>
-        </is>
-      </c>
-      <c r="F76" s="0" t="inlineStr">
-        <is>
-          <t>level</t>
+          <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
         </is>
       </c>
       <c r="G76" s="0" t="inlineStr">
         <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I76" s="0" t="inlineStr">
-        <is>
-          <t>据点建设等级卷轴边界</t>
-        </is>
-      </c>
-    </row>
-    <row r="77"/>
+          <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="B77" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbSecretBaseFacility</t>
+        </is>
+      </c>
+      <c r="C77" s="0" t="inlineStr">
+        <is>
+          <t>demo.SecretBaseFacility</t>
+        </is>
+      </c>
+      <c r="D77" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" s="0" t="inlineStr">
+        <is>
+          <t>secret_base_facility@secret_base_facility.xlsx</t>
+        </is>
+      </c>
+      <c r="I77" s="0" t="inlineStr">
+        <is>
+          <t>据点固定设施</t>
+        </is>
+      </c>
+    </row>
     <row r="78">
       <c r="B78" s="0" t="inlineStr">
         <is>
-          <t>demo.TbSecretBaseCharacter</t>
+          <t>demo.TbSecretBaseBuildLevel</t>
         </is>
       </c>
       <c r="C78" s="0" t="inlineStr">
         <is>
-          <t>demo.SecretBaseCharacter</t>
+          <t>demo.SecretBaseBuildLevel</t>
         </is>
       </c>
       <c r="D78" s="0" t="b">
@@ -2568,12 +2572,12 @@
       </c>
       <c r="E78" s="0" t="inlineStr">
         <is>
-          <t>secret_base_character@secret_base_character.xlsx</t>
+          <t>secret_base_build_level@secret_base_build_level.xlsx</t>
         </is>
       </c>
       <c r="F78" s="0" t="inlineStr">
         <is>
-          <t>slot_id</t>
+          <t>level</t>
         </is>
       </c>
       <c r="G78" s="0" t="inlineStr">
@@ -2583,54 +2587,20 @@
       </c>
       <c r="I78" s="0" t="inlineStr">
         <is>
-          <t>秘密据点角色</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbHumanWeapon</t>
-        </is>
-      </c>
-      <c r="C79" s="0" t="inlineStr">
-        <is>
-          <t>demo.HumanWeapon</t>
-        </is>
-      </c>
-      <c r="D79" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" s="0" t="inlineStr">
-        <is>
-          <t>human_weapon@human_weapon.xlsx</t>
-        </is>
-      </c>
-      <c r="F79" s="0" t="inlineStr">
-        <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G79" s="0" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I79" s="0" t="inlineStr">
-        <is>
-          <t>human_weapon</t>
-        </is>
-      </c>
-    </row>
+          <t>据点建设等级卷轴边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="79"/>
     <row r="80">
       <c r="B80" s="0" t="inlineStr">
         <is>
-          <t>demo.TbRuneData</t>
+          <t>demo.TbSecretBaseCharacter</t>
         </is>
       </c>
       <c r="C80" s="0" t="inlineStr">
         <is>
-          <t>demo.RuneData</t>
+          <t>demo.SecretBaseCharacter</t>
         </is>
       </c>
       <c r="D80" s="0" t="b">
@@ -2638,19 +2608,34 @@
       </c>
       <c r="E80" s="0" t="inlineStr">
         <is>
-          <t>rune_data@rune.xlsx</t>
+          <t>secret_base_character@secret_base_character.xlsx</t>
+        </is>
+      </c>
+      <c r="F80" s="0" t="inlineStr">
+        <is>
+          <t>slot_id</t>
+        </is>
+      </c>
+      <c r="G80" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I80" s="0" t="inlineStr">
+        <is>
+          <t>秘密据点角色</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>demo.TbBodyPartDef</t>
+          <t>demo.TbHumanWeapon</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>demo.BodyPartDef</t>
+          <t>demo.HumanWeapon</t>
         </is>
       </c>
       <c r="D81" s="0" t="b">
@@ -2658,121 +2643,126 @@
       </c>
       <c r="E81" s="0" t="inlineStr">
         <is>
-          <t>body_part_def@body_part.xlsx</t>
+          <t>human_weapon@human_weapon.xlsx</t>
+        </is>
+      </c>
+      <c r="F81" s="0" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G81" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I81" s="0" t="inlineStr">
+        <is>
+          <t>human_weapon</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>demo.TbBodyPartLevel</t>
+          <t>demo.TbRuneData</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>demo.BodyPartLevel</t>
+          <t>demo.RuneData</t>
         </is>
       </c>
       <c r="D82" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>body_part_level@body_part.xlsx</t>
-        </is>
-      </c>
-      <c r="F82" s="0" t="inlineStr">
-        <is>
-          <t>part_id+level</t>
-        </is>
-      </c>
-      <c r="G82" s="0" t="inlineStr">
-        <is>
-          <t>list</t>
+      <c r="E82" s="0" t="inlineStr">
+        <is>
+          <t>rune_data@rune.xlsx</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>demo.TbBodyPartProgressInfo</t>
+          <t>demo.TbBodyPartDef</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>demo.BodyPartProgressInfo</t>
+          <t>demo.BodyPartDef</t>
         </is>
       </c>
       <c r="D83" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>body_part_progress_info@body_part.xlsx</t>
-        </is>
-      </c>
-      <c r="F83" s="0" t="n"/>
-      <c r="G83" s="0" t="n"/>
+      <c r="E83" s="0" t="inlineStr">
+        <is>
+          <t>body_part_def@body_part.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>demo.TbPartLocalAttrDef</t>
+          <t>demo.TbBodyPartLevel</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>demo.PartLocalAttrDef</t>
+          <t>demo.BodyPartLevel</t>
         </is>
       </c>
       <c r="D84" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E84" s="0" t="inlineStr">
-        <is>
-          <t>part_local_attr_def@body_part.xlsx</t>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>body_part_level@body_part.xlsx</t>
+        </is>
+      </c>
+      <c r="F84" s="0" t="inlineStr">
+        <is>
+          <t>part_id+level</t>
+        </is>
+      </c>
+      <c r="G84" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>demo.TbPartGear</t>
+          <t>demo.TbBodyPartProgressInfo</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>demo.PartGear</t>
+          <t>demo.BodyPartProgressInfo</t>
         </is>
       </c>
       <c r="D85" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E85" s="0" t="inlineStr">
-        <is>
-          <t>partgear@partgear.xlsx</t>
-        </is>
-      </c>
-      <c r="F85" s="0" t="inlineStr">
-        <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G85" s="0" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>body_part_progress_info@body_part.xlsx</t>
+        </is>
+      </c>
+      <c r="F85" s="0" t="n"/>
+      <c r="G85" s="0" t="n"/>
     </row>
     <row r="86">
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>demo.TbRuneUpgradeInfo</t>
+          <t>demo.TbPartLocalAttrDef</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>demo.RuneUpgradeInfo</t>
+          <t>demo.PartLocalAttrDef</t>
         </is>
       </c>
       <c r="D86" s="0" t="b">
@@ -2780,75 +2770,125 @@
       </c>
       <c r="E86" s="0" t="inlineStr">
         <is>
-          <t>rune_upgrade_info@rune.xlsx</t>
-        </is>
-      </c>
-      <c r="F86" s="0" t="inlineStr">
-        <is>
-          <t>upgrade_id</t>
-        </is>
-      </c>
-      <c r="J86" s="0" t="inlineStr">
-        <is>
-          <t>符文升级项</t>
+          <t>part_local_attr_def@body_part.xlsx</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="0" t="inlineStr">
         <is>
+          <t>demo.TbPartGear</t>
+        </is>
+      </c>
+      <c r="C87" s="0" t="inlineStr">
+        <is>
+          <t>demo.PartGear</t>
+        </is>
+      </c>
+      <c r="D87" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="0" t="inlineStr">
+        <is>
+          <t>partgear@partgear.xlsx</t>
+        </is>
+      </c>
+      <c r="F87" s="0" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G87" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="B88" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbRuneUpgradeInfo</t>
+        </is>
+      </c>
+      <c r="C88" s="0" t="inlineStr">
+        <is>
+          <t>demo.RuneUpgradeInfo</t>
+        </is>
+      </c>
+      <c r="D88" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" s="0" t="inlineStr">
+        <is>
+          <t>rune_upgrade_info@rune.xlsx</t>
+        </is>
+      </c>
+      <c r="F88" s="0" t="inlineStr">
+        <is>
+          <t>upgrade_id</t>
+        </is>
+      </c>
+      <c r="J88" s="0" t="inlineStr">
+        <is>
+          <t>符文升级项</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="B89" s="0" t="inlineStr">
+        <is>
           <t>demo.TbRuneEquipSlot</t>
         </is>
       </c>
-      <c r="C87" s="0" t="inlineStr">
+      <c r="C89" s="0" t="inlineStr">
         <is>
           <t>demo.RuneEquipSlotInfo</t>
         </is>
       </c>
-      <c r="D87" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" s="0" t="inlineStr">
+      <c r="D89" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" s="0" t="inlineStr">
         <is>
           <t>rune_equip_slot@rune.xlsx</t>
         </is>
       </c>
-      <c r="F87" s="0" t="inlineStr">
+      <c r="F89" s="0" t="inlineStr">
         <is>
           <t>equip_slot</t>
         </is>
       </c>
-      <c r="J87" s="0" t="inlineStr">
+      <c r="J89" s="0" t="inlineStr">
         <is>
           <t>符文装配槽</t>
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="B88" t="inlineStr">
+    <row r="90">
+      <c r="B90" s="0" t="inlineStr">
         <is>
           <t>demo.TbEntitySkillLevel</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C90" s="0" t="inlineStr">
         <is>
           <t>demo.EntitySkillLevel</t>
         </is>
       </c>
-      <c r="D88" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" t="inlineStr">
+      <c r="D90" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" s="0" t="inlineStr">
         <is>
           <t>skill_level@skill.xlsx</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F90" s="0" t="inlineStr">
         <is>
           <t>skill_id+level</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G90" s="0" t="inlineStr">
         <is>
           <t>list</t>
         </is>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K90"/>
+  <dimension ref="A1:K92"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -1511,20 +1511,20 @@
       </c>
     </row>
     <row r="22">
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="0" t="inlineStr">
         <is>
           <t>demo.TbQuestInteractDialog</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>demo.QuestInteractDialogData</t>
         </is>
       </c>
-      <c r="D22" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="D22" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="0" t="inlineStr">
         <is>
           <t>quest_interact_dialog@dialog.xlsx</t>
         </is>
@@ -2891,6 +2891,76 @@
       <c r="G90" s="0" t="inlineStr">
         <is>
           <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbHomesteadBuilding</t>
+        </is>
+      </c>
+      <c r="C91" s="0" t="inlineStr">
+        <is>
+          <t>demo.HomesteadBuilding</t>
+        </is>
+      </c>
+      <c r="D91" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" s="0" t="inlineStr">
+        <is>
+          <t>homestead_building@map_homestead.xlsx</t>
+        </is>
+      </c>
+      <c r="F91" s="0" t="inlineStr">
+        <is>
+          <t>logic_area_id+building_id</t>
+        </is>
+      </c>
+      <c r="G91" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="I91" s="0" t="inlineStr">
+        <is>
+          <t>逻辑区域可管理建筑</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbHomesteadBuildingUpgrade</t>
+        </is>
+      </c>
+      <c r="C92" s="0" t="inlineStr">
+        <is>
+          <t>demo.HomesteadBuildingUpgrade</t>
+        </is>
+      </c>
+      <c r="D92" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" s="0" t="inlineStr">
+        <is>
+          <t>homestead_building_upgrade@map_homestead.xlsx</t>
+        </is>
+      </c>
+      <c r="F92" s="0" t="inlineStr">
+        <is>
+          <t>logic_area_id+building_id+level</t>
+        </is>
+      </c>
+      <c r="G92" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="I92" s="0" t="inlineStr">
+        <is>
+          <t>家园建筑升级项</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K92"/>
+  <dimension ref="A1:K98"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -2961,6 +2961,161 @@
       <c r="I92" s="0" t="inlineStr">
         <is>
           <t>家园建筑升级项</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbJingYuanCodexDef</t>
+        </is>
+      </c>
+      <c r="C93" s="0" t="inlineStr">
+        <is>
+          <t>demo.JingYuanCodexDef</t>
+        </is>
+      </c>
+      <c r="D93" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="0" t="inlineStr">
+        <is>
+          <t>jingyuan_codex_def@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F93" s="0" t="inlineStr">
+        <is>
+          <t>codex_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbJingYuanCodexLevel</t>
+        </is>
+      </c>
+      <c r="C94" s="0" t="inlineStr">
+        <is>
+          <t>demo.JingYuanCodexLevel</t>
+        </is>
+      </c>
+      <c r="D94" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" s="0" t="inlineStr">
+        <is>
+          <t>jingyuan_codex_level@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F94" s="0" t="inlineStr">
+        <is>
+          <t>codex_id+level</t>
+        </is>
+      </c>
+      <c r="G94" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="B95" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbJingYuanTuneTier</t>
+        </is>
+      </c>
+      <c r="C95" s="0" t="inlineStr">
+        <is>
+          <t>demo.JingYuanTuneTier</t>
+        </is>
+      </c>
+      <c r="D95" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" s="0" t="inlineStr">
+        <is>
+          <t>jingyuan_tune_tier@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F95" s="0" t="inlineStr">
+        <is>
+          <t>codex_id+tier</t>
+        </is>
+      </c>
+      <c r="G95" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="B96" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbTiaoJingConcentrationLevel</t>
+        </is>
+      </c>
+      <c r="C96" s="0" t="inlineStr">
+        <is>
+          <t>demo.TiaoJingConcentrationLevel</t>
+        </is>
+      </c>
+      <c r="D96" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" s="0" t="inlineStr">
+        <is>
+          <t>tiao_jing_concentration_level@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>demo.TbJingYuanTypeDef</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>demo.JingYuanTypeDef</t>
+        </is>
+      </c>
+      <c r="D97" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>jingyuan_type_def@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>type_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>demo.TbJingYuanTypePoolEntry</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>demo.JingYuanTypePoolEntry</t>
+        </is>
+      </c>
+      <c r="D98" t="b">
+        <v>1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>jingyuan_type_pool@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K98"/>
+  <dimension ref="A1:K99"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -3070,52 +3070,87 @@
       </c>
     </row>
     <row r="97">
-      <c r="B97" t="inlineStr">
+      <c r="B97" s="0" t="inlineStr">
         <is>
           <t>demo.TbJingYuanTypeDef</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
+      <c r="C97" s="0" t="inlineStr">
         <is>
           <t>demo.JingYuanTypeDef</t>
         </is>
       </c>
-      <c r="D97" t="b">
-        <v>1</v>
-      </c>
-      <c r="E97" t="inlineStr">
+      <c r="D97" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97" s="0" t="inlineStr">
         <is>
           <t>jingyuan_type_def@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" s="0" t="inlineStr">
         <is>
           <t>type_id</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" t="inlineStr">
+      <c r="B98" s="0" t="inlineStr">
         <is>
           <t>demo.TbJingYuanTypePoolEntry</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C98" s="0" t="inlineStr">
         <is>
           <t>demo.JingYuanTypePoolEntry</t>
         </is>
       </c>
-      <c r="D98" t="b">
-        <v>1</v>
-      </c>
-      <c r="E98" t="inlineStr">
+      <c r="D98" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E98" s="0" t="inlineStr">
         <is>
           <t>jingyuan_type_pool@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="G98" s="0" t="inlineStr">
         <is>
           <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>demo.TbProgressionHubTab</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>demo.ProgressionHubTabDef</t>
+        </is>
+      </c>
+      <c r="D99" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>progression_hub_tab@progression_hub_tab.xlsx</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>tab_id</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>养成总面板选项卡</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K99"/>
+  <dimension ref="A1:K100"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -3120,37 +3120,57 @@
       </c>
     </row>
     <row r="99">
-      <c r="B99" t="inlineStr">
+      <c r="B99" s="0" t="inlineStr">
         <is>
           <t>demo.TbProgressionHubTab</t>
         </is>
       </c>
-      <c r="C99" t="inlineStr">
+      <c r="C99" s="0" t="inlineStr">
         <is>
           <t>demo.ProgressionHubTabDef</t>
         </is>
       </c>
-      <c r="D99" t="b">
-        <v>1</v>
-      </c>
-      <c r="E99" t="inlineStr">
+      <c r="D99" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
         <is>
           <t>progression_hub_tab@progression_hub_tab.xlsx</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F99" s="0" t="inlineStr">
         <is>
           <t>tab_id</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="G99" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr">
+      <c r="I99" s="0" t="inlineStr">
         <is>
           <t>养成总面板选项卡</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>demo.TbPlayerAttachInfo</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>demo.PlayerAttachInfo</t>
+        </is>
+      </c>
+      <c r="D100" t="b">
+        <v>1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>player_attach@player_attach.xlsx</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1021,7 +1021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K100"/>
+  <dimension ref="A1:K101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -2487,34 +2487,39 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbDesireDensityTier</t>
-        </is>
-      </c>
-      <c r="C75" s="0" t="inlineStr">
-        <is>
-          <t>demo.DesireDensityTier</t>
-        </is>
-      </c>
-      <c r="D75" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E75" s="0" t="inlineStr">
-        <is>
-          <t>desire_density_tier@desire_density_tier.xlsx</t>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>demo.TbReviveRule</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>demo.ReviveRule</t>
+        </is>
+      </c>
+      <c r="D75" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>revive_rule@revive_rule.xlsx</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="0" t="inlineStr">
         <is>
-          <t>demo.TbMindFragmentPoolEntry</t>
+          <t>demo.TbDesireDensityTier</t>
         </is>
       </c>
       <c r="C76" s="0" t="inlineStr">
         <is>
-          <t>demo.MindFragmentPoolEntry</t>
+          <t>demo.DesireDensityTier</t>
         </is>
       </c>
       <c r="D76" s="0" t="b">
@@ -2522,24 +2527,19 @@
       </c>
       <c r="E76" s="0" t="inlineStr">
         <is>
-          <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
-        </is>
-      </c>
-      <c r="G76" s="0" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>desire_density_tier@desire_density_tier.xlsx</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="0" t="inlineStr">
         <is>
-          <t>demo.TbSecretBaseFacility</t>
+          <t>demo.TbMindFragmentPoolEntry</t>
         </is>
       </c>
       <c r="C77" s="0" t="inlineStr">
         <is>
-          <t>demo.SecretBaseFacility</t>
+          <t>demo.MindFragmentPoolEntry</t>
         </is>
       </c>
       <c r="D77" s="0" t="b">
@@ -2547,95 +2547,85 @@
       </c>
       <c r="E77" s="0" t="inlineStr">
         <is>
-          <t>secret_base_facility@secret_base_facility.xlsx</t>
-        </is>
-      </c>
-      <c r="I77" s="0" t="inlineStr">
-        <is>
-          <t>据点固定设施</t>
+          <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
+        </is>
+      </c>
+      <c r="G77" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="0" t="inlineStr">
         <is>
+          <t>demo.TbSecretBaseFacility</t>
+        </is>
+      </c>
+      <c r="C78" s="0" t="inlineStr">
+        <is>
+          <t>demo.SecretBaseFacility</t>
+        </is>
+      </c>
+      <c r="D78" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" s="0" t="inlineStr">
+        <is>
+          <t>secret_base_facility@secret_base_facility.xlsx</t>
+        </is>
+      </c>
+      <c r="I78" s="0" t="inlineStr">
+        <is>
+          <t>据点固定设施</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="B79" s="0" t="inlineStr">
+        <is>
           <t>demo.TbSecretBaseBuildLevel</t>
         </is>
       </c>
-      <c r="C78" s="0" t="inlineStr">
+      <c r="C79" s="0" t="inlineStr">
         <is>
           <t>demo.SecretBaseBuildLevel</t>
         </is>
       </c>
-      <c r="D78" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E78" s="0" t="inlineStr">
+      <c r="D79" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" s="0" t="inlineStr">
         <is>
           <t>secret_base_build_level@secret_base_build_level.xlsx</t>
         </is>
       </c>
-      <c r="F78" s="0" t="inlineStr">
+      <c r="F79" s="0" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="G78" s="0" t="inlineStr">
+      <c r="G79" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I78" s="0" t="inlineStr">
+      <c r="I79" s="0" t="inlineStr">
         <is>
           <t>据点建设等级卷轴边界</t>
         </is>
       </c>
     </row>
-    <row r="79"/>
-    <row r="80">
-      <c r="B80" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbSecretBaseCharacter</t>
-        </is>
-      </c>
-      <c r="C80" s="0" t="inlineStr">
-        <is>
-          <t>demo.SecretBaseCharacter</t>
-        </is>
-      </c>
-      <c r="D80" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E80" s="0" t="inlineStr">
-        <is>
-          <t>secret_base_character@secret_base_character.xlsx</t>
-        </is>
-      </c>
-      <c r="F80" s="0" t="inlineStr">
-        <is>
-          <t>slot_id</t>
-        </is>
-      </c>
-      <c r="G80" s="0" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I80" s="0" t="inlineStr">
-        <is>
-          <t>秘密据点角色</t>
-        </is>
-      </c>
-    </row>
+    <row r="80"/>
     <row r="81">
       <c r="B81" s="0" t="inlineStr">
         <is>
-          <t>demo.TbHumanWeapon</t>
+          <t>demo.TbSecretBaseCharacter</t>
         </is>
       </c>
       <c r="C81" s="0" t="inlineStr">
         <is>
-          <t>demo.HumanWeapon</t>
+          <t>demo.SecretBaseCharacter</t>
         </is>
       </c>
       <c r="D81" s="0" t="b">
@@ -2643,12 +2633,12 @@
       </c>
       <c r="E81" s="0" t="inlineStr">
         <is>
-          <t>human_weapon@human_weapon.xlsx</t>
+          <t>secret_base_character@secret_base_character.xlsx</t>
         </is>
       </c>
       <c r="F81" s="0" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>slot_id</t>
         </is>
       </c>
       <c r="G81" s="0" t="inlineStr">
@@ -2658,19 +2648,19 @@
       </c>
       <c r="I81" s="0" t="inlineStr">
         <is>
-          <t>human_weapon</t>
+          <t>秘密据点角色</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="0" t="inlineStr">
         <is>
-          <t>demo.TbRuneData</t>
+          <t>demo.TbHumanWeapon</t>
         </is>
       </c>
       <c r="C82" s="0" t="inlineStr">
         <is>
-          <t>demo.RuneData</t>
+          <t>demo.HumanWeapon</t>
         </is>
       </c>
       <c r="D82" s="0" t="b">
@@ -2678,19 +2668,34 @@
       </c>
       <c r="E82" s="0" t="inlineStr">
         <is>
-          <t>rune_data@rune.xlsx</t>
+          <t>human_weapon@human_weapon.xlsx</t>
+        </is>
+      </c>
+      <c r="F82" s="0" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G82" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I82" s="0" t="inlineStr">
+        <is>
+          <t>human_weapon</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="0" t="inlineStr">
         <is>
-          <t>demo.TbBodyPartDef</t>
+          <t>demo.TbRuneData</t>
         </is>
       </c>
       <c r="C83" s="0" t="inlineStr">
         <is>
-          <t>demo.BodyPartDef</t>
+          <t>demo.RuneData</t>
         </is>
       </c>
       <c r="D83" s="0" t="b">
@@ -2698,49 +2703,39 @@
       </c>
       <c r="E83" s="0" t="inlineStr">
         <is>
-          <t>body_part_def@body_part.xlsx</t>
+          <t>rune_data@rune.xlsx</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="0" t="inlineStr">
         <is>
-          <t>demo.TbBodyPartLevel</t>
+          <t>demo.TbBodyPartDef</t>
         </is>
       </c>
       <c r="C84" s="0" t="inlineStr">
         <is>
-          <t>demo.BodyPartLevel</t>
+          <t>demo.BodyPartDef</t>
         </is>
       </c>
       <c r="D84" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>body_part_level@body_part.xlsx</t>
-        </is>
-      </c>
-      <c r="F84" s="0" t="inlineStr">
-        <is>
-          <t>part_id+level</t>
-        </is>
-      </c>
-      <c r="G84" s="0" t="inlineStr">
-        <is>
-          <t>list</t>
+      <c r="E84" s="0" t="inlineStr">
+        <is>
+          <t>body_part_def@body_part.xlsx</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="0" t="inlineStr">
         <is>
-          <t>demo.TbBodyPartProgressInfo</t>
+          <t>demo.TbBodyPartLevel</t>
         </is>
       </c>
       <c r="C85" s="0" t="inlineStr">
         <is>
-          <t>demo.BodyPartProgressInfo</t>
+          <t>demo.BodyPartLevel</t>
         </is>
       </c>
       <c r="D85" s="0" t="b">
@@ -2748,41 +2743,51 @@
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>body_part_progress_info@body_part.xlsx</t>
-        </is>
-      </c>
-      <c r="F85" s="0" t="n"/>
-      <c r="G85" s="0" t="n"/>
+          <t>body_part_level@body_part.xlsx</t>
+        </is>
+      </c>
+      <c r="F85" s="0" t="inlineStr">
+        <is>
+          <t>part_id+level</t>
+        </is>
+      </c>
+      <c r="G85" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="B86" s="0" t="inlineStr">
         <is>
-          <t>demo.TbPartLocalAttrDef</t>
+          <t>demo.TbBodyPartProgressInfo</t>
         </is>
       </c>
       <c r="C86" s="0" t="inlineStr">
         <is>
-          <t>demo.PartLocalAttrDef</t>
+          <t>demo.BodyPartProgressInfo</t>
         </is>
       </c>
       <c r="D86" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E86" s="0" t="inlineStr">
-        <is>
-          <t>part_local_attr_def@body_part.xlsx</t>
-        </is>
-      </c>
+      <c r="E86" s="5" t="inlineStr">
+        <is>
+          <t>body_part_progress_info@body_part.xlsx</t>
+        </is>
+      </c>
+      <c r="F86" s="0" t="n"/>
+      <c r="G86" s="0" t="n"/>
     </row>
     <row r="87">
       <c r="B87" s="0" t="inlineStr">
         <is>
-          <t>demo.TbPartGear</t>
+          <t>demo.TbPartLocalAttrDef</t>
         </is>
       </c>
       <c r="C87" s="0" t="inlineStr">
         <is>
-          <t>demo.PartGear</t>
+          <t>demo.PartLocalAttrDef</t>
         </is>
       </c>
       <c r="D87" s="0" t="b">
@@ -2790,29 +2795,19 @@
       </c>
       <c r="E87" s="0" t="inlineStr">
         <is>
-          <t>partgear@partgear.xlsx</t>
-        </is>
-      </c>
-      <c r="F87" s="0" t="inlineStr">
-        <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G87" s="0" t="inlineStr">
-        <is>
-          <t>map</t>
+          <t>part_local_attr_def@body_part.xlsx</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="0" t="inlineStr">
         <is>
-          <t>demo.TbRuneUpgradeInfo</t>
+          <t>demo.TbPartGear</t>
         </is>
       </c>
       <c r="C88" s="0" t="inlineStr">
         <is>
-          <t>demo.RuneUpgradeInfo</t>
+          <t>demo.PartGear</t>
         </is>
       </c>
       <c r="D88" s="0" t="b">
@@ -2820,29 +2815,29 @@
       </c>
       <c r="E88" s="0" t="inlineStr">
         <is>
-          <t>rune_upgrade_info@rune.xlsx</t>
+          <t>partgear@partgear.xlsx</t>
         </is>
       </c>
       <c r="F88" s="0" t="inlineStr">
         <is>
-          <t>upgrade_id</t>
-        </is>
-      </c>
-      <c r="J88" s="0" t="inlineStr">
-        <is>
-          <t>符文升级项</t>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G88" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="0" t="inlineStr">
         <is>
-          <t>demo.TbRuneEquipSlot</t>
+          <t>demo.TbRuneUpgradeInfo</t>
         </is>
       </c>
       <c r="C89" s="0" t="inlineStr">
         <is>
-          <t>demo.RuneEquipSlotInfo</t>
+          <t>demo.RuneUpgradeInfo</t>
         </is>
       </c>
       <c r="D89" s="0" t="b">
@@ -2850,29 +2845,29 @@
       </c>
       <c r="E89" s="0" t="inlineStr">
         <is>
-          <t>rune_equip_slot@rune.xlsx</t>
+          <t>rune_upgrade_info@rune.xlsx</t>
         </is>
       </c>
       <c r="F89" s="0" t="inlineStr">
         <is>
-          <t>equip_slot</t>
+          <t>upgrade_id</t>
         </is>
       </c>
       <c r="J89" s="0" t="inlineStr">
         <is>
-          <t>符文装配槽</t>
+          <t>符文升级项</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="0" t="inlineStr">
         <is>
-          <t>demo.TbEntitySkillLevel</t>
+          <t>demo.TbRuneEquipSlot</t>
         </is>
       </c>
       <c r="C90" s="0" t="inlineStr">
         <is>
-          <t>demo.EntitySkillLevel</t>
+          <t>demo.RuneEquipSlotInfo</t>
         </is>
       </c>
       <c r="D90" s="0" t="b">
@@ -2880,29 +2875,29 @@
       </c>
       <c r="E90" s="0" t="inlineStr">
         <is>
-          <t>skill_level@skill.xlsx</t>
+          <t>rune_equip_slot@rune.xlsx</t>
         </is>
       </c>
       <c r="F90" s="0" t="inlineStr">
         <is>
-          <t>skill_id+level</t>
-        </is>
-      </c>
-      <c r="G90" s="0" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>equip_slot</t>
+        </is>
+      </c>
+      <c r="J90" s="0" t="inlineStr">
+        <is>
+          <t>符文装配槽</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="0" t="inlineStr">
         <is>
-          <t>demo.TbHomesteadBuilding</t>
+          <t>demo.TbEntitySkillLevel</t>
         </is>
       </c>
       <c r="C91" s="0" t="inlineStr">
         <is>
-          <t>demo.HomesteadBuilding</t>
+          <t>demo.EntitySkillLevel</t>
         </is>
       </c>
       <c r="D91" s="0" t="b">
@@ -2910,34 +2905,29 @@
       </c>
       <c r="E91" s="0" t="inlineStr">
         <is>
-          <t>homestead_building@map_homestead.xlsx</t>
+          <t>skill_level@skill.xlsx</t>
         </is>
       </c>
       <c r="F91" s="0" t="inlineStr">
         <is>
-          <t>logic_area_id+building_id</t>
+          <t>skill_id+level</t>
         </is>
       </c>
       <c r="G91" s="0" t="inlineStr">
         <is>
           <t>list</t>
-        </is>
-      </c>
-      <c r="I91" s="0" t="inlineStr">
-        <is>
-          <t>逻辑区域可管理建筑</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="0" t="inlineStr">
         <is>
-          <t>demo.TbHomesteadBuildingUpgrade</t>
+          <t>demo.TbHomesteadBuilding</t>
         </is>
       </c>
       <c r="C92" s="0" t="inlineStr">
         <is>
-          <t>demo.HomesteadBuildingUpgrade</t>
+          <t>demo.HomesteadBuilding</t>
         </is>
       </c>
       <c r="D92" s="0" t="b">
@@ -2945,12 +2935,12 @@
       </c>
       <c r="E92" s="0" t="inlineStr">
         <is>
-          <t>homestead_building_upgrade@map_homestead.xlsx</t>
+          <t>homestead_building@map_homestead.xlsx</t>
         </is>
       </c>
       <c r="F92" s="0" t="inlineStr">
         <is>
-          <t>logic_area_id+building_id+level</t>
+          <t>logic_area_id+building_id</t>
         </is>
       </c>
       <c r="G92" s="0" t="inlineStr">
@@ -2960,19 +2950,19 @@
       </c>
       <c r="I92" s="0" t="inlineStr">
         <is>
-          <t>家园建筑升级项</t>
+          <t>逻辑区域可管理建筑</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="0" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanCodexDef</t>
+          <t>demo.TbHomesteadBuildingUpgrade</t>
         </is>
       </c>
       <c r="C93" s="0" t="inlineStr">
         <is>
-          <t>demo.JingYuanCodexDef</t>
+          <t>demo.HomesteadBuildingUpgrade</t>
         </is>
       </c>
       <c r="D93" s="0" t="b">
@@ -2980,24 +2970,34 @@
       </c>
       <c r="E93" s="0" t="inlineStr">
         <is>
-          <t>jingyuan_codex_def@jingyuan_codex.xlsx</t>
+          <t>homestead_building_upgrade@map_homestead.xlsx</t>
         </is>
       </c>
       <c r="F93" s="0" t="inlineStr">
         <is>
-          <t>codex_id</t>
+          <t>logic_area_id+building_id+level</t>
+        </is>
+      </c>
+      <c r="G93" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="I93" s="0" t="inlineStr">
+        <is>
+          <t>家园建筑升级项</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="0" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanCodexLevel</t>
+          <t>demo.TbJingYuanCodexDef</t>
         </is>
       </c>
       <c r="C94" s="0" t="inlineStr">
         <is>
-          <t>demo.JingYuanCodexLevel</t>
+          <t>demo.JingYuanCodexDef</t>
         </is>
       </c>
       <c r="D94" s="0" t="b">
@@ -3005,29 +3005,24 @@
       </c>
       <c r="E94" s="0" t="inlineStr">
         <is>
-          <t>jingyuan_codex_level@jingyuan_codex.xlsx</t>
+          <t>jingyuan_codex_def@jingyuan_codex.xlsx</t>
         </is>
       </c>
       <c r="F94" s="0" t="inlineStr">
         <is>
-          <t>codex_id+level</t>
-        </is>
-      </c>
-      <c r="G94" s="0" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>codex_id</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="0" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanTuneTier</t>
+          <t>demo.TbJingYuanCodexLevel</t>
         </is>
       </c>
       <c r="C95" s="0" t="inlineStr">
         <is>
-          <t>demo.JingYuanTuneTier</t>
+          <t>demo.JingYuanCodexLevel</t>
         </is>
       </c>
       <c r="D95" s="0" t="b">
@@ -3035,12 +3030,12 @@
       </c>
       <c r="E95" s="0" t="inlineStr">
         <is>
-          <t>jingyuan_tune_tier@jingyuan_codex.xlsx</t>
+          <t>jingyuan_codex_level@jingyuan_codex.xlsx</t>
         </is>
       </c>
       <c r="F95" s="0" t="inlineStr">
         <is>
-          <t>codex_id+tier</t>
+          <t>codex_id+level</t>
         </is>
       </c>
       <c r="G95" s="0" t="inlineStr">
@@ -3052,12 +3047,12 @@
     <row r="96">
       <c r="B96" s="0" t="inlineStr">
         <is>
-          <t>demo.TbTiaoJingConcentrationLevel</t>
+          <t>demo.TbJingYuanTuneTier</t>
         </is>
       </c>
       <c r="C96" s="0" t="inlineStr">
         <is>
-          <t>demo.TiaoJingConcentrationLevel</t>
+          <t>demo.JingYuanTuneTier</t>
         </is>
       </c>
       <c r="D96" s="0" t="b">
@@ -3065,19 +3060,29 @@
       </c>
       <c r="E96" s="0" t="inlineStr">
         <is>
-          <t>tiao_jing_concentration_level@jingyuan_codex.xlsx</t>
+          <t>jingyuan_tune_tier@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F96" s="0" t="inlineStr">
+        <is>
+          <t>codex_id+tier</t>
+        </is>
+      </c>
+      <c r="G96" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="0" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanTypeDef</t>
+          <t>demo.TbTiaoJingConcentrationLevel</t>
         </is>
       </c>
       <c r="C97" s="0" t="inlineStr">
         <is>
-          <t>demo.JingYuanTypeDef</t>
+          <t>demo.TiaoJingConcentrationLevel</t>
         </is>
       </c>
       <c r="D97" s="0" t="b">
@@ -3085,24 +3090,19 @@
       </c>
       <c r="E97" s="0" t="inlineStr">
         <is>
-          <t>jingyuan_type_def@jingyuan_codex.xlsx</t>
-        </is>
-      </c>
-      <c r="F97" s="0" t="inlineStr">
-        <is>
-          <t>type_id</t>
+          <t>tiao_jing_concentration_level@jingyuan_codex.xlsx</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="0" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanTypePoolEntry</t>
+          <t>demo.TbJingYuanTypeDef</t>
         </is>
       </c>
       <c r="C98" s="0" t="inlineStr">
         <is>
-          <t>demo.JingYuanTypePoolEntry</t>
+          <t>demo.JingYuanTypeDef</t>
         </is>
       </c>
       <c r="D98" s="0" t="b">
@@ -3110,65 +3110,90 @@
       </c>
       <c r="E98" s="0" t="inlineStr">
         <is>
-          <t>jingyuan_type_pool@jingyuan_codex.xlsx</t>
-        </is>
-      </c>
-      <c r="G98" s="0" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>jingyuan_type_def@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F98" s="0" t="inlineStr">
+        <is>
+          <t>type_id</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="0" t="inlineStr">
         <is>
+          <t>demo.TbJingYuanTypePoolEntry</t>
+        </is>
+      </c>
+      <c r="C99" s="0" t="inlineStr">
+        <is>
+          <t>demo.JingYuanTypePoolEntry</t>
+        </is>
+      </c>
+      <c r="D99" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99" s="0" t="inlineStr">
+        <is>
+          <t>jingyuan_type_pool@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="G99" s="0" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="B100" s="0" t="inlineStr">
+        <is>
           <t>demo.TbProgressionHubTab</t>
         </is>
       </c>
-      <c r="C99" s="0" t="inlineStr">
+      <c r="C100" s="0" t="inlineStr">
         <is>
           <t>demo.ProgressionHubTabDef</t>
         </is>
       </c>
-      <c r="D99" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E99" s="0" t="inlineStr">
+      <c r="D100" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E100" s="0" t="inlineStr">
         <is>
           <t>progression_hub_tab@progression_hub_tab.xlsx</t>
         </is>
       </c>
-      <c r="F99" s="0" t="inlineStr">
+      <c r="F100" s="0" t="inlineStr">
         <is>
           <t>tab_id</t>
         </is>
       </c>
-      <c r="G99" s="0" t="inlineStr">
+      <c r="G100" s="0" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I99" s="0" t="inlineStr">
+      <c r="I100" s="0" t="inlineStr">
         <is>
           <t>养成总面板选项卡</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="B100" t="inlineStr">
+    <row r="101">
+      <c r="B101" s="0" t="inlineStr">
         <is>
           <t>demo.TbPlayerAttachInfo</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C101" s="0" t="inlineStr">
         <is>
           <t>demo.PlayerAttachInfo</t>
         </is>
       </c>
-      <c r="D100" t="b">
-        <v>1</v>
-      </c>
-      <c r="E100" t="inlineStr">
+      <c r="D101" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E101" s="0" t="inlineStr">
         <is>
           <t>player_attach@player_attach.xlsx</t>
         </is>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -3,20 +3,20 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17655" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="20">
+  <fonts count="5">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -33,7 +33,7 @@
     </font>
     <font>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
       <u val="single"/>
@@ -41,7 +41,7 @@
     </font>
     <font>
       <name val="等线"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <color rgb="FF800080"/>
       <sz val="11"/>
       <u val="single"/>
@@ -49,127 +49,12 @@
     </font>
     <font>
       <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="等线"/>
-      <charset val="0"/>
-      <color theme="1"/>
-      <sz val="11"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -182,188 +67,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -371,322 +76,37 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="22">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="2">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="6">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="3">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="好" xfId="2" builtinId="26"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1012,6 +432,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1021,7 +442,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -1212,7 +633,7 @@
       <c r="D5" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>logic_area_info@map.xlsx</t>
         </is>
@@ -1252,7 +673,7 @@
       <c r="D7" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="5" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>area_variant_info@map.xlsx</t>
         </is>
@@ -1398,7 +819,7 @@
       <c r="D15" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E15" s="3" t="inlineStr">
         <is>
           <t>unit_npc_attribute@unit_npc.xlsx</t>
         </is>
@@ -1418,7 +839,7 @@
       <c r="D16" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E16" s="5" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>desire_density_info@unit_npc.xlsx</t>
         </is>
@@ -2487,25 +1908,25 @@
       </c>
     </row>
     <row r="75">
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="0" t="inlineStr">
         <is>
           <t>demo.TbReviveRule</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
+      <c r="C75" s="0" t="inlineStr">
         <is>
           <t>demo.ReviveRule</t>
         </is>
       </c>
-      <c r="D75" t="b">
-        <v>1</v>
-      </c>
-      <c r="E75" t="inlineStr">
+      <c r="D75" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" s="0" t="inlineStr">
         <is>
           <t>revive_rule@revive_rule.xlsx</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="G75" s="0" t="inlineStr">
         <is>
           <t>list</t>
         </is>
@@ -2741,7 +2162,7 @@
       <c r="D85" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>body_part_level@body_part.xlsx</t>
         </is>
@@ -2771,7 +2192,7 @@
       <c r="D86" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="E86" s="5" t="inlineStr">
+      <c r="E86" s="3" t="inlineStr">
         <is>
           <t>body_part_progress_info@body_part.xlsx</t>
         </is>
@@ -3199,9 +2620,164 @@
         </is>
       </c>
     </row>
+    <row r="102" s="2">
+      <c r="B102" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbItemDismantle</t>
+        </is>
+      </c>
+      <c r="C102" s="0" t="inlineStr">
+        <is>
+          <t>demo.ItemDismantle</t>
+        </is>
+      </c>
+      <c r="D102" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E102" s="0" t="inlineStr">
+        <is>
+          <t>item_dismantle@item_dismantle.xlsx</t>
+        </is>
+      </c>
+      <c r="F102" s="0" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G102" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I102" s="0" t="inlineStr">
+        <is>
+          <t>物品分解产物配置</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" s="2">
+      <c r="B103" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbRenewableResourceNode</t>
+        </is>
+      </c>
+      <c r="C103" s="0" t="inlineStr">
+        <is>
+          <t>demo.RenewableResourceNode</t>
+        </is>
+      </c>
+      <c r="D103" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E103" s="0" t="inlineStr">
+        <is>
+          <t>renewable_resource_node@renewable_resource_node.xlsx</t>
+        </is>
+      </c>
+      <c r="F103" s="0" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G103" s="0" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I103" s="0" t="inlineStr">
+        <is>
+          <t>周期恢复资源节点</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="0" t="inlineStr">
+        <is>
+          <t>demo.TbItemTagInfo</t>
+        </is>
+      </c>
+      <c r="C104" s="0" t="inlineStr">
+        <is>
+          <t>demo.ItemTagInfo</t>
+        </is>
+      </c>
+      <c r="D104" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="E104" s="0" t="inlineStr">
+        <is>
+          <t>item_tag@item.xlsx</t>
+        </is>
+      </c>
+      <c r="F104" s="0" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="H104" s="0" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I104" s="0" t="inlineStr">
+        <is>
+          <t>物品标签元数据：显示字、隐藏控制、实例需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>demo.TbPlayerBagDef</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>demo.PlayerBagDef</t>
+        </is>
+      </c>
+      <c r="D105" t="b">
+        <v>1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>player_bag@player_bag.xlsx</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>玩家背包定义</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>demo.TbWarehouseFilter</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>demo.WarehouseFilter</t>
+        </is>
+      </c>
+      <c r="D106" t="b">
+        <v>1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>warehouse_filter@warehouse_filter.xlsx</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>仓库筛选定义</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" display="logic_area_info@map.xlsx" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" display="area_variant_info@map.xlsx" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" tooltip="mailto:area_overlay_state_info@map.xlsx" display="area_overlay_state_info@map.xlsx" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" display="unit_npc_attribute@unit_npc.xlsx" r:id="rId4"/>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1,15 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
-  </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -19,39 +15,27 @@
   <fonts count="5">
     <font>
       <name val="等线"/>
-      <charset val="134"/>
       <color theme="1"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="等线"/>
-      <charset val="134"/>
       <color rgb="FF006100"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="等线"/>
-      <charset val="134"/>
       <color rgb="FF0000FF"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="等线"/>
-      <charset val="134"/>
       <color rgb="FF800080"/>
       <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <name val="等线"/>
-      <charset val="134"/>
       <sz val="9"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -64,18 +48,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
   <borders count="1">
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
+    <border/>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -88,7 +65,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -102,13 +79,15 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="超链接" xfId="1" builtinId="8"/>
-    <cellStyle name="好" xfId="2" builtinId="26"/>
+    <cellStyle name="常规" xfId="0"/>
+    <cellStyle name="超链接" xfId="1"/>
+    <cellStyle name="好" xfId="2"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -224,73 +203,13 @@
     <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:ea typeface="Calibri"/>
+        <a:cs typeface="Calibri"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -302,23 +221,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="67000"/>
                 <a:lumMod val="110000"/>
                 <a:satMod val="105000"/>
-                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:tint val="73000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="103000"/>
-                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:tint val="81000"/>
                 <a:lumMod val="105000"/>
                 <a:satMod val="109000"/>
-                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -328,23 +247,23 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
+                <a:tint val="94000"/>
+                <a:lumMod val="102000"/>
                 <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
+                <a:shade val="100000"/>
+                <a:lumMod val="100000"/>
                 <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
+                <a:shade val="78000"/>
                 <a:lumMod val="99000"/>
                 <a:satMod val="120000"/>
-                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -352,26 +271,23 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="6350">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="19050">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -406,17 +322,17 @@
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="93000"/>
-                <a:satMod val="150000"/>
                 <a:shade val="98000"/>
                 <a:lumMod val="102000"/>
+                <a:satMod val="150000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="50000">
               <a:schemeClr val="phClr">
                 <a:tint val="98000"/>
-                <a:satMod val="130000"/>
                 <a:shade val="90000"/>
                 <a:lumMod val="103000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
@@ -431,8 +347,6 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -454,183 +368,183 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="1">
-      <c r="A1" s="0" t="inlineStr">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="0" t="inlineStr">
+      <c r="B1" s="5" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="C1" s="0" t="inlineStr">
+      <c r="C1" s="5" t="inlineStr">
         <is>
           <t>value_type</t>
         </is>
       </c>
-      <c r="D1" s="0" t="inlineStr">
+      <c r="D1" s="5" t="inlineStr">
         <is>
           <t>read_schema_from_file</t>
         </is>
       </c>
-      <c r="E1" s="0" t="inlineStr">
+      <c r="E1" s="5" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="F1" s="0" t="inlineStr">
+      <c r="F1" s="5" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="G1" s="0" t="inlineStr">
+      <c r="G1" s="5" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
-      <c r="H1" s="0" t="inlineStr">
+      <c r="H1" s="5" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="I1" s="0" t="inlineStr">
+      <c r="I1" s="5" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="J1" s="0" t="inlineStr">
+      <c r="J1" s="5" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="K1" s="0" t="inlineStr">
+      <c r="K1" s="5" t="inlineStr">
         <is>
           <t>output</t>
         </is>
       </c>
     </row>
     <row r="2" customFormat="1" s="1">
-      <c r="A2" s="0" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B2" s="0" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>全名(包含模块和名字)</t>
         </is>
       </c>
-      <c r="C2" s="0" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>记录类名</t>
         </is>
       </c>
-      <c r="D2" s="0" t="inlineStr">
+      <c r="D2" s="5" t="inlineStr">
         <is>
           <t>从excel读取定义</t>
         </is>
       </c>
-      <c r="E2" s="0" t="inlineStr">
+      <c r="E2" s="5" t="inlineStr">
         <is>
           <t>文件列表</t>
         </is>
       </c>
-      <c r="F2" s="0" t="inlineStr">
+      <c r="F2" s="5" t="inlineStr">
         <is>
           <t>表id字段</t>
         </is>
       </c>
-      <c r="G2" s="0" t="inlineStr">
+      <c r="G2" s="5" t="inlineStr">
         <is>
           <t>模式</t>
         </is>
       </c>
-      <c r="H2" s="0" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="I2" s="0" t="inlineStr">
+      <c r="I2" s="5" t="inlineStr">
         <is>
           <t>注释</t>
         </is>
       </c>
-      <c r="K2" s="0" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>输出文件名</t>
         </is>
       </c>
     </row>
     <row r="3" customFormat="1" s="1">
-      <c r="A3" s="0" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="D3" s="0" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
         </is>
       </c>
-      <c r="E3" s="0" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>可以多个，以逗号','分隔</t>
         </is>
       </c>
-      <c r="F3" s="0" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
         </is>
       </c>
-      <c r="G3" s="0" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>取值one|map|list，为空自动为map</t>
         </is>
       </c>
-      <c r="H3" s="0" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
         </is>
       </c>
-      <c r="K3" s="0" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="0" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>demo.TbReward</t>
         </is>
       </c>
-      <c r="C4" s="0" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>demo.Reward</t>
         </is>
       </c>
-      <c r="D4" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="0" t="inlineStr">
+      <c r="D4" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>1@reward.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="0" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>demo.TbLogicAreaInfo</t>
         </is>
       </c>
-      <c r="C5" s="0" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>demo.LogicAreaInfo</t>
         </is>
       </c>
-      <c r="D5" s="0" t="b">
+      <c r="D5" s="5" t="b">
         <v>1</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -640,37 +554,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="0" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>demo.TbLogicAreaHomesteadReq</t>
         </is>
       </c>
-      <c r="C6" s="0" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>demo.LogicAreaHomesteadReq</t>
         </is>
       </c>
-      <c r="D6" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="0" t="inlineStr">
+      <c r="D6" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>logic_area_homestead_req@map_homestead.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="0" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>demo.TbAreaVariantInfo</t>
         </is>
       </c>
-      <c r="C7" s="0" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>demo.AreaVariantInfo</t>
         </is>
       </c>
-      <c r="D7" s="0" t="b">
+      <c r="D7" s="5" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -680,17 +594,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="0" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>demo.TbAreaOverlayStateInfo</t>
         </is>
       </c>
-      <c r="C8" s="0" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>demo.AreaOverlayStateInfo</t>
         </is>
       </c>
-      <c r="D8" s="0" t="b">
+      <c r="D8" s="5" t="b">
         <v>1</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -700,123 +614,147 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="0" t="n"/>
-      <c r="C9" s="0" t="n"/>
-      <c r="D9" s="0" t="n"/>
-      <c r="E9" s="0" t="n"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>demo.TbEventGrant</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>demo.EventGrant</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="5" t="inlineStr">
+        <is>
+          <t>event_grant@event_grant.xlsx</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>通用事件授予（通识/被动成就）</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="B10" s="0" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>demo.TbDropBundle</t>
         </is>
       </c>
-      <c r="C10" s="0" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>demo.DropBundle</t>
         </is>
       </c>
-      <c r="D10" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="0" t="inlineStr">
+      <c r="D10" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>drop_bundle@drop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="0" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>demo.TbDropItem</t>
         </is>
       </c>
-      <c r="C11" s="0" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>demo.DropItem</t>
         </is>
       </c>
-      <c r="D11" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="0" t="inlineStr">
+      <c r="D11" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>drop_item@drop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="0" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>demo.TbFixedFacility</t>
         </is>
       </c>
-      <c r="C12" s="0" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>demo.FixedFacility</t>
         </is>
       </c>
-      <c r="D12" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="0" t="inlineStr">
+      <c r="D12" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>fixed_facility@home_facility.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="0" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>demo.TbBornPoint</t>
         </is>
       </c>
-      <c r="C13" s="0" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>demo.BornPoint</t>
         </is>
       </c>
-      <c r="D13" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="0" t="inlineStr">
+      <c r="D13" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>born_points@born_points.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="0" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>demo.TbUnitNpc</t>
         </is>
       </c>
-      <c r="C14" s="0" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>demo.UnitNpc</t>
         </is>
       </c>
-      <c r="D14" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="0" t="inlineStr">
+      <c r="D14" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>unit_npc@unit_npc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="0" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>demo.TbUnitNpcAttr</t>
         </is>
       </c>
-      <c r="C15" s="0" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>demo.UnitNpcAttr</t>
         </is>
       </c>
-      <c r="D15" s="0" t="b">
+      <c r="D15" s="5" t="b">
         <v>1</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -826,17 +764,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="0" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>demo.TbDesireDensityInfo</t>
         </is>
       </c>
-      <c r="C16" s="0" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>demo.DesireDensityInfo</t>
         </is>
       </c>
-      <c r="D16" s="0" t="b">
+      <c r="D16" s="5" t="b">
         <v>1</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -846,386 +784,386 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="0" t="n"/>
-      <c r="C17" s="0" t="n"/>
-      <c r="D17" s="0" t="n"/>
-      <c r="E17" s="0" t="n"/>
+      <c r="B17" s="5" t="n"/>
+      <c r="C17" s="5" t="n"/>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="0" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>demo.TbQuestData</t>
         </is>
       </c>
-      <c r="C18" s="0" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>demo.QuestData</t>
         </is>
       </c>
-      <c r="D18" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="0" t="inlineStr">
+      <c r="D18" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>quest_data@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="0" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>demo.TbQuestStepData</t>
         </is>
       </c>
-      <c r="C19" s="0" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>demo.QuestStepData</t>
         </is>
       </c>
-      <c r="D19" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="0" t="inlineStr">
+      <c r="D19" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>quest_step_data@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="0" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>demo.TbQuestStepOutcome</t>
         </is>
       </c>
-      <c r="C20" s="0" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>demo.QuestStepOutcome</t>
         </is>
       </c>
-      <c r="D20" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="0" t="inlineStr">
+      <c r="D20" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>quest_step_outcome@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="0" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>demo.TbQuestStepObjective</t>
         </is>
       </c>
-      <c r="C21" s="0" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>demo.QuestStepObjective</t>
         </is>
       </c>
-      <c r="D21" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="0" t="inlineStr">
+      <c r="D21" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>quest_step_objective@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="0" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>demo.TbQuestInteractDialog</t>
         </is>
       </c>
-      <c r="C22" s="0" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>demo.QuestInteractDialogData</t>
         </is>
       </c>
-      <c r="D22" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="0" t="inlineStr">
+      <c r="D22" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>quest_interact_dialog@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="0" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>demo.TbDialogMetaInfo</t>
         </is>
       </c>
-      <c r="C23" s="0" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>demo.DialogMetaInfo</t>
         </is>
       </c>
-      <c r="D23" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="0" t="inlineStr">
+      <c r="D23" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>dialog_meta_info@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="0" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>demo.TbItemData</t>
         </is>
       </c>
-      <c r="C24" s="0" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>demo.ItemData</t>
         </is>
       </c>
-      <c r="D24" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="0" t="inlineStr">
+      <c r="D24" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>item@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="0" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>demo.TbShop</t>
         </is>
       </c>
-      <c r="C25" s="0" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>demo.Shop</t>
         </is>
       </c>
-      <c r="D25" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="0" t="inlineStr">
+      <c r="D25" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>shop@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="0" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>demo.TbShopGoods</t>
         </is>
       </c>
-      <c r="C26" s="0" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>demo.ShopGoods</t>
         </is>
       </c>
-      <c r="D26" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="0" t="inlineStr">
+      <c r="D26" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>shop_goods@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="0" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>demo.TbItemUse</t>
         </is>
       </c>
-      <c r="C27" s="0" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>demo.ItemUse</t>
         </is>
       </c>
-      <c r="D27" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="0" t="inlineStr">
+      <c r="D27" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>item_use@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="0" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>demo.TbItemGift</t>
         </is>
       </c>
-      <c r="C28" s="0" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>demo.ItemGift</t>
         </is>
       </c>
-      <c r="D28" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="0" t="inlineStr">
+      <c r="D28" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>item_gift@item.xlsx</t>
         </is>
       </c>
-      <c r="F28" s="0" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="G28" s="0" t="inlineStr">
+      <c r="G28" s="5" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="0" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>demo.TbNpcDialogInfo</t>
         </is>
       </c>
-      <c r="C29" s="0" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>demo.NpcDialogInfo</t>
         </is>
       </c>
-      <c r="D29" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="0" t="inlineStr">
+      <c r="D29" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>npc_dialog_info@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="0" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>demo.TbWorldMapGlobal</t>
         </is>
       </c>
-      <c r="C30" s="0" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>demo.WorldMapGlobal</t>
         </is>
       </c>
-      <c r="D30" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="0" t="inlineStr">
+      <c r="D30" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>world_map_global@map.xlsx</t>
         </is>
       </c>
-      <c r="G30" s="0" t="inlineStr">
+      <c r="G30" s="5" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="0" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>demo.TbWorldMapBigMapLayer</t>
         </is>
       </c>
-      <c r="C31" s="0" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>demo.WorldMapBigMapLayer</t>
         </is>
       </c>
-      <c r="D31" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="0" t="inlineStr">
+      <c r="D31" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>world_map_big_map@map.xlsx</t>
         </is>
       </c>
-      <c r="G31" s="0" t="inlineStr">
+      <c r="G31" s="5" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="0" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>demo.TbDreamInfiltrationSpot</t>
         </is>
       </c>
-      <c r="C32" s="0" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>demo.DreamInfiltrationSpot</t>
         </is>
       </c>
-      <c r="D32" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="0" t="inlineStr">
+      <c r="D32" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>dream_infiltration@dream_infiltration.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="0" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>demo.TbCharDreamEntryInfo</t>
         </is>
       </c>
-      <c r="C33" s="0" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>demo.CharDreamEntryInfo</t>
         </is>
       </c>
-      <c r="D33" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="0" t="inlineStr">
+      <c r="D33" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>char_dream_entry@dream_infiltration.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="0" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>demo.TbFishingSpot</t>
         </is>
       </c>
-      <c r="C34" s="0" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>demo.FishingSpot</t>
         </is>
       </c>
-      <c r="D34" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="0" t="inlineStr">
+      <c r="D34" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>fishing_spot@fishing_spot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="0" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>demo.TbFishingSpotFish</t>
         </is>
       </c>
-      <c r="C35" s="0" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>demo.FishingSpotFish</t>
         </is>
       </c>
-      <c r="D35" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="0" t="inlineStr">
+      <c r="D35" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>fishing_spot_fish@fishing_spot.xlsx</t>
         </is>
@@ -1233,80 +1171,80 @@
     </row>
     <row r="36"/>
     <row r="37">
-      <c r="B37" s="0" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>demo.TbPlayerDesireLevel</t>
         </is>
       </c>
-      <c r="C37" s="0" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>demo.PlayerDesireLevel</t>
         </is>
       </c>
-      <c r="D37" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="0" t="inlineStr">
+      <c r="D37" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>player_desire_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="0" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>demo.TbPlayerJingYuLevel</t>
         </is>
       </c>
-      <c r="C38" s="0" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>demo.PlayerJingYuLevel</t>
         </is>
       </c>
-      <c r="D38" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="0" t="inlineStr">
+      <c r="D38" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>player_jingyu_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="0" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>demo.TbPlayerSanCorruptLevel</t>
         </is>
       </c>
-      <c r="C39" s="0" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>demo.PlayerSanCorruptLevel</t>
         </is>
       </c>
-      <c r="D39" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="0" t="inlineStr">
+      <c r="D39" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
         <is>
           <t>player_san_corrupt_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="0" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>demo.TbPlayerClothesExposeInfo</t>
         </is>
       </c>
-      <c r="C40" s="0" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>demo.PlayerClothesExposeInfo</t>
         </is>
       </c>
-      <c r="D40" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="0" t="inlineStr">
+      <c r="D40" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
         <is>
           <t>player_clothes_expose_info@player_status.xlsx</t>
         </is>
@@ -1314,300 +1252,300 @@
     </row>
     <row r="41"/>
     <row r="42">
-      <c r="B42" s="0" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>demo.TbWantedLevelInfo</t>
         </is>
       </c>
-      <c r="C42" s="0" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>demo.WantedLevelInfo</t>
         </is>
       </c>
-      <c r="D42" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="0" t="inlineStr">
+      <c r="D42" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
         <is>
           <t>wanted_level_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="0" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>demo.TbWantedBehaveInfo</t>
         </is>
       </c>
-      <c r="C43" s="0" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>demo.WantedBehaveInfo</t>
         </is>
       </c>
-      <c r="D43" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="0" t="inlineStr">
+      <c r="D43" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>wanted_behave_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="0" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>demo.TbTalentNode</t>
         </is>
       </c>
-      <c r="C44" s="0" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>demo.TalentNode</t>
         </is>
       </c>
-      <c r="D44" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="0" t="inlineStr">
+      <c r="D44" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
         <is>
           <t>talent@talent.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="0" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>demo.TbWantedGuardSpawnTier</t>
         </is>
       </c>
-      <c r="C45" s="0" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>demo.WantedGuardSpawnTier</t>
         </is>
       </c>
-      <c r="D45" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" s="0" t="inlineStr">
+      <c r="D45" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
         <is>
           <t>wanted_guard_spawn@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="0" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>demo.TbEntitySkillData</t>
         </is>
       </c>
-      <c r="C46" s="0" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>demo.EntitySkillData</t>
         </is>
       </c>
-      <c r="D46" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="0" t="inlineStr">
+      <c r="D46" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>entity_skill@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="0" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>demo.TbSkillSchool</t>
         </is>
       </c>
-      <c r="C47" s="0" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>demo.SkillSchool</t>
         </is>
       </c>
-      <c r="D47" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="0" t="inlineStr">
+      <c r="D47" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
         <is>
           <t>skill_school@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="0" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>demo.TbSkillLearnEntry</t>
         </is>
       </c>
-      <c r="C48" s="0" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>demo.SkillLearnEntry</t>
         </is>
       </c>
-      <c r="D48" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="0" t="inlineStr">
+      <c r="D48" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
         <is>
           <t>skill_learn@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="0" t="inlineStr">
+      <c r="B49" s="5" t="inlineStr">
         <is>
           <t>demo.TbDesireCrystalDef</t>
         </is>
       </c>
-      <c r="C49" s="0" t="inlineStr">
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>demo.DesireCrystalDef</t>
         </is>
       </c>
-      <c r="D49" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E49" s="0" t="inlineStr">
+      <c r="D49" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
         <is>
           <t>desire_crystal_def@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="0" t="inlineStr">
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>demo.TbMapDesireCrystalBudget</t>
         </is>
       </c>
-      <c r="C50" s="0" t="inlineStr">
+      <c r="C50" s="5" t="inlineStr">
         <is>
           <t>demo.MapDesireCrystalBudget</t>
         </is>
       </c>
-      <c r="D50" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E50" s="0" t="inlineStr">
+      <c r="D50" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
         <is>
           <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="0" t="inlineStr">
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>demo.TbMapWalkerDesireCrystalQuota</t>
         </is>
       </c>
-      <c r="C51" s="0" t="inlineStr">
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>demo.MapWalkerDesireCrystalQuota</t>
         </is>
       </c>
-      <c r="D51" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="0" t="inlineStr">
+      <c r="D51" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
         <is>
           <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="0" t="inlineStr">
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>demo.TbNamedNpcDesireCrystal</t>
         </is>
       </c>
-      <c r="C52" s="0" t="inlineStr">
+      <c r="C52" s="5" t="inlineStr">
         <is>
           <t>demo.NamedNpcDesireCrystal</t>
         </is>
       </c>
-      <c r="D52" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E52" s="0" t="inlineStr">
+      <c r="D52" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="0" t="inlineStr">
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>demo.TbSpiritMonsterTypeBudget</t>
         </is>
       </c>
-      <c r="C53" s="0" t="inlineStr">
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>demo.SpiritMonsterTypeBudget</t>
         </is>
       </c>
-      <c r="D53" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" s="0" t="inlineStr">
+      <c r="D53" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
         <is>
           <t>spirit_monster_budget@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="0" t="inlineStr">
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>demo.TbContainerItemStackOverride</t>
         </is>
       </c>
-      <c r="C54" s="0" t="inlineStr">
+      <c r="C54" s="5" t="inlineStr">
         <is>
           <t>demo.ContainerItemStackOverride</t>
         </is>
       </c>
-      <c r="D54" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E54" s="0" t="inlineStr">
+      <c r="D54" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
         <is>
           <t>container_item_stack_override@container_stack.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="0" t="inlineStr">
+      <c r="B55" s="5" t="inlineStr">
         <is>
           <t>demo.TbContainerStackTagRule</t>
         </is>
       </c>
-      <c r="C55" s="0" t="inlineStr">
+      <c r="C55" s="5" t="inlineStr">
         <is>
           <t>demo.ContainerStackTagRule</t>
         </is>
       </c>
-      <c r="D55" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="0" t="inlineStr">
+      <c r="D55" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
         <is>
           <t>container_stack_tag_rule@container_stack.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="0" t="inlineStr">
+      <c r="B56" s="5" t="inlineStr">
         <is>
           <t>demo.TbMapAreaEffect</t>
         </is>
       </c>
-      <c r="C56" s="0" t="inlineStr">
+      <c r="C56" s="5" t="inlineStr">
         <is>
           <t>demo.MapAreaEffect</t>
         </is>
       </c>
-      <c r="D56" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" s="0" t="inlineStr">
+      <c r="D56" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
         <is>
           <t>map_area_effect@map_area_effect.xlsx</t>
         </is>
@@ -1615,80 +1553,80 @@
     </row>
     <row r="57"/>
     <row r="58">
-      <c r="B58" s="0" t="inlineStr">
+      <c r="B58" s="5" t="inlineStr">
         <is>
           <t>demo.TbFallenAmountProgressInfo</t>
         </is>
       </c>
-      <c r="C58" s="0" t="inlineStr">
+      <c r="C58" s="5" t="inlineStr">
         <is>
           <t>demo.FallenAmountProgressInfo</t>
         </is>
       </c>
-      <c r="D58" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E58" s="0" t="inlineStr">
+      <c r="D58" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
         <is>
           <t>fallen_amount_progress_info@fallen_amount_progress_info.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="0" t="inlineStr">
+      <c r="B59" s="5" t="inlineStr">
         <is>
           <t>demo.TbRumorIntel</t>
         </is>
       </c>
-      <c r="C59" s="0" t="inlineStr">
+      <c r="C59" s="5" t="inlineStr">
         <is>
           <t>demo.RumorIntel</t>
         </is>
       </c>
-      <c r="D59" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" s="0" t="inlineStr">
+      <c r="D59" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
         <is>
           <t>rumor_intel@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="0" t="inlineStr">
+      <c r="B60" s="5" t="inlineStr">
         <is>
           <t>demo.TbRumorRandomPool</t>
         </is>
       </c>
-      <c r="C60" s="0" t="inlineStr">
+      <c r="C60" s="5" t="inlineStr">
         <is>
           <t>demo.RumorRandomPool</t>
         </is>
       </c>
-      <c r="D60" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="0" t="inlineStr">
+      <c r="D60" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
         <is>
           <t>rumor_random_pool@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="0" t="inlineStr">
+      <c r="B61" s="5" t="inlineStr">
         <is>
           <t>demo.TbRumorGlobal</t>
         </is>
       </c>
-      <c r="C61" s="0" t="inlineStr">
+      <c r="C61" s="5" t="inlineStr">
         <is>
           <t>demo.RumorGlobal</t>
         </is>
       </c>
-      <c r="D61" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="0" t="inlineStr">
+      <c r="D61" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
         <is>
           <t>rumor_global@rumor_tables.xlsx</t>
         </is>
@@ -1696,100 +1634,100 @@
     </row>
     <row r="62"/>
     <row r="63">
-      <c r="B63" s="0" t="inlineStr">
+      <c r="B63" s="5" t="inlineStr">
         <is>
           <t>demo.TbCharacterInfo</t>
         </is>
       </c>
-      <c r="C63" s="0" t="inlineStr">
+      <c r="C63" s="5" t="inlineStr">
         <is>
           <t>demo.CharacterInfo</t>
         </is>
       </c>
-      <c r="D63" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="0" t="inlineStr">
+      <c r="D63" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
         <is>
           <t>character_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="0" t="inlineStr">
+      <c r="B64" s="5" t="inlineStr">
         <is>
           <t>demo.TbCharacterFavorInfo</t>
         </is>
       </c>
-      <c r="C64" s="0" t="inlineStr">
+      <c r="C64" s="5" t="inlineStr">
         <is>
           <t>demo.CharacterFavorInfo</t>
         </is>
       </c>
-      <c r="D64" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" s="0" t="inlineStr">
+      <c r="D64" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
         <is>
           <t>character_favor_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="0" t="inlineStr">
+      <c r="B65" s="5" t="inlineStr">
         <is>
           <t>demo.TbMicroPlotDef</t>
         </is>
       </c>
-      <c r="C65" s="0" t="inlineStr">
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>demo.MicroPlotDef</t>
         </is>
       </c>
-      <c r="D65" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" s="0" t="inlineStr">
+      <c r="D65" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>micro_plot_def@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="0" t="inlineStr">
+      <c r="B66" s="5" t="inlineStr">
         <is>
           <t>demo.TbMapMicroPlotTrigger</t>
         </is>
       </c>
-      <c r="C66" s="0" t="inlineStr">
+      <c r="C66" s="5" t="inlineStr">
         <is>
           <t>demo.MapMicroPlotTrigger</t>
         </is>
       </c>
-      <c r="D66" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="0" t="inlineStr">
+      <c r="D66" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="5" t="inlineStr">
         <is>
           <t>map_micro_plot_trigger@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="0" t="inlineStr">
+      <c r="B67" s="5" t="inlineStr">
         <is>
           <t>demo.TbMicroPlotTimelineEvent</t>
         </is>
       </c>
-      <c r="C67" s="0" t="inlineStr">
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>demo.MicroPlotTimelineEvent</t>
         </is>
       </c>
-      <c r="D67" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="0" t="inlineStr">
+      <c r="D67" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>micro_plot_timeline_event@micro_plot.xlsx</t>
         </is>
@@ -1797,40 +1735,40 @@
     </row>
     <row r="68"/>
     <row r="69">
-      <c r="B69" s="0" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>demo.TbTrapSpec</t>
         </is>
       </c>
-      <c r="C69" s="0" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>demo.TrapSpec</t>
         </is>
       </c>
-      <c r="D69" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E69" s="0" t="inlineStr">
+      <c r="D69" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>trap_spec@trap_spec.xlsx</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="0" t="inlineStr">
+      <c r="B70" s="5" t="inlineStr">
         <is>
           <t>demo.TbForgeRecipe</t>
         </is>
       </c>
-      <c r="C70" s="0" t="inlineStr">
+      <c r="C70" s="5" t="inlineStr">
         <is>
           <t>demo.ForgeRecipe</t>
         </is>
       </c>
-      <c r="D70" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E70" s="0" t="inlineStr">
+      <c r="D70" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
         <is>
           <t>forge_recipe@forge_recipe.xlsx</t>
         </is>
@@ -1838,200 +1776,200 @@
     </row>
     <row r="71"/>
     <row r="72">
-      <c r="B72" s="0" t="inlineStr">
+      <c r="B72" s="5" t="inlineStr">
         <is>
           <t>demo.TbHActInfo</t>
         </is>
       </c>
-      <c r="C72" s="0" t="inlineStr">
+      <c r="C72" s="5" t="inlineStr">
         <is>
           <t>demo.HActInfo</t>
         </is>
       </c>
-      <c r="D72" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E72" s="0" t="inlineStr">
+      <c r="D72" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>h_act_info@h_act_info.xlsx</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="0" t="inlineStr">
+      <c r="B73" s="5" t="inlineStr">
         <is>
           <t>demo.TbTalentNodeLevel</t>
         </is>
       </c>
-      <c r="C73" s="0" t="inlineStr">
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>demo.TalentNodeLevel</t>
         </is>
       </c>
-      <c r="D73" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E73" s="0" t="inlineStr">
+      <c r="D73" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>talent_level@talent.xlsx</t>
         </is>
       </c>
-      <c r="F73" s="0" t="inlineStr">
+      <c r="F73" s="5" t="inlineStr">
         <is>
           <t>node_id+level</t>
         </is>
       </c>
-      <c r="G73" s="0" t="inlineStr">
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="0" t="inlineStr">
+      <c r="B74" s="5" t="inlineStr">
         <is>
           <t>demo.TbSavePoint</t>
         </is>
       </c>
-      <c r="C74" s="0" t="inlineStr">
+      <c r="C74" s="5" t="inlineStr">
         <is>
           <t>demo.SavePoint</t>
         </is>
       </c>
-      <c r="D74" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E74" s="0" t="inlineStr">
+      <c r="D74" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" s="5" t="inlineStr">
         <is>
           <t>save_point@save_point.xlsx</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="0" t="inlineStr">
+      <c r="B75" s="5" t="inlineStr">
         <is>
           <t>demo.TbReviveRule</t>
         </is>
       </c>
-      <c r="C75" s="0" t="inlineStr">
+      <c r="C75" s="5" t="inlineStr">
         <is>
           <t>demo.ReviveRule</t>
         </is>
       </c>
-      <c r="D75" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E75" s="0" t="inlineStr">
+      <c r="D75" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
         <is>
           <t>revive_rule@revive_rule.xlsx</t>
         </is>
       </c>
-      <c r="G75" s="0" t="inlineStr">
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="0" t="inlineStr">
+      <c r="B76" s="5" t="inlineStr">
         <is>
           <t>demo.TbDesireDensityTier</t>
         </is>
       </c>
-      <c r="C76" s="0" t="inlineStr">
+      <c r="C76" s="5" t="inlineStr">
         <is>
           <t>demo.DesireDensityTier</t>
         </is>
       </c>
-      <c r="D76" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E76" s="0" t="inlineStr">
+      <c r="D76" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E76" s="5" t="inlineStr">
         <is>
           <t>desire_density_tier@desire_density_tier.xlsx</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="0" t="inlineStr">
+      <c r="B77" s="5" t="inlineStr">
         <is>
           <t>demo.TbMindFragmentPoolEntry</t>
         </is>
       </c>
-      <c r="C77" s="0" t="inlineStr">
+      <c r="C77" s="5" t="inlineStr">
         <is>
           <t>demo.MindFragmentPoolEntry</t>
         </is>
       </c>
-      <c r="D77" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E77" s="0" t="inlineStr">
+      <c r="D77" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" s="5" t="inlineStr">
         <is>
           <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
         </is>
       </c>
-      <c r="G77" s="0" t="inlineStr">
+      <c r="G77" s="5" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="0" t="inlineStr">
+      <c r="B78" s="5" t="inlineStr">
         <is>
           <t>demo.TbSecretBaseFacility</t>
         </is>
       </c>
-      <c r="C78" s="0" t="inlineStr">
+      <c r="C78" s="5" t="inlineStr">
         <is>
           <t>demo.SecretBaseFacility</t>
         </is>
       </c>
-      <c r="D78" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E78" s="0" t="inlineStr">
+      <c r="D78" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" s="5" t="inlineStr">
         <is>
           <t>secret_base_facility@secret_base_facility.xlsx</t>
         </is>
       </c>
-      <c r="I78" s="0" t="inlineStr">
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>据点固定设施</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="0" t="inlineStr">
+      <c r="B79" s="5" t="inlineStr">
         <is>
           <t>demo.TbSecretBaseBuildLevel</t>
         </is>
       </c>
-      <c r="C79" s="0" t="inlineStr">
+      <c r="C79" s="5" t="inlineStr">
         <is>
           <t>demo.SecretBaseBuildLevel</t>
         </is>
       </c>
-      <c r="D79" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" s="0" t="inlineStr">
+      <c r="D79" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" s="5" t="inlineStr">
         <is>
           <t>secret_base_build_level@secret_base_build_level.xlsx</t>
         </is>
       </c>
-      <c r="F79" s="0" t="inlineStr">
+      <c r="F79" s="5" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="G79" s="0" t="inlineStr">
+      <c r="G79" s="5" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I79" s="0" t="inlineStr">
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>据点建设等级卷轴边界</t>
         </is>
@@ -2039,127 +1977,127 @@
     </row>
     <row r="80"/>
     <row r="81">
-      <c r="B81" s="0" t="inlineStr">
+      <c r="B81" s="5" t="inlineStr">
         <is>
           <t>demo.TbSecretBaseCharacter</t>
         </is>
       </c>
-      <c r="C81" s="0" t="inlineStr">
+      <c r="C81" s="5" t="inlineStr">
         <is>
           <t>demo.SecretBaseCharacter</t>
         </is>
       </c>
-      <c r="D81" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E81" s="0" t="inlineStr">
+      <c r="D81" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
         <is>
           <t>secret_base_character@secret_base_character.xlsx</t>
         </is>
       </c>
-      <c r="F81" s="0" t="inlineStr">
+      <c r="F81" s="5" t="inlineStr">
         <is>
           <t>slot_id</t>
         </is>
       </c>
-      <c r="G81" s="0" t="inlineStr">
+      <c r="G81" s="5" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I81" s="0" t="inlineStr">
+      <c r="I81" s="5" t="inlineStr">
         <is>
           <t>秘密据点角色</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="0" t="inlineStr">
+      <c r="B82" s="5" t="inlineStr">
         <is>
           <t>demo.TbHumanWeapon</t>
         </is>
       </c>
-      <c r="C82" s="0" t="inlineStr">
+      <c r="C82" s="5" t="inlineStr">
         <is>
           <t>demo.HumanWeapon</t>
         </is>
       </c>
-      <c r="D82" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E82" s="0" t="inlineStr">
+      <c r="D82" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" s="5" t="inlineStr">
         <is>
           <t>human_weapon@human_weapon.xlsx</t>
         </is>
       </c>
-      <c r="F82" s="0" t="inlineStr">
+      <c r="F82" s="5" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="G82" s="0" t="inlineStr">
+      <c r="G82" s="5" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I82" s="0" t="inlineStr">
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>human_weapon</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="0" t="inlineStr">
+      <c r="B83" s="5" t="inlineStr">
         <is>
           <t>demo.TbRuneData</t>
         </is>
       </c>
-      <c r="C83" s="0" t="inlineStr">
+      <c r="C83" s="5" t="inlineStr">
         <is>
           <t>demo.RuneData</t>
         </is>
       </c>
-      <c r="D83" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E83" s="0" t="inlineStr">
+      <c r="D83" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
         <is>
           <t>rune_data@rune.xlsx</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="0" t="inlineStr">
+      <c r="B84" s="5" t="inlineStr">
         <is>
           <t>demo.TbBodyPartDef</t>
         </is>
       </c>
-      <c r="C84" s="0" t="inlineStr">
+      <c r="C84" s="5" t="inlineStr">
         <is>
           <t>demo.BodyPartDef</t>
         </is>
       </c>
-      <c r="D84" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E84" s="0" t="inlineStr">
+      <c r="D84" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
         <is>
           <t>body_part_def@body_part.xlsx</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="0" t="inlineStr">
+      <c r="B85" s="5" t="inlineStr">
         <is>
           <t>demo.TbBodyPartLevel</t>
         </is>
       </c>
-      <c r="C85" s="0" t="inlineStr">
+      <c r="C85" s="5" t="inlineStr">
         <is>
           <t>demo.BodyPartLevel</t>
         </is>
       </c>
-      <c r="D85" s="0" t="b">
+      <c r="D85" s="5" t="b">
         <v>1</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -2167,29 +2105,29 @@
           <t>body_part_level@body_part.xlsx</t>
         </is>
       </c>
-      <c r="F85" s="0" t="inlineStr">
+      <c r="F85" s="5" t="inlineStr">
         <is>
           <t>part_id+level</t>
         </is>
       </c>
-      <c r="G85" s="0" t="inlineStr">
+      <c r="G85" s="5" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="0" t="inlineStr">
+      <c r="B86" s="5" t="inlineStr">
         <is>
           <t>demo.TbBodyPartProgressInfo</t>
         </is>
       </c>
-      <c r="C86" s="0" t="inlineStr">
+      <c r="C86" s="5" t="inlineStr">
         <is>
           <t>demo.BodyPartProgressInfo</t>
         </is>
       </c>
-      <c r="D86" s="0" t="b">
+      <c r="D86" s="5" t="b">
         <v>1</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -2197,595 +2135,582 @@
           <t>body_part_progress_info@body_part.xlsx</t>
         </is>
       </c>
-      <c r="F86" s="0" t="n"/>
-      <c r="G86" s="0" t="n"/>
+      <c r="F86" s="5" t="n"/>
+      <c r="G86" s="5" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="0" t="inlineStr">
+      <c r="B87" s="5" t="inlineStr">
         <is>
           <t>demo.TbPartLocalAttrDef</t>
         </is>
       </c>
-      <c r="C87" s="0" t="inlineStr">
+      <c r="C87" s="5" t="inlineStr">
         <is>
           <t>demo.PartLocalAttrDef</t>
         </is>
       </c>
-      <c r="D87" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" s="0" t="inlineStr">
+      <c r="D87" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
         <is>
           <t>part_local_attr_def@body_part.xlsx</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="0" t="inlineStr">
+      <c r="B88" s="5" t="inlineStr">
         <is>
           <t>demo.TbPartGear</t>
         </is>
       </c>
-      <c r="C88" s="0" t="inlineStr">
+      <c r="C88" s="5" t="inlineStr">
         <is>
           <t>demo.PartGear</t>
         </is>
       </c>
-      <c r="D88" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" s="0" t="inlineStr">
+      <c r="D88" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
         <is>
           <t>partgear@partgear.xlsx</t>
         </is>
       </c>
-      <c r="F88" s="0" t="inlineStr">
+      <c r="F88" s="5" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="G88" s="0" t="inlineStr">
+      <c r="G88" s="5" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="0" t="inlineStr">
+      <c r="B89" s="5" t="inlineStr">
         <is>
           <t>demo.TbRuneUpgradeInfo</t>
         </is>
       </c>
-      <c r="C89" s="0" t="inlineStr">
+      <c r="C89" s="5" t="inlineStr">
         <is>
           <t>demo.RuneUpgradeInfo</t>
         </is>
       </c>
-      <c r="D89" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E89" s="0" t="inlineStr">
+      <c r="D89" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
         <is>
           <t>rune_upgrade_info@rune.xlsx</t>
         </is>
       </c>
-      <c r="F89" s="0" t="inlineStr">
+      <c r="F89" s="5" t="inlineStr">
         <is>
           <t>upgrade_id</t>
         </is>
       </c>
-      <c r="J89" s="0" t="inlineStr">
+      <c r="J89" s="5" t="inlineStr">
         <is>
           <t>符文升级项</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="0" t="inlineStr">
+      <c r="B90" s="5" t="inlineStr">
         <is>
           <t>demo.TbRuneEquipSlot</t>
         </is>
       </c>
-      <c r="C90" s="0" t="inlineStr">
+      <c r="C90" s="5" t="inlineStr">
         <is>
           <t>demo.RuneEquipSlotInfo</t>
         </is>
       </c>
-      <c r="D90" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E90" s="0" t="inlineStr">
+      <c r="D90" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" s="5" t="inlineStr">
         <is>
           <t>rune_equip_slot@rune.xlsx</t>
         </is>
       </c>
-      <c r="F90" s="0" t="inlineStr">
+      <c r="F90" s="5" t="inlineStr">
         <is>
           <t>equip_slot</t>
         </is>
       </c>
-      <c r="J90" s="0" t="inlineStr">
+      <c r="J90" s="5" t="inlineStr">
         <is>
           <t>符文装配槽</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="0" t="inlineStr">
+      <c r="B91" s="5" t="inlineStr">
         <is>
           <t>demo.TbEntitySkillLevel</t>
         </is>
       </c>
-      <c r="C91" s="0" t="inlineStr">
+      <c r="C91" s="5" t="inlineStr">
         <is>
           <t>demo.EntitySkillLevel</t>
         </is>
       </c>
-      <c r="D91" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E91" s="0" t="inlineStr">
+      <c r="D91" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
         <is>
           <t>skill_level@skill.xlsx</t>
         </is>
       </c>
-      <c r="F91" s="0" t="inlineStr">
+      <c r="F91" s="5" t="inlineStr">
         <is>
           <t>skill_id+level</t>
         </is>
       </c>
-      <c r="G91" s="0" t="inlineStr">
+      <c r="G91" s="5" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="0" t="inlineStr">
+      <c r="B92" s="5" t="inlineStr">
         <is>
           <t>demo.TbHomesteadBuilding</t>
         </is>
       </c>
-      <c r="C92" s="0" t="inlineStr">
+      <c r="C92" s="5" t="inlineStr">
         <is>
           <t>demo.HomesteadBuilding</t>
         </is>
       </c>
-      <c r="D92" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E92" s="0" t="inlineStr">
+      <c r="D92" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" s="5" t="inlineStr">
         <is>
           <t>homestead_building@map_homestead.xlsx</t>
         </is>
       </c>
-      <c r="F92" s="0" t="inlineStr">
+      <c r="F92" s="5" t="inlineStr">
         <is>
           <t>logic_area_id+building_id</t>
         </is>
       </c>
-      <c r="G92" s="0" t="inlineStr">
+      <c r="G92" s="5" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
-      <c r="I92" s="0" t="inlineStr">
+      <c r="I92" s="5" t="inlineStr">
         <is>
           <t>逻辑区域可管理建筑</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="0" t="inlineStr">
+      <c r="B93" s="5" t="inlineStr">
         <is>
           <t>demo.TbHomesteadBuildingUpgrade</t>
         </is>
       </c>
-      <c r="C93" s="0" t="inlineStr">
+      <c r="C93" s="5" t="inlineStr">
         <is>
           <t>demo.HomesteadBuildingUpgrade</t>
         </is>
       </c>
-      <c r="D93" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" s="0" t="inlineStr">
+      <c r="D93" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
         <is>
           <t>homestead_building_upgrade@map_homestead.xlsx</t>
         </is>
       </c>
-      <c r="F93" s="0" t="inlineStr">
+      <c r="F93" s="5" t="inlineStr">
         <is>
           <t>logic_area_id+building_id+level</t>
         </is>
       </c>
-      <c r="G93" s="0" t="inlineStr">
+      <c r="G93" s="5" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
-      <c r="I93" s="0" t="inlineStr">
+      <c r="I93" s="5" t="inlineStr">
         <is>
           <t>家园建筑升级项</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="0" t="inlineStr">
+      <c r="B94" s="5" t="inlineStr">
         <is>
           <t>demo.TbJingYuanCodexDef</t>
         </is>
       </c>
-      <c r="C94" s="0" t="inlineStr">
+      <c r="C94" s="5" t="inlineStr">
         <is>
           <t>demo.JingYuanCodexDef</t>
         </is>
       </c>
-      <c r="D94" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E94" s="0" t="inlineStr">
+      <c r="D94" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" s="5" t="inlineStr">
         <is>
           <t>jingyuan_codex_def@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F94" s="0" t="inlineStr">
+      <c r="F94" s="5" t="inlineStr">
         <is>
           <t>codex_id</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="0" t="inlineStr">
+      <c r="B95" s="5" t="inlineStr">
         <is>
           <t>demo.TbJingYuanCodexLevel</t>
         </is>
       </c>
-      <c r="C95" s="0" t="inlineStr">
+      <c r="C95" s="5" t="inlineStr">
         <is>
           <t>demo.JingYuanCodexLevel</t>
         </is>
       </c>
-      <c r="D95" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E95" s="0" t="inlineStr">
+      <c r="D95" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
         <is>
           <t>jingyuan_codex_level@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F95" s="0" t="inlineStr">
+      <c r="F95" s="5" t="inlineStr">
         <is>
           <t>codex_id+level</t>
         </is>
       </c>
-      <c r="G95" s="0" t="inlineStr">
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="0" t="inlineStr">
+      <c r="B96" s="5" t="inlineStr">
         <is>
           <t>demo.TbJingYuanTuneTier</t>
         </is>
       </c>
-      <c r="C96" s="0" t="inlineStr">
+      <c r="C96" s="5" t="inlineStr">
         <is>
           <t>demo.JingYuanTuneTier</t>
         </is>
       </c>
-      <c r="D96" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E96" s="0" t="inlineStr">
+      <c r="D96" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" s="5" t="inlineStr">
         <is>
           <t>jingyuan_tune_tier@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F96" s="0" t="inlineStr">
+      <c r="F96" s="5" t="inlineStr">
         <is>
           <t>codex_id+tier</t>
         </is>
       </c>
-      <c r="G96" s="0" t="inlineStr">
+      <c r="G96" s="5" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="0" t="inlineStr">
+      <c r="B97" s="5" t="inlineStr">
         <is>
           <t>demo.TbTiaoJingConcentrationLevel</t>
         </is>
       </c>
-      <c r="C97" s="0" t="inlineStr">
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>demo.TiaoJingConcentrationLevel</t>
         </is>
       </c>
-      <c r="D97" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E97" s="0" t="inlineStr">
+      <c r="D97" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>tiao_jing_concentration_level@jingyuan_codex.xlsx</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="0" t="inlineStr">
+      <c r="B98" s="5" t="inlineStr">
         <is>
           <t>demo.TbJingYuanTypeDef</t>
         </is>
       </c>
-      <c r="C98" s="0" t="inlineStr">
+      <c r="C98" s="5" t="inlineStr">
         <is>
           <t>demo.JingYuanTypeDef</t>
         </is>
       </c>
-      <c r="D98" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E98" s="0" t="inlineStr">
+      <c r="D98" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
         <is>
           <t>jingyuan_type_def@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F98" s="0" t="inlineStr">
+      <c r="F98" s="5" t="inlineStr">
         <is>
           <t>type_id</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="0" t="inlineStr">
+      <c r="B99" s="5" t="inlineStr">
         <is>
           <t>demo.TbJingYuanTypePoolEntry</t>
         </is>
       </c>
-      <c r="C99" s="0" t="inlineStr">
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>demo.JingYuanTypePoolEntry</t>
         </is>
       </c>
-      <c r="D99" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E99" s="0" t="inlineStr">
+      <c r="D99" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
         <is>
           <t>jingyuan_type_pool@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="G99" s="0" t="inlineStr">
+      <c r="G99" s="5" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="0" t="inlineStr">
+      <c r="B100" s="5" t="inlineStr">
         <is>
           <t>demo.TbProgressionHubTab</t>
         </is>
       </c>
-      <c r="C100" s="0" t="inlineStr">
+      <c r="C100" s="5" t="inlineStr">
         <is>
           <t>demo.ProgressionHubTabDef</t>
         </is>
       </c>
-      <c r="D100" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E100" s="0" t="inlineStr">
+      <c r="D100" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E100" s="5" t="inlineStr">
         <is>
           <t>progression_hub_tab@progression_hub_tab.xlsx</t>
         </is>
       </c>
-      <c r="F100" s="0" t="inlineStr">
+      <c r="F100" s="5" t="inlineStr">
         <is>
           <t>tab_id</t>
         </is>
       </c>
-      <c r="G100" s="0" t="inlineStr">
+      <c r="G100" s="5" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I100" s="0" t="inlineStr">
+      <c r="I100" s="5" t="inlineStr">
         <is>
           <t>养成总面板选项卡</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="0" t="inlineStr">
+      <c r="B101" s="5" t="inlineStr">
         <is>
           <t>demo.TbPlayerAttachInfo</t>
         </is>
       </c>
-      <c r="C101" s="0" t="inlineStr">
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>demo.PlayerAttachInfo</t>
         </is>
       </c>
-      <c r="D101" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E101" s="0" t="inlineStr">
+      <c r="D101" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E101" s="5" t="inlineStr">
         <is>
           <t>player_attach@player_attach.xlsx</t>
         </is>
       </c>
     </row>
     <row r="102" s="2">
-      <c r="B102" s="0" t="inlineStr">
+      <c r="B102" s="5" t="inlineStr">
         <is>
           <t>demo.TbItemDismantle</t>
         </is>
       </c>
-      <c r="C102" s="0" t="inlineStr">
+      <c r="C102" s="5" t="inlineStr">
         <is>
           <t>demo.ItemDismantle</t>
         </is>
       </c>
-      <c r="D102" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E102" s="0" t="inlineStr">
+      <c r="D102" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
         <is>
           <t>item_dismantle@item_dismantle.xlsx</t>
         </is>
       </c>
-      <c r="F102" s="0" t="inlineStr">
+      <c r="F102" s="5" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="G102" s="0" t="inlineStr">
+      <c r="G102" s="5" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I102" s="0" t="inlineStr">
+      <c r="I102" s="5" t="inlineStr">
         <is>
           <t>物品分解产物配置</t>
         </is>
       </c>
     </row>
     <row r="103" s="2">
-      <c r="B103" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbRenewableResourceNode</t>
-        </is>
-      </c>
-      <c r="C103" s="0" t="inlineStr">
-        <is>
-          <t>demo.RenewableResourceNode</t>
-        </is>
-      </c>
-      <c r="D103" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E103" s="0" t="inlineStr">
-        <is>
-          <t>renewable_resource_node@renewable_resource_node.xlsx</t>
-        </is>
-      </c>
-      <c r="F103" s="0" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G103" s="0" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I103" s="0" t="inlineStr">
-        <is>
-          <t>周期恢复资源节点</t>
-        </is>
-      </c>
+      <c r="A103" s="5" t="n"/>
+      <c r="B103" s="5" t="inlineStr">
+        <is>
+          <t>demo.TbItemTagInfo</t>
+        </is>
+      </c>
+      <c r="C103" s="5" t="inlineStr">
+        <is>
+          <t>demo.ItemTagInfo</t>
+        </is>
+      </c>
+      <c r="D103" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>item_tag@item.xlsx</t>
+        </is>
+      </c>
+      <c r="F103" s="5" t="inlineStr">
+        <is>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="G103" s="5" t="n"/>
+      <c r="H103" s="5" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>物品标签元数据：显示字、隐藏控制、实例需求</t>
+        </is>
+      </c>
+      <c r="J103" s="5" t="n"/>
+      <c r="K103" s="5" t="n"/>
     </row>
     <row r="104">
-      <c r="B104" s="0" t="inlineStr">
-        <is>
-          <t>demo.TbItemTagInfo</t>
-        </is>
-      </c>
-      <c r="C104" s="0" t="inlineStr">
-        <is>
-          <t>demo.ItemTagInfo</t>
-        </is>
-      </c>
-      <c r="D104" s="0" t="b">
-        <v>1</v>
-      </c>
-      <c r="E104" s="0" t="inlineStr">
-        <is>
-          <t>item_tag@item.xlsx</t>
-        </is>
-      </c>
-      <c r="F104" s="0" t="inlineStr">
-        <is>
-          <t>tag</t>
-        </is>
-      </c>
-      <c r="H104" s="0" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="I104" s="0" t="inlineStr">
-        <is>
-          <t>物品标签元数据：显示字、隐藏控制、实例需求</t>
-        </is>
-      </c>
+      <c r="A104" s="5" t="n"/>
+      <c r="B104" s="5" t="inlineStr">
+        <is>
+          <t>demo.TbPlayerBagDef</t>
+        </is>
+      </c>
+      <c r="C104" s="5" t="inlineStr">
+        <is>
+          <t>demo.PlayerBagDef</t>
+        </is>
+      </c>
+      <c r="D104" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E104" s="5" t="inlineStr">
+        <is>
+          <t>player_bag@player_bag.xlsx</t>
+        </is>
+      </c>
+      <c r="F104" s="5" t="n"/>
+      <c r="G104" s="5" t="n"/>
+      <c r="H104" s="5" t="n"/>
+      <c r="I104" s="5" t="inlineStr">
+        <is>
+          <t>玩家背包定义</t>
+        </is>
+      </c>
+      <c r="J104" s="5" t="n"/>
+      <c r="K104" s="5" t="n"/>
     </row>
     <row r="105">
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>demo.TbPlayerBagDef</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>demo.PlayerBagDef</t>
-        </is>
-      </c>
-      <c r="D105" t="b">
-        <v>1</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>player_bag@player_bag.xlsx</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>玩家背包定义</t>
-        </is>
-      </c>
+      <c r="A105" s="5" t="n"/>
+      <c r="B105" s="5" t="inlineStr">
+        <is>
+          <t>demo.TbWarehouseFilter</t>
+        </is>
+      </c>
+      <c r="C105" s="5" t="inlineStr">
+        <is>
+          <t>demo.WarehouseFilter</t>
+        </is>
+      </c>
+      <c r="D105" s="5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>warehouse_filter@warehouse_filter.xlsx</t>
+        </is>
+      </c>
+      <c r="F105" s="5" t="n"/>
+      <c r="G105" s="5" t="n"/>
+      <c r="H105" s="5" t="n"/>
+      <c r="I105" s="5" t="inlineStr">
+        <is>
+          <t>仓库筛选定义</t>
+        </is>
+      </c>
+      <c r="J105" s="5" t="n"/>
+      <c r="K105" s="5" t="n"/>
     </row>
     <row r="106">
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>demo.TbWarehouseFilter</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>demo.WarehouseFilter</t>
-        </is>
-      </c>
-      <c r="D106" t="b">
-        <v>1</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>warehouse_filter@warehouse_filter.xlsx</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>仓库筛选定义</t>
-        </is>
-      </c>
+      <c r="B106" s="5" t="n"/>
+      <c r="C106" s="5" t="n"/>
+      <c r="D106" s="5" t="n"/>
+      <c r="E106" s="5" t="n"/>
+      <c r="I106" s="5" t="n"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" display="area_variant_info@map.xlsx" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" tooltip="mailto:area_overlay_state_info@map.xlsx" display="area_overlay_state_info@map.xlsx" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" display="unit_npc_attribute@unit_npc.xlsx" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" display="desire_density_info@unit_npc.xlsx" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" display="body_part_level@body_part.xlsx" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" display="body_part_progress_info@body_part.xlsx" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -65,7 +65,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -77,6 +77,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -356,7 +359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K112"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -368,183 +371,183 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="1">
-      <c r="A1" s="5" t="inlineStr">
+      <c r="A1" s="6" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="5" t="inlineStr">
+      <c r="B1" s="6" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="C1" s="5" t="inlineStr">
+      <c r="C1" s="6" t="inlineStr">
         <is>
           <t>value_type</t>
         </is>
       </c>
-      <c r="D1" s="5" t="inlineStr">
+      <c r="D1" s="6" t="inlineStr">
         <is>
           <t>read_schema_from_file</t>
         </is>
       </c>
-      <c r="E1" s="5" t="inlineStr">
+      <c r="E1" s="6" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="F1" s="5" t="inlineStr">
+      <c r="F1" s="6" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="G1" s="5" t="inlineStr">
+      <c r="G1" s="6" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
-      <c r="H1" s="5" t="inlineStr">
+      <c r="H1" s="6" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="I1" s="5" t="inlineStr">
+      <c r="I1" s="6" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="J1" s="5" t="inlineStr">
+      <c r="J1" s="6" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="K1" s="5" t="inlineStr">
+      <c r="K1" s="6" t="inlineStr">
         <is>
           <t>output</t>
         </is>
       </c>
     </row>
     <row r="2" customFormat="1" s="1">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" s="6" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="6" t="inlineStr">
         <is>
           <t>全名(包含模块和名字)</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" s="6" t="inlineStr">
         <is>
           <t>记录类名</t>
         </is>
       </c>
-      <c r="D2" s="5" t="inlineStr">
+      <c r="D2" s="6" t="inlineStr">
         <is>
           <t>从excel读取定义</t>
         </is>
       </c>
-      <c r="E2" s="5" t="inlineStr">
+      <c r="E2" s="6" t="inlineStr">
         <is>
           <t>文件列表</t>
         </is>
       </c>
-      <c r="F2" s="5" t="inlineStr">
+      <c r="F2" s="6" t="inlineStr">
         <is>
           <t>表id字段</t>
         </is>
       </c>
-      <c r="G2" s="5" t="inlineStr">
+      <c r="G2" s="6" t="inlineStr">
         <is>
           <t>模式</t>
         </is>
       </c>
-      <c r="H2" s="5" t="inlineStr">
+      <c r="H2" s="6" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>注释</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="K2" s="6" t="inlineStr">
         <is>
           <t>输出文件名</t>
         </is>
       </c>
     </row>
     <row r="3" customFormat="1" s="1">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="6" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="D3" s="5" t="inlineStr">
+      <c r="D3" s="6" t="inlineStr">
         <is>
           <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E3" s="6" t="inlineStr">
         <is>
           <t>可以多个，以逗号','分隔</t>
         </is>
       </c>
-      <c r="F3" s="5" t="inlineStr">
+      <c r="F3" s="6" t="inlineStr">
         <is>
           <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G3" s="6" t="inlineStr">
         <is>
           <t>取值one|map|list，为空自动为map</t>
         </is>
       </c>
-      <c r="H3" s="5" t="inlineStr">
+      <c r="H3" s="6" t="inlineStr">
         <is>
           <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="K3" s="6" t="inlineStr">
         <is>
           <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="6" t="inlineStr">
         <is>
           <t>demo.TbReward</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="6" t="inlineStr">
         <is>
           <t>demo.Reward</t>
         </is>
       </c>
-      <c r="D4" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="D4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
         <is>
           <t>1@reward.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="6" t="inlineStr">
         <is>
           <t>demo.TbLogicAreaInfo</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="6" t="inlineStr">
         <is>
           <t>demo.LogicAreaInfo</t>
         </is>
       </c>
-      <c r="D5" s="5" t="b">
+      <c r="D5" s="6" t="b">
         <v>1</v>
       </c>
       <c r="E5" s="3" t="inlineStr">
@@ -554,37 +557,37 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>demo.TbLogicAreaHomesteadReq</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" s="6" t="inlineStr">
         <is>
           <t>demo.LogicAreaHomesteadReq</t>
         </is>
       </c>
-      <c r="D6" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
+      <c r="D6" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>logic_area_homestead_req@map_homestead.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>demo.TbAreaVariantInfo</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="6" t="inlineStr">
         <is>
           <t>demo.AreaVariantInfo</t>
         </is>
       </c>
-      <c r="D7" s="5" t="b">
+      <c r="D7" s="6" t="b">
         <v>1</v>
       </c>
       <c r="E7" s="3" t="inlineStr">
@@ -594,17 +597,17 @@
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="6" t="inlineStr">
         <is>
           <t>demo.TbAreaOverlayStateInfo</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" s="6" t="inlineStr">
         <is>
           <t>demo.AreaOverlayStateInfo</t>
         </is>
       </c>
-      <c r="D8" s="5" t="b">
+      <c r="D8" s="6" t="b">
         <v>1</v>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -614,147 +617,147 @@
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="6" t="inlineStr">
         <is>
           <t>demo.TbEventGrant</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="6" t="inlineStr">
         <is>
           <t>demo.EventGrant</t>
         </is>
       </c>
-      <c r="D9" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
+      <c r="D9" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>event_grant@event_grant.xlsx</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>通用事件授予（通识/被动成就）</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="6" t="inlineStr">
         <is>
           <t>demo.TbDropBundle</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" s="6" t="inlineStr">
         <is>
           <t>demo.DropBundle</t>
         </is>
       </c>
-      <c r="D10" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
+      <c r="D10" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>drop_bundle@drop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="6" t="inlineStr">
         <is>
           <t>demo.TbDropItem</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="6" t="inlineStr">
         <is>
           <t>demo.DropItem</t>
         </is>
       </c>
-      <c r="D11" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
+      <c r="D11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>drop_item@drop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>demo.TbFixedFacility</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" s="6" t="inlineStr">
         <is>
           <t>demo.FixedFacility</t>
         </is>
       </c>
-      <c r="D12" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
+      <c r="D12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>fixed_facility@home_facility.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
         <is>
           <t>demo.TbBornPoint</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" s="6" t="inlineStr">
         <is>
           <t>demo.BornPoint</t>
         </is>
       </c>
-      <c r="D13" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="D13" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>born_points@born_points.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="6" t="inlineStr">
         <is>
           <t>demo.TbUnitNpc</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" s="6" t="inlineStr">
         <is>
           <t>demo.UnitNpc</t>
         </is>
       </c>
-      <c r="D14" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
+      <c r="D14" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>unit_npc@unit_npc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>demo.TbUnitNpcAttr</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" s="6" t="inlineStr">
         <is>
           <t>demo.UnitNpcAttr</t>
         </is>
       </c>
-      <c r="D15" s="5" t="b">
+      <c r="D15" s="6" t="b">
         <v>1</v>
       </c>
       <c r="E15" s="3" t="inlineStr">
@@ -764,17 +767,17 @@
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="6" t="inlineStr">
         <is>
           <t>demo.TbDesireDensityInfo</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" s="6" t="inlineStr">
         <is>
           <t>demo.DesireDensityInfo</t>
         </is>
       </c>
-      <c r="D16" s="5" t="b">
+      <c r="D16" s="6" t="b">
         <v>1</v>
       </c>
       <c r="E16" s="3" t="inlineStr">
@@ -784,386 +787,386 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="5" t="n"/>
-      <c r="C17" s="5" t="n"/>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="6" t="inlineStr">
         <is>
           <t>demo.TbQuestData</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" s="6" t="inlineStr">
         <is>
           <t>demo.QuestData</t>
         </is>
       </c>
-      <c r="D18" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
+      <c r="D18" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>quest_data@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="6" t="inlineStr">
         <is>
           <t>demo.TbQuestStepData</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" s="6" t="inlineStr">
         <is>
           <t>demo.QuestStepData</t>
         </is>
       </c>
-      <c r="D19" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
+      <c r="D19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>quest_step_data@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="6" t="inlineStr">
         <is>
           <t>demo.TbQuestStepOutcome</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" s="6" t="inlineStr">
         <is>
           <t>demo.QuestStepOutcome</t>
         </is>
       </c>
-      <c r="D20" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="5" t="inlineStr">
+      <c r="D20" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>quest_step_outcome@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="6" t="inlineStr">
         <is>
           <t>demo.TbQuestStepObjective</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" s="6" t="inlineStr">
         <is>
           <t>demo.QuestStepObjective</t>
         </is>
       </c>
-      <c r="D21" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
+      <c r="D21" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>quest_step_objective@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
         <is>
           <t>demo.TbQuestInteractDialog</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>demo.QuestInteractDialogData</t>
         </is>
       </c>
-      <c r="D22" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="5" t="inlineStr">
+      <c r="D22" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>quest_interact_dialog@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="6" t="inlineStr">
         <is>
           <t>demo.TbDialogMetaInfo</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>demo.DialogMetaInfo</t>
         </is>
       </c>
-      <c r="D23" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="D23" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>dialog_meta_info@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>demo.TbItemData</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>demo.ItemData</t>
         </is>
       </c>
-      <c r="D24" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="D24" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>item@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="6" t="inlineStr">
         <is>
           <t>demo.TbShop</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" s="6" t="inlineStr">
         <is>
           <t>demo.Shop</t>
         </is>
       </c>
-      <c r="D25" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
+      <c r="D25" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>shop@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="6" t="inlineStr">
         <is>
           <t>demo.TbShopGoods</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" s="6" t="inlineStr">
         <is>
           <t>demo.ShopGoods</t>
         </is>
       </c>
-      <c r="D26" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
+      <c r="D26" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
         <is>
           <t>shop_goods@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="6" t="inlineStr">
         <is>
           <t>demo.TbItemUse</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" s="6" t="inlineStr">
         <is>
           <t>demo.ItemUse</t>
         </is>
       </c>
-      <c r="D27" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
+      <c r="D27" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
         <is>
           <t>item_use@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>demo.TbItemGift</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" s="6" t="inlineStr">
         <is>
           <t>demo.ItemGift</t>
         </is>
       </c>
-      <c r="D28" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
+      <c r="D28" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
         <is>
           <t>item_gift@item.xlsx</t>
         </is>
       </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="G28" s="5" t="inlineStr">
+      <c r="G28" s="6" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>demo.TbNpcDialogInfo</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" s="6" t="inlineStr">
         <is>
           <t>demo.NpcDialogInfo</t>
         </is>
       </c>
-      <c r="D29" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
+      <c r="D29" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
         <is>
           <t>npc_dialog_info@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>demo.TbWorldMapGlobal</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" s="6" t="inlineStr">
         <is>
           <t>demo.WorldMapGlobal</t>
         </is>
       </c>
-      <c r="D30" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
+      <c r="D30" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
         <is>
           <t>world_map_global@map.xlsx</t>
         </is>
       </c>
-      <c r="G30" s="5" t="inlineStr">
+      <c r="G30" s="6" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="6" t="inlineStr">
         <is>
           <t>demo.TbWorldMapBigMapLayer</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" s="6" t="inlineStr">
         <is>
           <t>demo.WorldMapBigMapLayer</t>
         </is>
       </c>
-      <c r="D31" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="D31" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
         <is>
           <t>world_map_big_map@map.xlsx</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G31" s="6" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="6" t="inlineStr">
         <is>
           <t>demo.TbDreamInfiltrationSpot</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" s="6" t="inlineStr">
         <is>
           <t>demo.DreamInfiltrationSpot</t>
         </is>
       </c>
-      <c r="D32" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
+      <c r="D32" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
         <is>
           <t>dream_infiltration@dream_infiltration.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>demo.TbCharDreamEntryInfo</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>demo.CharDreamEntryInfo</t>
         </is>
       </c>
-      <c r="D33" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
+      <c r="D33" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>char_dream_entry@dream_infiltration.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>demo.TbFishingSpot</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>demo.FishingSpot</t>
         </is>
       </c>
-      <c r="D34" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="D34" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>fishing_spot@fishing_spot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>demo.TbFishingSpotFish</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>demo.FishingSpotFish</t>
         </is>
       </c>
-      <c r="D35" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="D35" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>fishing_spot_fish@fishing_spot.xlsx</t>
         </is>
@@ -1171,80 +1174,80 @@
     </row>
     <row r="36"/>
     <row r="37">
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>demo.TbPlayerDesireLevel</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>demo.PlayerDesireLevel</t>
         </is>
       </c>
-      <c r="D37" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
+      <c r="D37" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>player_desire_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>demo.TbPlayerJingYuLevel</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>demo.PlayerJingYuLevel</t>
         </is>
       </c>
-      <c r="D38" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="5" t="inlineStr">
+      <c r="D38" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>player_jingyu_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="6" t="inlineStr">
         <is>
           <t>demo.TbPlayerSanCorruptLevel</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" s="6" t="inlineStr">
         <is>
           <t>demo.PlayerSanCorruptLevel</t>
         </is>
       </c>
-      <c r="D39" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="D39" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="6" t="inlineStr">
         <is>
           <t>player_san_corrupt_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="6" t="inlineStr">
         <is>
           <t>demo.TbPlayerClothesExposeInfo</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" s="6" t="inlineStr">
         <is>
           <t>demo.PlayerClothesExposeInfo</t>
         </is>
       </c>
-      <c r="D40" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
+      <c r="D40" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>player_clothes_expose_info@player_status.xlsx</t>
         </is>
@@ -1252,300 +1255,310 @@
     </row>
     <row r="41"/>
     <row r="42">
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="6" t="inlineStr">
         <is>
           <t>demo.TbWantedLevelInfo</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" s="6" t="inlineStr">
         <is>
           <t>demo.WantedLevelInfo</t>
         </is>
       </c>
-      <c r="D42" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
+      <c r="D42" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
         <is>
           <t>wanted_level_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="6" t="inlineStr">
         <is>
           <t>demo.TbWantedBehaveInfo</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
         <is>
           <t>demo.WantedBehaveInfo</t>
         </is>
       </c>
-      <c r="D43" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
+      <c r="D43" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="6" t="inlineStr">
         <is>
           <t>wanted_behave_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="6" t="inlineStr">
         <is>
           <t>demo.TbTalentNode</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" s="6" t="inlineStr">
         <is>
           <t>demo.TalentNode</t>
         </is>
       </c>
-      <c r="D44" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="D44" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="6" t="inlineStr">
         <is>
           <t>talent@talent.xlsx</t>
         </is>
       </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="45">
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="6" t="inlineStr">
         <is>
           <t>demo.TbWantedGuardSpawnTier</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" s="6" t="inlineStr">
         <is>
           <t>demo.WantedGuardSpawnTier</t>
         </is>
       </c>
-      <c r="D45" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
+      <c r="D45" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="6" t="inlineStr">
         <is>
           <t>wanted_guard_spawn@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" s="6" t="inlineStr">
         <is>
           <t>demo.TbEntitySkillData</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" s="6" t="inlineStr">
         <is>
           <t>demo.EntitySkillData</t>
         </is>
       </c>
-      <c r="D46" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
+      <c r="D46" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
         <is>
           <t>entity_skill@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="6" t="inlineStr">
         <is>
           <t>demo.TbSkillSchool</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" s="6" t="inlineStr">
         <is>
           <t>demo.SkillSchool</t>
         </is>
       </c>
-      <c r="D47" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="D47" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="6" t="inlineStr">
         <is>
           <t>skill_school@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="6" t="inlineStr">
         <is>
           <t>demo.TbSkillLearnEntry</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" s="6" t="inlineStr">
         <is>
           <t>demo.SkillLearnEntry</t>
         </is>
       </c>
-      <c r="D48" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
+      <c r="D48" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
         <is>
           <t>skill_learn@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" s="6" t="inlineStr">
         <is>
           <t>demo.TbDesireCrystalDef</t>
         </is>
       </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="C49" s="6" t="inlineStr">
         <is>
           <t>demo.DesireCrystalDef</t>
         </is>
       </c>
-      <c r="D49" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="D49" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="6" t="inlineStr">
         <is>
           <t>desire_crystal_def@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" s="6" t="inlineStr">
         <is>
           <t>demo.TbMapDesireCrystalBudget</t>
         </is>
       </c>
-      <c r="C50" s="5" t="inlineStr">
+      <c r="C50" s="6" t="inlineStr">
         <is>
           <t>demo.MapDesireCrystalBudget</t>
         </is>
       </c>
-      <c r="D50" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
+      <c r="D50" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
         <is>
           <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="5" t="inlineStr">
+      <c r="B51" s="6" t="inlineStr">
         <is>
           <t>demo.TbMapWalkerDesireCrystalQuota</t>
         </is>
       </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="C51" s="6" t="inlineStr">
         <is>
           <t>demo.MapWalkerDesireCrystalQuota</t>
         </is>
       </c>
-      <c r="D51" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="D51" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="6" t="inlineStr">
         <is>
           <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="5" t="inlineStr">
+      <c r="B52" s="6" t="inlineStr">
         <is>
           <t>demo.TbNamedNpcDesireCrystal</t>
         </is>
       </c>
-      <c r="C52" s="5" t="inlineStr">
+      <c r="C52" s="6" t="inlineStr">
         <is>
           <t>demo.NamedNpcDesireCrystal</t>
         </is>
       </c>
-      <c r="D52" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
+      <c r="D52" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
         <is>
           <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="5" t="inlineStr">
+      <c r="B53" s="6" t="inlineStr">
         <is>
           <t>demo.TbSpiritMonsterTypeBudget</t>
         </is>
       </c>
-      <c r="C53" s="5" t="inlineStr">
+      <c r="C53" s="6" t="inlineStr">
         <is>
           <t>demo.SpiritMonsterTypeBudget</t>
         </is>
       </c>
-      <c r="D53" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
+      <c r="D53" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" s="6" t="inlineStr">
         <is>
           <t>spirit_monster_budget@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="5" t="inlineStr">
+      <c r="B54" s="6" t="inlineStr">
         <is>
           <t>demo.TbContainerItemStackOverride</t>
         </is>
       </c>
-      <c r="C54" s="5" t="inlineStr">
+      <c r="C54" s="6" t="inlineStr">
         <is>
           <t>demo.ContainerItemStackOverride</t>
         </is>
       </c>
-      <c r="D54" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
+      <c r="D54" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
         <is>
           <t>container_item_stack_override@container_stack.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="5" t="inlineStr">
+      <c r="B55" s="6" t="inlineStr">
         <is>
           <t>demo.TbContainerStackTagRule</t>
         </is>
       </c>
-      <c r="C55" s="5" t="inlineStr">
+      <c r="C55" s="6" t="inlineStr">
         <is>
           <t>demo.ContainerStackTagRule</t>
         </is>
       </c>
-      <c r="D55" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
+      <c r="D55" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
         <is>
           <t>container_stack_tag_rule@container_stack.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="5" t="inlineStr">
+      <c r="B56" s="6" t="inlineStr">
         <is>
           <t>demo.TbMapAreaEffect</t>
         </is>
       </c>
-      <c r="C56" s="5" t="inlineStr">
+      <c r="C56" s="6" t="inlineStr">
         <is>
           <t>demo.MapAreaEffect</t>
         </is>
       </c>
-      <c r="D56" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
+      <c r="D56" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
         <is>
           <t>map_area_effect@map_area_effect.xlsx</t>
         </is>
@@ -1553,80 +1566,80 @@
     </row>
     <row r="57"/>
     <row r="58">
-      <c r="B58" s="5" t="inlineStr">
+      <c r="B58" s="6" t="inlineStr">
         <is>
           <t>demo.TbFallenAmountProgressInfo</t>
         </is>
       </c>
-      <c r="C58" s="5" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>demo.FallenAmountProgressInfo</t>
         </is>
       </c>
-      <c r="D58" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
+      <c r="D58" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" s="6" t="inlineStr">
         <is>
           <t>fallen_amount_progress_info@fallen_amount_progress_info.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="5" t="inlineStr">
+      <c r="B59" s="6" t="inlineStr">
         <is>
           <t>demo.TbRumorIntel</t>
         </is>
       </c>
-      <c r="C59" s="5" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>demo.RumorIntel</t>
         </is>
       </c>
-      <c r="D59" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
+      <c r="D59" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="6" t="inlineStr">
         <is>
           <t>rumor_intel@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="5" t="inlineStr">
+      <c r="B60" s="6" t="inlineStr">
         <is>
           <t>demo.TbRumorRandomPool</t>
         </is>
       </c>
-      <c r="C60" s="5" t="inlineStr">
+      <c r="C60" s="6" t="inlineStr">
         <is>
           <t>demo.RumorRandomPool</t>
         </is>
       </c>
-      <c r="D60" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
+      <c r="D60" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="6" t="inlineStr">
         <is>
           <t>rumor_random_pool@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="5" t="inlineStr">
+      <c r="B61" s="6" t="inlineStr">
         <is>
           <t>demo.TbRumorGlobal</t>
         </is>
       </c>
-      <c r="C61" s="5" t="inlineStr">
+      <c r="C61" s="6" t="inlineStr">
         <is>
           <t>demo.RumorGlobal</t>
         </is>
       </c>
-      <c r="D61" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="5" t="inlineStr">
+      <c r="D61" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
         <is>
           <t>rumor_global@rumor_tables.xlsx</t>
         </is>
@@ -1634,100 +1647,100 @@
     </row>
     <row r="62"/>
     <row r="63">
-      <c r="B63" s="5" t="inlineStr">
+      <c r="B63" s="6" t="inlineStr">
         <is>
           <t>demo.TbCharacterInfo</t>
         </is>
       </c>
-      <c r="C63" s="5" t="inlineStr">
+      <c r="C63" s="6" t="inlineStr">
         <is>
           <t>demo.CharacterInfo</t>
         </is>
       </c>
-      <c r="D63" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="5" t="inlineStr">
+      <c r="D63" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="6" t="inlineStr">
         <is>
           <t>character_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B64" s="6" t="inlineStr">
         <is>
           <t>demo.TbCharacterFavorInfo</t>
         </is>
       </c>
-      <c r="C64" s="5" t="inlineStr">
+      <c r="C64" s="6" t="inlineStr">
         <is>
           <t>demo.CharacterFavorInfo</t>
         </is>
       </c>
-      <c r="D64" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
+      <c r="D64" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
         <is>
           <t>character_favor_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>demo.TbMicroPlotDef</t>
         </is>
       </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>demo.MicroPlotDef</t>
         </is>
       </c>
-      <c r="D65" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="D65" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="6" t="inlineStr">
         <is>
           <t>micro_plot_def@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B66" s="6" t="inlineStr">
         <is>
           <t>demo.TbMapMicroPlotTrigger</t>
         </is>
       </c>
-      <c r="C66" s="5" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>demo.MapMicroPlotTrigger</t>
         </is>
       </c>
-      <c r="D66" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="5" t="inlineStr">
+      <c r="D66" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>map_micro_plot_trigger@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" s="6" t="inlineStr">
         <is>
           <t>demo.TbMicroPlotTimelineEvent</t>
         </is>
       </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>demo.MicroPlotTimelineEvent</t>
         </is>
       </c>
-      <c r="D67" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="D67" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
         <is>
           <t>micro_plot_timeline_event@micro_plot.xlsx</t>
         </is>
@@ -1735,40 +1748,40 @@
     </row>
     <row r="68"/>
     <row r="69">
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" s="6" t="inlineStr">
         <is>
           <t>demo.TbTrapSpec</t>
         </is>
       </c>
-      <c r="C69" s="5" t="inlineStr">
+      <c r="C69" s="6" t="inlineStr">
         <is>
           <t>demo.TrapSpec</t>
         </is>
       </c>
-      <c r="D69" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
+      <c r="D69" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" s="6" t="inlineStr">
         <is>
           <t>trap_spec@trap_spec.xlsx</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B70" s="6" t="inlineStr">
         <is>
           <t>demo.TbForgeRecipe</t>
         </is>
       </c>
-      <c r="C70" s="5" t="inlineStr">
+      <c r="C70" s="6" t="inlineStr">
         <is>
           <t>demo.ForgeRecipe</t>
         </is>
       </c>
-      <c r="D70" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
+      <c r="D70" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
         <is>
           <t>forge_recipe@forge_recipe.xlsx</t>
         </is>
@@ -1776,200 +1789,200 @@
     </row>
     <row r="71"/>
     <row r="72">
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B72" s="6" t="inlineStr">
         <is>
           <t>demo.TbHActInfo</t>
         </is>
       </c>
-      <c r="C72" s="5" t="inlineStr">
+      <c r="C72" s="6" t="inlineStr">
         <is>
           <t>demo.HActInfo</t>
         </is>
       </c>
-      <c r="D72" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
+      <c r="D72" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" s="6" t="inlineStr">
         <is>
           <t>h_act_info@h_act_info.xlsx</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" s="6" t="inlineStr">
         <is>
           <t>demo.TbTalentNodeLevel</t>
         </is>
       </c>
-      <c r="C73" s="5" t="inlineStr">
+      <c r="C73" s="6" t="inlineStr">
         <is>
           <t>demo.TalentNodeLevel</t>
         </is>
       </c>
-      <c r="D73" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
+      <c r="D73" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="6" t="inlineStr">
         <is>
           <t>talent_level@talent.xlsx</t>
         </is>
       </c>
-      <c r="F73" s="5" t="inlineStr">
+      <c r="F73" s="6" t="inlineStr">
         <is>
           <t>node_id+level</t>
         </is>
       </c>
-      <c r="G73" s="5" t="inlineStr">
+      <c r="G73" s="6" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B74" s="6" t="inlineStr">
         <is>
           <t>demo.TbSavePoint</t>
         </is>
       </c>
-      <c r="C74" s="5" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>demo.SavePoint</t>
         </is>
       </c>
-      <c r="D74" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
+      <c r="D74" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" s="6" t="inlineStr">
         <is>
           <t>save_point@save_point.xlsx</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" s="6" t="inlineStr">
         <is>
           <t>demo.TbReviveRule</t>
         </is>
       </c>
-      <c r="C75" s="5" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>demo.ReviveRule</t>
         </is>
       </c>
-      <c r="D75" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E75" s="5" t="inlineStr">
+      <c r="D75" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" s="6" t="inlineStr">
         <is>
           <t>revive_rule@revive_rule.xlsx</t>
         </is>
       </c>
-      <c r="G75" s="5" t="inlineStr">
+      <c r="G75" s="6" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B76" s="6" t="inlineStr">
         <is>
           <t>demo.TbDesireDensityTier</t>
         </is>
       </c>
-      <c r="C76" s="5" t="inlineStr">
+      <c r="C76" s="6" t="inlineStr">
         <is>
           <t>demo.DesireDensityTier</t>
         </is>
       </c>
-      <c r="D76" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
+      <c r="D76" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E76" s="6" t="inlineStr">
         <is>
           <t>desire_density_tier@desire_density_tier.xlsx</t>
         </is>
       </c>
     </row>
     <row r="77">
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" s="6" t="inlineStr">
         <is>
           <t>demo.TbMindFragmentPoolEntry</t>
         </is>
       </c>
-      <c r="C77" s="5" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>demo.MindFragmentPoolEntry</t>
         </is>
       </c>
-      <c r="D77" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E77" s="5" t="inlineStr">
+      <c r="D77" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" s="6" t="inlineStr">
         <is>
           <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
         </is>
       </c>
-      <c r="G77" s="5" t="inlineStr">
+      <c r="G77" s="6" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="78">
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B78" s="6" t="inlineStr">
         <is>
           <t>demo.TbSecretBaseFacility</t>
         </is>
       </c>
-      <c r="C78" s="5" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>demo.SecretBaseFacility</t>
         </is>
       </c>
-      <c r="D78" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E78" s="5" t="inlineStr">
+      <c r="D78" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
         <is>
           <t>secret_base_facility@secret_base_facility.xlsx</t>
         </is>
       </c>
-      <c r="I78" s="5" t="inlineStr">
+      <c r="I78" s="6" t="inlineStr">
         <is>
           <t>据点固定设施</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" s="6" t="inlineStr">
         <is>
           <t>demo.TbSecretBaseBuildLevel</t>
         </is>
       </c>
-      <c r="C79" s="5" t="inlineStr">
+      <c r="C79" s="6" t="inlineStr">
         <is>
           <t>demo.SecretBaseBuildLevel</t>
         </is>
       </c>
-      <c r="D79" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
+      <c r="D79" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
         <is>
           <t>secret_base_build_level@secret_base_build_level.xlsx</t>
         </is>
       </c>
-      <c r="F79" s="5" t="inlineStr">
+      <c r="F79" s="6" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="G79" s="5" t="inlineStr">
+      <c r="G79" s="6" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I79" s="5" t="inlineStr">
+      <c r="I79" s="6" t="inlineStr">
         <is>
           <t>据点建设等级卷轴边界</t>
         </is>
@@ -1977,127 +1990,127 @@
     </row>
     <row r="80"/>
     <row r="81">
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" s="6" t="inlineStr">
         <is>
           <t>demo.TbSecretBaseCharacter</t>
         </is>
       </c>
-      <c r="C81" s="5" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>demo.SecretBaseCharacter</t>
         </is>
       </c>
-      <c r="D81" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="D81" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" s="6" t="inlineStr">
         <is>
           <t>secret_base_character@secret_base_character.xlsx</t>
         </is>
       </c>
-      <c r="F81" s="5" t="inlineStr">
+      <c r="F81" s="6" t="inlineStr">
         <is>
           <t>slot_id</t>
         </is>
       </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="G81" s="6" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I81" s="5" t="inlineStr">
+      <c r="I81" s="6" t="inlineStr">
         <is>
           <t>秘密据点角色</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B82" s="6" t="inlineStr">
         <is>
           <t>demo.TbHumanWeapon</t>
         </is>
       </c>
-      <c r="C82" s="5" t="inlineStr">
+      <c r="C82" s="6" t="inlineStr">
         <is>
           <t>demo.HumanWeapon</t>
         </is>
       </c>
-      <c r="D82" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
+      <c r="D82" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
         <is>
           <t>human_weapon@human_weapon.xlsx</t>
         </is>
       </c>
-      <c r="F82" s="5" t="inlineStr">
+      <c r="F82" s="6" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="G82" s="5" t="inlineStr">
+      <c r="G82" s="6" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I82" s="5" t="inlineStr">
+      <c r="I82" s="6" t="inlineStr">
         <is>
           <t>human_weapon</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" s="6" t="inlineStr">
         <is>
           <t>demo.TbRuneData</t>
         </is>
       </c>
-      <c r="C83" s="5" t="inlineStr">
+      <c r="C83" s="6" t="inlineStr">
         <is>
           <t>demo.RuneData</t>
         </is>
       </c>
-      <c r="D83" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="D83" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" s="6" t="inlineStr">
         <is>
           <t>rune_data@rune.xlsx</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="5" t="inlineStr">
+      <c r="B84" s="6" t="inlineStr">
         <is>
           <t>demo.TbBodyPartDef</t>
         </is>
       </c>
-      <c r="C84" s="5" t="inlineStr">
+      <c r="C84" s="6" t="inlineStr">
         <is>
           <t>demo.BodyPartDef</t>
         </is>
       </c>
-      <c r="D84" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
+      <c r="D84" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>body_part_def@body_part.xlsx</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B85" s="6" t="inlineStr">
         <is>
           <t>demo.TbBodyPartLevel</t>
         </is>
       </c>
-      <c r="C85" s="5" t="inlineStr">
+      <c r="C85" s="6" t="inlineStr">
         <is>
           <t>demo.BodyPartLevel</t>
         </is>
       </c>
-      <c r="D85" s="5" t="b">
+      <c r="D85" s="6" t="b">
         <v>1</v>
       </c>
       <c r="E85" s="3" t="inlineStr">
@@ -2105,29 +2118,29 @@
           <t>body_part_level@body_part.xlsx</t>
         </is>
       </c>
-      <c r="F85" s="5" t="inlineStr">
+      <c r="F85" s="6" t="inlineStr">
         <is>
           <t>part_id+level</t>
         </is>
       </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="G85" s="6" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B86" s="6" t="inlineStr">
         <is>
           <t>demo.TbBodyPartProgressInfo</t>
         </is>
       </c>
-      <c r="C86" s="5" t="inlineStr">
+      <c r="C86" s="6" t="inlineStr">
         <is>
           <t>demo.BodyPartProgressInfo</t>
         </is>
       </c>
-      <c r="D86" s="5" t="b">
+      <c r="D86" s="6" t="b">
         <v>1</v>
       </c>
       <c r="E86" s="3" t="inlineStr">
@@ -2135,571 +2148,773 @@
           <t>body_part_progress_info@body_part.xlsx</t>
         </is>
       </c>
-      <c r="F86" s="5" t="n"/>
-      <c r="G86" s="5" t="n"/>
+      <c r="F86" s="6" t="n"/>
+      <c r="G86" s="6" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" s="6" t="inlineStr">
         <is>
           <t>demo.TbPartLocalAttrDef</t>
         </is>
       </c>
-      <c r="C87" s="5" t="inlineStr">
+      <c r="C87" s="6" t="inlineStr">
         <is>
           <t>demo.PartLocalAttrDef</t>
         </is>
       </c>
-      <c r="D87" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="D87" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="6" t="inlineStr">
         <is>
           <t>part_local_attr_def@body_part.xlsx</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B88" s="6" t="inlineStr">
         <is>
           <t>demo.TbPartGear</t>
         </is>
       </c>
-      <c r="C88" s="5" t="inlineStr">
+      <c r="C88" s="6" t="inlineStr">
         <is>
           <t>demo.PartGear</t>
         </is>
       </c>
-      <c r="D88" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="D88" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" s="6" t="inlineStr">
         <is>
           <t>partgear@partgear.xlsx</t>
         </is>
       </c>
-      <c r="F88" s="5" t="inlineStr">
+      <c r="F88" s="6" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="G88" s="5" t="inlineStr">
+      <c r="G88" s="6" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" s="6" t="inlineStr">
         <is>
           <t>demo.TbRuneUpgradeInfo</t>
         </is>
       </c>
-      <c r="C89" s="5" t="inlineStr">
+      <c r="C89" s="6" t="inlineStr">
         <is>
           <t>demo.RuneUpgradeInfo</t>
         </is>
       </c>
-      <c r="D89" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
+      <c r="D89" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" s="6" t="inlineStr">
         <is>
           <t>rune_upgrade_info@rune.xlsx</t>
         </is>
       </c>
-      <c r="F89" s="5" t="inlineStr">
+      <c r="F89" s="6" t="inlineStr">
         <is>
           <t>upgrade_id</t>
         </is>
       </c>
-      <c r="J89" s="5" t="inlineStr">
+      <c r="J89" s="6" t="inlineStr">
         <is>
           <t>符文升级项</t>
         </is>
       </c>
     </row>
     <row r="90">
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B90" s="6" t="inlineStr">
         <is>
           <t>demo.TbRuneEquipSlot</t>
         </is>
       </c>
-      <c r="C90" s="5" t="inlineStr">
+      <c r="C90" s="6" t="inlineStr">
         <is>
           <t>demo.RuneEquipSlotInfo</t>
         </is>
       </c>
-      <c r="D90" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
+      <c r="D90" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
         <is>
           <t>rune_equip_slot@rune.xlsx</t>
         </is>
       </c>
-      <c r="F90" s="5" t="inlineStr">
+      <c r="F90" s="6" t="inlineStr">
         <is>
           <t>equip_slot</t>
         </is>
       </c>
-      <c r="J90" s="5" t="inlineStr">
+      <c r="J90" s="6" t="inlineStr">
         <is>
           <t>符文装配槽</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" s="6" t="inlineStr">
         <is>
           <t>demo.TbEntitySkillLevel</t>
         </is>
       </c>
-      <c r="C91" s="5" t="inlineStr">
+      <c r="C91" s="6" t="inlineStr">
         <is>
           <t>demo.EntitySkillLevel</t>
         </is>
       </c>
-      <c r="D91" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
+      <c r="D91" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
         <is>
           <t>skill_level@skill.xlsx</t>
         </is>
       </c>
-      <c r="F91" s="5" t="inlineStr">
+      <c r="F91" s="6" t="inlineStr">
         <is>
           <t>skill_id+level</t>
         </is>
       </c>
-      <c r="G91" s="5" t="inlineStr">
+      <c r="G91" s="6" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B92" s="6" t="inlineStr">
         <is>
           <t>demo.TbHomesteadBuilding</t>
         </is>
       </c>
-      <c r="C92" s="5" t="inlineStr">
+      <c r="C92" s="6" t="inlineStr">
         <is>
           <t>demo.HomesteadBuilding</t>
         </is>
       </c>
-      <c r="D92" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E92" s="5" t="inlineStr">
+      <c r="D92" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
         <is>
           <t>homestead_building@map_homestead.xlsx</t>
         </is>
       </c>
-      <c r="F92" s="5" t="inlineStr">
+      <c r="F92" s="6" t="inlineStr">
         <is>
           <t>logic_area_id+building_id</t>
         </is>
       </c>
-      <c r="G92" s="5" t="inlineStr">
+      <c r="G92" s="6" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
-      <c r="I92" s="5" t="inlineStr">
+      <c r="I92" s="6" t="inlineStr">
         <is>
           <t>逻辑区域可管理建筑</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" s="6" t="inlineStr">
         <is>
           <t>demo.TbHomesteadBuildingUpgrade</t>
         </is>
       </c>
-      <c r="C93" s="5" t="inlineStr">
+      <c r="C93" s="6" t="inlineStr">
         <is>
           <t>demo.HomesteadBuildingUpgrade</t>
         </is>
       </c>
-      <c r="D93" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
+      <c r="D93" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
         <is>
           <t>homestead_building_upgrade@map_homestead.xlsx</t>
         </is>
       </c>
-      <c r="F93" s="5" t="inlineStr">
+      <c r="F93" s="6" t="inlineStr">
         <is>
           <t>logic_area_id+building_id+level</t>
         </is>
       </c>
-      <c r="G93" s="5" t="inlineStr">
+      <c r="G93" s="6" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
-      <c r="I93" s="5" t="inlineStr">
+      <c r="I93" s="6" t="inlineStr">
         <is>
           <t>家园建筑升级项</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B94" s="6" t="inlineStr">
         <is>
           <t>demo.TbJingYuanCodexDef</t>
         </is>
       </c>
-      <c r="C94" s="5" t="inlineStr">
+      <c r="C94" s="6" t="inlineStr">
         <is>
           <t>demo.JingYuanCodexDef</t>
         </is>
       </c>
-      <c r="D94" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E94" s="5" t="inlineStr">
+      <c r="D94" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
         <is>
           <t>jingyuan_codex_def@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F94" s="5" t="inlineStr">
+      <c r="F94" s="6" t="inlineStr">
         <is>
           <t>codex_id</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B95" s="6" t="inlineStr">
         <is>
           <t>demo.TbJingYuanCodexLevel</t>
         </is>
       </c>
-      <c r="C95" s="5" t="inlineStr">
+      <c r="C95" s="6" t="inlineStr">
         <is>
           <t>demo.JingYuanCodexLevel</t>
         </is>
       </c>
-      <c r="D95" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
+      <c r="D95" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" s="6" t="inlineStr">
         <is>
           <t>jingyuan_codex_level@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F95" s="5" t="inlineStr">
+      <c r="F95" s="6" t="inlineStr">
         <is>
           <t>codex_id+level</t>
         </is>
       </c>
-      <c r="G95" s="5" t="inlineStr">
+      <c r="G95" s="6" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B96" s="6" t="inlineStr">
         <is>
           <t>demo.TbJingYuanTuneTier</t>
         </is>
       </c>
-      <c r="C96" s="5" t="inlineStr">
+      <c r="C96" s="6" t="inlineStr">
         <is>
           <t>demo.JingYuanTuneTier</t>
         </is>
       </c>
-      <c r="D96" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E96" s="5" t="inlineStr">
+      <c r="D96" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
         <is>
           <t>jingyuan_tune_tier@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F96" s="5" t="inlineStr">
+      <c r="F96" s="6" t="inlineStr">
         <is>
           <t>codex_id+tier</t>
         </is>
       </c>
-      <c r="G96" s="5" t="inlineStr">
+      <c r="G96" s="6" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B97" s="6" t="inlineStr">
         <is>
           <t>demo.TbTiaoJingConcentrationLevel</t>
         </is>
       </c>
-      <c r="C97" s="5" t="inlineStr">
+      <c r="C97" s="6" t="inlineStr">
         <is>
           <t>demo.TiaoJingConcentrationLevel</t>
         </is>
       </c>
-      <c r="D97" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
+      <c r="D97" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97" s="6" t="inlineStr">
         <is>
           <t>tiao_jing_concentration_level@jingyuan_codex.xlsx</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B98" s="6" t="inlineStr">
         <is>
           <t>demo.TbJingYuanTypeDef</t>
         </is>
       </c>
-      <c r="C98" s="5" t="inlineStr">
+      <c r="C98" s="6" t="inlineStr">
         <is>
           <t>demo.JingYuanTypeDef</t>
         </is>
       </c>
-      <c r="D98" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
+      <c r="D98" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E98" s="6" t="inlineStr">
         <is>
           <t>jingyuan_type_def@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F98" s="5" t="inlineStr">
+      <c r="F98" s="6" t="inlineStr">
         <is>
           <t>type_id</t>
         </is>
       </c>
     </row>
     <row r="99">
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" s="6" t="inlineStr">
         <is>
           <t>demo.TbJingYuanTypePoolEntry</t>
         </is>
       </c>
-      <c r="C99" s="5" t="inlineStr">
+      <c r="C99" s="6" t="inlineStr">
         <is>
           <t>demo.JingYuanTypePoolEntry</t>
         </is>
       </c>
-      <c r="D99" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
+      <c r="D99" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
         <is>
           <t>jingyuan_type_pool@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="G99" s="5" t="inlineStr">
+      <c r="G99" s="6" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="100">
-      <c r="B100" s="5" t="inlineStr">
+      <c r="B100" s="6" t="inlineStr">
         <is>
           <t>demo.TbProgressionHubTab</t>
         </is>
       </c>
-      <c r="C100" s="5" t="inlineStr">
+      <c r="C100" s="6" t="inlineStr">
         <is>
           <t>demo.ProgressionHubTabDef</t>
         </is>
       </c>
-      <c r="D100" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E100" s="5" t="inlineStr">
+      <c r="D100" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E100" s="6" t="inlineStr">
         <is>
           <t>progression_hub_tab@progression_hub_tab.xlsx</t>
         </is>
       </c>
-      <c r="F100" s="5" t="inlineStr">
+      <c r="F100" s="6" t="inlineStr">
         <is>
           <t>tab_id</t>
         </is>
       </c>
-      <c r="G100" s="5" t="inlineStr">
+      <c r="G100" s="6" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I100" s="5" t="inlineStr">
+      <c r="I100" s="6" t="inlineStr">
         <is>
           <t>养成总面板选项卡</t>
         </is>
       </c>
     </row>
     <row r="101">
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B101" s="6" t="inlineStr">
         <is>
           <t>demo.TbPlayerAttachInfo</t>
         </is>
       </c>
-      <c r="C101" s="5" t="inlineStr">
+      <c r="C101" s="6" t="inlineStr">
         <is>
           <t>demo.PlayerAttachInfo</t>
         </is>
       </c>
-      <c r="D101" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
+      <c r="D101" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E101" s="6" t="inlineStr">
         <is>
           <t>player_attach@player_attach.xlsx</t>
         </is>
       </c>
     </row>
     <row r="102" s="2">
-      <c r="B102" s="5" t="inlineStr">
+      <c r="B102" s="6" t="inlineStr">
         <is>
           <t>demo.TbItemDismantle</t>
         </is>
       </c>
-      <c r="C102" s="5" t="inlineStr">
+      <c r="C102" s="6" t="inlineStr">
         <is>
           <t>demo.ItemDismantle</t>
         </is>
       </c>
-      <c r="D102" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E102" s="5" t="inlineStr">
+      <c r="D102" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E102" s="6" t="inlineStr">
         <is>
           <t>item_dismantle@item_dismantle.xlsx</t>
         </is>
       </c>
-      <c r="F102" s="5" t="inlineStr">
+      <c r="F102" s="6" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="G102" s="5" t="inlineStr">
+      <c r="G102" s="6" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I102" s="5" t="inlineStr">
+      <c r="I102" s="6" t="inlineStr">
         <is>
           <t>物品分解产物配置</t>
         </is>
       </c>
     </row>
     <row r="103" s="2">
-      <c r="A103" s="5" t="n"/>
-      <c r="B103" s="5" t="inlineStr">
+      <c r="A103" s="6" t="n"/>
+      <c r="B103" s="6" t="inlineStr">
         <is>
           <t>demo.TbItemTagInfo</t>
         </is>
       </c>
-      <c r="C103" s="5" t="inlineStr">
+      <c r="C103" s="6" t="inlineStr">
         <is>
           <t>demo.ItemTagInfo</t>
         </is>
       </c>
-      <c r="D103" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E103" s="5" t="inlineStr">
+      <c r="D103" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
         <is>
           <t>item_tag@item.xlsx</t>
         </is>
       </c>
-      <c r="F103" s="5" t="inlineStr">
+      <c r="F103" s="6" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="G103" s="5" t="n"/>
-      <c r="H103" s="5" t="inlineStr">
+      <c r="G103" s="6" t="n"/>
+      <c r="H103" s="6" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="I103" s="5" t="inlineStr">
+      <c r="I103" s="6" t="inlineStr">
         <is>
           <t>物品标签元数据：显示字、隐藏控制、实例需求</t>
         </is>
       </c>
-      <c r="J103" s="5" t="n"/>
-      <c r="K103" s="5" t="n"/>
+      <c r="J103" s="6" t="n"/>
+      <c r="K103" s="6" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="5" t="n"/>
-      <c r="B104" s="5" t="inlineStr">
+      <c r="A104" s="6" t="n"/>
+      <c r="B104" s="6" t="inlineStr">
         <is>
           <t>demo.TbPlayerBagDef</t>
         </is>
       </c>
-      <c r="C104" s="5" t="inlineStr">
+      <c r="C104" s="6" t="inlineStr">
         <is>
           <t>demo.PlayerBagDef</t>
         </is>
       </c>
-      <c r="D104" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E104" s="5" t="inlineStr">
+      <c r="D104" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
         <is>
           <t>player_bag@player_bag.xlsx</t>
         </is>
       </c>
-      <c r="F104" s="5" t="n"/>
-      <c r="G104" s="5" t="n"/>
-      <c r="H104" s="5" t="n"/>
-      <c r="I104" s="5" t="inlineStr">
+      <c r="F104" s="6" t="n"/>
+      <c r="G104" s="6" t="n"/>
+      <c r="H104" s="6" t="n"/>
+      <c r="I104" s="6" t="inlineStr">
         <is>
           <t>玩家背包定义</t>
         </is>
       </c>
-      <c r="J104" s="5" t="n"/>
-      <c r="K104" s="5" t="n"/>
+      <c r="J104" s="6" t="n"/>
+      <c r="K104" s="6" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="5" t="n"/>
-      <c r="B105" s="5" t="inlineStr">
+      <c r="A105" s="6" t="n"/>
+      <c r="B105" s="6" t="inlineStr">
         <is>
           <t>demo.TbWarehouseFilter</t>
         </is>
       </c>
-      <c r="C105" s="5" t="inlineStr">
+      <c r="C105" s="6" t="inlineStr">
         <is>
           <t>demo.WarehouseFilter</t>
         </is>
       </c>
-      <c r="D105" s="5" t="b">
-        <v>1</v>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
+      <c r="D105" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
         <is>
           <t>warehouse_filter@warehouse_filter.xlsx</t>
         </is>
       </c>
-      <c r="F105" s="5" t="n"/>
-      <c r="G105" s="5" t="n"/>
-      <c r="H105" s="5" t="n"/>
-      <c r="I105" s="5" t="inlineStr">
+      <c r="F105" s="6" t="n"/>
+      <c r="G105" s="6" t="n"/>
+      <c r="H105" s="6" t="n"/>
+      <c r="I105" s="6" t="inlineStr">
         <is>
           <t>仓库筛选定义</t>
         </is>
       </c>
-      <c r="J105" s="5" t="n"/>
-      <c r="K105" s="5" t="n"/>
+      <c r="J105" s="6" t="n"/>
+      <c r="K105" s="6" t="n"/>
     </row>
     <row r="106">
-      <c r="B106" s="5" t="n"/>
-      <c r="C106" s="5" t="n"/>
-      <c r="D106" s="5" t="n"/>
-      <c r="E106" s="5" t="n"/>
-      <c r="I106" s="5" t="n"/>
+      <c r="A106" s="6" t="n"/>
+      <c r="B106" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbCharacterGiftRule</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>demo.CharacterGiftRule</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E106" s="6" t="inlineStr">
+        <is>
+          <t>character_gift_rule@character.xlsx</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H106" s="6" t="n"/>
+      <c r="I106" s="6" t="inlineStr">
+        <is>
+          <t>角色礼物固定覆盖规则</t>
+        </is>
+      </c>
+      <c r="J106" s="6" t="n"/>
+      <c r="K106" s="6" t="n"/>
+    </row>
+    <row r="107">
+      <c r="B107" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbTalentTree</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>demo.TalentTree</t>
+        </is>
+      </c>
+      <c r="D107" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E107" s="6" t="inlineStr">
+        <is>
+          <t>talent_tree@talent.xlsx</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="inlineStr">
+        <is>
+          <t>tree_id</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I107" s="6" t="inlineStr">
+        <is>
+          <t>天赋树定义</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="B108" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbSecretBaseCharacterOption</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>demo.SecretBaseCharacterOption</t>
+        </is>
+      </c>
+      <c r="D108" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>secret_base_character_option@secret_base_character.xlsx</t>
+        </is>
+      </c>
+      <c r="F108" s="6" t="inlineStr">
+        <is>
+          <t>option_id</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>秘密据点角色自定义选项</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="B109" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbHumanCivilizationLevel</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>demo.HumanCivilizationLevel</t>
+        </is>
+      </c>
+      <c r="D109" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E109" s="6" t="inlineStr">
+        <is>
+          <t>civilization_level@human_civilization.xlsx</t>
+        </is>
+      </c>
+      <c r="F109" s="6" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="B110" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbHumanTechTree</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>demo.HumanTechTree</t>
+        </is>
+      </c>
+      <c r="D110" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E110" s="6" t="inlineStr">
+        <is>
+          <t>human_tech_tree@human_tech.xlsx</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>tree_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="B111" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbHumanTechNode</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>demo.HumanTechNode</t>
+        </is>
+      </c>
+      <c r="D111" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E111" s="6" t="inlineStr">
+        <is>
+          <t>human_tech@human_tech.xlsx</t>
+        </is>
+      </c>
+      <c r="F111" s="6" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="B112" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbHumanTechNodeLevel</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>demo.HumanTechNodeLevel</t>
+        </is>
+      </c>
+      <c r="D112" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E112" s="6" t="inlineStr">
+        <is>
+          <t>human_tech_level@human_tech.xlsx</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>node_id+level</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -359,7 +359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K120"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -550,7 +550,7 @@
       <c r="D5" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="E5" s="3" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>logic_area_info@map.xlsx</t>
         </is>
@@ -590,7 +590,7 @@
       <c r="D7" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="3" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>area_variant_info@map.xlsx</t>
         </is>
@@ -610,7 +610,7 @@
       <c r="D8" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="4" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>area_overlay_state_info@map.xlsx</t>
         </is>
@@ -760,7 +760,7 @@
       <c r="D15" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="E15" s="3" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>unit_npc_attribute@unit_npc.xlsx</t>
         </is>
@@ -780,18 +780,13 @@
       <c r="D16" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>desire_density_info@unit_npc.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="E17" s="6" t="n"/>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
@@ -875,12 +870,12 @@
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>demo.TbQuestInteractDialog</t>
+          <t>demo.TbDialogMetaInfo</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>demo.QuestInteractDialogData</t>
+          <t>demo.DialogMetaInfo</t>
         </is>
       </c>
       <c r="D22" s="6" t="b">
@@ -888,19 +883,19 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>quest_interact_dialog@dialog.xlsx</t>
+          <t>dialog_meta_info@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>demo.TbDialogMetaInfo</t>
+          <t>demo.TbItemData</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>demo.DialogMetaInfo</t>
+          <t>demo.ItemData</t>
         </is>
       </c>
       <c r="D23" s="6" t="b">
@@ -908,19 +903,19 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>dialog_meta_info@dialog.xlsx</t>
+          <t>item@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>demo.TbItemData</t>
+          <t>demo.TbShop</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>demo.ItemData</t>
+          <t>demo.Shop</t>
         </is>
       </c>
       <c r="D24" s="6" t="b">
@@ -928,19 +923,19 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>item@item.xlsx</t>
+          <t>shop@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>demo.TbShop</t>
+          <t>demo.TbShopGoods</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>demo.Shop</t>
+          <t>demo.ShopGoods</t>
         </is>
       </c>
       <c r="D25" s="6" t="b">
@@ -948,19 +943,19 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>shop@shop.xlsx</t>
+          <t>shop_goods@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>demo.TbShopGoods</t>
+          <t>demo.TbItemUse</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>demo.ShopGoods</t>
+          <t>demo.ItemUse</t>
         </is>
       </c>
       <c r="D26" s="6" t="b">
@@ -968,19 +963,19 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>shop_goods@shop.xlsx</t>
+          <t>item_use@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>demo.TbItemUse</t>
+          <t>demo.TbItemGift</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>demo.ItemUse</t>
+          <t>demo.ItemGift</t>
         </is>
       </c>
       <c r="D27" s="6" t="b">
@@ -988,19 +983,29 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>item_use@item.xlsx</t>
+          <t>item_gift@item.xlsx</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>demo.TbItemGift</t>
+          <t>demo.TbNpcDialogInfo</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>demo.ItemGift</t>
+          <t>demo.NpcDialogInfo</t>
         </is>
       </c>
       <c r="D28" s="6" t="b">
@@ -1008,29 +1013,19 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>item_gift@item.xlsx</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
+          <t>npc_dialog_info@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>demo.TbNpcDialogInfo</t>
+          <t>demo.TbWorldMapGlobal</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>demo.NpcDialogInfo</t>
+          <t>demo.WorldMapGlobal</t>
         </is>
       </c>
       <c r="D29" s="6" t="b">
@@ -1038,19 +1033,24 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>npc_dialog_info@dialog.xlsx</t>
+          <t>world_map_global@map.xlsx</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>one</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWorldMapGlobal</t>
+          <t>demo.TbWorldMapBigMapLayer</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>demo.WorldMapGlobal</t>
+          <t>demo.WorldMapBigMapLayer</t>
         </is>
       </c>
       <c r="D30" s="6" t="b">
@@ -1058,24 +1058,24 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>world_map_global@map.xlsx</t>
+          <t>world_map_big_map@map.xlsx</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>one</t>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWorldMapBigMapLayer</t>
+          <t>demo.TbDreamInfiltrationSpot</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>demo.WorldMapBigMapLayer</t>
+          <t>demo.DreamInfiltrationSpot</t>
         </is>
       </c>
       <c r="D31" s="6" t="b">
@@ -1083,24 +1083,19 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>world_map_big_map@map.xlsx</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>dream_infiltration@dream_infiltration.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>demo.TbDreamInfiltrationSpot</t>
+          <t>demo.TbCharDreamEntryInfo</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>demo.DreamInfiltrationSpot</t>
+          <t>demo.CharDreamEntryInfo</t>
         </is>
       </c>
       <c r="D32" s="6" t="b">
@@ -1108,19 +1103,19 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>dream_infiltration@dream_infiltration.xlsx</t>
+          <t>char_dream_entry@dream_infiltration.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>demo.TbCharDreamEntryInfo</t>
+          <t>demo.TbFishingSpot</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>demo.CharDreamEntryInfo</t>
+          <t>demo.FishingSpot</t>
         </is>
       </c>
       <c r="D33" s="6" t="b">
@@ -1128,19 +1123,19 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>char_dream_entry@dream_infiltration.xlsx</t>
+          <t>fishing_spot@fishing_spot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>demo.TbFishingSpot</t>
+          <t>demo.TbFishingSpotFish</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>demo.FishingSpot</t>
+          <t>demo.FishingSpotFish</t>
         </is>
       </c>
       <c r="D34" s="6" t="b">
@@ -1148,40 +1143,40 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>fishing_spot@fishing_spot.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbFishingSpotFish</t>
-        </is>
-      </c>
-      <c r="C35" s="6" t="inlineStr">
-        <is>
-          <t>demo.FishingSpotFish</t>
-        </is>
-      </c>
-      <c r="D35" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
-        <is>
           <t>fishing_spot_fish@fishing_spot.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="36"/>
+    <row r="35"/>
+    <row r="36">
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbPlayerDesireLevel</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>demo.PlayerDesireLevel</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="6" t="inlineStr">
+        <is>
+          <t>player_desire_level@player_status.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="37">
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerDesireLevel</t>
+          <t>demo.TbPlayerJingYuLevel</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerDesireLevel</t>
+          <t>demo.PlayerJingYuLevel</t>
         </is>
       </c>
       <c r="D37" s="6" t="b">
@@ -1189,19 +1184,19 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>player_desire_level@player_status.xlsx</t>
+          <t>player_jingyu_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerJingYuLevel</t>
+          <t>demo.TbPlayerSanCorruptLevel</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerJingYuLevel</t>
+          <t>demo.PlayerSanCorruptLevel</t>
         </is>
       </c>
       <c r="D38" s="6" t="b">
@@ -1209,19 +1204,19 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>player_jingyu_level@player_status.xlsx</t>
+          <t>player_san_corrupt_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerSanCorruptLevel</t>
+          <t>demo.TbPlayerClothesExposeInfo</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerSanCorruptLevel</t>
+          <t>demo.PlayerClothesExposeInfo</t>
         </is>
       </c>
       <c r="D39" s="6" t="b">
@@ -1229,40 +1224,40 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>player_san_corrupt_level@player_status.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbPlayerClothesExposeInfo</t>
-        </is>
-      </c>
-      <c r="C40" s="6" t="inlineStr">
-        <is>
-          <t>demo.PlayerClothesExposeInfo</t>
-        </is>
-      </c>
-      <c r="D40" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
           <t>player_clothes_expose_info@player_status.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="41"/>
+    <row r="40"/>
+    <row r="41">
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbWantedLevelInfo</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>demo.WantedLevelInfo</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="6" t="inlineStr">
+        <is>
+          <t>wanted_level_info@wanted.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWantedLevelInfo</t>
+          <t>demo.TbWantedBehaveInfo</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>demo.WantedLevelInfo</t>
+          <t>demo.WantedBehaveInfo</t>
         </is>
       </c>
       <c r="D42" s="6" t="b">
@@ -1270,19 +1265,19 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>wanted_level_info@wanted.xlsx</t>
+          <t>wanted_behave_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWantedBehaveInfo</t>
+          <t>demo.TbTalentNode</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>demo.WantedBehaveInfo</t>
+          <t>demo.TalentNode</t>
         </is>
       </c>
       <c r="D43" s="6" t="b">
@@ -1290,19 +1285,29 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>wanted_behave_info@wanted.xlsx</t>
+          <t>talent@talent.xlsx</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>demo.TbTalentNode</t>
+          <t>demo.TbWantedGuardSpawnTier</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>demo.TalentNode</t>
+          <t>demo.WantedGuardSpawnTier</t>
         </is>
       </c>
       <c r="D44" s="6" t="b">
@@ -1310,29 +1315,19 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>talent@talent.xlsx</t>
-        </is>
-      </c>
-      <c r="F44" s="6" t="inlineStr">
-        <is>
-          <t>node_id</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
+          <t>wanted_guard_spawn@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWantedGuardSpawnTier</t>
+          <t>demo.TbEntitySkillData</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>demo.WantedGuardSpawnTier</t>
+          <t>demo.EntitySkillData</t>
         </is>
       </c>
       <c r="D45" s="6" t="b">
@@ -1340,19 +1335,19 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>wanted_guard_spawn@wanted.xlsx</t>
+          <t>entity_skill@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>demo.TbEntitySkillData</t>
+          <t>demo.TbSkillSchool</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>demo.EntitySkillData</t>
+          <t>demo.SkillSchool</t>
         </is>
       </c>
       <c r="D46" s="6" t="b">
@@ -1360,19 +1355,19 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>entity_skill@skill.xlsx</t>
+          <t>skill_school@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSkillSchool</t>
+          <t>demo.TbSkillLearnEntry</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>demo.SkillSchool</t>
+          <t>demo.SkillLearnEntry</t>
         </is>
       </c>
       <c r="D47" s="6" t="b">
@@ -1380,19 +1375,19 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>skill_school@skill.xlsx</t>
+          <t>skill_learn@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSkillLearnEntry</t>
+          <t>demo.TbDesireCrystalDef</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>demo.SkillLearnEntry</t>
+          <t>demo.DesireCrystalDef</t>
         </is>
       </c>
       <c r="D48" s="6" t="b">
@@ -1400,19 +1395,19 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>skill_learn@skill.xlsx</t>
+          <t>desire_crystal_def@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>demo.TbDesireCrystalDef</t>
+          <t>demo.TbMapDesireCrystalBudget</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>demo.DesireCrystalDef</t>
+          <t>demo.MapDesireCrystalBudget</t>
         </is>
       </c>
       <c r="D49" s="6" t="b">
@@ -1420,19 +1415,19 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>desire_crystal_def@desire_crystal.xlsx</t>
+          <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMapDesireCrystalBudget</t>
+          <t>demo.TbMapWalkerDesireCrystalQuota</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>demo.MapDesireCrystalBudget</t>
+          <t>demo.MapWalkerDesireCrystalQuota</t>
         </is>
       </c>
       <c r="D50" s="6" t="b">
@@ -1440,19 +1435,19 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
+          <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMapWalkerDesireCrystalQuota</t>
+          <t>demo.TbNamedNpcDesireCrystal</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>demo.MapWalkerDesireCrystalQuota</t>
+          <t>demo.NamedNpcDesireCrystal</t>
         </is>
       </c>
       <c r="D51" s="6" t="b">
@@ -1460,19 +1455,19 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
+          <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>demo.TbNamedNpcDesireCrystal</t>
+          <t>demo.TbSpiritMonsterTypeBudget</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>demo.NamedNpcDesireCrystal</t>
+          <t>demo.SpiritMonsterTypeBudget</t>
         </is>
       </c>
       <c r="D52" s="6" t="b">
@@ -1480,19 +1475,19 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
+          <t>spirit_monster_budget@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSpiritMonsterTypeBudget</t>
+          <t>demo.TbContainerItemStackOverride</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>demo.SpiritMonsterTypeBudget</t>
+          <t>demo.ContainerItemStackOverride</t>
         </is>
       </c>
       <c r="D53" s="6" t="b">
@@ -1500,19 +1495,19 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>spirit_monster_budget@player_status.xlsx</t>
+          <t>container_item_stack_override@container_stack.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>demo.TbContainerItemStackOverride</t>
+          <t>demo.TbContainerStackTagRule</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>demo.ContainerItemStackOverride</t>
+          <t>demo.ContainerStackTagRule</t>
         </is>
       </c>
       <c r="D54" s="6" t="b">
@@ -1520,19 +1515,19 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>container_item_stack_override@container_stack.xlsx</t>
+          <t>container_stack_tag_rule@container_stack.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>demo.TbContainerStackTagRule</t>
+          <t>demo.TbMapAreaEffect</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>demo.ContainerStackTagRule</t>
+          <t>demo.MapAreaEffect</t>
         </is>
       </c>
       <c r="D55" s="6" t="b">
@@ -1540,40 +1535,40 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>container_stack_tag_rule@container_stack.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbMapAreaEffect</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>demo.MapAreaEffect</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
           <t>map_area_effect@map_area_effect.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="57"/>
+    <row r="56"/>
+    <row r="57">
+      <c r="B57" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbFallenAmountProgressInfo</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>demo.FallenAmountProgressInfo</t>
+        </is>
+      </c>
+      <c r="D57" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="6" t="inlineStr">
+        <is>
+          <t>fallen_amount_progress_info@fallen_amount_progress_info.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>demo.TbFallenAmountProgressInfo</t>
+          <t>demo.TbRumorIntel</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>demo.FallenAmountProgressInfo</t>
+          <t>demo.RumorIntel</t>
         </is>
       </c>
       <c r="D58" s="6" t="b">
@@ -1581,19 +1576,19 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>fallen_amount_progress_info@fallen_amount_progress_info.xlsx</t>
+          <t>rumor_intel@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRumorIntel</t>
+          <t>demo.TbRumorRandomPool</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>demo.RumorIntel</t>
+          <t>demo.RumorRandomPool</t>
         </is>
       </c>
       <c r="D59" s="6" t="b">
@@ -1601,19 +1596,19 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>rumor_intel@rumor_tables.xlsx</t>
+          <t>rumor_random_pool@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRumorRandomPool</t>
+          <t>demo.TbRumorGlobal</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>demo.RumorRandomPool</t>
+          <t>demo.RumorGlobal</t>
         </is>
       </c>
       <c r="D60" s="6" t="b">
@@ -1621,40 +1616,40 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>rumor_random_pool@rumor_tables.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="B61" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbRumorGlobal</t>
-        </is>
-      </c>
-      <c r="C61" s="6" t="inlineStr">
-        <is>
-          <t>demo.RumorGlobal</t>
-        </is>
-      </c>
-      <c r="D61" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
           <t>rumor_global@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="62"/>
+    <row r="61"/>
+    <row r="62">
+      <c r="B62" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbCharacterInfo</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>demo.CharacterInfo</t>
+        </is>
+      </c>
+      <c r="D62" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" s="6" t="inlineStr">
+        <is>
+          <t>character_info@character.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>demo.TbCharacterInfo</t>
+          <t>demo.TbCharacterFavorInfo</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>demo.CharacterInfo</t>
+          <t>demo.CharacterFavorInfo</t>
         </is>
       </c>
       <c r="D63" s="6" t="b">
@@ -1662,19 +1657,19 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>character_info@character.xlsx</t>
+          <t>character_favor_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>demo.TbCharacterFavorInfo</t>
+          <t>demo.TbMicroPlotDef</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>demo.CharacterFavorInfo</t>
+          <t>demo.MicroPlotDef</t>
         </is>
       </c>
       <c r="D64" s="6" t="b">
@@ -1682,19 +1677,19 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>character_favor_info@character.xlsx</t>
+          <t>micro_plot_def@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMicroPlotDef</t>
+          <t>demo.TbMapMicroPlotTrigger</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>demo.MicroPlotDef</t>
+          <t>demo.MapMicroPlotTrigger</t>
         </is>
       </c>
       <c r="D65" s="6" t="b">
@@ -1702,19 +1697,19 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>micro_plot_def@micro_plot.xlsx</t>
+          <t>map_micro_plot_trigger@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMapMicroPlotTrigger</t>
+          <t>demo.TbMicroPlotTimelineEvent</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>demo.MapMicroPlotTrigger</t>
+          <t>demo.MicroPlotTimelineEvent</t>
         </is>
       </c>
       <c r="D66" s="6" t="b">
@@ -1722,40 +1717,40 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>map_micro_plot_trigger@micro_plot.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="B67" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbMicroPlotTimelineEvent</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>demo.MicroPlotTimelineEvent</t>
-        </is>
-      </c>
-      <c r="D67" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
-        <is>
           <t>micro_plot_timeline_event@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="68"/>
+    <row r="67"/>
+    <row r="68">
+      <c r="B68" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbTrapSpec</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>demo.TrapSpec</t>
+        </is>
+      </c>
+      <c r="D68" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" s="6" t="inlineStr">
+        <is>
+          <t>trap_spec@trap_spec.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>demo.TbTrapSpec</t>
+          <t>demo.TbForgeRecipe</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>demo.TrapSpec</t>
+          <t>demo.ForgeRecipe</t>
         </is>
       </c>
       <c r="D69" s="6" t="b">
@@ -1763,40 +1758,40 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>trap_spec@trap_spec.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="B70" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbForgeRecipe</t>
-        </is>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>demo.ForgeRecipe</t>
-        </is>
-      </c>
-      <c r="D70" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
-        <is>
           <t>forge_recipe@forge_recipe.xlsx</t>
         </is>
       </c>
     </row>
-    <row r="71"/>
+    <row r="70"/>
+    <row r="71">
+      <c r="B71" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbHActInfo</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>demo.HActInfo</t>
+        </is>
+      </c>
+      <c r="D71" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" s="6" t="inlineStr">
+        <is>
+          <t>h_act_info@h_act_info.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="72">
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHActInfo</t>
+          <t>demo.TbTalentNodeLevel</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>demo.HActInfo</t>
+          <t>demo.TalentNodeLevel</t>
         </is>
       </c>
       <c r="D72" s="6" t="b">
@@ -1804,19 +1799,29 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>h_act_info@h_act_info.xlsx</t>
+          <t>talent_level@talent.xlsx</t>
+        </is>
+      </c>
+      <c r="F72" s="6" t="inlineStr">
+        <is>
+          <t>node_id+level</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>demo.TbTalentNodeLevel</t>
+          <t>demo.TbSavePoint</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>demo.TalentNodeLevel</t>
+          <t>demo.SavePoint</t>
         </is>
       </c>
       <c r="D73" s="6" t="b">
@@ -1824,29 +1829,19 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>talent_level@talent.xlsx</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>node_id+level</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>save_point@save_point.xlsx</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSavePoint</t>
+          <t>demo.TbReviveRule</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>demo.SavePoint</t>
+          <t>demo.ReviveRule</t>
         </is>
       </c>
       <c r="D74" s="6" t="b">
@@ -1854,19 +1849,24 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>save_point@save_point.xlsx</t>
+          <t>revive_rule@revive_rule.xlsx</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>demo.TbReviveRule</t>
+          <t>demo.TbDesireDensityTier</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>demo.ReviveRule</t>
+          <t>demo.DesireDensityTier</t>
         </is>
       </c>
       <c r="D75" s="6" t="b">
@@ -1874,24 +1874,19 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>revive_rule@revive_rule.xlsx</t>
-        </is>
-      </c>
-      <c r="G75" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>desire_density_tier@desire_density_tier.xlsx</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>demo.TbDesireDensityTier</t>
+          <t>demo.TbMindFragmentPoolEntry</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>demo.DesireDensityTier</t>
+          <t>demo.MindFragmentPoolEntry</t>
         </is>
       </c>
       <c r="D76" s="6" t="b">
@@ -1899,19 +1894,24 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>desire_density_tier@desire_density_tier.xlsx</t>
+          <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMindFragmentPoolEntry</t>
+          <t>demo.TbSecretBaseFacility</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>demo.MindFragmentPoolEntry</t>
+          <t>demo.SecretBaseFacility</t>
         </is>
       </c>
       <c r="D77" s="6" t="b">
@@ -1919,24 +1919,24 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
-        </is>
-      </c>
-      <c r="G77" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>secret_base_facility@secret_base_facility.xlsx</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="inlineStr">
+        <is>
+          <t>据点固定设施</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSecretBaseFacility</t>
+          <t>demo.TbSecretBaseBuildLevel</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>demo.SecretBaseFacility</t>
+          <t>demo.SecretBaseBuildLevel</t>
         </is>
       </c>
       <c r="D78" s="6" t="b">
@@ -1944,60 +1944,70 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>secret_base_facility@secret_base_facility.xlsx</t>
+          <t>secret_base_build_level@secret_base_build_level.xlsx</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
       <c r="I78" s="6" t="inlineStr">
         <is>
-          <t>据点固定设施</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="B79" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbSecretBaseBuildLevel</t>
-        </is>
-      </c>
-      <c r="C79" s="6" t="inlineStr">
-        <is>
-          <t>demo.SecretBaseBuildLevel</t>
-        </is>
-      </c>
-      <c r="D79" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
-        <is>
-          <t>secret_base_build_level@secret_base_build_level.xlsx</t>
-        </is>
-      </c>
-      <c r="F79" s="6" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
+          <t>据点建设等级卷轴边界</t>
+        </is>
+      </c>
+    </row>
+    <row r="79"/>
+    <row r="80">
+      <c r="B80" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbSecretBaseCharacter</t>
+        </is>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>demo.SecretBaseCharacter</t>
+        </is>
+      </c>
+      <c r="D80" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" s="6" t="inlineStr">
+        <is>
+          <t>secret_base_character@secret_base_character.xlsx</t>
+        </is>
+      </c>
+      <c r="F80" s="6" t="inlineStr">
+        <is>
+          <t>slot_id</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I79" s="6" t="inlineStr">
-        <is>
-          <t>据点建设等级卷轴边界</t>
-        </is>
-      </c>
-    </row>
-    <row r="80"/>
+      <c r="I80" s="6" t="inlineStr">
+        <is>
+          <t>秘密据点角色</t>
+        </is>
+      </c>
+    </row>
     <row r="81">
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSecretBaseCharacter</t>
+          <t>demo.TbHumanWeapon</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>demo.SecretBaseCharacter</t>
+          <t>demo.HumanWeapon</t>
         </is>
       </c>
       <c r="D81" s="6" t="b">
@@ -2005,12 +2015,12 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>secret_base_character@secret_base_character.xlsx</t>
+          <t>human_weapon@human_weapon.xlsx</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>slot_id</t>
+          <t>item_id</t>
         </is>
       </c>
       <c r="G81" s="6" t="inlineStr">
@@ -2020,19 +2030,19 @@
       </c>
       <c r="I81" s="6" t="inlineStr">
         <is>
-          <t>秘密据点角色</t>
+          <t>human_weapon</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHumanWeapon</t>
+          <t>demo.TbRuneData</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>demo.HumanWeapon</t>
+          <t>demo.RuneData</t>
         </is>
       </c>
       <c r="D82" s="6" t="b">
@@ -2040,34 +2050,19 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>human_weapon@human_weapon.xlsx</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="inlineStr">
-        <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I82" s="6" t="inlineStr">
-        <is>
-          <t>human_weapon</t>
+          <t>rune_data@rune.xlsx</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRuneData</t>
+          <t>demo.TbBodyPartDef</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>demo.RuneData</t>
+          <t>demo.BodyPartDef</t>
         </is>
       </c>
       <c r="D83" s="6" t="b">
@@ -2075,19 +2070,19 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>rune_data@rune.xlsx</t>
+          <t>body_part_def@body_part.xlsx</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>demo.TbBodyPartDef</t>
+          <t>demo.TbBodyPartLevel</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>demo.BodyPartDef</t>
+          <t>demo.BodyPartLevel</t>
         </is>
       </c>
       <c r="D84" s="6" t="b">
@@ -2095,71 +2090,69 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>body_part_def@body_part.xlsx</t>
+          <t>body_part_level@body_part.xlsx</t>
+        </is>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>part_id+level</t>
+        </is>
+      </c>
+      <c r="G84" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>demo.TbBodyPartLevel</t>
+          <t>demo.TbBodyPartProgressInfo</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>demo.BodyPartLevel</t>
+          <t>demo.BodyPartProgressInfo</t>
         </is>
       </c>
       <c r="D85" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>body_part_level@body_part.xlsx</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>part_id+level</t>
-        </is>
-      </c>
-      <c r="G85" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
+      <c r="E85" s="6" t="inlineStr">
+        <is>
+          <t>body_part_progress_info@body_part.xlsx</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>demo.TbBodyPartProgressInfo</t>
+          <t>demo.TbPartLocalAttrDef</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>demo.BodyPartProgressInfo</t>
+          <t>demo.PartLocalAttrDef</t>
         </is>
       </c>
       <c r="D86" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="E86" s="3" t="inlineStr">
-        <is>
-          <t>body_part_progress_info@body_part.xlsx</t>
-        </is>
-      </c>
-      <c r="F86" s="6" t="n"/>
-      <c r="G86" s="6" t="n"/>
+      <c r="E86" s="6" t="inlineStr">
+        <is>
+          <t>part_local_attr_def@body_part.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPartLocalAttrDef</t>
+          <t>demo.TbPartGear</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>demo.PartLocalAttrDef</t>
+          <t>demo.PartGear</t>
         </is>
       </c>
       <c r="D87" s="6" t="b">
@@ -2167,19 +2160,29 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>part_local_attr_def@body_part.xlsx</t>
+          <t>partgear@partgear.xlsx</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G87" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPartGear</t>
+          <t>demo.TbRuneUpgradeInfo</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>demo.PartGear</t>
+          <t>demo.RuneUpgradeInfo</t>
         </is>
       </c>
       <c r="D88" s="6" t="b">
@@ -2187,29 +2190,29 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>partgear@partgear.xlsx</t>
+          <t>rune_upgrade_info@rune.xlsx</t>
         </is>
       </c>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G88" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
+          <t>upgrade_id</t>
+        </is>
+      </c>
+      <c r="J88" s="6" t="inlineStr">
+        <is>
+          <t>符文升级项</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRuneUpgradeInfo</t>
+          <t>demo.TbRuneEquipSlot</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>demo.RuneUpgradeInfo</t>
+          <t>demo.RuneEquipSlotInfo</t>
         </is>
       </c>
       <c r="D89" s="6" t="b">
@@ -2217,29 +2220,29 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>rune_upgrade_info@rune.xlsx</t>
+          <t>rune_equip_slot@rune.xlsx</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>upgrade_id</t>
+          <t>equip_slot</t>
         </is>
       </c>
       <c r="J89" s="6" t="inlineStr">
         <is>
-          <t>符文升级项</t>
+          <t>符文装配槽</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRuneEquipSlot</t>
+          <t>demo.TbEntitySkillLevel</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>demo.RuneEquipSlotInfo</t>
+          <t>demo.EntitySkillLevel</t>
         </is>
       </c>
       <c r="D90" s="6" t="b">
@@ -2247,29 +2250,29 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>rune_equip_slot@rune.xlsx</t>
+          <t>skill_level@skill.xlsx</t>
         </is>
       </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>equip_slot</t>
-        </is>
-      </c>
-      <c r="J90" s="6" t="inlineStr">
-        <is>
-          <t>符文装配槽</t>
+          <t>skill_id+level</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>demo.TbEntitySkillLevel</t>
+          <t>demo.TbHomesteadBuilding</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>demo.EntitySkillLevel</t>
+          <t>demo.HomesteadBuilding</t>
         </is>
       </c>
       <c r="D91" s="6" t="b">
@@ -2277,29 +2280,34 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>skill_level@skill.xlsx</t>
+          <t>homestead_building@map_homestead.xlsx</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>skill_id+level</t>
+          <t>logic_area_id+building_id</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
           <t>list</t>
+        </is>
+      </c>
+      <c r="I91" s="6" t="inlineStr">
+        <is>
+          <t>逻辑区域可管理建筑</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHomesteadBuilding</t>
+          <t>demo.TbHomesteadBuildingUpgrade</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>demo.HomesteadBuilding</t>
+          <t>demo.HomesteadBuildingUpgrade</t>
         </is>
       </c>
       <c r="D92" s="6" t="b">
@@ -2307,12 +2315,12 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>homestead_building@map_homestead.xlsx</t>
+          <t>homestead_building_upgrade@map_homestead.xlsx</t>
         </is>
       </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>logic_area_id+building_id</t>
+          <t>logic_area_id+building_id+level</t>
         </is>
       </c>
       <c r="G92" s="6" t="inlineStr">
@@ -2322,19 +2330,19 @@
       </c>
       <c r="I92" s="6" t="inlineStr">
         <is>
-          <t>逻辑区域可管理建筑</t>
+          <t>家园建筑升级项</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHomesteadBuildingUpgrade</t>
+          <t>demo.TbJingYuanCodexDef</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>demo.HomesteadBuildingUpgrade</t>
+          <t>demo.JingYuanCodexDef</t>
         </is>
       </c>
       <c r="D93" s="6" t="b">
@@ -2342,34 +2350,24 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>homestead_building_upgrade@map_homestead.xlsx</t>
+          <t>jingyuan_codex_def@jingyuan_codex.xlsx</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>logic_area_id+building_id+level</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>家园建筑升级项</t>
+          <t>codex_id</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanCodexDef</t>
+          <t>demo.TbJingYuanCodexLevel</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>demo.JingYuanCodexDef</t>
+          <t>demo.JingYuanCodexLevel</t>
         </is>
       </c>
       <c r="D94" s="6" t="b">
@@ -2377,24 +2375,29 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>jingyuan_codex_def@jingyuan_codex.xlsx</t>
+          <t>jingyuan_codex_level@jingyuan_codex.xlsx</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>codex_id</t>
+          <t>codex_id+level</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanCodexLevel</t>
+          <t>demo.TbJingYuanTuneTier</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>demo.JingYuanCodexLevel</t>
+          <t>demo.JingYuanTuneTier</t>
         </is>
       </c>
       <c r="D95" s="6" t="b">
@@ -2402,12 +2405,12 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>jingyuan_codex_level@jingyuan_codex.xlsx</t>
+          <t>jingyuan_tune_tier@jingyuan_codex.xlsx</t>
         </is>
       </c>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>codex_id+level</t>
+          <t>codex_id+tier</t>
         </is>
       </c>
       <c r="G95" s="6" t="inlineStr">
@@ -2419,12 +2422,12 @@
     <row r="96">
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanTuneTier</t>
+          <t>demo.TbTiaoJingConcentrationLevel</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>demo.JingYuanTuneTier</t>
+          <t>demo.TiaoJingConcentrationLevel</t>
         </is>
       </c>
       <c r="D96" s="6" t="b">
@@ -2432,29 +2435,19 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>jingyuan_tune_tier@jingyuan_codex.xlsx</t>
-        </is>
-      </c>
-      <c r="F96" s="6" t="inlineStr">
-        <is>
-          <t>codex_id+tier</t>
-        </is>
-      </c>
-      <c r="G96" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>tiao_jing_concentration_level@jingyuan_codex.xlsx</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>demo.TbTiaoJingConcentrationLevel</t>
+          <t>demo.TbJingYuanTypeDef</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>demo.TiaoJingConcentrationLevel</t>
+          <t>demo.JingYuanTypeDef</t>
         </is>
       </c>
       <c r="D97" s="6" t="b">
@@ -2462,19 +2455,24 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>tiao_jing_concentration_level@jingyuan_codex.xlsx</t>
+          <t>jingyuan_type_def@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F97" s="6" t="inlineStr">
+        <is>
+          <t>type_id</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanTypeDef</t>
+          <t>demo.TbJingYuanTypePoolEntry</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>demo.JingYuanTypeDef</t>
+          <t>demo.JingYuanTypePoolEntry</t>
         </is>
       </c>
       <c r="D98" s="6" t="b">
@@ -2482,24 +2480,24 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>jingyuan_type_def@jingyuan_codex.xlsx</t>
-        </is>
-      </c>
-      <c r="F98" s="6" t="inlineStr">
-        <is>
-          <t>type_id</t>
+          <t>jingyuan_type_pool@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanTypePoolEntry</t>
+          <t>demo.TbProgressionHubTab</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>demo.JingYuanTypePoolEntry</t>
+          <t>demo.ProgressionHubTabDef</t>
         </is>
       </c>
       <c r="D99" s="6" t="b">
@@ -2507,24 +2505,34 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>jingyuan_type_pool@jingyuan_codex.xlsx</t>
+          <t>progression_hub_tab@progression_hub_tab.xlsx</t>
+        </is>
+      </c>
+      <c r="F99" s="6" t="inlineStr">
+        <is>
+          <t>tab_id</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I99" s="6" t="inlineStr">
+        <is>
+          <t>养成总面板选项卡</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>demo.TbProgressionHubTab</t>
+          <t>demo.TbPlayerAttachInfo</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>demo.ProgressionHubTabDef</t>
+          <t>demo.PlayerAttachInfo</t>
         </is>
       </c>
       <c r="D100" s="6" t="b">
@@ -2532,34 +2540,19 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>progression_hub_tab@progression_hub_tab.xlsx</t>
-        </is>
-      </c>
-      <c r="F100" s="6" t="inlineStr">
-        <is>
-          <t>tab_id</t>
-        </is>
-      </c>
-      <c r="G100" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I100" s="6" t="inlineStr">
-        <is>
-          <t>养成总面板选项卡</t>
+          <t>player_attach@player_attach.xlsx</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerAttachInfo</t>
+          <t>demo.TbItemDismantle</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerAttachInfo</t>
+          <t>demo.ItemDismantle</t>
         </is>
       </c>
       <c r="D101" s="6" t="b">
@@ -2567,19 +2560,34 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>player_attach@player_attach.xlsx</t>
+          <t>item_dismantle@item_dismantle.xlsx</t>
+        </is>
+      </c>
+      <c r="F101" s="6" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>物品分解产物配置</t>
         </is>
       </c>
     </row>
     <row r="102" s="2">
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>demo.TbItemDismantle</t>
+          <t>demo.TbItemTagInfo</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>demo.ItemDismantle</t>
+          <t>demo.ItemTagInfo</t>
         </is>
       </c>
       <c r="D102" s="6" t="b">
@@ -2587,136 +2595,119 @@
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>item_dismantle@item_dismantle.xlsx</t>
+          <t>item_tag@item.xlsx</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G102" s="6" t="inlineStr">
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I102" s="6" t="inlineStr">
+        <is>
+          <t>物品标签元数据：显示字、隐藏控制、实例需求</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" s="2">
+      <c r="B103" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbPlayerBagDef</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>demo.PlayerBagDef</t>
+        </is>
+      </c>
+      <c r="D103" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E103" s="6" t="inlineStr">
+        <is>
+          <t>player_bag@player_bag.xlsx</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="inlineStr">
+        <is>
+          <t>玩家背包定义</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="B104" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbWarehouseFilter</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>demo.WarehouseFilter</t>
+        </is>
+      </c>
+      <c r="D104" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>warehouse_filter@warehouse_filter.xlsx</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>仓库筛选定义</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="B105" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbCharacterGiftRule</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>demo.CharacterGiftRule</t>
+        </is>
+      </c>
+      <c r="D105" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E105" s="6" t="inlineStr">
+        <is>
+          <t>character_gift_rule@character.xlsx</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>物品分解产物配置</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" s="2">
-      <c r="A103" s="6" t="n"/>
-      <c r="B103" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbItemTagInfo</t>
-        </is>
-      </c>
-      <c r="C103" s="6" t="inlineStr">
-        <is>
-          <t>demo.ItemTagInfo</t>
-        </is>
-      </c>
-      <c r="D103" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
-        <is>
-          <t>item_tag@item.xlsx</t>
-        </is>
-      </c>
-      <c r="F103" s="6" t="inlineStr">
-        <is>
-          <t>tag</t>
-        </is>
-      </c>
-      <c r="G103" s="6" t="n"/>
-      <c r="H103" s="6" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="I103" s="6" t="inlineStr">
-        <is>
-          <t>物品标签元数据：显示字、隐藏控制、实例需求</t>
-        </is>
-      </c>
-      <c r="J103" s="6" t="n"/>
-      <c r="K103" s="6" t="n"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="6" t="n"/>
-      <c r="B104" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbPlayerBagDef</t>
-        </is>
-      </c>
-      <c r="C104" s="6" t="inlineStr">
-        <is>
-          <t>demo.PlayerBagDef</t>
-        </is>
-      </c>
-      <c r="D104" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E104" s="6" t="inlineStr">
-        <is>
-          <t>player_bag@player_bag.xlsx</t>
-        </is>
-      </c>
-      <c r="F104" s="6" t="n"/>
-      <c r="G104" s="6" t="n"/>
-      <c r="H104" s="6" t="n"/>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>玩家背包定义</t>
-        </is>
-      </c>
-      <c r="J104" s="6" t="n"/>
-      <c r="K104" s="6" t="n"/>
-    </row>
-    <row r="105">
-      <c r="A105" s="6" t="n"/>
-      <c r="B105" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbWarehouseFilter</t>
-        </is>
-      </c>
-      <c r="C105" s="6" t="inlineStr">
-        <is>
-          <t>demo.WarehouseFilter</t>
-        </is>
-      </c>
-      <c r="D105" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
-        <is>
-          <t>warehouse_filter@warehouse_filter.xlsx</t>
-        </is>
-      </c>
-      <c r="F105" s="6" t="n"/>
-      <c r="G105" s="6" t="n"/>
-      <c r="H105" s="6" t="n"/>
       <c r="I105" s="6" t="inlineStr">
         <is>
-          <t>仓库筛选定义</t>
-        </is>
-      </c>
-      <c r="J105" s="6" t="n"/>
-      <c r="K105" s="6" t="n"/>
+          <t>角色礼物固定覆盖规则</t>
+        </is>
+      </c>
     </row>
     <row r="106">
-      <c r="A106" s="6" t="n"/>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>demo.TbCharacterGiftRule</t>
+          <t>demo.TbTalentTree</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>demo.CharacterGiftRule</t>
+          <t>demo.TalentTree</t>
         </is>
       </c>
       <c r="D106" s="6" t="b">
@@ -2724,12 +2715,12 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>character_gift_rule@character.xlsx</t>
+          <t>talent_tree@talent.xlsx</t>
         </is>
       </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>tree_id</t>
         </is>
       </c>
       <c r="G106" s="6" t="inlineStr">
@@ -2737,24 +2728,21 @@
           <t>map</t>
         </is>
       </c>
-      <c r="H106" s="6" t="n"/>
       <c r="I106" s="6" t="inlineStr">
         <is>
-          <t>角色礼物固定覆盖规则</t>
-        </is>
-      </c>
-      <c r="J106" s="6" t="n"/>
-      <c r="K106" s="6" t="n"/>
+          <t>天赋树定义</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>demo.TbTalentTree</t>
+          <t>demo.TbSecretBaseCharacterOption</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>demo.TalentTree</t>
+          <t>demo.SecretBaseCharacterOption</t>
         </is>
       </c>
       <c r="D107" s="6" t="b">
@@ -2762,12 +2750,12 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>talent_tree@talent.xlsx</t>
+          <t>secret_base_character_option@secret_base_character.xlsx</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>tree_id</t>
+          <t>option_id</t>
         </is>
       </c>
       <c r="G107" s="6" t="inlineStr">
@@ -2777,19 +2765,19 @@
       </c>
       <c r="I107" s="6" t="inlineStr">
         <is>
-          <t>天赋树定义</t>
+          <t>秘密据点角色自定义选项</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSecretBaseCharacterOption</t>
+          <t>demo.TbHumanCivilizationLevel</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>demo.SecretBaseCharacterOption</t>
+          <t>demo.HumanCivilizationLevel</t>
         </is>
       </c>
       <c r="D108" s="6" t="b">
@@ -2797,34 +2785,24 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>secret_base_character_option@secret_base_character.xlsx</t>
+          <t>civilization_level@human_civilization.xlsx</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>option_id</t>
-        </is>
-      </c>
-      <c r="G108" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I108" s="6" t="inlineStr">
-        <is>
-          <t>秘密据点角色自定义选项</t>
+          <t>level</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHumanCivilizationLevel</t>
+          <t>demo.TbHumanTechTree</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>demo.HumanCivilizationLevel</t>
+          <t>demo.HumanTechTree</t>
         </is>
       </c>
       <c r="D109" s="6" t="b">
@@ -2832,24 +2810,24 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>civilization_level@human_civilization.xlsx</t>
+          <t>human_tech_tree@human_tech.xlsx</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>tree_id</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHumanTechTree</t>
+          <t>demo.TbHumanTechNode</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>demo.HumanTechTree</t>
+          <t>demo.HumanTechNode</t>
         </is>
       </c>
       <c r="D110" s="6" t="b">
@@ -2857,24 +2835,24 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>human_tech_tree@human_tech.xlsx</t>
+          <t>human_tech@human_tech.xlsx</t>
         </is>
       </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>tree_id</t>
+          <t>node_id</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHumanTechNode</t>
+          <t>demo.TbHumanTechNodeLevel</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>demo.HumanTechNode</t>
+          <t>demo.HumanTechNodeLevel</t>
         </is>
       </c>
       <c r="D111" s="6" t="b">
@@ -2882,24 +2860,24 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>human_tech@human_tech.xlsx</t>
+          <t>human_tech_level@human_tech.xlsx</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>node_id</t>
+          <t>node_id+level</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHumanTechNodeLevel</t>
+          <t>demo.TbQuestAcceptDialog</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>demo.HumanTechNodeLevel</t>
+          <t>demo.QuestAcceptDialog</t>
         </is>
       </c>
       <c r="D112" s="6" t="b">
@@ -2907,25 +2885,201 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>human_tech_level@human_tech.xlsx</t>
-        </is>
-      </c>
-      <c r="F112" s="6" t="inlineStr">
+          <t>quest_accept_dialog@dialog.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbQuestRemindDialog</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>demo.QuestRemindDialog</t>
+        </is>
+      </c>
+      <c r="D113" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E113" s="6" t="inlineStr">
+        <is>
+          <t>quest_remind_dialog@dialog.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbQuestObjectiveDialog</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>demo.QuestObjectiveDialog</t>
+        </is>
+      </c>
+      <c r="D114" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>quest_objective_dialog@dialog.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbNpcRoutineProfile</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>demo.NpcRoutineProfile</t>
+        </is>
+      </c>
+      <c r="D115" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E115" s="6" t="inlineStr">
+        <is>
+          <t>npc_routine_profile@npc_routine.xlsx</t>
+        </is>
+      </c>
+      <c r="F115" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbNpcRoutineRule</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>demo.NpcRoutineRule</t>
+        </is>
+      </c>
+      <c r="D116" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E116" s="6" t="inlineStr">
+        <is>
+          <t>npc_routine_rule@npc_routine.xlsx</t>
+        </is>
+      </c>
+      <c r="F116" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbNpcRoutineBinding</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>demo.NpcRoutineBinding</t>
+        </is>
+      </c>
+      <c r="D117" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E117" s="6" t="inlineStr">
+        <is>
+          <t>npc_routine_binding@npc_routine.xlsx</t>
+        </is>
+      </c>
+      <c r="F117" s="6" t="inlineStr">
+        <is>
+          <t>map_variant+overlay_id+character_key</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbCultTechNode</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>demo.CultTechNode</t>
+        </is>
+      </c>
+      <c r="D118" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E118" s="6" t="inlineStr">
+        <is>
+          <t>cult_tech_node@cult_tech.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbCultTechNodeLevel</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>demo.CultTechNodeLevel</t>
+        </is>
+      </c>
+      <c r="D119" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E119" s="6" t="inlineStr">
+        <is>
+          <t>cult_tech_node_level@cult_tech.xlsx</t>
+        </is>
+      </c>
+      <c r="F119" s="6" t="inlineStr">
         <is>
           <t>node_id+level</t>
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>demo.TbNpcLocomotionProfile</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>demo.NpcLocomotionProfile</t>
+        </is>
+      </c>
+      <c r="D120" t="b">
+        <v>1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>npc_locomotion_profile@npc_routine.xlsx</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E7" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E14" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E15" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E82" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId7"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -359,7 +359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K120"/>
+  <dimension ref="A1:K125"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -786,16 +786,35 @@
         </is>
       </c>
     </row>
-    <row r="17"/>
+    <row r="17">
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbQuestData</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>demo.QuestData</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>quest_data@quests.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>demo.TbQuestData</t>
+          <t>demo.TbQuestStepData</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>demo.QuestData</t>
+          <t>demo.QuestStepData</t>
         </is>
       </c>
       <c r="D18" s="6" t="b">
@@ -803,19 +822,19 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>quest_data@quests.xlsx</t>
+          <t>quest_step_data@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>demo.TbQuestStepData</t>
+          <t>demo.TbQuestStepOutcome</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>demo.QuestStepData</t>
+          <t>demo.QuestStepOutcome</t>
         </is>
       </c>
       <c r="D19" s="6" t="b">
@@ -823,19 +842,19 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>quest_step_data@quests.xlsx</t>
+          <t>quest_step_outcome@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>demo.TbQuestStepOutcome</t>
+          <t>demo.TbQuestStepObjective</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>demo.QuestStepOutcome</t>
+          <t>demo.QuestStepObjective</t>
         </is>
       </c>
       <c r="D20" s="6" t="b">
@@ -843,19 +862,19 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>quest_step_outcome@quests.xlsx</t>
+          <t>quest_step_objective@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>demo.TbQuestStepObjective</t>
+          <t>demo.TbDialogMetaInfo</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>demo.QuestStepObjective</t>
+          <t>demo.DialogMetaInfo</t>
         </is>
       </c>
       <c r="D21" s="6" t="b">
@@ -863,19 +882,19 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>quest_step_objective@quests.xlsx</t>
+          <t>dialog_meta_info@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>demo.TbDialogMetaInfo</t>
+          <t>demo.TbItemData</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>demo.DialogMetaInfo</t>
+          <t>demo.ItemData</t>
         </is>
       </c>
       <c r="D22" s="6" t="b">
@@ -883,19 +902,19 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>dialog_meta_info@dialog.xlsx</t>
+          <t>item@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>demo.TbItemData</t>
+          <t>demo.TbShop</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>demo.ItemData</t>
+          <t>demo.Shop</t>
         </is>
       </c>
       <c r="D23" s="6" t="b">
@@ -903,19 +922,19 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>item@item.xlsx</t>
+          <t>shop@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>demo.TbShop</t>
+          <t>demo.TbShopGoods</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>demo.Shop</t>
+          <t>demo.ShopGoods</t>
         </is>
       </c>
       <c r="D24" s="6" t="b">
@@ -923,19 +942,19 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>shop@shop.xlsx</t>
+          <t>shop_goods@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>demo.TbShopGoods</t>
+          <t>demo.TbItemUse</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>demo.ShopGoods</t>
+          <t>demo.ItemUse</t>
         </is>
       </c>
       <c r="D25" s="6" t="b">
@@ -943,19 +962,19 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>shop_goods@shop.xlsx</t>
+          <t>item_use@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>demo.TbItemUse</t>
+          <t>demo.TbItemGift</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>demo.ItemUse</t>
+          <t>demo.ItemGift</t>
         </is>
       </c>
       <c r="D26" s="6" t="b">
@@ -963,19 +982,29 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>item_use@item.xlsx</t>
+          <t>item_gift@item.xlsx</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>demo.TbItemGift</t>
+          <t>demo.TbNpcDialogInfo</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>demo.ItemGift</t>
+          <t>demo.NpcDialogInfo</t>
         </is>
       </c>
       <c r="D27" s="6" t="b">
@@ -983,29 +1012,21 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>item_gift@item.xlsx</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
+          <t>npc_dialog_info@dialog.xlsx</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n"/>
+      <c r="G27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>demo.TbNpcDialogInfo</t>
+          <t>demo.TbWorldMapGlobal</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>demo.NpcDialogInfo</t>
+          <t>demo.WorldMapGlobal</t>
         </is>
       </c>
       <c r="D28" s="6" t="b">
@@ -1013,19 +1034,24 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>npc_dialog_info@dialog.xlsx</t>
+          <t>world_map_global@map.xlsx</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>one</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWorldMapGlobal</t>
+          <t>demo.TbWorldMapBigMapLayer</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>demo.WorldMapGlobal</t>
+          <t>demo.WorldMapBigMapLayer</t>
         </is>
       </c>
       <c r="D29" s="6" t="b">
@@ -1033,24 +1059,24 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>world_map_global@map.xlsx</t>
+          <t>world_map_big_map@map.xlsx</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>one</t>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWorldMapBigMapLayer</t>
+          <t>demo.TbDreamInfiltrationSpot</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>demo.WorldMapBigMapLayer</t>
+          <t>demo.DreamInfiltrationSpot</t>
         </is>
       </c>
       <c r="D30" s="6" t="b">
@@ -1058,24 +1084,20 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>world_map_big_map@map.xlsx</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
+          <t>dream_infiltration@dream_infiltration.xlsx</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>demo.TbDreamInfiltrationSpot</t>
+          <t>demo.TbCharDreamEntryInfo</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>demo.DreamInfiltrationSpot</t>
+          <t>demo.CharDreamEntryInfo</t>
         </is>
       </c>
       <c r="D31" s="6" t="b">
@@ -1083,19 +1105,19 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>dream_infiltration@dream_infiltration.xlsx</t>
+          <t>char_dream_entry@dream_infiltration.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>demo.TbCharDreamEntryInfo</t>
+          <t>demo.TbFishingSpot</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>demo.CharDreamEntryInfo</t>
+          <t>demo.FishingSpot</t>
         </is>
       </c>
       <c r="D32" s="6" t="b">
@@ -1103,19 +1125,19 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>char_dream_entry@dream_infiltration.xlsx</t>
+          <t>fishing_spot@fishing_spot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>demo.TbFishingSpot</t>
+          <t>demo.TbFishingSpotFish</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>demo.FishingSpot</t>
+          <t>demo.FishingSpotFish</t>
         </is>
       </c>
       <c r="D33" s="6" t="b">
@@ -1123,19 +1145,19 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>fishing_spot@fishing_spot.xlsx</t>
+          <t>fishing_spot_fish@fishing_spot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>demo.TbFishingSpotFish</t>
+          <t>demo.TbPlayerDesireLevel</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>demo.FishingSpotFish</t>
+          <t>demo.PlayerDesireLevel</t>
         </is>
       </c>
       <c r="D34" s="6" t="b">
@@ -1143,20 +1165,39 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>fishing_spot_fish@fishing_spot.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="35"/>
+          <t>player_desire_level@player_status.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbPlayerJingYuLevel</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>demo.PlayerJingYuLevel</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="6" t="inlineStr">
+        <is>
+          <t>player_jingyu_level@player_status.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="36">
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerDesireLevel</t>
+          <t>demo.TbPlayerSanCorruptLevel</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerDesireLevel</t>
+          <t>demo.PlayerSanCorruptLevel</t>
         </is>
       </c>
       <c r="D36" s="6" t="b">
@@ -1164,19 +1205,19 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>player_desire_level@player_status.xlsx</t>
+          <t>player_san_corrupt_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerJingYuLevel</t>
+          <t>demo.TbPlayerClothesExposeInfo</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerJingYuLevel</t>
+          <t>demo.PlayerClothesExposeInfo</t>
         </is>
       </c>
       <c r="D37" s="6" t="b">
@@ -1184,19 +1225,19 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>player_jingyu_level@player_status.xlsx</t>
+          <t>player_clothes_expose_info@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerSanCorruptLevel</t>
+          <t>demo.TbWantedLevelInfo</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerSanCorruptLevel</t>
+          <t>demo.WantedLevelInfo</t>
         </is>
       </c>
       <c r="D38" s="6" t="b">
@@ -1204,19 +1245,19 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>player_san_corrupt_level@player_status.xlsx</t>
+          <t>wanted_level_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerClothesExposeInfo</t>
+          <t>demo.TbWantedBehaveInfo</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerClothesExposeInfo</t>
+          <t>demo.WantedBehaveInfo</t>
         </is>
       </c>
       <c r="D39" s="6" t="b">
@@ -1224,20 +1265,49 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>player_clothes_expose_info@player_status.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="40"/>
+          <t>wanted_behave_info@wanted.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbTalentNode</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>demo.TalentNode</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
+        <is>
+          <t>talent@talent.xlsx</t>
+        </is>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+    </row>
     <row r="41">
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWantedLevelInfo</t>
+          <t>demo.TbWantedGuardSpawnTier</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>demo.WantedLevelInfo</t>
+          <t>demo.WantedGuardSpawnTier</t>
         </is>
       </c>
       <c r="D41" s="6" t="b">
@@ -1245,19 +1315,19 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>wanted_level_info@wanted.xlsx</t>
+          <t>wanted_guard_spawn@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWantedBehaveInfo</t>
+          <t>demo.TbEntitySkillData</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>demo.WantedBehaveInfo</t>
+          <t>demo.EntitySkillData</t>
         </is>
       </c>
       <c r="D42" s="6" t="b">
@@ -1265,19 +1335,19 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>wanted_behave_info@wanted.xlsx</t>
+          <t>entity_skill@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>demo.TbTalentNode</t>
+          <t>demo.TbSkillSchool</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>demo.TalentNode</t>
+          <t>demo.SkillSchool</t>
         </is>
       </c>
       <c r="D43" s="6" t="b">
@@ -1285,29 +1355,21 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>talent@talent.xlsx</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="inlineStr">
-        <is>
-          <t>node_id</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
+          <t>skill_school@skill.xlsx</t>
+        </is>
+      </c>
+      <c r="F43" s="6" t="n"/>
+      <c r="G43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWantedGuardSpawnTier</t>
+          <t>demo.TbSkillLearnEntry</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>demo.WantedGuardSpawnTier</t>
+          <t>demo.SkillLearnEntry</t>
         </is>
       </c>
       <c r="D44" s="6" t="b">
@@ -1315,19 +1377,19 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>wanted_guard_spawn@wanted.xlsx</t>
+          <t>skill_learn@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>demo.TbEntitySkillData</t>
+          <t>demo.TbDesireCrystalDef</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>demo.EntitySkillData</t>
+          <t>demo.DesireCrystalDef</t>
         </is>
       </c>
       <c r="D45" s="6" t="b">
@@ -1335,19 +1397,19 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>entity_skill@skill.xlsx</t>
+          <t>desire_crystal_def@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSkillSchool</t>
+          <t>demo.TbMapDesireCrystalBudget</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>demo.SkillSchool</t>
+          <t>demo.MapDesireCrystalBudget</t>
         </is>
       </c>
       <c r="D46" s="6" t="b">
@@ -1355,19 +1417,19 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>skill_school@skill.xlsx</t>
+          <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSkillLearnEntry</t>
+          <t>demo.TbMapWalkerDesireCrystalQuota</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>demo.SkillLearnEntry</t>
+          <t>demo.MapWalkerDesireCrystalQuota</t>
         </is>
       </c>
       <c r="D47" s="6" t="b">
@@ -1375,19 +1437,19 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>skill_learn@skill.xlsx</t>
+          <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>demo.TbDesireCrystalDef</t>
+          <t>demo.TbNamedNpcDesireCrystal</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>demo.DesireCrystalDef</t>
+          <t>demo.NamedNpcDesireCrystal</t>
         </is>
       </c>
       <c r="D48" s="6" t="b">
@@ -1395,19 +1457,19 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>desire_crystal_def@desire_crystal.xlsx</t>
+          <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMapDesireCrystalBudget</t>
+          <t>demo.TbSpiritMonsterTypeBudget</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>demo.MapDesireCrystalBudget</t>
+          <t>demo.SpiritMonsterTypeBudget</t>
         </is>
       </c>
       <c r="D49" s="6" t="b">
@@ -1415,19 +1477,19 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
+          <t>spirit_monster_budget@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMapWalkerDesireCrystalQuota</t>
+          <t>demo.TbContainerItemStackOverride</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>demo.MapWalkerDesireCrystalQuota</t>
+          <t>demo.ContainerItemStackOverride</t>
         </is>
       </c>
       <c r="D50" s="6" t="b">
@@ -1435,19 +1497,19 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
+          <t>container_item_stack_override@container_stack.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>demo.TbNamedNpcDesireCrystal</t>
+          <t>demo.TbContainerStackTagRule</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>demo.NamedNpcDesireCrystal</t>
+          <t>demo.ContainerStackTagRule</t>
         </is>
       </c>
       <c r="D51" s="6" t="b">
@@ -1455,19 +1517,19 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
+          <t>container_stack_tag_rule@container_stack.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSpiritMonsterTypeBudget</t>
+          <t>demo.TbMapAreaEffect</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>demo.SpiritMonsterTypeBudget</t>
+          <t>demo.MapAreaEffect</t>
         </is>
       </c>
       <c r="D52" s="6" t="b">
@@ -1475,19 +1537,19 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>spirit_monster_budget@player_status.xlsx</t>
+          <t>map_area_effect@map_area_effect.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>demo.TbContainerItemStackOverride</t>
+          <t>demo.TbFallenAmountProgressInfo</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>demo.ContainerItemStackOverride</t>
+          <t>demo.FallenAmountProgressInfo</t>
         </is>
       </c>
       <c r="D53" s="6" t="b">
@@ -1495,19 +1557,19 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>container_item_stack_override@container_stack.xlsx</t>
+          <t>fallen_amount_progress_info@fallen_amount_progress_info.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>demo.TbContainerStackTagRule</t>
+          <t>demo.TbRumorIntel</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>demo.ContainerStackTagRule</t>
+          <t>demo.RumorIntel</t>
         </is>
       </c>
       <c r="D54" s="6" t="b">
@@ -1515,19 +1577,19 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>container_stack_tag_rule@container_stack.xlsx</t>
+          <t>rumor_intel@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMapAreaEffect</t>
+          <t>demo.TbRumorRandomPool</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>demo.MapAreaEffect</t>
+          <t>demo.RumorRandomPool</t>
         </is>
       </c>
       <c r="D55" s="6" t="b">
@@ -1535,20 +1597,39 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>map_area_effect@map_area_effect.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="56"/>
+          <t>rumor_random_pool@rumor_tables.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="B56" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbRumorGlobal</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>demo.RumorGlobal</t>
+        </is>
+      </c>
+      <c r="D56" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="6" t="inlineStr">
+        <is>
+          <t>rumor_global@rumor_tables.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>demo.TbFallenAmountProgressInfo</t>
+          <t>demo.TbCharacterInfo</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>demo.FallenAmountProgressInfo</t>
+          <t>demo.CharacterInfo</t>
         </is>
       </c>
       <c r="D57" s="6" t="b">
@@ -1556,19 +1637,19 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>fallen_amount_progress_info@fallen_amount_progress_info.xlsx</t>
+          <t>character_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRumorIntel</t>
+          <t>demo.TbCharacterFavorInfo</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>demo.RumorIntel</t>
+          <t>demo.CharacterFavorInfo</t>
         </is>
       </c>
       <c r="D58" s="6" t="b">
@@ -1576,19 +1657,19 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>rumor_intel@rumor_tables.xlsx</t>
+          <t>character_favor_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRumorRandomPool</t>
+          <t>demo.TbMicroPlotDef</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>demo.RumorRandomPool</t>
+          <t>demo.MicroPlotDef</t>
         </is>
       </c>
       <c r="D59" s="6" t="b">
@@ -1596,19 +1677,19 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>rumor_random_pool@rumor_tables.xlsx</t>
+          <t>micro_plot_def@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRumorGlobal</t>
+          <t>demo.TbMapMicroPlotTrigger</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>demo.RumorGlobal</t>
+          <t>demo.MapMicroPlotTrigger</t>
         </is>
       </c>
       <c r="D60" s="6" t="b">
@@ -1616,20 +1697,39 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>rumor_global@rumor_tables.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="61"/>
+          <t>map_micro_plot_trigger@micro_plot.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="B61" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbMicroPlotTimelineEvent</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>demo.MicroPlotTimelineEvent</t>
+        </is>
+      </c>
+      <c r="D61" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>micro_plot_timeline_event@micro_plot.xlsx</t>
+        </is>
+      </c>
+    </row>
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>demo.TbCharacterInfo</t>
+          <t>demo.TbTrapSpec</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>demo.CharacterInfo</t>
+          <t>demo.TrapSpec</t>
         </is>
       </c>
       <c r="D62" s="6" t="b">
@@ -1637,19 +1737,19 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>character_info@character.xlsx</t>
+          <t>trap_spec@trap_spec.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>demo.TbCharacterFavorInfo</t>
+          <t>demo.TbForgeRecipe</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>demo.CharacterFavorInfo</t>
+          <t>demo.ForgeRecipe</t>
         </is>
       </c>
       <c r="D63" s="6" t="b">
@@ -1657,19 +1757,19 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>character_favor_info@character.xlsx</t>
+          <t>forge_recipe@forge_recipe.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMicroPlotDef</t>
+          <t>demo.TbHActInfo</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>demo.MicroPlotDef</t>
+          <t>demo.HActInfo</t>
         </is>
       </c>
       <c r="D64" s="6" t="b">
@@ -1677,19 +1777,19 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>micro_plot_def@micro_plot.xlsx</t>
+          <t>h_act_info@h_act_info.xlsx</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMapMicroPlotTrigger</t>
+          <t>demo.TbTalentNodeLevel</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>demo.MapMicroPlotTrigger</t>
+          <t>demo.TalentNodeLevel</t>
         </is>
       </c>
       <c r="D65" s="6" t="b">
@@ -1697,19 +1797,29 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>map_micro_plot_trigger@micro_plot.xlsx</t>
+          <t>talent_level@talent.xlsx</t>
+        </is>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>node_id+level</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMicroPlotTimelineEvent</t>
+          <t>demo.TbSavePoint</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>demo.MicroPlotTimelineEvent</t>
+          <t>demo.SavePoint</t>
         </is>
       </c>
       <c r="D66" s="6" t="b">
@@ -1717,20 +1827,44 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>micro_plot_timeline_event@micro_plot.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="67"/>
+          <t>save_point@save_point.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="B67" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbReviveRule</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>demo.ReviveRule</t>
+        </is>
+      </c>
+      <c r="D67" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="6" t="inlineStr">
+        <is>
+          <t>revive_rule@revive_rule.xlsx</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+    </row>
     <row r="68">
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>demo.TbTrapSpec</t>
+          <t>demo.TbDesireDensityTier</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>demo.TrapSpec</t>
+          <t>demo.DesireDensityTier</t>
         </is>
       </c>
       <c r="D68" s="6" t="b">
@@ -1738,19 +1872,19 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>trap_spec@trap_spec.xlsx</t>
+          <t>desire_density_tier@desire_density_tier.xlsx</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>demo.TbForgeRecipe</t>
+          <t>demo.TbMindFragmentPoolEntry</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>demo.ForgeRecipe</t>
+          <t>demo.MindFragmentPoolEntry</t>
         </is>
       </c>
       <c r="D69" s="6" t="b">
@@ -1758,20 +1892,49 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>forge_recipe@forge_recipe.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="70"/>
+          <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbSecretBaseFacility</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>demo.SecretBaseFacility</t>
+        </is>
+      </c>
+      <c r="D70" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" s="6" t="inlineStr">
+        <is>
+          <t>secret_base_facility@secret_base_facility.xlsx</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>据点固定设施</t>
+        </is>
+      </c>
+    </row>
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHActInfo</t>
+          <t>demo.TbSecretBaseBuildLevel</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>demo.HActInfo</t>
+          <t>demo.SecretBaseBuildLevel</t>
         </is>
       </c>
       <c r="D71" s="6" t="b">
@@ -1779,19 +1942,34 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>h_act_info@h_act_info.xlsx</t>
+          <t>secret_base_build_level@secret_base_build_level.xlsx</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>据点建设等级卷轴边界</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>demo.TbTalentNodeLevel</t>
+          <t>demo.TbSecretBaseCharacter</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>demo.TalentNodeLevel</t>
+          <t>demo.SecretBaseCharacter</t>
         </is>
       </c>
       <c r="D72" s="6" t="b">
@@ -1799,29 +1977,34 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>talent_level@talent.xlsx</t>
+          <t>secret_base_character@secret_base_character.xlsx</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>node_id+level</t>
+          <t>slot_id</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>秘密据点角色</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSavePoint</t>
+          <t>demo.TbHumanWeapon</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>demo.SavePoint</t>
+          <t>demo.HumanWeapon</t>
         </is>
       </c>
       <c r="D73" s="6" t="b">
@@ -1829,19 +2012,34 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>save_point@save_point.xlsx</t>
+          <t>human_weapon@human_weapon.xlsx</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>human_weapon</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>demo.TbReviveRule</t>
+          <t>demo.TbRuneData</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>demo.ReviveRule</t>
+          <t>demo.RuneData</t>
         </is>
       </c>
       <c r="D74" s="6" t="b">
@@ -1849,24 +2047,20 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>revive_rule@revive_rule.xlsx</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
+          <t>rune_data@rune.xlsx</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="n"/>
     </row>
     <row r="75">
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>demo.TbDesireDensityTier</t>
+          <t>demo.TbBodyPartDef</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>demo.DesireDensityTier</t>
+          <t>demo.BodyPartDef</t>
         </is>
       </c>
       <c r="D75" s="6" t="b">
@@ -1874,19 +2068,19 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>desire_density_tier@desire_density_tier.xlsx</t>
+          <t>body_part_def@body_part.xlsx</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMindFragmentPoolEntry</t>
+          <t>demo.TbBodyPartLevel</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>demo.MindFragmentPoolEntry</t>
+          <t>demo.BodyPartLevel</t>
         </is>
       </c>
       <c r="D76" s="6" t="b">
@@ -1894,7 +2088,12 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
+          <t>body_part_level@body_part.xlsx</t>
+        </is>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>part_id+level</t>
         </is>
       </c>
       <c r="G76" s="6" t="inlineStr">
@@ -1906,12 +2105,12 @@
     <row r="77">
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSecretBaseFacility</t>
+          <t>demo.TbBodyPartProgressInfo</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>demo.SecretBaseFacility</t>
+          <t>demo.BodyPartProgressInfo</t>
         </is>
       </c>
       <c r="D77" s="6" t="b">
@@ -1919,24 +2118,20 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>secret_base_facility@secret_base_facility.xlsx</t>
-        </is>
-      </c>
-      <c r="I77" s="6" t="inlineStr">
-        <is>
-          <t>据点固定设施</t>
-        </is>
-      </c>
+          <t>body_part_progress_info@body_part.xlsx</t>
+        </is>
+      </c>
+      <c r="I77" s="6" t="n"/>
     </row>
     <row r="78">
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSecretBaseBuildLevel</t>
+          <t>demo.TbPartLocalAttrDef</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>demo.SecretBaseBuildLevel</t>
+          <t>demo.PartLocalAttrDef</t>
         </is>
       </c>
       <c r="D78" s="6" t="b">
@@ -1944,35 +2139,52 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>secret_base_build_level@secret_base_build_level.xlsx</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
-      <c r="G78" s="6" t="inlineStr">
+          <t>part_local_attr_def@body_part.xlsx</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="n"/>
+      <c r="G78" s="6" t="n"/>
+      <c r="I78" s="6" t="n"/>
+    </row>
+    <row r="79">
+      <c r="B79" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbPartGear</t>
+        </is>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>demo.PartGear</t>
+        </is>
+      </c>
+      <c r="D79" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" s="6" t="inlineStr">
+        <is>
+          <t>partgear@partgear.xlsx</t>
+        </is>
+      </c>
+      <c r="F79" s="6" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I78" s="6" t="inlineStr">
-        <is>
-          <t>据点建设等级卷轴边界</t>
-        </is>
-      </c>
-    </row>
-    <row r="79"/>
+    </row>
     <row r="80">
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSecretBaseCharacter</t>
+          <t>demo.TbRuneUpgradeInfo</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>demo.SecretBaseCharacter</t>
+          <t>demo.RuneUpgradeInfo</t>
         </is>
       </c>
       <c r="D80" s="6" t="b">
@@ -1980,34 +2192,31 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>secret_base_character@secret_base_character.xlsx</t>
+          <t>rune_upgrade_info@rune.xlsx</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>slot_id</t>
-        </is>
-      </c>
-      <c r="G80" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>秘密据点角色</t>
+          <t>upgrade_id</t>
+        </is>
+      </c>
+      <c r="G80" s="6" t="n"/>
+      <c r="I80" s="6" t="n"/>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>符文升级项</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHumanWeapon</t>
+          <t>demo.TbRuneEquipSlot</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>demo.HumanWeapon</t>
+          <t>demo.RuneEquipSlotInfo</t>
         </is>
       </c>
       <c r="D81" s="6" t="b">
@@ -2015,34 +2224,31 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>human_weapon@human_weapon.xlsx</t>
+          <t>rune_equip_slot@rune.xlsx</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I81" s="6" t="inlineStr">
-        <is>
-          <t>human_weapon</t>
+          <t>equip_slot</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="n"/>
+      <c r="I81" s="6" t="n"/>
+      <c r="J81" s="6" t="inlineStr">
+        <is>
+          <t>符文装配槽</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRuneData</t>
+          <t>demo.TbEntitySkillLevel</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>demo.RuneData</t>
+          <t>demo.EntitySkillLevel</t>
         </is>
       </c>
       <c r="D82" s="6" t="b">
@@ -2050,19 +2256,29 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>rune_data@rune.xlsx</t>
+          <t>skill_level@skill.xlsx</t>
+        </is>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>skill_id+level</t>
+        </is>
+      </c>
+      <c r="G82" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>demo.TbBodyPartDef</t>
+          <t>demo.TbHomesteadBuilding</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>demo.BodyPartDef</t>
+          <t>demo.HomesteadBuilding</t>
         </is>
       </c>
       <c r="D83" s="6" t="b">
@@ -2070,19 +2286,34 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>body_part_def@body_part.xlsx</t>
+          <t>homestead_building@map_homestead.xlsx</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>logic_area_id+building_id</t>
+        </is>
+      </c>
+      <c r="G83" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="I83" s="6" t="inlineStr">
+        <is>
+          <t>逻辑区域可管理建筑</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>demo.TbBodyPartLevel</t>
+          <t>demo.TbHomesteadBuildingUpgrade</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>demo.BodyPartLevel</t>
+          <t>demo.HomesteadBuildingUpgrade</t>
         </is>
       </c>
       <c r="D84" s="6" t="b">
@@ -2090,29 +2321,34 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>body_part_level@body_part.xlsx</t>
+          <t>homestead_building_upgrade@map_homestead.xlsx</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>part_id+level</t>
+          <t>logic_area_id+building_id+level</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
           <t>list</t>
+        </is>
+      </c>
+      <c r="I84" s="6" t="inlineStr">
+        <is>
+          <t>家园建筑升级项</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>demo.TbBodyPartProgressInfo</t>
+          <t>demo.TbJingYuanCodexDef</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>demo.BodyPartProgressInfo</t>
+          <t>demo.JingYuanCodexDef</t>
         </is>
       </c>
       <c r="D85" s="6" t="b">
@@ -2120,19 +2356,24 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>body_part_progress_info@body_part.xlsx</t>
+          <t>jingyuan_codex_def@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>codex_id</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPartLocalAttrDef</t>
+          <t>demo.TbJingYuanCodexLevel</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>demo.PartLocalAttrDef</t>
+          <t>demo.JingYuanCodexLevel</t>
         </is>
       </c>
       <c r="D86" s="6" t="b">
@@ -2140,19 +2381,29 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>part_local_attr_def@body_part.xlsx</t>
+          <t>jingyuan_codex_level@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>codex_id+level</t>
+        </is>
+      </c>
+      <c r="G86" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPartGear</t>
+          <t>demo.TbJingYuanTuneTier</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>demo.PartGear</t>
+          <t>demo.JingYuanTuneTier</t>
         </is>
       </c>
       <c r="D87" s="6" t="b">
@@ -2160,29 +2411,29 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>partgear@partgear.xlsx</t>
+          <t>jingyuan_tune_tier@jingyuan_codex.xlsx</t>
         </is>
       </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>codex_id+tier</t>
         </is>
       </c>
       <c r="G87" s="6" t="inlineStr">
         <is>
-          <t>map</t>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRuneUpgradeInfo</t>
+          <t>demo.TbTiaoJingConcentrationLevel</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>demo.RuneUpgradeInfo</t>
+          <t>demo.TiaoJingConcentrationLevel</t>
         </is>
       </c>
       <c r="D88" s="6" t="b">
@@ -2190,29 +2441,21 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>rune_upgrade_info@rune.xlsx</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>upgrade_id</t>
-        </is>
-      </c>
-      <c r="J88" s="6" t="inlineStr">
-        <is>
-          <t>符文升级项</t>
-        </is>
-      </c>
+          <t>tiao_jing_concentration_level@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="n"/>
+      <c r="J88" s="6" t="n"/>
     </row>
     <row r="89">
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRuneEquipSlot</t>
+          <t>demo.TbJingYuanTypeDef</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>demo.RuneEquipSlotInfo</t>
+          <t>demo.JingYuanTypeDef</t>
         </is>
       </c>
       <c r="D89" s="6" t="b">
@@ -2220,29 +2463,25 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>rune_equip_slot@rune.xlsx</t>
+          <t>jingyuan_type_def@jingyuan_codex.xlsx</t>
         </is>
       </c>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>equip_slot</t>
-        </is>
-      </c>
-      <c r="J89" s="6" t="inlineStr">
-        <is>
-          <t>符文装配槽</t>
-        </is>
-      </c>
+          <t>type_id</t>
+        </is>
+      </c>
+      <c r="J89" s="6" t="n"/>
     </row>
     <row r="90">
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>demo.TbEntitySkillLevel</t>
+          <t>demo.TbJingYuanTypePoolEntry</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>demo.EntitySkillLevel</t>
+          <t>demo.JingYuanTypePoolEntry</t>
         </is>
       </c>
       <c r="D90" s="6" t="b">
@@ -2250,14 +2489,10 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>skill_level@skill.xlsx</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>skill_id+level</t>
-        </is>
-      </c>
+          <t>jingyuan_type_pool@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="n"/>
       <c r="G90" s="6" t="inlineStr">
         <is>
           <t>list</t>
@@ -2267,12 +2502,12 @@
     <row r="91">
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHomesteadBuilding</t>
+          <t>demo.TbProgressionHubTab</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>demo.HomesteadBuilding</t>
+          <t>demo.ProgressionHubTabDef</t>
         </is>
       </c>
       <c r="D91" s="6" t="b">
@@ -2280,34 +2515,34 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>homestead_building@map_homestead.xlsx</t>
+          <t>progression_hub_tab@progression_hub_tab.xlsx</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>logic_area_id+building_id</t>
+          <t>tab_id</t>
         </is>
       </c>
       <c r="G91" s="6" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>map</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>逻辑区域可管理建筑</t>
+          <t>养成总面板选项卡</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHomesteadBuildingUpgrade</t>
+          <t>demo.TbPlayerAttachInfo</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>demo.HomesteadBuildingUpgrade</t>
+          <t>demo.PlayerAttachInfo</t>
         </is>
       </c>
       <c r="D92" s="6" t="b">
@@ -2315,34 +2550,22 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>homestead_building_upgrade@map_homestead.xlsx</t>
-        </is>
-      </c>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>logic_area_id+building_id+level</t>
-        </is>
-      </c>
-      <c r="G92" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
-      <c r="I92" s="6" t="inlineStr">
-        <is>
-          <t>家园建筑升级项</t>
-        </is>
-      </c>
+          <t>player_attach@player_attach.xlsx</t>
+        </is>
+      </c>
+      <c r="F92" s="6" t="n"/>
+      <c r="G92" s="6" t="n"/>
+      <c r="I92" s="6" t="n"/>
     </row>
     <row r="93">
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanCodexDef</t>
+          <t>demo.TbItemDismantle</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>demo.JingYuanCodexDef</t>
+          <t>demo.ItemDismantle</t>
         </is>
       </c>
       <c r="D93" s="6" t="b">
@@ -2350,24 +2573,34 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>jingyuan_codex_def@jingyuan_codex.xlsx</t>
+          <t>item_dismantle@item_dismantle.xlsx</t>
         </is>
       </c>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>codex_id</t>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>物品分解产物配置</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanCodexLevel</t>
+          <t>demo.TbItemTagInfo</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>demo.JingYuanCodexLevel</t>
+          <t>demo.ItemTagInfo</t>
         </is>
       </c>
       <c r="D94" s="6" t="b">
@@ -2375,29 +2608,35 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>jingyuan_codex_level@jingyuan_codex.xlsx</t>
+          <t>item_tag@item.xlsx</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>codex_id+level</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="n"/>
+      <c r="H94" s="6" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>物品标签元数据：显示字、隐藏控制、实例需求</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanTuneTier</t>
+          <t>demo.TbPlayerBagDef</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>demo.JingYuanTuneTier</t>
+          <t>demo.PlayerBagDef</t>
         </is>
       </c>
       <c r="D95" s="6" t="b">
@@ -2405,29 +2644,26 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>jingyuan_tune_tier@jingyuan_codex.xlsx</t>
-        </is>
-      </c>
-      <c r="F95" s="6" t="inlineStr">
-        <is>
-          <t>codex_id+tier</t>
-        </is>
-      </c>
-      <c r="G95" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>player_bag@player_bag.xlsx</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="n"/>
+      <c r="G95" s="6" t="n"/>
+      <c r="I95" s="6" t="inlineStr">
+        <is>
+          <t>玩家背包定义</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>demo.TbTiaoJingConcentrationLevel</t>
+          <t>demo.TbWarehouseFilter</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>demo.TiaoJingConcentrationLevel</t>
+          <t>demo.WarehouseFilter</t>
         </is>
       </c>
       <c r="D96" s="6" t="b">
@@ -2435,19 +2671,24 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>tiao_jing_concentration_level@jingyuan_codex.xlsx</t>
+          <t>warehouse_filter@warehouse_filter.xlsx</t>
+        </is>
+      </c>
+      <c r="I96" s="6" t="inlineStr">
+        <is>
+          <t>仓库筛选定义</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanTypeDef</t>
+          <t>demo.TbCharacterGiftRule</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>demo.JingYuanTypeDef</t>
+          <t>demo.CharacterGiftRule</t>
         </is>
       </c>
       <c r="D97" s="6" t="b">
@@ -2455,24 +2696,34 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>jingyuan_type_def@jingyuan_codex.xlsx</t>
+          <t>character_gift_rule@character.xlsx</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>type_id</t>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I97" s="6" t="inlineStr">
+        <is>
+          <t>角色礼物固定覆盖规则</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanTypePoolEntry</t>
+          <t>demo.TbTalentTree</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>demo.JingYuanTypePoolEntry</t>
+          <t>demo.TalentTree</t>
         </is>
       </c>
       <c r="D98" s="6" t="b">
@@ -2480,24 +2731,34 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>jingyuan_type_pool@jingyuan_codex.xlsx</t>
+          <t>talent_tree@talent.xlsx</t>
+        </is>
+      </c>
+      <c r="F98" s="6" t="inlineStr">
+        <is>
+          <t>tree_id</t>
         </is>
       </c>
       <c r="G98" s="6" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>天赋树定义</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>demo.TbProgressionHubTab</t>
+          <t>demo.TbSecretBaseCharacterOption</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>demo.ProgressionHubTabDef</t>
+          <t>demo.SecretBaseCharacterOption</t>
         </is>
       </c>
       <c r="D99" s="6" t="b">
@@ -2505,12 +2766,12 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>progression_hub_tab@progression_hub_tab.xlsx</t>
+          <t>secret_base_character_option@secret_base_character.xlsx</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>tab_id</t>
+          <t>option_id</t>
         </is>
       </c>
       <c r="G99" s="6" t="inlineStr">
@@ -2520,19 +2781,19 @@
       </c>
       <c r="I99" s="6" t="inlineStr">
         <is>
-          <t>养成总面板选项卡</t>
+          <t>秘密据点角色自定义选项</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerAttachInfo</t>
+          <t>demo.TbHumanCivilizationLevel</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerAttachInfo</t>
+          <t>demo.HumanCivilizationLevel</t>
         </is>
       </c>
       <c r="D100" s="6" t="b">
@@ -2540,19 +2801,24 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>player_attach@player_attach.xlsx</t>
+          <t>civilization_level@human_civilization.xlsx</t>
+        </is>
+      </c>
+      <c r="F100" s="6" t="inlineStr">
+        <is>
+          <t>level</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>demo.TbItemDismantle</t>
+          <t>demo.TbHumanTechTree</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>demo.ItemDismantle</t>
+          <t>demo.HumanTechTree</t>
         </is>
       </c>
       <c r="D101" s="6" t="b">
@@ -2560,34 +2826,26 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>item_dismantle@item_dismantle.xlsx</t>
+          <t>human_tech_tree@human_tech.xlsx</t>
         </is>
       </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G101" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>物品分解产物配置</t>
-        </is>
-      </c>
+          <t>tree_id</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="n"/>
+      <c r="I101" s="6" t="n"/>
     </row>
     <row r="102" s="2">
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>demo.TbItemTagInfo</t>
+          <t>demo.TbHumanTechNode</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>demo.ItemTagInfo</t>
+          <t>demo.HumanTechNode</t>
         </is>
       </c>
       <c r="D102" s="6" t="b">
@@ -2595,34 +2853,26 @@
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>item_tag@item.xlsx</t>
+          <t>human_tech@human_tech.xlsx</t>
         </is>
       </c>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>tag</t>
-        </is>
-      </c>
-      <c r="H102" s="6" t="inlineStr">
-        <is>
-          <t>c,s</t>
-        </is>
-      </c>
-      <c r="I102" s="6" t="inlineStr">
-        <is>
-          <t>物品标签元数据：显示字、隐藏控制、实例需求</t>
-        </is>
-      </c>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="H102" s="6" t="n"/>
+      <c r="I102" s="6" t="n"/>
     </row>
     <row r="103" s="2">
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerBagDef</t>
+          <t>demo.TbHumanTechNodeLevel</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerBagDef</t>
+          <t>demo.HumanTechNodeLevel</t>
         </is>
       </c>
       <c r="D103" s="6" t="b">
@@ -2630,24 +2880,25 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>player_bag@player_bag.xlsx</t>
-        </is>
-      </c>
-      <c r="I103" s="6" t="inlineStr">
-        <is>
-          <t>玩家背包定义</t>
-        </is>
-      </c>
+          <t>human_tech_level@human_tech.xlsx</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="inlineStr">
+        <is>
+          <t>node_id+level</t>
+        </is>
+      </c>
+      <c r="I103" s="6" t="n"/>
     </row>
     <row r="104">
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWarehouseFilter</t>
+          <t>demo.TbQuestAcceptDialog</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>demo.WarehouseFilter</t>
+          <t>demo.QuestAcceptDialog</t>
         </is>
       </c>
       <c r="D104" s="6" t="b">
@@ -2655,24 +2906,20 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>warehouse_filter@warehouse_filter.xlsx</t>
-        </is>
-      </c>
-      <c r="I104" s="6" t="inlineStr">
-        <is>
-          <t>仓库筛选定义</t>
-        </is>
-      </c>
+          <t>quest_accept_dialog@dialog.xlsx</t>
+        </is>
+      </c>
+      <c r="I104" s="6" t="n"/>
     </row>
     <row r="105">
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>demo.TbCharacterGiftRule</t>
+          <t>demo.TbQuestRemindDialog</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>demo.CharacterGiftRule</t>
+          <t>demo.QuestRemindDialog</t>
         </is>
       </c>
       <c r="D105" s="6" t="b">
@@ -2680,34 +2927,22 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>character_gift_rule@character.xlsx</t>
-        </is>
-      </c>
-      <c r="F105" s="6" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G105" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I105" s="6" t="inlineStr">
-        <is>
-          <t>角色礼物固定覆盖规则</t>
-        </is>
-      </c>
+          <t>quest_remind_dialog@dialog.xlsx</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="n"/>
+      <c r="G105" s="6" t="n"/>
+      <c r="I105" s="6" t="n"/>
     </row>
     <row r="106">
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>demo.TbTalentTree</t>
+          <t>demo.TbQuestObjectiveDialog</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>demo.TalentTree</t>
+          <t>demo.QuestObjectiveDialog</t>
         </is>
       </c>
       <c r="D106" s="6" t="b">
@@ -2715,34 +2950,22 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>talent_tree@talent.xlsx</t>
-        </is>
-      </c>
-      <c r="F106" s="6" t="inlineStr">
-        <is>
-          <t>tree_id</t>
-        </is>
-      </c>
-      <c r="G106" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I106" s="6" t="inlineStr">
-        <is>
-          <t>天赋树定义</t>
-        </is>
-      </c>
+          <t>quest_objective_dialog@dialog.xlsx</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="n"/>
+      <c r="G106" s="6" t="n"/>
+      <c r="I106" s="6" t="n"/>
     </row>
     <row r="107">
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSecretBaseCharacterOption</t>
+          <t>demo.TbNpcRoutineProfile</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>demo.SecretBaseCharacterOption</t>
+          <t>demo.NpcRoutineProfile</t>
         </is>
       </c>
       <c r="D107" s="6" t="b">
@@ -2750,34 +2973,26 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>secret_base_character_option@secret_base_character.xlsx</t>
+          <t>npc_routine_profile@npc_routine.xlsx</t>
         </is>
       </c>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>option_id</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I107" s="6" t="inlineStr">
-        <is>
-          <t>秘密据点角色自定义选项</t>
-        </is>
-      </c>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="n"/>
+      <c r="I107" s="6" t="n"/>
     </row>
     <row r="108">
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHumanCivilizationLevel</t>
+          <t>demo.TbNpcRoutineRule</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>demo.HumanCivilizationLevel</t>
+          <t>demo.NpcRoutineRule</t>
         </is>
       </c>
       <c r="D108" s="6" t="b">
@@ -2785,24 +3000,24 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>civilization_level@human_civilization.xlsx</t>
+          <t>npc_routine_rule@npc_routine.xlsx</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>id</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHumanTechTree</t>
+          <t>demo.TbNpcRoutineBinding</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>demo.HumanTechTree</t>
+          <t>demo.NpcRoutineBinding</t>
         </is>
       </c>
       <c r="D109" s="6" t="b">
@@ -2810,24 +3025,29 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>human_tech_tree@human_tech.xlsx</t>
+          <t>npc_routine_binding@npc_routine.xlsx</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>tree_id</t>
+          <t>map_variant+overlay_id+character_key</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHumanTechNode</t>
+          <t>demo.TbCultTechNode</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>demo.HumanTechNode</t>
+          <t>demo.CultTechNode</t>
         </is>
       </c>
       <c r="D110" s="6" t="b">
@@ -2835,24 +3055,20 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>human_tech@human_tech.xlsx</t>
-        </is>
-      </c>
-      <c r="F110" s="6" t="inlineStr">
-        <is>
-          <t>node_id</t>
-        </is>
-      </c>
+          <t>cult_tech_node@cult_tech.xlsx</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="n"/>
     </row>
     <row r="111">
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHumanTechNodeLevel</t>
+          <t>demo.TbCultTechNodeLevel</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>demo.HumanTechNodeLevel</t>
+          <t>demo.CultTechNodeLevel</t>
         </is>
       </c>
       <c r="D111" s="6" t="b">
@@ -2860,7 +3076,7 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>human_tech_level@human_tech.xlsx</t>
+          <t>cult_tech_node_level@cult_tech.xlsx</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
@@ -2872,12 +3088,12 @@
     <row r="112">
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>demo.TbQuestAcceptDialog</t>
+          <t>demo.TbNpcLocomotionProfile</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>demo.QuestAcceptDialog</t>
+          <t>demo.NpcLocomotionProfile</t>
         </is>
       </c>
       <c r="D112" s="6" t="b">
@@ -2885,19 +3101,24 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>quest_accept_dialog@dialog.xlsx</t>
+          <t>npc_locomotion_profile@npc_routine.xlsx</t>
+        </is>
+      </c>
+      <c r="F112" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>demo.TbQuestRemindDialog</t>
+          <t>demo.TbFacilityDefinition</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>demo.QuestRemindDialog</t>
+          <t>demo.FacilityDefinition</t>
         </is>
       </c>
       <c r="D113" s="6" t="b">
@@ -2905,19 +3126,24 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>quest_remind_dialog@dialog.xlsx</t>
+          <t>facility_definition@facility_definition.xlsx</t>
+        </is>
+      </c>
+      <c r="F113" s="6" t="inlineStr">
+        <is>
+          <t>facility_id</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>demo.TbQuestObjectiveDialog</t>
+          <t>demo.TbFacilityDevelopmentDefinition</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>demo.QuestObjectiveDialog</t>
+          <t>demo.FacilityDevelopmentDefinition</t>
         </is>
       </c>
       <c r="D114" s="6" t="b">
@@ -2925,19 +3151,25 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>quest_objective_dialog@dialog.xlsx</t>
-        </is>
-      </c>
+          <t>facility_development_definition@facility_development.xlsx</t>
+        </is>
+      </c>
+      <c r="F114" s="6" t="inlineStr">
+        <is>
+          <t>facility_id</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="n"/>
     </row>
     <row r="115">
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>demo.TbNpcRoutineProfile</t>
+          <t>demo.TbFacilityDevelopmentLevel</t>
         </is>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>demo.NpcRoutineProfile</t>
+          <t>demo.FacilityDevelopmentLevel</t>
         </is>
       </c>
       <c r="D115" s="6" t="b">
@@ -2945,24 +3177,25 @@
       </c>
       <c r="E115" s="6" t="inlineStr">
         <is>
-          <t>npc_routine_profile@npc_routine.xlsx</t>
+          <t>facility_development_level@facility_development.xlsx</t>
         </is>
       </c>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
+          <t>facility_id+level</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="n"/>
     </row>
     <row r="116">
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>demo.TbNpcRoutineRule</t>
+          <t>demo.TbTownFacilitySite</t>
         </is>
       </c>
       <c r="C116" s="6" t="inlineStr">
         <is>
-          <t>demo.NpcRoutineRule</t>
+          <t>demo.TownFacilitySite</t>
         </is>
       </c>
       <c r="D116" s="6" t="b">
@@ -2970,7 +3203,7 @@
       </c>
       <c r="E116" s="6" t="inlineStr">
         <is>
-          <t>npc_routine_rule@npc_routine.xlsx</t>
+          <t>town_facility_site@facility_development.xlsx</t>
         </is>
       </c>
       <c r="F116" s="6" t="inlineStr">
@@ -2982,12 +3215,12 @@
     <row r="117">
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>demo.TbNpcRoutineBinding</t>
+          <t>demo.TbFacilityRenovation</t>
         </is>
       </c>
       <c r="C117" s="6" t="inlineStr">
         <is>
-          <t>demo.NpcRoutineBinding</t>
+          <t>demo.FacilityRenovation</t>
         </is>
       </c>
       <c r="D117" s="6" t="b">
@@ -2995,87 +3228,86 @@
       </c>
       <c r="E117" s="6" t="inlineStr">
         <is>
-          <t>npc_routine_binding@npc_routine.xlsx</t>
+          <t>facility_renovation@facility_development.xlsx</t>
         </is>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>map_variant+overlay_id+character_key</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
+          <t>facility_cfg_id+renovation_id</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="n"/>
     </row>
     <row r="118">
-      <c r="B118" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbCultTechNode</t>
-        </is>
-      </c>
-      <c r="C118" s="6" t="inlineStr">
-        <is>
-          <t>demo.CultTechNode</t>
-        </is>
-      </c>
-      <c r="D118" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E118" s="6" t="inlineStr">
-        <is>
-          <t>cult_tech_node@cult_tech.xlsx</t>
-        </is>
-      </c>
+      <c r="B118" s="6" t="n"/>
+      <c r="C118" s="6" t="n"/>
+      <c r="D118" s="6" t="n"/>
+      <c r="E118" s="6" t="n"/>
     </row>
     <row r="119">
-      <c r="B119" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbCultTechNodeLevel</t>
-        </is>
-      </c>
-      <c r="C119" s="6" t="inlineStr">
-        <is>
-          <t>demo.CultTechNodeLevel</t>
-        </is>
-      </c>
-      <c r="D119" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E119" s="6" t="inlineStr">
-        <is>
-          <t>cult_tech_node_level@cult_tech.xlsx</t>
-        </is>
-      </c>
-      <c r="F119" s="6" t="inlineStr">
-        <is>
-          <t>node_id+level</t>
-        </is>
-      </c>
+      <c r="B119" s="6" t="n"/>
+      <c r="C119" s="6" t="n"/>
+      <c r="D119" s="6" t="n"/>
+      <c r="E119" s="6" t="n"/>
+      <c r="F119" s="6" t="n"/>
     </row>
     <row r="120">
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>demo.TbNpcLocomotionProfile</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>demo.NpcLocomotionProfile</t>
-        </is>
-      </c>
-      <c r="D120" t="b">
-        <v>1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>npc_locomotion_profile@npc_routine.xlsx</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>id</t>
+      <c r="B120" s="6" t="n"/>
+      <c r="C120" s="6" t="n"/>
+      <c r="D120" s="6" t="n"/>
+      <c r="E120" s="6" t="n"/>
+      <c r="F120" s="6" t="n"/>
+    </row>
+    <row r="121">
+      <c r="B121" s="6" t="n"/>
+      <c r="C121" s="6" t="n"/>
+      <c r="D121" s="6" t="n"/>
+      <c r="E121" s="6" t="n"/>
+      <c r="F121" s="6" t="n"/>
+    </row>
+    <row r="122">
+      <c r="B122" s="6" t="n"/>
+      <c r="C122" s="6" t="n"/>
+      <c r="D122" s="6" t="n"/>
+      <c r="E122" s="6" t="n"/>
+      <c r="F122" s="6" t="n"/>
+    </row>
+    <row r="123">
+      <c r="B123" s="6" t="n"/>
+      <c r="C123" s="6" t="n"/>
+      <c r="D123" s="6" t="n"/>
+      <c r="E123" s="6" t="n"/>
+      <c r="F123" s="6" t="n"/>
+    </row>
+    <row r="124">
+      <c r="B124" s="6" t="n"/>
+      <c r="C124" s="6" t="n"/>
+      <c r="D124" s="6" t="n"/>
+      <c r="E124" s="6" t="n"/>
+      <c r="F124" s="6" t="n"/>
+    </row>
+    <row r="125">
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbCharacterFacilitySupervisor</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>demo.CharacterFacilitySupervisor</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>character_facility_supervisor@facility_development.xlsx</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>character_key</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
 </workbook>
@@ -359,7 +359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K125"/>
+  <dimension ref="A1:K124"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -572,7 +572,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>logic_area_homestead_req@map_homestead.xlsx</t>
+          <t>logic_area_homestead_req@facility_development.xlsx</t>
         </is>
       </c>
     </row>
@@ -689,12 +689,12 @@
     <row r="12">
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>demo.TbFixedFacility</t>
+          <t>demo.TbBornPoint</t>
         </is>
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>demo.FixedFacility</t>
+          <t>demo.BornPoint</t>
         </is>
       </c>
       <c r="D12" s="6" t="b">
@@ -702,19 +702,19 @@
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>fixed_facility@home_facility.xlsx</t>
+          <t>born_points@born_points.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>demo.TbBornPoint</t>
+          <t>demo.TbUnitNpc</t>
         </is>
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>demo.BornPoint</t>
+          <t>demo.UnitNpc</t>
         </is>
       </c>
       <c r="D13" s="6" t="b">
@@ -722,19 +722,19 @@
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>born_points@born_points.xlsx</t>
+          <t>unit_npc@unit_npc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>demo.TbUnitNpc</t>
+          <t>demo.TbUnitNpcAttr</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>demo.UnitNpc</t>
+          <t>demo.UnitNpcAttr</t>
         </is>
       </c>
       <c r="D14" s="6" t="b">
@@ -742,19 +742,19 @@
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>unit_npc@unit_npc.xlsx</t>
+          <t>unit_npc_attribute@unit_npc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>demo.TbUnitNpcAttr</t>
+          <t>demo.TbDesireDensityInfo</t>
         </is>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>demo.UnitNpcAttr</t>
+          <t>demo.DesireDensityInfo</t>
         </is>
       </c>
       <c r="D15" s="6" t="b">
@@ -762,19 +762,19 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>unit_npc_attribute@unit_npc.xlsx</t>
+          <t>desire_density_info@unit_npc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>demo.TbDesireDensityInfo</t>
+          <t>demo.TbQuestData</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>demo.DesireDensityInfo</t>
+          <t>demo.QuestData</t>
         </is>
       </c>
       <c r="D16" s="6" t="b">
@@ -782,19 +782,19 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>desire_density_info@unit_npc.xlsx</t>
+          <t>quest_data@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>demo.TbQuestData</t>
+          <t>demo.TbQuestStepData</t>
         </is>
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>demo.QuestData</t>
+          <t>demo.QuestStepData</t>
         </is>
       </c>
       <c r="D17" s="6" t="b">
@@ -802,19 +802,19 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>quest_data@quests.xlsx</t>
+          <t>quest_step_data@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>demo.TbQuestStepData</t>
+          <t>demo.TbQuestStepOutcome</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>demo.QuestStepData</t>
+          <t>demo.QuestStepOutcome</t>
         </is>
       </c>
       <c r="D18" s="6" t="b">
@@ -822,19 +822,19 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>quest_step_data@quests.xlsx</t>
+          <t>quest_step_outcome@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>demo.TbQuestStepOutcome</t>
+          <t>demo.TbQuestStepObjective</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>demo.QuestStepOutcome</t>
+          <t>demo.QuestStepObjective</t>
         </is>
       </c>
       <c r="D19" s="6" t="b">
@@ -842,19 +842,19 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>quest_step_outcome@quests.xlsx</t>
+          <t>quest_step_objective@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>demo.TbQuestStepObjective</t>
+          <t>demo.TbDialogMetaInfo</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>demo.QuestStepObjective</t>
+          <t>demo.DialogMetaInfo</t>
         </is>
       </c>
       <c r="D20" s="6" t="b">
@@ -862,19 +862,19 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>quest_step_objective@quests.xlsx</t>
+          <t>dialog_meta_info@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>demo.TbDialogMetaInfo</t>
+          <t>demo.TbItemData</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>demo.DialogMetaInfo</t>
+          <t>demo.ItemData</t>
         </is>
       </c>
       <c r="D21" s="6" t="b">
@@ -882,19 +882,19 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>dialog_meta_info@dialog.xlsx</t>
+          <t>item@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>demo.TbItemData</t>
+          <t>demo.TbShop</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>demo.ItemData</t>
+          <t>demo.Shop</t>
         </is>
       </c>
       <c r="D22" s="6" t="b">
@@ -902,19 +902,19 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>item@item.xlsx</t>
+          <t>shop@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>demo.TbShop</t>
+          <t>demo.TbShopGoods</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>demo.Shop</t>
+          <t>demo.ShopGoods</t>
         </is>
       </c>
       <c r="D23" s="6" t="b">
@@ -922,19 +922,19 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>shop@shop.xlsx</t>
+          <t>shop_goods@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>demo.TbShopGoods</t>
+          <t>demo.TbItemUse</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>demo.ShopGoods</t>
+          <t>demo.ItemUse</t>
         </is>
       </c>
       <c r="D24" s="6" t="b">
@@ -942,19 +942,19 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>shop_goods@shop.xlsx</t>
+          <t>item_use@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="6" t="inlineStr">
         <is>
-          <t>demo.TbItemUse</t>
+          <t>demo.TbItemGift</t>
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>demo.ItemUse</t>
+          <t>demo.ItemGift</t>
         </is>
       </c>
       <c r="D25" s="6" t="b">
@@ -962,19 +962,29 @@
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>item_use@item.xlsx</t>
+          <t>item_gift@item.xlsx</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>demo.TbItemGift</t>
+          <t>demo.TbNpcDialogInfo</t>
         </is>
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>demo.ItemGift</t>
+          <t>demo.NpcDialogInfo</t>
         </is>
       </c>
       <c r="D26" s="6" t="b">
@@ -982,29 +992,21 @@
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>item_gift@item.xlsx</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
+          <t>npc_dialog_info@dialog.xlsx</t>
+        </is>
+      </c>
+      <c r="F26" s="6" t="n"/>
+      <c r="G26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>demo.TbNpcDialogInfo</t>
+          <t>demo.TbWorldMapGlobal</t>
         </is>
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>demo.NpcDialogInfo</t>
+          <t>demo.WorldMapGlobal</t>
         </is>
       </c>
       <c r="D27" s="6" t="b">
@@ -1012,21 +1014,24 @@
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>npc_dialog_info@dialog.xlsx</t>
-        </is>
-      </c>
-      <c r="F27" s="6" t="n"/>
-      <c r="G27" s="6" t="n"/>
+          <t>world_map_global@map.xlsx</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>one</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWorldMapGlobal</t>
+          <t>demo.TbWorldMapBigMapLayer</t>
         </is>
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>demo.WorldMapGlobal</t>
+          <t>demo.WorldMapBigMapLayer</t>
         </is>
       </c>
       <c r="D28" s="6" t="b">
@@ -1034,24 +1039,24 @@
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>world_map_global@map.xlsx</t>
+          <t>world_map_big_map@map.xlsx</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>one</t>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWorldMapBigMapLayer</t>
+          <t>demo.TbDreamInfiltrationSpot</t>
         </is>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>demo.WorldMapBigMapLayer</t>
+          <t>demo.DreamInfiltrationSpot</t>
         </is>
       </c>
       <c r="D29" s="6" t="b">
@@ -1059,24 +1064,20 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>world_map_big_map@map.xlsx</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
+          <t>dream_infiltration@dream_infiltration.xlsx</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>demo.TbDreamInfiltrationSpot</t>
+          <t>demo.TbCharDreamEntryInfo</t>
         </is>
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>demo.DreamInfiltrationSpot</t>
+          <t>demo.CharDreamEntryInfo</t>
         </is>
       </c>
       <c r="D30" s="6" t="b">
@@ -1084,20 +1085,19 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>dream_infiltration@dream_infiltration.xlsx</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="n"/>
+          <t>char_dream_entry@dream_infiltration.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>demo.TbCharDreamEntryInfo</t>
+          <t>demo.TbFishingSpot</t>
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>demo.CharDreamEntryInfo</t>
+          <t>demo.FishingSpot</t>
         </is>
       </c>
       <c r="D31" s="6" t="b">
@@ -1105,19 +1105,19 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>char_dream_entry@dream_infiltration.xlsx</t>
+          <t>fishing_spot@fishing_spot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>demo.TbFishingSpot</t>
+          <t>demo.TbFishingSpotFish</t>
         </is>
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>demo.FishingSpot</t>
+          <t>demo.FishingSpotFish</t>
         </is>
       </c>
       <c r="D32" s="6" t="b">
@@ -1125,19 +1125,19 @@
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>fishing_spot@fishing_spot.xlsx</t>
+          <t>fishing_spot_fish@fishing_spot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>demo.TbFishingSpotFish</t>
+          <t>demo.TbPlayerDesireLevel</t>
         </is>
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>demo.FishingSpotFish</t>
+          <t>demo.PlayerDesireLevel</t>
         </is>
       </c>
       <c r="D33" s="6" t="b">
@@ -1145,19 +1145,19 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>fishing_spot_fish@fishing_spot.xlsx</t>
+          <t>player_desire_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerDesireLevel</t>
+          <t>demo.TbPlayerJingYuLevel</t>
         </is>
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerDesireLevel</t>
+          <t>demo.PlayerJingYuLevel</t>
         </is>
       </c>
       <c r="D34" s="6" t="b">
@@ -1165,19 +1165,19 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>player_desire_level@player_status.xlsx</t>
+          <t>player_jingyu_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerJingYuLevel</t>
+          <t>demo.TbPlayerSanCorruptLevel</t>
         </is>
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerJingYuLevel</t>
+          <t>demo.PlayerSanCorruptLevel</t>
         </is>
       </c>
       <c r="D35" s="6" t="b">
@@ -1185,19 +1185,19 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>player_jingyu_level@player_status.xlsx</t>
+          <t>player_san_corrupt_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerSanCorruptLevel</t>
+          <t>demo.TbPlayerClothesExposeInfo</t>
         </is>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerSanCorruptLevel</t>
+          <t>demo.PlayerClothesExposeInfo</t>
         </is>
       </c>
       <c r="D36" s="6" t="b">
@@ -1205,19 +1205,19 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>player_san_corrupt_level@player_status.xlsx</t>
+          <t>player_clothes_expose_info@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerClothesExposeInfo</t>
+          <t>demo.TbWantedLevelInfo</t>
         </is>
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerClothesExposeInfo</t>
+          <t>demo.WantedLevelInfo</t>
         </is>
       </c>
       <c r="D37" s="6" t="b">
@@ -1225,19 +1225,19 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>player_clothes_expose_info@player_status.xlsx</t>
+          <t>wanted_level_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWantedLevelInfo</t>
+          <t>demo.TbWantedBehaveInfo</t>
         </is>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>demo.WantedLevelInfo</t>
+          <t>demo.WantedBehaveInfo</t>
         </is>
       </c>
       <c r="D38" s="6" t="b">
@@ -1245,19 +1245,19 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>wanted_level_info@wanted.xlsx</t>
+          <t>wanted_behave_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWantedBehaveInfo</t>
+          <t>demo.TbTalentNode</t>
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>demo.WantedBehaveInfo</t>
+          <t>demo.TalentNode</t>
         </is>
       </c>
       <c r="D39" s="6" t="b">
@@ -1265,19 +1265,29 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>wanted_behave_info@wanted.xlsx</t>
+          <t>talent@talent.xlsx</t>
+        </is>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>demo.TbTalentNode</t>
+          <t>demo.TbWantedGuardSpawnTier</t>
         </is>
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>demo.TalentNode</t>
+          <t>demo.WantedGuardSpawnTier</t>
         </is>
       </c>
       <c r="D40" s="6" t="b">
@@ -1285,29 +1295,19 @@
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>talent@talent.xlsx</t>
-        </is>
-      </c>
-      <c r="F40" s="6" t="inlineStr">
-        <is>
-          <t>node_id</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
+          <t>wanted_guard_spawn@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWantedGuardSpawnTier</t>
+          <t>demo.TbEntitySkillData</t>
         </is>
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>demo.WantedGuardSpawnTier</t>
+          <t>demo.EntitySkillData</t>
         </is>
       </c>
       <c r="D41" s="6" t="b">
@@ -1315,19 +1315,19 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>wanted_guard_spawn@wanted.xlsx</t>
+          <t>entity_skill@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>demo.TbEntitySkillData</t>
+          <t>demo.TbSkillSchool</t>
         </is>
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>demo.EntitySkillData</t>
+          <t>demo.SkillSchool</t>
         </is>
       </c>
       <c r="D42" s="6" t="b">
@@ -1335,19 +1335,21 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>entity_skill@skill.xlsx</t>
-        </is>
-      </c>
+          <t>skill_school@skill.xlsx</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n"/>
+      <c r="G42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSkillSchool</t>
+          <t>demo.TbSkillLearnEntry</t>
         </is>
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>demo.SkillSchool</t>
+          <t>demo.SkillLearnEntry</t>
         </is>
       </c>
       <c r="D43" s="6" t="b">
@@ -1355,21 +1357,19 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>skill_school@skill.xlsx</t>
-        </is>
-      </c>
-      <c r="F43" s="6" t="n"/>
-      <c r="G43" s="6" t="n"/>
+          <t>skill_learn@skill.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSkillLearnEntry</t>
+          <t>demo.TbDesireCrystalDef</t>
         </is>
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>demo.SkillLearnEntry</t>
+          <t>demo.DesireCrystalDef</t>
         </is>
       </c>
       <c r="D44" s="6" t="b">
@@ -1377,19 +1377,19 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>skill_learn@skill.xlsx</t>
+          <t>desire_crystal_def@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>demo.TbDesireCrystalDef</t>
+          <t>demo.TbMapDesireCrystalBudget</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>demo.DesireCrystalDef</t>
+          <t>demo.MapDesireCrystalBudget</t>
         </is>
       </c>
       <c r="D45" s="6" t="b">
@@ -1397,19 +1397,19 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>desire_crystal_def@desire_crystal.xlsx</t>
+          <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMapDesireCrystalBudget</t>
+          <t>demo.TbMapWalkerDesireCrystalQuota</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>demo.MapDesireCrystalBudget</t>
+          <t>demo.MapWalkerDesireCrystalQuota</t>
         </is>
       </c>
       <c r="D46" s="6" t="b">
@@ -1417,19 +1417,19 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
+          <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMapWalkerDesireCrystalQuota</t>
+          <t>demo.TbNamedNpcDesireCrystal</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>demo.MapWalkerDesireCrystalQuota</t>
+          <t>demo.NamedNpcDesireCrystal</t>
         </is>
       </c>
       <c r="D47" s="6" t="b">
@@ -1437,19 +1437,19 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
+          <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="6" t="inlineStr">
         <is>
-          <t>demo.TbNamedNpcDesireCrystal</t>
+          <t>demo.TbSpiritMonsterTypeBudget</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>demo.NamedNpcDesireCrystal</t>
+          <t>demo.SpiritMonsterTypeBudget</t>
         </is>
       </c>
       <c r="D48" s="6" t="b">
@@ -1457,19 +1457,19 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
+          <t>spirit_monster_budget@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSpiritMonsterTypeBudget</t>
+          <t>demo.TbContainerItemStackOverride</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>demo.SpiritMonsterTypeBudget</t>
+          <t>demo.ContainerItemStackOverride</t>
         </is>
       </c>
       <c r="D49" s="6" t="b">
@@ -1477,19 +1477,19 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>spirit_monster_budget@player_status.xlsx</t>
+          <t>container_item_stack_override@container_stack.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>demo.TbContainerItemStackOverride</t>
+          <t>demo.TbContainerStackTagRule</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>demo.ContainerItemStackOverride</t>
+          <t>demo.ContainerStackTagRule</t>
         </is>
       </c>
       <c r="D50" s="6" t="b">
@@ -1497,19 +1497,19 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>container_item_stack_override@container_stack.xlsx</t>
+          <t>container_stack_tag_rule@container_stack.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="6" t="inlineStr">
         <is>
-          <t>demo.TbContainerStackTagRule</t>
+          <t>demo.TbMapAreaEffect</t>
         </is>
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>demo.ContainerStackTagRule</t>
+          <t>demo.MapAreaEffect</t>
         </is>
       </c>
       <c r="D51" s="6" t="b">
@@ -1517,19 +1517,19 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>container_stack_tag_rule@container_stack.xlsx</t>
+          <t>map_area_effect@map_area_effect.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMapAreaEffect</t>
+          <t>demo.TbFallenAmountProgressInfo</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>demo.MapAreaEffect</t>
+          <t>demo.FallenAmountProgressInfo</t>
         </is>
       </c>
       <c r="D52" s="6" t="b">
@@ -1537,19 +1537,19 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>map_area_effect@map_area_effect.xlsx</t>
+          <t>fallen_amount_progress_info@fallen_amount_progress_info.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="6" t="inlineStr">
         <is>
-          <t>demo.TbFallenAmountProgressInfo</t>
+          <t>demo.TbRumorIntel</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>demo.FallenAmountProgressInfo</t>
+          <t>demo.RumorIntel</t>
         </is>
       </c>
       <c r="D53" s="6" t="b">
@@ -1557,19 +1557,19 @@
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>fallen_amount_progress_info@fallen_amount_progress_info.xlsx</t>
+          <t>rumor_intel@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRumorIntel</t>
+          <t>demo.TbRumorRandomPool</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>demo.RumorIntel</t>
+          <t>demo.RumorRandomPool</t>
         </is>
       </c>
       <c r="D54" s="6" t="b">
@@ -1577,19 +1577,19 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>rumor_intel@rumor_tables.xlsx</t>
+          <t>rumor_random_pool@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRumorRandomPool</t>
+          <t>demo.TbRumorGlobal</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>demo.RumorRandomPool</t>
+          <t>demo.RumorGlobal</t>
         </is>
       </c>
       <c r="D55" s="6" t="b">
@@ -1597,19 +1597,19 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>rumor_random_pool@rumor_tables.xlsx</t>
+          <t>rumor_global@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRumorGlobal</t>
+          <t>demo.TbCharacterInfo</t>
         </is>
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>demo.RumorGlobal</t>
+          <t>demo.CharacterInfo</t>
         </is>
       </c>
       <c r="D56" s="6" t="b">
@@ -1617,19 +1617,19 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>rumor_global@rumor_tables.xlsx</t>
+          <t>character_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="6" t="inlineStr">
         <is>
-          <t>demo.TbCharacterInfo</t>
+          <t>demo.TbCharacterFavorInfo</t>
         </is>
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>demo.CharacterInfo</t>
+          <t>demo.CharacterFavorInfo</t>
         </is>
       </c>
       <c r="D57" s="6" t="b">
@@ -1637,19 +1637,19 @@
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>character_info@character.xlsx</t>
+          <t>character_favor_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="6" t="inlineStr">
         <is>
-          <t>demo.TbCharacterFavorInfo</t>
+          <t>demo.TbMicroPlotDef</t>
         </is>
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>demo.CharacterFavorInfo</t>
+          <t>demo.MicroPlotDef</t>
         </is>
       </c>
       <c r="D58" s="6" t="b">
@@ -1657,19 +1657,19 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>character_favor_info@character.xlsx</t>
+          <t>micro_plot_def@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMicroPlotDef</t>
+          <t>demo.TbMapMicroPlotTrigger</t>
         </is>
       </c>
       <c r="C59" s="6" t="inlineStr">
         <is>
-          <t>demo.MicroPlotDef</t>
+          <t>demo.MapMicroPlotTrigger</t>
         </is>
       </c>
       <c r="D59" s="6" t="b">
@@ -1677,19 +1677,19 @@
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>micro_plot_def@micro_plot.xlsx</t>
+          <t>map_micro_plot_trigger@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMapMicroPlotTrigger</t>
+          <t>demo.TbMicroPlotTimelineEvent</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
         <is>
-          <t>demo.MapMicroPlotTrigger</t>
+          <t>demo.MicroPlotTimelineEvent</t>
         </is>
       </c>
       <c r="D60" s="6" t="b">
@@ -1697,19 +1697,19 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>map_micro_plot_trigger@micro_plot.xlsx</t>
+          <t>micro_plot_timeline_event@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMicroPlotTimelineEvent</t>
+          <t>demo.TbTrapSpec</t>
         </is>
       </c>
       <c r="C61" s="6" t="inlineStr">
         <is>
-          <t>demo.MicroPlotTimelineEvent</t>
+          <t>demo.TrapSpec</t>
         </is>
       </c>
       <c r="D61" s="6" t="b">
@@ -1717,19 +1717,19 @@
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>micro_plot_timeline_event@micro_plot.xlsx</t>
+          <t>trap_spec@trap_spec.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="6" t="inlineStr">
         <is>
-          <t>demo.TbTrapSpec</t>
+          <t>demo.TbForgeRecipe</t>
         </is>
       </c>
       <c r="C62" s="6" t="inlineStr">
         <is>
-          <t>demo.TrapSpec</t>
+          <t>demo.ForgeRecipe</t>
         </is>
       </c>
       <c r="D62" s="6" t="b">
@@ -1737,19 +1737,19 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>trap_spec@trap_spec.xlsx</t>
+          <t>forge_recipe@forge_recipe.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>demo.TbForgeRecipe</t>
+          <t>demo.TbHActInfo</t>
         </is>
       </c>
       <c r="C63" s="6" t="inlineStr">
         <is>
-          <t>demo.ForgeRecipe</t>
+          <t>demo.HActInfo</t>
         </is>
       </c>
       <c r="D63" s="6" t="b">
@@ -1757,19 +1757,19 @@
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>forge_recipe@forge_recipe.xlsx</t>
+          <t>h_act_info@h_act_info.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHActInfo</t>
+          <t>demo.TbTalentNodeLevel</t>
         </is>
       </c>
       <c r="C64" s="6" t="inlineStr">
         <is>
-          <t>demo.HActInfo</t>
+          <t>demo.TalentNodeLevel</t>
         </is>
       </c>
       <c r="D64" s="6" t="b">
@@ -1777,19 +1777,29 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>h_act_info@h_act_info.xlsx</t>
+          <t>talent_level@talent.xlsx</t>
+        </is>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>node_id+level</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>demo.TbTalentNodeLevel</t>
+          <t>demo.TbSavePoint</t>
         </is>
       </c>
       <c r="C65" s="6" t="inlineStr">
         <is>
-          <t>demo.TalentNodeLevel</t>
+          <t>demo.SavePoint</t>
         </is>
       </c>
       <c r="D65" s="6" t="b">
@@ -1797,29 +1807,19 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>talent_level@talent.xlsx</t>
-        </is>
-      </c>
-      <c r="F65" s="6" t="inlineStr">
-        <is>
-          <t>node_id+level</t>
-        </is>
-      </c>
-      <c r="G65" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>save_point@save_point.xlsx</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSavePoint</t>
+          <t>demo.TbReviveRule</t>
         </is>
       </c>
       <c r="C66" s="6" t="inlineStr">
         <is>
-          <t>demo.SavePoint</t>
+          <t>demo.ReviveRule</t>
         </is>
       </c>
       <c r="D66" s="6" t="b">
@@ -1827,19 +1827,24 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>save_point@save_point.xlsx</t>
+          <t>revive_rule@revive_rule.xlsx</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>demo.TbReviveRule</t>
+          <t>demo.TbDesireDensityTier</t>
         </is>
       </c>
       <c r="C67" s="6" t="inlineStr">
         <is>
-          <t>demo.ReviveRule</t>
+          <t>demo.DesireDensityTier</t>
         </is>
       </c>
       <c r="D67" s="6" t="b">
@@ -1847,24 +1852,19 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>revive_rule@revive_rule.xlsx</t>
-        </is>
-      </c>
-      <c r="G67" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>desire_density_tier@desire_density_tier.xlsx</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>demo.TbDesireDensityTier</t>
+          <t>demo.TbMindFragmentPoolEntry</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
         <is>
-          <t>demo.DesireDensityTier</t>
+          <t>demo.MindFragmentPoolEntry</t>
         </is>
       </c>
       <c r="D68" s="6" t="b">
@@ -1872,19 +1872,24 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>desire_density_tier@desire_density_tier.xlsx</t>
+          <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>demo.TbMindFragmentPoolEntry</t>
+          <t>demo.TbSecretBaseFacility</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
         <is>
-          <t>demo.MindFragmentPoolEntry</t>
+          <t>demo.SecretBaseFacility</t>
         </is>
       </c>
       <c r="D69" s="6" t="b">
@@ -1892,24 +1897,24 @@
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
-        </is>
-      </c>
-      <c r="G69" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>secret_base_facility@secret_base_facility.xlsx</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>据点固定设施</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSecretBaseFacility</t>
+          <t>demo.TbSecretBaseBuildLevel</t>
         </is>
       </c>
       <c r="C70" s="6" t="inlineStr">
         <is>
-          <t>demo.SecretBaseFacility</t>
+          <t>demo.SecretBaseBuildLevel</t>
         </is>
       </c>
       <c r="D70" s="6" t="b">
@@ -1917,24 +1922,34 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>secret_base_facility@secret_base_facility.xlsx</t>
+          <t>secret_base_build_level@secret_base_build_level.xlsx</t>
+        </is>
+      </c>
+      <c r="F70" s="6" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
       <c r="I70" s="6" t="inlineStr">
         <is>
-          <t>据点固定设施</t>
+          <t>据点建设等级卷轴边界</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSecretBaseBuildLevel</t>
+          <t>demo.TbSecretBaseCharacter</t>
         </is>
       </c>
       <c r="C71" s="6" t="inlineStr">
         <is>
-          <t>demo.SecretBaseBuildLevel</t>
+          <t>demo.SecretBaseCharacter</t>
         </is>
       </c>
       <c r="D71" s="6" t="b">
@@ -1942,12 +1957,12 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>secret_base_build_level@secret_base_build_level.xlsx</t>
+          <t>secret_base_character@secret_base_character.xlsx</t>
         </is>
       </c>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>level</t>
+          <t>slot_id</t>
         </is>
       </c>
       <c r="G71" s="6" t="inlineStr">
@@ -1957,19 +1972,19 @@
       </c>
       <c r="I71" s="6" t="inlineStr">
         <is>
-          <t>据点建设等级卷轴边界</t>
+          <t>秘密据点角色</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSecretBaseCharacter</t>
+          <t>demo.TbHumanWeapon</t>
         </is>
       </c>
       <c r="C72" s="6" t="inlineStr">
         <is>
-          <t>demo.SecretBaseCharacter</t>
+          <t>demo.HumanWeapon</t>
         </is>
       </c>
       <c r="D72" s="6" t="b">
@@ -1977,12 +1992,12 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>secret_base_character@secret_base_character.xlsx</t>
+          <t>human_weapon@human_weapon.xlsx</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>slot_id</t>
+          <t>item_id</t>
         </is>
       </c>
       <c r="G72" s="6" t="inlineStr">
@@ -1992,19 +2007,19 @@
       </c>
       <c r="I72" s="6" t="inlineStr">
         <is>
-          <t>秘密据点角色</t>
+          <t>human_weapon</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHumanWeapon</t>
+          <t>demo.TbRuneData</t>
         </is>
       </c>
       <c r="C73" s="6" t="inlineStr">
         <is>
-          <t>demo.HumanWeapon</t>
+          <t>demo.RuneData</t>
         </is>
       </c>
       <c r="D73" s="6" t="b">
@@ -2012,34 +2027,20 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>human_weapon@human_weapon.xlsx</t>
-        </is>
-      </c>
-      <c r="F73" s="6" t="inlineStr">
-        <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G73" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I73" s="6" t="inlineStr">
-        <is>
-          <t>human_weapon</t>
-        </is>
-      </c>
+          <t>rune_data@rune.xlsx</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="n"/>
     </row>
     <row r="74">
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRuneData</t>
+          <t>demo.TbBodyPartDef</t>
         </is>
       </c>
       <c r="C74" s="6" t="inlineStr">
         <is>
-          <t>demo.RuneData</t>
+          <t>demo.BodyPartDef</t>
         </is>
       </c>
       <c r="D74" s="6" t="b">
@@ -2047,20 +2048,19 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>rune_data@rune.xlsx</t>
-        </is>
-      </c>
-      <c r="G74" s="6" t="n"/>
+          <t>body_part_def@body_part.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>demo.TbBodyPartDef</t>
+          <t>demo.TbBodyPartLevel</t>
         </is>
       </c>
       <c r="C75" s="6" t="inlineStr">
         <is>
-          <t>demo.BodyPartDef</t>
+          <t>demo.BodyPartLevel</t>
         </is>
       </c>
       <c r="D75" s="6" t="b">
@@ -2068,19 +2068,29 @@
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>body_part_def@body_part.xlsx</t>
+          <t>body_part_level@body_part.xlsx</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>part_id+level</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>demo.TbBodyPartLevel</t>
+          <t>demo.TbBodyPartProgressInfo</t>
         </is>
       </c>
       <c r="C76" s="6" t="inlineStr">
         <is>
-          <t>demo.BodyPartLevel</t>
+          <t>demo.BodyPartProgressInfo</t>
         </is>
       </c>
       <c r="D76" s="6" t="b">
@@ -2088,29 +2098,20 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>body_part_level@body_part.xlsx</t>
-        </is>
-      </c>
-      <c r="F76" s="6" t="inlineStr">
-        <is>
-          <t>part_id+level</t>
-        </is>
-      </c>
-      <c r="G76" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
+          <t>body_part_progress_info@body_part.xlsx</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="n"/>
     </row>
     <row r="77">
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>demo.TbBodyPartProgressInfo</t>
+          <t>demo.TbPartLocalAttrDef</t>
         </is>
       </c>
       <c r="C77" s="6" t="inlineStr">
         <is>
-          <t>demo.BodyPartProgressInfo</t>
+          <t>demo.PartLocalAttrDef</t>
         </is>
       </c>
       <c r="D77" s="6" t="b">
@@ -2118,20 +2119,22 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>body_part_progress_info@body_part.xlsx</t>
-        </is>
-      </c>
+          <t>part_local_attr_def@body_part.xlsx</t>
+        </is>
+      </c>
+      <c r="F77" s="6" t="n"/>
+      <c r="G77" s="6" t="n"/>
       <c r="I77" s="6" t="n"/>
     </row>
     <row r="78">
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPartLocalAttrDef</t>
+          <t>demo.TbPartGear</t>
         </is>
       </c>
       <c r="C78" s="6" t="inlineStr">
         <is>
-          <t>demo.PartLocalAttrDef</t>
+          <t>demo.PartGear</t>
         </is>
       </c>
       <c r="D78" s="6" t="b">
@@ -2139,22 +2142,29 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>part_local_attr_def@body_part.xlsx</t>
-        </is>
-      </c>
-      <c r="F78" s="6" t="n"/>
-      <c r="G78" s="6" t="n"/>
-      <c r="I78" s="6" t="n"/>
+          <t>partgear@partgear.xlsx</t>
+        </is>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G78" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPartGear</t>
+          <t>demo.TbRuneUpgradeInfo</t>
         </is>
       </c>
       <c r="C79" s="6" t="inlineStr">
         <is>
-          <t>demo.PartGear</t>
+          <t>demo.RuneUpgradeInfo</t>
         </is>
       </c>
       <c r="D79" s="6" t="b">
@@ -2162,29 +2172,31 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>partgear@partgear.xlsx</t>
+          <t>rune_upgrade_info@rune.xlsx</t>
         </is>
       </c>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G79" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
+          <t>upgrade_id</t>
+        </is>
+      </c>
+      <c r="G79" s="6" t="n"/>
+      <c r="I79" s="6" t="n"/>
+      <c r="J79" s="6" t="inlineStr">
+        <is>
+          <t>符文升级项</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRuneUpgradeInfo</t>
+          <t>demo.TbRuneEquipSlot</t>
         </is>
       </c>
       <c r="C80" s="6" t="inlineStr">
         <is>
-          <t>demo.RuneUpgradeInfo</t>
+          <t>demo.RuneEquipSlotInfo</t>
         </is>
       </c>
       <c r="D80" s="6" t="b">
@@ -2192,31 +2204,31 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>rune_upgrade_info@rune.xlsx</t>
+          <t>rune_equip_slot@rune.xlsx</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>upgrade_id</t>
+          <t>equip_slot</t>
         </is>
       </c>
       <c r="G80" s="6" t="n"/>
       <c r="I80" s="6" t="n"/>
       <c r="J80" s="6" t="inlineStr">
         <is>
-          <t>符文升级项</t>
+          <t>符文装配槽</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>demo.TbRuneEquipSlot</t>
+          <t>demo.TbEntitySkillLevel</t>
         </is>
       </c>
       <c r="C81" s="6" t="inlineStr">
         <is>
-          <t>demo.RuneEquipSlotInfo</t>
+          <t>demo.EntitySkillLevel</t>
         </is>
       </c>
       <c r="D81" s="6" t="b">
@@ -2224,31 +2236,29 @@
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>rune_equip_slot@rune.xlsx</t>
+          <t>skill_level@skill.xlsx</t>
         </is>
       </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>equip_slot</t>
-        </is>
-      </c>
-      <c r="G81" s="6" t="n"/>
-      <c r="I81" s="6" t="n"/>
-      <c r="J81" s="6" t="inlineStr">
-        <is>
-          <t>符文装配槽</t>
+          <t>skill_id+level</t>
+        </is>
+      </c>
+      <c r="G81" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>demo.TbEntitySkillLevel</t>
+          <t>demo.TbJingYuanCodexDef</t>
         </is>
       </c>
       <c r="C82" s="6" t="inlineStr">
         <is>
-          <t>demo.EntitySkillLevel</t>
+          <t>demo.JingYuanCodexDef</t>
         </is>
       </c>
       <c r="D82" s="6" t="b">
@@ -2256,29 +2266,24 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>skill_level@skill.xlsx</t>
+          <t>jingyuan_codex_def@jingyuan_codex.xlsx</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>skill_id+level</t>
-        </is>
-      </c>
-      <c r="G82" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>codex_id</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHomesteadBuilding</t>
+          <t>demo.TbJingYuanCodexLevel</t>
         </is>
       </c>
       <c r="C83" s="6" t="inlineStr">
         <is>
-          <t>demo.HomesteadBuilding</t>
+          <t>demo.JingYuanCodexLevel</t>
         </is>
       </c>
       <c r="D83" s="6" t="b">
@@ -2286,34 +2291,29 @@
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>homestead_building@map_homestead.xlsx</t>
+          <t>jingyuan_codex_level@jingyuan_codex.xlsx</t>
         </is>
       </c>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>logic_area_id+building_id</t>
+          <t>codex_id+level</t>
         </is>
       </c>
       <c r="G83" s="6" t="inlineStr">
         <is>
           <t>list</t>
-        </is>
-      </c>
-      <c r="I83" s="6" t="inlineStr">
-        <is>
-          <t>逻辑区域可管理建筑</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHomesteadBuildingUpgrade</t>
+          <t>demo.TbJingYuanTuneTier</t>
         </is>
       </c>
       <c r="C84" s="6" t="inlineStr">
         <is>
-          <t>demo.HomesteadBuildingUpgrade</t>
+          <t>demo.JingYuanTuneTier</t>
         </is>
       </c>
       <c r="D84" s="6" t="b">
@@ -2321,34 +2321,29 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>homestead_building_upgrade@map_homestead.xlsx</t>
+          <t>jingyuan_tune_tier@jingyuan_codex.xlsx</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>logic_area_id+building_id+level</t>
+          <t>codex_id+tier</t>
         </is>
       </c>
       <c r="G84" s="6" t="inlineStr">
         <is>
           <t>list</t>
-        </is>
-      </c>
-      <c r="I84" s="6" t="inlineStr">
-        <is>
-          <t>家园建筑升级项</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanCodexDef</t>
+          <t>demo.TbTiaoJingConcentrationLevel</t>
         </is>
       </c>
       <c r="C85" s="6" t="inlineStr">
         <is>
-          <t>demo.JingYuanCodexDef</t>
+          <t>demo.TiaoJingConcentrationLevel</t>
         </is>
       </c>
       <c r="D85" s="6" t="b">
@@ -2356,24 +2351,21 @@
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>jingyuan_codex_def@jingyuan_codex.xlsx</t>
-        </is>
-      </c>
-      <c r="F85" s="6" t="inlineStr">
-        <is>
-          <t>codex_id</t>
-        </is>
-      </c>
+          <t>tiao_jing_concentration_level@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F85" s="6" t="n"/>
+      <c r="J85" s="6" t="n"/>
     </row>
     <row r="86">
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanCodexLevel</t>
+          <t>demo.TbJingYuanTypeDef</t>
         </is>
       </c>
       <c r="C86" s="6" t="inlineStr">
         <is>
-          <t>demo.JingYuanCodexLevel</t>
+          <t>demo.JingYuanTypeDef</t>
         </is>
       </c>
       <c r="D86" s="6" t="b">
@@ -2381,29 +2373,25 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>jingyuan_codex_level@jingyuan_codex.xlsx</t>
+          <t>jingyuan_type_def@jingyuan_codex.xlsx</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>codex_id+level</t>
-        </is>
-      </c>
-      <c r="G86" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
-        </is>
-      </c>
+          <t>type_id</t>
+        </is>
+      </c>
+      <c r="J86" s="6" t="n"/>
     </row>
     <row r="87">
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanTuneTier</t>
+          <t>demo.TbJingYuanTypePoolEntry</t>
         </is>
       </c>
       <c r="C87" s="6" t="inlineStr">
         <is>
-          <t>demo.JingYuanTuneTier</t>
+          <t>demo.JingYuanTypePoolEntry</t>
         </is>
       </c>
       <c r="D87" s="6" t="b">
@@ -2411,14 +2399,10 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>jingyuan_tune_tier@jingyuan_codex.xlsx</t>
-        </is>
-      </c>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>codex_id+tier</t>
-        </is>
-      </c>
+          <t>jingyuan_type_pool@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F87" s="6" t="n"/>
       <c r="G87" s="6" t="inlineStr">
         <is>
           <t>list</t>
@@ -2428,12 +2412,12 @@
     <row r="88">
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>demo.TbTiaoJingConcentrationLevel</t>
+          <t>demo.TbProgressionHubTab</t>
         </is>
       </c>
       <c r="C88" s="6" t="inlineStr">
         <is>
-          <t>demo.TiaoJingConcentrationLevel</t>
+          <t>demo.ProgressionHubTabDef</t>
         </is>
       </c>
       <c r="D88" s="6" t="b">
@@ -2441,21 +2425,34 @@
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>tiao_jing_concentration_level@jingyuan_codex.xlsx</t>
-        </is>
-      </c>
-      <c r="F88" s="6" t="n"/>
-      <c r="J88" s="6" t="n"/>
+          <t>progression_hub_tab@progression_hub_tab.xlsx</t>
+        </is>
+      </c>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>tab_id</t>
+        </is>
+      </c>
+      <c r="G88" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I88" s="6" t="inlineStr">
+        <is>
+          <t>养成总面板选项卡</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanTypeDef</t>
+          <t>demo.TbPlayerAttachInfo</t>
         </is>
       </c>
       <c r="C89" s="6" t="inlineStr">
         <is>
-          <t>demo.JingYuanTypeDef</t>
+          <t>demo.PlayerAttachInfo</t>
         </is>
       </c>
       <c r="D89" s="6" t="b">
@@ -2463,25 +2460,22 @@
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>jingyuan_type_def@jingyuan_codex.xlsx</t>
-        </is>
-      </c>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>type_id</t>
-        </is>
-      </c>
-      <c r="J89" s="6" t="n"/>
+          <t>player_attach@player_attach.xlsx</t>
+        </is>
+      </c>
+      <c r="F89" s="6" t="n"/>
+      <c r="G89" s="6" t="n"/>
+      <c r="I89" s="6" t="n"/>
     </row>
     <row r="90">
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>demo.TbJingYuanTypePoolEntry</t>
+          <t>demo.TbItemDismantle</t>
         </is>
       </c>
       <c r="C90" s="6" t="inlineStr">
         <is>
-          <t>demo.JingYuanTypePoolEntry</t>
+          <t>demo.ItemDismantle</t>
         </is>
       </c>
       <c r="D90" s="6" t="b">
@@ -2489,25 +2483,34 @@
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>jingyuan_type_pool@jingyuan_codex.xlsx</t>
-        </is>
-      </c>
-      <c r="F90" s="6" t="n"/>
+          <t>item_dismantle@item_dismantle.xlsx</t>
+        </is>
+      </c>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
       <c r="G90" s="6" t="inlineStr">
         <is>
-          <t>list</t>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="I90" s="6" t="inlineStr">
+        <is>
+          <t>物品分解产物配置</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>demo.TbProgressionHubTab</t>
+          <t>demo.TbItemTagInfo</t>
         </is>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>demo.ProgressionHubTabDef</t>
+          <t>demo.ItemTagInfo</t>
         </is>
       </c>
       <c r="D91" s="6" t="b">
@@ -2515,34 +2518,35 @@
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>progression_hub_tab@progression_hub_tab.xlsx</t>
+          <t>item_tag@item_define.xlsx</t>
         </is>
       </c>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>tab_id</t>
-        </is>
-      </c>
-      <c r="G91" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
+          <t>tag</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="n"/>
+      <c r="H91" s="6" t="inlineStr">
+        <is>
+          <t>c,s</t>
         </is>
       </c>
       <c r="I91" s="6" t="inlineStr">
         <is>
-          <t>养成总面板选项卡</t>
+          <t>物品标签元数据：显示字、隐藏控制、实例需求</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerAttachInfo</t>
+          <t>demo.TbPlayerBagDef</t>
         </is>
       </c>
       <c r="C92" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerAttachInfo</t>
+          <t>demo.PlayerBagDef</t>
         </is>
       </c>
       <c r="D92" s="6" t="b">
@@ -2550,22 +2554,26 @@
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>player_attach@player_attach.xlsx</t>
+          <t>player_bag@player_bag.xlsx</t>
         </is>
       </c>
       <c r="F92" s="6" t="n"/>
       <c r="G92" s="6" t="n"/>
-      <c r="I92" s="6" t="n"/>
+      <c r="I92" s="6" t="inlineStr">
+        <is>
+          <t>玩家背包定义</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>demo.TbItemDismantle</t>
+          <t>demo.TbWarehouseFilter</t>
         </is>
       </c>
       <c r="C93" s="6" t="inlineStr">
         <is>
-          <t>demo.ItemDismantle</t>
+          <t>demo.WarehouseFilter</t>
         </is>
       </c>
       <c r="D93" s="6" t="b">
@@ -2573,34 +2581,24 @@
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>item_dismantle@item_dismantle.xlsx</t>
-        </is>
-      </c>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>item_id</t>
-        </is>
-      </c>
-      <c r="G93" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
+          <t>warehouse_filter@warehouse_filter.xlsx</t>
         </is>
       </c>
       <c r="I93" s="6" t="inlineStr">
         <is>
-          <t>物品分解产物配置</t>
+          <t>仓库筛选定义</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>demo.TbItemTagInfo</t>
+          <t>demo.TbCharacterGiftRule</t>
         </is>
       </c>
       <c r="C94" s="6" t="inlineStr">
         <is>
-          <t>demo.ItemTagInfo</t>
+          <t>demo.CharacterGiftRule</t>
         </is>
       </c>
       <c r="D94" s="6" t="b">
@@ -2608,35 +2606,34 @@
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>item_tag@item.xlsx</t>
+          <t>character_gift_rule@character.xlsx</t>
         </is>
       </c>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>tag</t>
-        </is>
-      </c>
-      <c r="G94" s="6" t="n"/>
-      <c r="H94" s="6" t="inlineStr">
-        <is>
-          <t>c,s</t>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
       <c r="I94" s="6" t="inlineStr">
         <is>
-          <t>物品标签元数据：显示字、隐藏控制、实例需求</t>
+          <t>角色礼物固定覆盖规则</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>demo.TbPlayerBagDef</t>
+          <t>demo.TbTalentTree</t>
         </is>
       </c>
       <c r="C95" s="6" t="inlineStr">
         <is>
-          <t>demo.PlayerBagDef</t>
+          <t>demo.TalentTree</t>
         </is>
       </c>
       <c r="D95" s="6" t="b">
@@ -2644,26 +2641,34 @@
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>player_bag@player_bag.xlsx</t>
-        </is>
-      </c>
-      <c r="F95" s="6" t="n"/>
-      <c r="G95" s="6" t="n"/>
+          <t>talent_tree@talent.xlsx</t>
+        </is>
+      </c>
+      <c r="F95" s="6" t="inlineStr">
+        <is>
+          <t>tree_id</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
       <c r="I95" s="6" t="inlineStr">
         <is>
-          <t>玩家背包定义</t>
+          <t>天赋树定义</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>demo.TbWarehouseFilter</t>
+          <t>demo.TbSecretBaseCharacterOption</t>
         </is>
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
-          <t>demo.WarehouseFilter</t>
+          <t>demo.SecretBaseCharacterOption</t>
         </is>
       </c>
       <c r="D96" s="6" t="b">
@@ -2671,24 +2676,34 @@
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>warehouse_filter@warehouse_filter.xlsx</t>
+          <t>secret_base_character_option@secret_base_character.xlsx</t>
+        </is>
+      </c>
+      <c r="F96" s="6" t="inlineStr">
+        <is>
+          <t>option_id</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
         </is>
       </c>
       <c r="I96" s="6" t="inlineStr">
         <is>
-          <t>仓库筛选定义</t>
+          <t>秘密据点角色自定义选项</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>demo.TbCharacterGiftRule</t>
+          <t>demo.TbHumanCivilizationLevel</t>
         </is>
       </c>
       <c r="C97" s="6" t="inlineStr">
         <is>
-          <t>demo.CharacterGiftRule</t>
+          <t>demo.HumanCivilizationLevel</t>
         </is>
       </c>
       <c r="D97" s="6" t="b">
@@ -2696,34 +2711,24 @@
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>character_gift_rule@character.xlsx</t>
+          <t>civilization_level@human_civilization.xlsx</t>
         </is>
       </c>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G97" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I97" s="6" t="inlineStr">
-        <is>
-          <t>角色礼物固定覆盖规则</t>
+          <t>level</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>demo.TbTalentTree</t>
+          <t>demo.TbHumanTechTree</t>
         </is>
       </c>
       <c r="C98" s="6" t="inlineStr">
         <is>
-          <t>demo.TalentTree</t>
+          <t>demo.HumanTechTree</t>
         </is>
       </c>
       <c r="D98" s="6" t="b">
@@ -2731,7 +2736,7 @@
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>talent_tree@talent.xlsx</t>
+          <t>human_tech_tree@human_tech.xlsx</t>
         </is>
       </c>
       <c r="F98" s="6" t="inlineStr">
@@ -2739,26 +2744,18 @@
           <t>tree_id</t>
         </is>
       </c>
-      <c r="G98" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>天赋树定义</t>
-        </is>
-      </c>
+      <c r="G98" s="6" t="n"/>
+      <c r="I98" s="6" t="n"/>
     </row>
     <row r="99">
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>demo.TbSecretBaseCharacterOption</t>
+          <t>demo.TbHumanTechNode</t>
         </is>
       </c>
       <c r="C99" s="6" t="inlineStr">
         <is>
-          <t>demo.SecretBaseCharacterOption</t>
+          <t>demo.HumanTechNode</t>
         </is>
       </c>
       <c r="D99" s="6" t="b">
@@ -2766,34 +2763,26 @@
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>secret_base_character_option@secret_base_character.xlsx</t>
+          <t>human_tech@human_tech.xlsx</t>
         </is>
       </c>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>option_id</t>
-        </is>
-      </c>
-      <c r="G99" s="6" t="inlineStr">
-        <is>
-          <t>map</t>
-        </is>
-      </c>
-      <c r="I99" s="6" t="inlineStr">
-        <is>
-          <t>秘密据点角色自定义选项</t>
-        </is>
-      </c>
+          <t>node_id</t>
+        </is>
+      </c>
+      <c r="H99" s="6" t="n"/>
+      <c r="I99" s="6" t="n"/>
     </row>
     <row r="100">
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHumanCivilizationLevel</t>
+          <t>demo.TbHumanTechNodeLevel</t>
         </is>
       </c>
       <c r="C100" s="6" t="inlineStr">
         <is>
-          <t>demo.HumanCivilizationLevel</t>
+          <t>demo.HumanTechNodeLevel</t>
         </is>
       </c>
       <c r="D100" s="6" t="b">
@@ -2801,24 +2790,25 @@
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>civilization_level@human_civilization.xlsx</t>
+          <t>human_tech_level@human_tech.xlsx</t>
         </is>
       </c>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>level</t>
-        </is>
-      </c>
+          <t>node_id+level</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="n"/>
     </row>
     <row r="101">
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHumanTechTree</t>
+          <t>demo.TbQuestAcceptDialog</t>
         </is>
       </c>
       <c r="C101" s="6" t="inlineStr">
         <is>
-          <t>demo.HumanTechTree</t>
+          <t>demo.QuestAcceptDialog</t>
         </is>
       </c>
       <c r="D101" s="6" t="b">
@@ -2826,26 +2816,20 @@
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>human_tech_tree@human_tech.xlsx</t>
-        </is>
-      </c>
-      <c r="F101" s="6" t="inlineStr">
-        <is>
-          <t>tree_id</t>
-        </is>
-      </c>
-      <c r="G101" s="6" t="n"/>
+          <t>quest_accept_dialog@dialog.xlsx</t>
+        </is>
+      </c>
       <c r="I101" s="6" t="n"/>
     </row>
     <row r="102" s="2">
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHumanTechNode</t>
+          <t>demo.TbQuestRemindDialog</t>
         </is>
       </c>
       <c r="C102" s="6" t="inlineStr">
         <is>
-          <t>demo.HumanTechNode</t>
+          <t>demo.QuestRemindDialog</t>
         </is>
       </c>
       <c r="D102" s="6" t="b">
@@ -2853,26 +2837,22 @@
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>human_tech@human_tech.xlsx</t>
-        </is>
-      </c>
-      <c r="F102" s="6" t="inlineStr">
-        <is>
-          <t>node_id</t>
-        </is>
-      </c>
-      <c r="H102" s="6" t="n"/>
+          <t>quest_remind_dialog@dialog.xlsx</t>
+        </is>
+      </c>
+      <c r="F102" s="6" t="n"/>
+      <c r="G102" s="6" t="n"/>
       <c r="I102" s="6" t="n"/>
     </row>
     <row r="103" s="2">
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>demo.TbHumanTechNodeLevel</t>
+          <t>demo.TbQuestObjectiveDialog</t>
         </is>
       </c>
       <c r="C103" s="6" t="inlineStr">
         <is>
-          <t>demo.HumanTechNodeLevel</t>
+          <t>demo.QuestObjectiveDialog</t>
         </is>
       </c>
       <c r="D103" s="6" t="b">
@@ -2880,25 +2860,22 @@
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>human_tech_level@human_tech.xlsx</t>
-        </is>
-      </c>
-      <c r="F103" s="6" t="inlineStr">
-        <is>
-          <t>node_id+level</t>
-        </is>
-      </c>
+          <t>quest_objective_dialog@dialog.xlsx</t>
+        </is>
+      </c>
+      <c r="F103" s="6" t="n"/>
+      <c r="G103" s="6" t="n"/>
       <c r="I103" s="6" t="n"/>
     </row>
     <row r="104">
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>demo.TbQuestAcceptDialog</t>
+          <t>demo.TbNpcRoutineProfile</t>
         </is>
       </c>
       <c r="C104" s="6" t="inlineStr">
         <is>
-          <t>demo.QuestAcceptDialog</t>
+          <t>demo.NpcRoutineProfile</t>
         </is>
       </c>
       <c r="D104" s="6" t="b">
@@ -2906,20 +2883,26 @@
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>quest_accept_dialog@dialog.xlsx</t>
-        </is>
-      </c>
+          <t>npc_routine_profile@npc_routine.xlsx</t>
+        </is>
+      </c>
+      <c r="F104" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="n"/>
       <c r="I104" s="6" t="n"/>
     </row>
     <row r="105">
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>demo.TbQuestRemindDialog</t>
+          <t>demo.TbNpcRoutineRule</t>
         </is>
       </c>
       <c r="C105" s="6" t="inlineStr">
         <is>
-          <t>demo.QuestRemindDialog</t>
+          <t>demo.NpcRoutineRule</t>
         </is>
       </c>
       <c r="D105" s="6" t="b">
@@ -2927,22 +2910,24 @@
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>quest_remind_dialog@dialog.xlsx</t>
-        </is>
-      </c>
-      <c r="F105" s="6" t="n"/>
-      <c r="G105" s="6" t="n"/>
-      <c r="I105" s="6" t="n"/>
+          <t>npc_routine_rule@npc_routine.xlsx</t>
+        </is>
+      </c>
+      <c r="F105" s="6" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>demo.TbQuestObjectiveDialog</t>
+          <t>demo.TbNpcRoutineBinding</t>
         </is>
       </c>
       <c r="C106" s="6" t="inlineStr">
         <is>
-          <t>demo.QuestObjectiveDialog</t>
+          <t>demo.NpcRoutineBinding</t>
         </is>
       </c>
       <c r="D106" s="6" t="b">
@@ -2950,22 +2935,29 @@
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>quest_objective_dialog@dialog.xlsx</t>
-        </is>
-      </c>
-      <c r="F106" s="6" t="n"/>
-      <c r="G106" s="6" t="n"/>
-      <c r="I106" s="6" t="n"/>
+          <t>npc_routine_binding@npc_routine.xlsx</t>
+        </is>
+      </c>
+      <c r="F106" s="6" t="inlineStr">
+        <is>
+          <t>map_variant+overlay_id+character_key</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>demo.TbNpcRoutineProfile</t>
+          <t>demo.TbCultTechNode</t>
         </is>
       </c>
       <c r="C107" s="6" t="inlineStr">
         <is>
-          <t>demo.NpcRoutineProfile</t>
+          <t>demo.CultTechNode</t>
         </is>
       </c>
       <c r="D107" s="6" t="b">
@@ -2973,26 +2965,20 @@
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>npc_routine_profile@npc_routine.xlsx</t>
-        </is>
-      </c>
-      <c r="F107" s="6" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
-      <c r="G107" s="6" t="n"/>
-      <c r="I107" s="6" t="n"/>
+          <t>cult_tech_node@cult_tech.xlsx</t>
+        </is>
+      </c>
+      <c r="F107" s="6" t="n"/>
     </row>
     <row r="108">
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>demo.TbNpcRoutineRule</t>
+          <t>demo.TbCultTechNodeLevel</t>
         </is>
       </c>
       <c r="C108" s="6" t="inlineStr">
         <is>
-          <t>demo.NpcRoutineRule</t>
+          <t>demo.CultTechNodeLevel</t>
         </is>
       </c>
       <c r="D108" s="6" t="b">
@@ -3000,24 +2986,24 @@
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>npc_routine_rule@npc_routine.xlsx</t>
+          <t>cult_tech_node_level@cult_tech.xlsx</t>
         </is>
       </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>id</t>
+          <t>node_id+level</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>demo.TbNpcRoutineBinding</t>
+          <t>demo.TbNpcLocomotionProfile</t>
         </is>
       </c>
       <c r="C109" s="6" t="inlineStr">
         <is>
-          <t>demo.NpcRoutineBinding</t>
+          <t>demo.NpcLocomotionProfile</t>
         </is>
       </c>
       <c r="D109" s="6" t="b">
@@ -3025,29 +3011,24 @@
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>npc_routine_binding@npc_routine.xlsx</t>
+          <t>npc_locomotion_profile@npc_routine.xlsx</t>
         </is>
       </c>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>map_variant+overlay_id+character_key</t>
-        </is>
-      </c>
-      <c r="G109" s="6" t="inlineStr">
-        <is>
-          <t>list</t>
+          <t>id</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>demo.TbCultTechNode</t>
+          <t>demo.TbFacilityDefinition</t>
         </is>
       </c>
       <c r="C110" s="6" t="inlineStr">
         <is>
-          <t>demo.CultTechNode</t>
+          <t>demo.FacilityDefinition</t>
         </is>
       </c>
       <c r="D110" s="6" t="b">
@@ -3055,20 +3036,24 @@
       </c>
       <c r="E110" s="6" t="inlineStr">
         <is>
-          <t>cult_tech_node@cult_tech.xlsx</t>
-        </is>
-      </c>
-      <c r="F110" s="6" t="n"/>
+          <t>facility_definition@facility_definition.xlsx</t>
+        </is>
+      </c>
+      <c r="F110" s="6" t="inlineStr">
+        <is>
+          <t>facility_id</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>demo.TbCultTechNodeLevel</t>
+          <t>demo.TbFacilityDevelopmentDefinition</t>
         </is>
       </c>
       <c r="C111" s="6" t="inlineStr">
         <is>
-          <t>demo.CultTechNodeLevel</t>
+          <t>demo.FacilityDevelopmentDefinition</t>
         </is>
       </c>
       <c r="D111" s="6" t="b">
@@ -3076,24 +3061,25 @@
       </c>
       <c r="E111" s="6" t="inlineStr">
         <is>
-          <t>cult_tech_node_level@cult_tech.xlsx</t>
+          <t>facility_development_definition@facility_development.xlsx</t>
         </is>
       </c>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>node_id+level</t>
-        </is>
-      </c>
+          <t>facility_id</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="n"/>
     </row>
     <row r="112">
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>demo.TbNpcLocomotionProfile</t>
+          <t>demo.TbFacilityDevelopmentLevel</t>
         </is>
       </c>
       <c r="C112" s="6" t="inlineStr">
         <is>
-          <t>demo.NpcLocomotionProfile</t>
+          <t>demo.FacilityDevelopmentLevel</t>
         </is>
       </c>
       <c r="D112" s="6" t="b">
@@ -3101,24 +3087,25 @@
       </c>
       <c r="E112" s="6" t="inlineStr">
         <is>
-          <t>npc_locomotion_profile@npc_routine.xlsx</t>
+          <t>facility_development_level@facility_development.xlsx</t>
         </is>
       </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>id</t>
-        </is>
-      </c>
+          <t>facility_id+level</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="n"/>
     </row>
     <row r="113">
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>demo.TbFacilityDefinition</t>
+          <t>demo.TbTownFacilitySite</t>
         </is>
       </c>
       <c r="C113" s="6" t="inlineStr">
         <is>
-          <t>demo.FacilityDefinition</t>
+          <t>demo.TownFacilitySite</t>
         </is>
       </c>
       <c r="D113" s="6" t="b">
@@ -3126,24 +3113,24 @@
       </c>
       <c r="E113" s="6" t="inlineStr">
         <is>
-          <t>facility_definition@facility_definition.xlsx</t>
+          <t>town_facility_site@facility_development.xlsx</t>
         </is>
       </c>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>facility_id</t>
+          <t>id</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>demo.TbFacilityDevelopmentDefinition</t>
+          <t>demo.TbFacilityRenovation</t>
         </is>
       </c>
       <c r="C114" s="6" t="inlineStr">
         <is>
-          <t>demo.FacilityDevelopmentDefinition</t>
+          <t>demo.FacilityRenovation</t>
         </is>
       </c>
       <c r="D114" s="6" t="b">
@@ -3151,98 +3138,42 @@
       </c>
       <c r="E114" s="6" t="inlineStr">
         <is>
-          <t>facility_development_definition@facility_development.xlsx</t>
+          <t>facility_renovation@facility_development.xlsx</t>
         </is>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>facility_id</t>
+          <t>facility_cfg_id+renovation_id</t>
         </is>
       </c>
       <c r="G114" s="6" t="n"/>
     </row>
     <row r="115">
-      <c r="B115" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbFacilityDevelopmentLevel</t>
-        </is>
-      </c>
-      <c r="C115" s="6" t="inlineStr">
-        <is>
-          <t>demo.FacilityDevelopmentLevel</t>
-        </is>
-      </c>
-      <c r="D115" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E115" s="6" t="inlineStr">
-        <is>
-          <t>facility_development_level@facility_development.xlsx</t>
-        </is>
-      </c>
-      <c r="F115" s="6" t="inlineStr">
-        <is>
-          <t>facility_id+level</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="n"/>
+      <c r="B115" s="6" t="n"/>
+      <c r="C115" s="6" t="n"/>
+      <c r="D115" s="6" t="n"/>
+      <c r="E115" s="6" t="n"/>
     </row>
     <row r="116">
-      <c r="B116" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbTownFacilitySite</t>
-        </is>
-      </c>
-      <c r="C116" s="6" t="inlineStr">
-        <is>
-          <t>demo.TownFacilitySite</t>
-        </is>
-      </c>
-      <c r="D116" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E116" s="6" t="inlineStr">
-        <is>
-          <t>town_facility_site@facility_development.xlsx</t>
-        </is>
-      </c>
-      <c r="F116" s="6" t="inlineStr">
-        <is>
-          <t>id</t>
-        </is>
-      </c>
+      <c r="B116" s="6" t="n"/>
+      <c r="C116" s="6" t="n"/>
+      <c r="D116" s="6" t="n"/>
+      <c r="E116" s="6" t="n"/>
+      <c r="F116" s="6" t="n"/>
     </row>
     <row r="117">
-      <c r="B117" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbFacilityRenovation</t>
-        </is>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>demo.FacilityRenovation</t>
-        </is>
-      </c>
-      <c r="D117" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E117" s="6" t="inlineStr">
-        <is>
-          <t>facility_renovation@facility_development.xlsx</t>
-        </is>
-      </c>
-      <c r="F117" s="6" t="inlineStr">
-        <is>
-          <t>facility_cfg_id+renovation_id</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="n"/>
+      <c r="B117" s="6" t="n"/>
+      <c r="C117" s="6" t="n"/>
+      <c r="D117" s="6" t="n"/>
+      <c r="E117" s="6" t="n"/>
+      <c r="F117" s="6" t="n"/>
     </row>
     <row r="118">
       <c r="B118" s="6" t="n"/>
       <c r="C118" s="6" t="n"/>
       <c r="D118" s="6" t="n"/>
       <c r="E118" s="6" t="n"/>
+      <c r="F118" s="6" t="n"/>
     </row>
     <row r="119">
       <c r="B119" s="6" t="n"/>
@@ -3266,48 +3197,99 @@
       <c r="F121" s="6" t="n"/>
     </row>
     <row r="122">
-      <c r="B122" s="6" t="n"/>
-      <c r="C122" s="6" t="n"/>
-      <c r="D122" s="6" t="n"/>
-      <c r="E122" s="6" t="n"/>
-      <c r="F122" s="6" t="n"/>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbCharacterFacilitySupervisor</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>demo.CharacterFacilitySupervisor</t>
+        </is>
+      </c>
+      <c r="D122" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E122" s="6" t="inlineStr">
+        <is>
+          <t>character_facility_supervisor@facility_development.xlsx</t>
+        </is>
+      </c>
+      <c r="F122" s="6" t="inlineStr">
+        <is>
+          <t>character_key</t>
+        </is>
+      </c>
     </row>
     <row r="123">
-      <c r="B123" s="6" t="n"/>
-      <c r="C123" s="6" t="n"/>
-      <c r="D123" s="6" t="n"/>
-      <c r="E123" s="6" t="n"/>
-      <c r="F123" s="6" t="n"/>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbHumanArmar</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>demo.HumanArmar</t>
+        </is>
+      </c>
+      <c r="D123" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E123" s="6" t="inlineStr">
+        <is>
+          <t>human_armar@human_armar.xlsx</t>
+        </is>
+      </c>
+      <c r="F123" s="6" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>map</t>
+        </is>
+      </c>
+      <c r="H123" s="6" t="n"/>
     </row>
     <row r="124">
-      <c r="B124" s="6" t="n"/>
-      <c r="C124" s="6" t="n"/>
-      <c r="D124" s="6" t="n"/>
-      <c r="E124" s="6" t="n"/>
-      <c r="F124" s="6" t="n"/>
-    </row>
-    <row r="125">
-      <c r="B125" s="6" t="inlineStr">
-        <is>
-          <t>demo.TbCharacterFacilitySupervisor</t>
-        </is>
-      </c>
-      <c r="C125" s="6" t="inlineStr">
-        <is>
-          <t>demo.CharacterFacilitySupervisor</t>
-        </is>
-      </c>
-      <c r="D125" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
-        <is>
-          <t>character_facility_supervisor@facility_development.xlsx</t>
-        </is>
-      </c>
-      <c r="F125" s="6" t="inlineStr">
-        <is>
-          <t>character_key</t>
+      <c r="A124" s="6" t="n"/>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbNpcViewRandomization</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>demo.NpcViewRandomization</t>
+        </is>
+      </c>
+      <c r="D124" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E124" s="6" t="inlineStr">
+        <is>
+          <t>npc_view_randomization@npc_view_randomization.xlsx</t>
+        </is>
+      </c>
+      <c r="F124" s="6" t="inlineStr">
+        <is>
+          <t>npc_id+view_prefab_name</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>list</t>
+        </is>
+      </c>
+      <c r="H124" s="6" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I124" s="6" t="inlineStr">
+        <is>
+          <t>?? NPC ?????</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -359,7 +359,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K124"/>
+  <dimension ref="A1:K135"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -3293,6 +3293,281 @@
         </is>
       </c>
     </row>
+    <row r="125">
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbCultAncientSeat</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>demo.CultAncientSeat</t>
+        </is>
+      </c>
+      <c r="D125" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E125" s="6" t="inlineStr">
+        <is>
+          <t>cult_ancient_seat@cult_ancient_seat.xlsx</t>
+        </is>
+      </c>
+      <c r="F125" s="6" t="inlineStr">
+        <is>
+          <t>seat_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbCultSeatTechNode</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>demo.CultSeatTechNode</t>
+        </is>
+      </c>
+      <c r="D126" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E126" s="6" t="inlineStr">
+        <is>
+          <t>cult_seat_tech_node@cult_ancient_seat.xlsx</t>
+        </is>
+      </c>
+      <c r="F126" s="6" t="inlineStr">
+        <is>
+          <t>node_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>demo.TbCultSeatTechNodeLevel</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>demo.CultSeatTechNodeLevel</t>
+        </is>
+      </c>
+      <c r="D127" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E127" s="6" t="inlineStr">
+        <is>
+          <t>cult_seat_tech_node_level@cult_ancient_seat.xlsx</t>
+        </is>
+      </c>
+      <c r="F127" s="6" t="inlineStr">
+        <is>
+          <t>node_id+level</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>demo.TbJingYuanTypeInfo</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>demo.JingYuanTypeInfo</t>
+        </is>
+      </c>
+      <c r="D128" t="b">
+        <v>1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>jingyuan_type_info@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>type_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>demo.TbJingYuanPremiumEssence</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>demo.JingYuanPremiumEssence</t>
+        </is>
+      </c>
+      <c r="D129" t="b">
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>jingyuan_premium_essence@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>essence_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>demo.TbJingYuanPremiumEffect</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>demo.JingYuanPremiumEffect</t>
+        </is>
+      </c>
+      <c r="D130" t="b">
+        <v>1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>jingyuan_premium_effect@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>type_id+drop_level+concentration_floor</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>demo.TbJingYuanEssenceLevelMap</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>demo.JingYuanEssenceLevelMap</t>
+        </is>
+      </c>
+      <c r="D131" t="b">
+        <v>1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>jingyuan_essence_level_map@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>map_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>demo.TbJingYuanTypePoolEnum</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>demo.JingYuanTypePoolEnum</t>
+        </is>
+      </c>
+      <c r="D132" t="b">
+        <v>1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>jingyuan_type_pool_enum@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>entry_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>demo.TbNamedNpcJingYuanType</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>demo.NamedNpcJingYuanType</t>
+        </is>
+      </c>
+      <c r="D133" t="b">
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>named_npc_jingyuan_type@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>character_key</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>demo.TbJingYuanTuneRule</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>demo.JingYuanTuneRule</t>
+        </is>
+      </c>
+      <c r="D134" t="b">
+        <v>1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>jingyuan_tune_rule@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>rule_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>demo.TbJingYuanRenewalRule</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>demo.JingYuanRenewalRule</t>
+        </is>
+      </c>
+      <c r="D135" t="b">
+        <v>1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>jingyuan_renewal_rule@jingyuan_codex.xlsx</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>rule_id</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -65,7 +65,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -77,6 +77,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -359,7 +362,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K135"/>
+  <dimension ref="A1:K143"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -371,3200 +374,3410 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="1">
-      <c r="A1" s="6" t="inlineStr">
+      <c r="A1" s="7" t="inlineStr">
         <is>
           <t>##var</t>
         </is>
       </c>
-      <c r="B1" s="6" t="inlineStr">
+      <c r="B1" s="7" t="inlineStr">
         <is>
           <t>full_name</t>
         </is>
       </c>
-      <c r="C1" s="6" t="inlineStr">
+      <c r="C1" s="7" t="inlineStr">
         <is>
           <t>value_type</t>
         </is>
       </c>
-      <c r="D1" s="6" t="inlineStr">
+      <c r="D1" s="7" t="inlineStr">
         <is>
           <t>read_schema_from_file</t>
         </is>
       </c>
-      <c r="E1" s="6" t="inlineStr">
+      <c r="E1" s="7" t="inlineStr">
         <is>
           <t>input</t>
         </is>
       </c>
-      <c r="F1" s="6" t="inlineStr">
+      <c r="F1" s="7" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="G1" s="6" t="inlineStr">
+      <c r="G1" s="7" t="inlineStr">
         <is>
           <t>mode</t>
         </is>
       </c>
-      <c r="H1" s="6" t="inlineStr">
+      <c r="H1" s="7" t="inlineStr">
         <is>
           <t>group</t>
         </is>
       </c>
-      <c r="I1" s="6" t="inlineStr">
+      <c r="I1" s="7" t="inlineStr">
         <is>
           <t>comment</t>
         </is>
       </c>
-      <c r="J1" s="6" t="inlineStr">
+      <c r="J1" s="7" t="inlineStr">
         <is>
           <t>tags</t>
         </is>
       </c>
-      <c r="K1" s="6" t="inlineStr">
+      <c r="K1" s="7" t="inlineStr">
         <is>
           <t>output</t>
         </is>
       </c>
     </row>
     <row r="2" customFormat="1" s="1">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="7" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="B2" s="6" t="inlineStr">
+      <c r="B2" s="7" t="inlineStr">
         <is>
           <t>全名(包含模块和名字)</t>
         </is>
       </c>
-      <c r="C2" s="6" t="inlineStr">
+      <c r="C2" s="7" t="inlineStr">
         <is>
           <t>记录类名</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>从excel读取定义</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>文件列表</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>表id字段</t>
         </is>
       </c>
-      <c r="G2" s="6" t="inlineStr">
+      <c r="G2" s="7" t="inlineStr">
         <is>
           <t>模式</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="7" t="inlineStr">
         <is>
           <t>分组</t>
         </is>
       </c>
-      <c r="I2" s="6" t="inlineStr">
+      <c r="I2" s="7" t="inlineStr">
         <is>
           <t>注释</t>
         </is>
       </c>
-      <c r="K2" s="6" t="inlineStr">
+      <c r="K2" s="7" t="inlineStr">
         <is>
           <t>输出文件名</t>
         </is>
       </c>
     </row>
     <row r="3" customFormat="1" s="1">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="7" t="inlineStr">
         <is>
           <t>##</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>false时取已有定义，true为从excel标题头和属性栏读取定义</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>可以多个，以逗号','分隔</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>为空的话自动取value_type中第一个字段,多主键联合索引为key1+key2,多主键独立索引为"key1,key2"</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="7" t="inlineStr">
         <is>
           <t>取值one|map|list，为空自动为map</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="7" t="inlineStr">
         <is>
           <t>取值c|s|e，可以有多个，以逗号','分隔。空则表示属于所有分组</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K3" s="7" t="inlineStr">
         <is>
           <t>默认为 &lt;module&gt;_&lt;name&gt;.&lt;suffix&gt;</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="7" t="inlineStr">
         <is>
           <t>demo.TbReward</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>demo.Reward</t>
         </is>
       </c>
-      <c r="D4" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>1@reward.xlsx</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>demo.TbLogicAreaInfo</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>demo.LogicAreaInfo</t>
         </is>
       </c>
-      <c r="D5" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>logic_area_info@map.xlsx</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>demo.TbLogicAreaHomesteadReq</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>demo.LogicAreaHomesteadReq</t>
         </is>
       </c>
-      <c r="D6" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>logic_area_homestead_req@facility_development.xlsx</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>demo.TbAreaVariantInfo</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="7" t="inlineStr">
         <is>
           <t>demo.AreaVariantInfo</t>
         </is>
       </c>
-      <c r="D7" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>area_variant_info@map.xlsx</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>demo.TbAreaOverlayStateInfo</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>demo.AreaOverlayStateInfo</t>
         </is>
       </c>
-      <c r="D8" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="D8" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>area_overlay_state_info@map.xlsx</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>demo.TbEventGrant</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>demo.EventGrant</t>
         </is>
       </c>
-      <c r="D9" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>event_grant@event_grant.xlsx</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>通用事件授予（通识/被动成就）</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>demo.TbDropBundle</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>demo.DropBundle</t>
         </is>
       </c>
-      <c r="D10" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="D10" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>drop_bundle@drop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>demo.TbDropItem</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="7" t="inlineStr">
         <is>
           <t>demo.DropItem</t>
         </is>
       </c>
-      <c r="D11" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="D11" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>drop_item@drop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>demo.TbBornPoint</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>demo.BornPoint</t>
         </is>
       </c>
-      <c r="D12" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="D12" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>born_points@born_points.xlsx</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>demo.TbUnitNpc</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>demo.UnitNpc</t>
         </is>
       </c>
-      <c r="D13" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="D13" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>unit_npc@unit_npc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>demo.TbUnitNpcAttr</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>demo.UnitNpcAttr</t>
         </is>
       </c>
-      <c r="D14" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="D14" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>unit_npc_attribute@unit_npc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>demo.TbDesireDensityInfo</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="7" t="inlineStr">
         <is>
           <t>demo.DesireDensityInfo</t>
         </is>
       </c>
-      <c r="D15" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="D15" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>desire_density_info@unit_npc.xlsx</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>demo.TbQuestData</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="7" t="inlineStr">
         <is>
           <t>demo.QuestData</t>
         </is>
       </c>
-      <c r="D16" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="D16" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>quest_data@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>demo.TbQuestStepData</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>demo.QuestStepData</t>
         </is>
       </c>
-      <c r="D17" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="D17" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>quest_step_data@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>demo.TbQuestStepOutcome</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>demo.QuestStepOutcome</t>
         </is>
       </c>
-      <c r="D18" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="D18" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>quest_step_outcome@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>demo.TbQuestStepObjective</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="7" t="inlineStr">
         <is>
           <t>demo.QuestStepObjective</t>
         </is>
       </c>
-      <c r="D19" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="D19" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>quest_step_objective@quests.xlsx</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>demo.TbDialogMetaInfo</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>demo.DialogMetaInfo</t>
         </is>
       </c>
-      <c r="D20" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="D20" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>dialog_meta_info@dialog.xlsx</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>demo.TbItemData</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="7" t="inlineStr">
         <is>
           <t>demo.ItemData</t>
         </is>
       </c>
-      <c r="D21" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="D21" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>item@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>demo.TbShop</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="7" t="inlineStr">
         <is>
           <t>demo.Shop</t>
         </is>
       </c>
-      <c r="D22" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>shop@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>demo.TbShopGoods</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>demo.ShopGoods</t>
         </is>
       </c>
-      <c r="D23" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="D23" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>shop_goods@shop.xlsx</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>demo.TbItemUse</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>demo.ItemUse</t>
         </is>
       </c>
-      <c r="D24" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="D24" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>item_use@item.xlsx</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>demo.TbItemGift</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>demo.ItemGift</t>
         </is>
       </c>
-      <c r="D25" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="D25" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>item_gift@item.xlsx</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="7" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>demo.TbNpcDialogInfo</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>demo.NpcDialogInfo</t>
         </is>
       </c>
-      <c r="D26" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="D26" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>npc_dialog_info@dialog.xlsx</t>
         </is>
       </c>
-      <c r="F26" s="6" t="n"/>
-      <c r="G26" s="6" t="n"/>
+      <c r="F26" s="7" t="n"/>
+      <c r="G26" s="7" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>demo.TbWorldMapGlobal</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>demo.WorldMapGlobal</t>
         </is>
       </c>
-      <c r="D27" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="D27" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>world_map_global@map.xlsx</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr">
+      <c r="G27" s="7" t="inlineStr">
         <is>
           <t>one</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>demo.TbWorldMapBigMapLayer</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>demo.WorldMapBigMapLayer</t>
         </is>
       </c>
-      <c r="D28" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="D28" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
         <is>
           <t>world_map_big_map@map.xlsx</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr">
+      <c r="G28" s="7" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>demo.TbDreamInfiltrationSpot</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>demo.DreamInfiltrationSpot</t>
         </is>
       </c>
-      <c r="D29" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E29" s="6" t="inlineStr">
+      <c r="D29" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
         <is>
           <t>dream_infiltration@dream_infiltration.xlsx</t>
         </is>
       </c>
-      <c r="G29" s="6" t="n"/>
+      <c r="G29" s="7" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>demo.TbCharDreamEntryInfo</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
         <is>
           <t>demo.CharDreamEntryInfo</t>
         </is>
       </c>
-      <c r="D30" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
+      <c r="D30" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
         <is>
           <t>char_dream_entry@dream_infiltration.xlsx</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>demo.TbFishingSpot</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>demo.FishingSpot</t>
         </is>
       </c>
-      <c r="D31" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
+      <c r="D31" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
         <is>
           <t>fishing_spot@fishing_spot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>demo.TbFishingSpotFish</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="7" t="inlineStr">
         <is>
           <t>demo.FishingSpotFish</t>
         </is>
       </c>
-      <c r="D32" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E32" s="6" t="inlineStr">
+      <c r="D32" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
         <is>
           <t>fishing_spot_fish@fishing_spot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="7" t="inlineStr">
         <is>
           <t>demo.TbPlayerDesireLevel</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="7" t="inlineStr">
         <is>
           <t>demo.PlayerDesireLevel</t>
         </is>
       </c>
-      <c r="D33" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
+      <c r="D33" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
         <is>
           <t>player_desire_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="7" t="inlineStr">
         <is>
           <t>demo.TbPlayerJingYuLevel</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="7" t="inlineStr">
         <is>
           <t>demo.PlayerJingYuLevel</t>
         </is>
       </c>
-      <c r="D34" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E34" s="6" t="inlineStr">
+      <c r="D34" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
         <is>
           <t>player_jingyu_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>demo.TbPlayerSanCorruptLevel</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="7" t="inlineStr">
         <is>
           <t>demo.PlayerSanCorruptLevel</t>
         </is>
       </c>
-      <c r="D35" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
         <is>
           <t>player_san_corrupt_level@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="7" t="inlineStr">
         <is>
           <t>demo.TbPlayerClothesExposeInfo</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>demo.PlayerClothesExposeInfo</t>
         </is>
       </c>
-      <c r="D36" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
+      <c r="D36" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
         <is>
           <t>player_clothes_expose_info@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>demo.TbWantedLevelInfo</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="7" t="inlineStr">
         <is>
           <t>demo.WantedLevelInfo</t>
         </is>
       </c>
-      <c r="D37" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E37" s="6" t="inlineStr">
+      <c r="D37" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
         <is>
           <t>wanted_level_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>demo.TbWantedBehaveInfo</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="7" t="inlineStr">
         <is>
           <t>demo.WantedBehaveInfo</t>
         </is>
       </c>
-      <c r="D38" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E38" s="6" t="inlineStr">
+      <c r="D38" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
         <is>
           <t>wanted_behave_info@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="7" t="inlineStr">
         <is>
           <t>demo.TbTalentNode</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="7" t="inlineStr">
         <is>
           <t>demo.TalentNode</t>
         </is>
       </c>
-      <c r="D39" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E39" s="6" t="inlineStr">
+      <c r="D39" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
         <is>
           <t>talent@talent.xlsx</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>node_id</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr">
+      <c r="G39" s="7" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="7" t="inlineStr">
         <is>
           <t>demo.TbWantedGuardSpawnTier</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>demo.WantedGuardSpawnTier</t>
         </is>
       </c>
-      <c r="D40" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
+      <c r="D40" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
         <is>
           <t>wanted_guard_spawn@wanted.xlsx</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>demo.TbEntitySkillData</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="7" t="inlineStr">
         <is>
           <t>demo.EntitySkillData</t>
         </is>
       </c>
-      <c r="D41" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E41" s="6" t="inlineStr">
+      <c r="D41" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>entity_skill@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>demo.TbSkillSchool</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>demo.SkillSchool</t>
         </is>
       </c>
-      <c r="D42" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="D42" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
         <is>
           <t>skill_school@skill.xlsx</t>
         </is>
       </c>
-      <c r="F42" s="6" t="n"/>
-      <c r="G42" s="6" t="n"/>
+      <c r="F42" s="7" t="n"/>
+      <c r="G42" s="7" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>demo.TbSkillLearnEntry</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="7" t="inlineStr">
         <is>
           <t>demo.SkillLearnEntry</t>
         </is>
       </c>
-      <c r="D43" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E43" s="6" t="inlineStr">
+      <c r="D43" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
         <is>
           <t>skill_learn@skill.xlsx</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="7" t="inlineStr">
         <is>
           <t>demo.TbDesireCrystalDef</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="7" t="inlineStr">
         <is>
           <t>demo.DesireCrystalDef</t>
         </is>
       </c>
-      <c r="D44" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E44" s="6" t="inlineStr">
+      <c r="D44" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
         <is>
           <t>desire_crystal_def@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>demo.TbMapDesireCrystalBudget</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>demo.MapDesireCrystalBudget</t>
         </is>
       </c>
-      <c r="D45" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="D45" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
         <is>
           <t>map_desire_crystal_budget@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>demo.TbMapWalkerDesireCrystalQuota</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="7" t="inlineStr">
         <is>
           <t>demo.MapWalkerDesireCrystalQuota</t>
         </is>
       </c>
-      <c r="D46" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
+      <c r="D46" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
         <is>
           <t>map_walker_desire_crystal_quota@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" s="7" t="inlineStr">
         <is>
           <t>demo.TbNamedNpcDesireCrystal</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C47" s="7" t="inlineStr">
         <is>
           <t>demo.NamedNpcDesireCrystal</t>
         </is>
       </c>
-      <c r="D47" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E47" s="6" t="inlineStr">
+      <c r="D47" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>named_npc_desire_crystal@desire_crystal.xlsx</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="7" t="inlineStr">
         <is>
           <t>demo.TbSpiritMonsterTypeBudget</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>demo.SpiritMonsterTypeBudget</t>
         </is>
       </c>
-      <c r="D48" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E48" s="6" t="inlineStr">
+      <c r="D48" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>spirit_monster_budget@player_status.xlsx</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="B49" s="6" t="inlineStr">
+      <c r="B49" s="7" t="inlineStr">
         <is>
           <t>demo.TbContainerItemStackOverride</t>
         </is>
       </c>
-      <c r="C49" s="6" t="inlineStr">
+      <c r="C49" s="7" t="inlineStr">
         <is>
           <t>demo.ContainerItemStackOverride</t>
         </is>
       </c>
-      <c r="D49" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E49" s="6" t="inlineStr">
+      <c r="D49" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
         <is>
           <t>container_item_stack_override@container_stack.xlsx</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="B50" s="6" t="inlineStr">
+      <c r="B50" s="7" t="inlineStr">
         <is>
           <t>demo.TbContainerStackTagRule</t>
         </is>
       </c>
-      <c r="C50" s="6" t="inlineStr">
+      <c r="C50" s="7" t="inlineStr">
         <is>
           <t>demo.ContainerStackTagRule</t>
         </is>
       </c>
-      <c r="D50" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E50" s="6" t="inlineStr">
+      <c r="D50" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
         <is>
           <t>container_stack_tag_rule@container_stack.xlsx</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="B51" s="6" t="inlineStr">
+      <c r="B51" s="7" t="inlineStr">
         <is>
           <t>demo.TbMapAreaEffect</t>
         </is>
       </c>
-      <c r="C51" s="6" t="inlineStr">
+      <c r="C51" s="7" t="inlineStr">
         <is>
           <t>demo.MapAreaEffect</t>
         </is>
       </c>
-      <c r="D51" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E51" s="6" t="inlineStr">
+      <c r="D51" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
         <is>
           <t>map_area_effect@map_area_effect.xlsx</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="B52" s="6" t="inlineStr">
+      <c r="B52" s="7" t="inlineStr">
         <is>
           <t>demo.TbFallenAmountProgressInfo</t>
         </is>
       </c>
-      <c r="C52" s="6" t="inlineStr">
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>demo.FallenAmountProgressInfo</t>
         </is>
       </c>
-      <c r="D52" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
+      <c r="D52" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
         <is>
           <t>fallen_amount_progress_info@fallen_amount_progress_info.xlsx</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="B53" s="6" t="inlineStr">
+      <c r="B53" s="7" t="inlineStr">
         <is>
           <t>demo.TbRumorIntel</t>
         </is>
       </c>
-      <c r="C53" s="6" t="inlineStr">
+      <c r="C53" s="7" t="inlineStr">
         <is>
           <t>demo.RumorIntel</t>
         </is>
       </c>
-      <c r="D53" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
+      <c r="D53" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
         <is>
           <t>rumor_intel@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="B54" s="6" t="inlineStr">
+      <c r="B54" s="7" t="inlineStr">
         <is>
           <t>demo.TbRumorRandomPool</t>
         </is>
       </c>
-      <c r="C54" s="6" t="inlineStr">
+      <c r="C54" s="7" t="inlineStr">
         <is>
           <t>demo.RumorRandomPool</t>
         </is>
       </c>
-      <c r="D54" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E54" s="6" t="inlineStr">
+      <c r="D54" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
         <is>
           <t>rumor_random_pool@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="B55" s="6" t="inlineStr">
+      <c r="B55" s="7" t="inlineStr">
         <is>
           <t>demo.TbRumorGlobal</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C55" s="7" t="inlineStr">
         <is>
           <t>demo.RumorGlobal</t>
         </is>
       </c>
-      <c r="D55" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
+      <c r="D55" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
         <is>
           <t>rumor_global@rumor_tables.xlsx</t>
         </is>
       </c>
     </row>
     <row r="56">
-      <c r="B56" s="6" t="inlineStr">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>demo.TbCharacterInfo</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C56" s="7" t="inlineStr">
         <is>
           <t>demo.CharacterInfo</t>
         </is>
       </c>
-      <c r="D56" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
+      <c r="D56" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
         <is>
           <t>character_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="B57" s="6" t="inlineStr">
+      <c r="B57" s="7" t="inlineStr">
         <is>
           <t>demo.TbCharacterFavorInfo</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C57" s="7" t="inlineStr">
         <is>
           <t>demo.CharacterFavorInfo</t>
         </is>
       </c>
-      <c r="D57" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E57" s="6" t="inlineStr">
+      <c r="D57" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
         <is>
           <t>character_favor_info@character.xlsx</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="B58" s="6" t="inlineStr">
+      <c r="B58" s="7" t="inlineStr">
         <is>
           <t>demo.TbMicroPlotDef</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C58" s="7" t="inlineStr">
         <is>
           <t>demo.MicroPlotDef</t>
         </is>
       </c>
-      <c r="D58" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E58" s="6" t="inlineStr">
+      <c r="D58" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
         <is>
           <t>micro_plot_def@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="B59" s="6" t="inlineStr">
+      <c r="B59" s="7" t="inlineStr">
         <is>
           <t>demo.TbMapMicroPlotTrigger</t>
         </is>
       </c>
-      <c r="C59" s="6" t="inlineStr">
+      <c r="C59" s="7" t="inlineStr">
         <is>
           <t>demo.MapMicroPlotTrigger</t>
         </is>
       </c>
-      <c r="D59" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E59" s="6" t="inlineStr">
+      <c r="D59" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>map_micro_plot_trigger@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="60">
-      <c r="B60" s="6" t="inlineStr">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>demo.TbMicroPlotTimelineEvent</t>
         </is>
       </c>
-      <c r="C60" s="6" t="inlineStr">
+      <c r="C60" s="7" t="inlineStr">
         <is>
           <t>demo.MicroPlotTimelineEvent</t>
         </is>
       </c>
-      <c r="D60" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E60" s="6" t="inlineStr">
+      <c r="D60" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>micro_plot_timeline_event@micro_plot.xlsx</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="B61" s="6" t="inlineStr">
+      <c r="B61" s="7" t="inlineStr">
         <is>
           <t>demo.TbTrapSpec</t>
         </is>
       </c>
-      <c r="C61" s="6" t="inlineStr">
+      <c r="C61" s="7" t="inlineStr">
         <is>
           <t>demo.TrapSpec</t>
         </is>
       </c>
-      <c r="D61" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
+      <c r="D61" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>trap_spec@trap_spec.xlsx</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="B62" s="6" t="inlineStr">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>demo.TbForgeRecipe</t>
         </is>
       </c>
-      <c r="C62" s="6" t="inlineStr">
+      <c r="C62" s="7" t="inlineStr">
         <is>
           <t>demo.ForgeRecipe</t>
         </is>
       </c>
-      <c r="D62" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E62" s="6" t="inlineStr">
+      <c r="D62" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>forge_recipe@forge_recipe.xlsx</t>
         </is>
       </c>
     </row>
     <row r="63">
-      <c r="B63" s="6" t="inlineStr">
+      <c r="B63" s="7" t="inlineStr">
         <is>
           <t>demo.TbHActInfo</t>
         </is>
       </c>
-      <c r="C63" s="6" t="inlineStr">
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>demo.HActInfo</t>
         </is>
       </c>
-      <c r="D63" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E63" s="6" t="inlineStr">
+      <c r="D63" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
         <is>
           <t>h_act_info@h_act_info.xlsx</t>
         </is>
       </c>
     </row>
     <row r="64">
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B64" s="7" t="inlineStr">
         <is>
           <t>demo.TbTalentNodeLevel</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C64" s="7" t="inlineStr">
         <is>
           <t>demo.TalentNodeLevel</t>
         </is>
       </c>
-      <c r="D64" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E64" s="6" t="inlineStr">
+      <c r="D64" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
         <is>
           <t>talent_level@talent.xlsx</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>node_id+level</t>
         </is>
       </c>
-      <c r="G64" s="6" t="inlineStr">
+      <c r="G64" s="7" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="B65" s="6" t="inlineStr">
+      <c r="B65" s="7" t="inlineStr">
         <is>
           <t>demo.TbSavePoint</t>
         </is>
       </c>
-      <c r="C65" s="6" t="inlineStr">
+      <c r="C65" s="7" t="inlineStr">
         <is>
           <t>demo.SavePoint</t>
         </is>
       </c>
-      <c r="D65" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E65" s="6" t="inlineStr">
+      <c r="D65" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
         <is>
           <t>save_point@save_point.xlsx</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="B66" s="6" t="inlineStr">
+      <c r="B66" s="7" t="inlineStr">
         <is>
           <t>demo.TbReviveRule</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C66" s="7" t="inlineStr">
         <is>
           <t>demo.ReviveRule</t>
         </is>
       </c>
-      <c r="D66" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
+      <c r="D66" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
         <is>
           <t>revive_rule@revive_rule.xlsx</t>
         </is>
       </c>
-      <c r="G66" s="6" t="inlineStr">
+      <c r="G66" s="7" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="B67" s="6" t="inlineStr">
+      <c r="B67" s="7" t="inlineStr">
         <is>
           <t>demo.TbDesireDensityTier</t>
         </is>
       </c>
-      <c r="C67" s="6" t="inlineStr">
+      <c r="C67" s="7" t="inlineStr">
         <is>
           <t>demo.DesireDensityTier</t>
         </is>
       </c>
-      <c r="D67" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E67" s="6" t="inlineStr">
+      <c r="D67" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
         <is>
           <t>desire_density_tier@desire_density_tier.xlsx</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="B68" s="6" t="inlineStr">
+      <c r="B68" s="7" t="inlineStr">
         <is>
           <t>demo.TbMindFragmentPoolEntry</t>
         </is>
       </c>
-      <c r="C68" s="6" t="inlineStr">
+      <c r="C68" s="7" t="inlineStr">
         <is>
           <t>demo.MindFragmentPoolEntry</t>
         </is>
       </c>
-      <c r="D68" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
+      <c r="D68" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
         <is>
           <t>mind_fragment_pool@mind_fragment_pool.xlsx</t>
         </is>
       </c>
-      <c r="G68" s="6" t="inlineStr">
+      <c r="G68" s="7" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="B69" s="6" t="inlineStr">
+      <c r="B69" s="7" t="inlineStr">
         <is>
           <t>demo.TbSecretBaseFacility</t>
         </is>
       </c>
-      <c r="C69" s="6" t="inlineStr">
+      <c r="C69" s="7" t="inlineStr">
         <is>
           <t>demo.SecretBaseFacility</t>
         </is>
       </c>
-      <c r="D69" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E69" s="6" t="inlineStr">
+      <c r="D69" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
         <is>
           <t>secret_base_facility@secret_base_facility.xlsx</t>
         </is>
       </c>
-      <c r="I69" s="6" t="inlineStr">
+      <c r="I69" s="7" t="inlineStr">
         <is>
           <t>据点固定设施</t>
         </is>
       </c>
     </row>
     <row r="70">
-      <c r="B70" s="6" t="inlineStr">
+      <c r="B70" s="7" t="inlineStr">
         <is>
           <t>demo.TbSecretBaseBuildLevel</t>
         </is>
       </c>
-      <c r="C70" s="6" t="inlineStr">
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>demo.SecretBaseBuildLevel</t>
         </is>
       </c>
-      <c r="D70" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E70" s="6" t="inlineStr">
+      <c r="D70" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
         <is>
           <t>secret_base_build_level@secret_base_build_level.xlsx</t>
         </is>
       </c>
-      <c r="F70" s="6" t="inlineStr">
+      <c r="F70" s="7" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
-      <c r="G70" s="6" t="inlineStr">
+      <c r="G70" s="7" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I70" s="6" t="inlineStr">
+      <c r="I70" s="7" t="inlineStr">
         <is>
           <t>据点建设等级卷轴边界</t>
         </is>
       </c>
     </row>
     <row r="71">
-      <c r="B71" s="6" t="inlineStr">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>demo.TbSecretBaseCharacter</t>
         </is>
       </c>
-      <c r="C71" s="6" t="inlineStr">
+      <c r="C71" s="7" t="inlineStr">
         <is>
           <t>demo.SecretBaseCharacter</t>
         </is>
       </c>
-      <c r="D71" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
+      <c r="D71" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
         <is>
           <t>secret_base_character@secret_base_character.xlsx</t>
         </is>
       </c>
-      <c r="F71" s="6" t="inlineStr">
+      <c r="F71" s="7" t="inlineStr">
         <is>
           <t>slot_id</t>
         </is>
       </c>
-      <c r="G71" s="6" t="inlineStr">
+      <c r="G71" s="7" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I71" s="6" t="inlineStr">
+      <c r="I71" s="7" t="inlineStr">
         <is>
           <t>秘密据点角色</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="B72" s="6" t="inlineStr">
+      <c r="B72" s="7" t="inlineStr">
         <is>
           <t>demo.TbHumanWeapon</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>demo.HumanWeapon</t>
         </is>
       </c>
-      <c r="D72" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E72" s="6" t="inlineStr">
+      <c r="D72" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
         <is>
           <t>human_weapon@human_weapon.xlsx</t>
         </is>
       </c>
-      <c r="F72" s="6" t="inlineStr">
+      <c r="F72" s="7" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="G72" s="6" t="inlineStr">
+      <c r="G72" s="7" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I72" s="6" t="inlineStr">
+      <c r="I72" s="7" t="inlineStr">
         <is>
           <t>human_weapon</t>
         </is>
       </c>
     </row>
     <row r="73">
-      <c r="B73" s="6" t="inlineStr">
+      <c r="B73" s="7" t="inlineStr">
         <is>
           <t>demo.TbRuneData</t>
         </is>
       </c>
-      <c r="C73" s="6" t="inlineStr">
+      <c r="C73" s="7" t="inlineStr">
         <is>
           <t>demo.RuneData</t>
         </is>
       </c>
-      <c r="D73" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E73" s="6" t="inlineStr">
+      <c r="D73" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>rune_data@rune.xlsx</t>
         </is>
       </c>
-      <c r="G73" s="6" t="n"/>
+      <c r="G73" s="7" t="n"/>
     </row>
     <row r="74">
-      <c r="B74" s="6" t="inlineStr">
+      <c r="B74" s="7" t="inlineStr">
         <is>
           <t>demo.TbBodyPartDef</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C74" s="7" t="inlineStr">
         <is>
           <t>demo.BodyPartDef</t>
         </is>
       </c>
-      <c r="D74" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E74" s="6" t="inlineStr">
+      <c r="D74" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>body_part_def@body_part.xlsx</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="B75" s="6" t="inlineStr">
+      <c r="B75" s="7" t="inlineStr">
         <is>
           <t>demo.TbBodyPartLevel</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C75" s="7" t="inlineStr">
         <is>
           <t>demo.BodyPartLevel</t>
         </is>
       </c>
-      <c r="D75" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E75" s="6" t="inlineStr">
+      <c r="D75" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
         <is>
           <t>body_part_level@body_part.xlsx</t>
         </is>
       </c>
-      <c r="F75" s="6" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
         <is>
           <t>part_id+level</t>
         </is>
       </c>
-      <c r="G75" s="6" t="inlineStr">
+      <c r="G75" s="7" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="B76" s="6" t="inlineStr">
+      <c r="B76" s="7" t="inlineStr">
         <is>
           <t>demo.TbBodyPartProgressInfo</t>
         </is>
       </c>
-      <c r="C76" s="6" t="inlineStr">
+      <c r="C76" s="7" t="inlineStr">
         <is>
           <t>demo.BodyPartProgressInfo</t>
         </is>
       </c>
-      <c r="D76" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E76" s="6" t="inlineStr">
+      <c r="D76" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
         <is>
           <t>body_part_progress_info@body_part.xlsx</t>
         </is>
       </c>
-      <c r="I76" s="6" t="n"/>
+      <c r="I76" s="7" t="n"/>
     </row>
     <row r="77">
-      <c r="B77" s="6" t="inlineStr">
+      <c r="B77" s="7" t="inlineStr">
         <is>
           <t>demo.TbPartLocalAttrDef</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C77" s="7" t="inlineStr">
         <is>
           <t>demo.PartLocalAttrDef</t>
         </is>
       </c>
-      <c r="D77" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
+      <c r="D77" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
         <is>
           <t>part_local_attr_def@body_part.xlsx</t>
         </is>
       </c>
-      <c r="F77" s="6" t="n"/>
-      <c r="G77" s="6" t="n"/>
-      <c r="I77" s="6" t="n"/>
+      <c r="F77" s="7" t="n"/>
+      <c r="G77" s="7" t="n"/>
+      <c r="I77" s="7" t="n"/>
     </row>
     <row r="78">
-      <c r="B78" s="6" t="inlineStr">
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>demo.TbPartGear</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C78" s="7" t="inlineStr">
         <is>
           <t>demo.PartGear</t>
         </is>
       </c>
-      <c r="D78" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
+      <c r="D78" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
         <is>
           <t>partgear@partgear.xlsx</t>
         </is>
       </c>
-      <c r="F78" s="6" t="inlineStr">
+      <c r="F78" s="7" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="G78" s="6" t="inlineStr">
+      <c r="G78" s="7" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
     </row>
     <row r="79">
-      <c r="B79" s="6" t="inlineStr">
+      <c r="B79" s="7" t="inlineStr">
         <is>
           <t>demo.TbRuneUpgradeInfo</t>
         </is>
       </c>
-      <c r="C79" s="6" t="inlineStr">
+      <c r="C79" s="7" t="inlineStr">
         <is>
           <t>demo.RuneUpgradeInfo</t>
         </is>
       </c>
-      <c r="D79" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E79" s="6" t="inlineStr">
+      <c r="D79" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
         <is>
           <t>rune_upgrade_info@rune.xlsx</t>
         </is>
       </c>
-      <c r="F79" s="6" t="inlineStr">
+      <c r="F79" s="7" t="inlineStr">
         <is>
           <t>upgrade_id</t>
         </is>
       </c>
-      <c r="G79" s="6" t="n"/>
-      <c r="I79" s="6" t="n"/>
-      <c r="J79" s="6" t="inlineStr">
+      <c r="G79" s="7" t="n"/>
+      <c r="I79" s="7" t="n"/>
+      <c r="J79" s="7" t="inlineStr">
         <is>
           <t>符文升级项</t>
         </is>
       </c>
     </row>
     <row r="80">
-      <c r="B80" s="6" t="inlineStr">
+      <c r="B80" s="7" t="inlineStr">
         <is>
           <t>demo.TbRuneEquipSlot</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C80" s="7" t="inlineStr">
         <is>
           <t>demo.RuneEquipSlotInfo</t>
         </is>
       </c>
-      <c r="D80" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
+      <c r="D80" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
         <is>
           <t>rune_equip_slot@rune.xlsx</t>
         </is>
       </c>
-      <c r="F80" s="6" t="inlineStr">
+      <c r="F80" s="7" t="inlineStr">
         <is>
           <t>equip_slot</t>
         </is>
       </c>
-      <c r="G80" s="6" t="n"/>
-      <c r="I80" s="6" t="n"/>
-      <c r="J80" s="6" t="inlineStr">
+      <c r="G80" s="7" t="n"/>
+      <c r="I80" s="7" t="n"/>
+      <c r="J80" s="7" t="inlineStr">
         <is>
           <t>符文装配槽</t>
         </is>
       </c>
     </row>
     <row r="81">
-      <c r="B81" s="6" t="inlineStr">
+      <c r="B81" s="7" t="inlineStr">
         <is>
           <t>demo.TbEntitySkillLevel</t>
         </is>
       </c>
-      <c r="C81" s="6" t="inlineStr">
+      <c r="C81" s="7" t="inlineStr">
         <is>
           <t>demo.EntitySkillLevel</t>
         </is>
       </c>
-      <c r="D81" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E81" s="6" t="inlineStr">
+      <c r="D81" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
         <is>
           <t>skill_level@skill.xlsx</t>
         </is>
       </c>
-      <c r="F81" s="6" t="inlineStr">
+      <c r="F81" s="7" t="inlineStr">
         <is>
           <t>skill_id+level</t>
         </is>
       </c>
-      <c r="G81" s="6" t="inlineStr">
+      <c r="G81" s="7" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="B82" s="6" t="inlineStr">
+      <c r="B82" s="7" t="inlineStr">
         <is>
           <t>demo.TbJingYuanCodexDef</t>
         </is>
       </c>
-      <c r="C82" s="6" t="inlineStr">
+      <c r="C82" s="7" t="inlineStr">
         <is>
           <t>demo.JingYuanCodexDef</t>
         </is>
       </c>
-      <c r="D82" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E82" s="6" t="inlineStr">
+      <c r="D82" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E82" s="7" t="inlineStr">
         <is>
           <t>jingyuan_codex_def@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F82" s="6" t="inlineStr">
+      <c r="F82" s="7" t="inlineStr">
         <is>
           <t>codex_id</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="B83" s="6" t="inlineStr">
+      <c r="B83" s="7" t="inlineStr">
         <is>
           <t>demo.TbJingYuanCodexLevel</t>
         </is>
       </c>
-      <c r="C83" s="6" t="inlineStr">
+      <c r="C83" s="7" t="inlineStr">
         <is>
           <t>demo.JingYuanCodexLevel</t>
         </is>
       </c>
-      <c r="D83" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E83" s="6" t="inlineStr">
+      <c r="D83" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E83" s="7" t="inlineStr">
         <is>
           <t>jingyuan_codex_level@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F83" s="6" t="inlineStr">
+      <c r="F83" s="7" t="inlineStr">
         <is>
           <t>codex_id+level</t>
         </is>
       </c>
-      <c r="G83" s="6" t="inlineStr">
+      <c r="G83" s="7" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="B84" s="6" t="inlineStr">
+      <c r="B84" s="7" t="inlineStr">
         <is>
           <t>demo.TbJingYuanTuneTier</t>
         </is>
       </c>
-      <c r="C84" s="6" t="inlineStr">
+      <c r="C84" s="7" t="inlineStr">
         <is>
           <t>demo.JingYuanTuneTier</t>
         </is>
       </c>
-      <c r="D84" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
+      <c r="D84" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E84" s="7" t="inlineStr">
         <is>
           <t>jingyuan_tune_tier@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F84" s="6" t="inlineStr">
+      <c r="F84" s="7" t="inlineStr">
         <is>
           <t>codex_id+tier</t>
         </is>
       </c>
-      <c r="G84" s="6" t="inlineStr">
+      <c r="G84" s="7" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="B85" s="6" t="inlineStr">
+      <c r="B85" s="7" t="inlineStr">
         <is>
           <t>demo.TbTiaoJingConcentrationLevel</t>
         </is>
       </c>
-      <c r="C85" s="6" t="inlineStr">
+      <c r="C85" s="7" t="inlineStr">
         <is>
           <t>demo.TiaoJingConcentrationLevel</t>
         </is>
       </c>
-      <c r="D85" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E85" s="6" t="inlineStr">
+      <c r="D85" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E85" s="7" t="inlineStr">
         <is>
           <t>tiao_jing_concentration_level@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F85" s="6" t="n"/>
-      <c r="J85" s="6" t="n"/>
+      <c r="F85" s="7" t="n"/>
+      <c r="J85" s="7" t="n"/>
     </row>
     <row r="86">
-      <c r="B86" s="6" t="inlineStr">
+      <c r="B86" s="7" t="inlineStr">
         <is>
           <t>demo.TbJingYuanTypeDef</t>
         </is>
       </c>
-      <c r="C86" s="6" t="inlineStr">
+      <c r="C86" s="7" t="inlineStr">
         <is>
           <t>demo.JingYuanTypeDef</t>
         </is>
       </c>
-      <c r="D86" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="D86" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E86" s="7" t="inlineStr">
         <is>
           <t>jingyuan_type_def@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F86" s="6" t="inlineStr">
+      <c r="F86" s="7" t="inlineStr">
         <is>
           <t>type_id</t>
         </is>
       </c>
-      <c r="J86" s="6" t="n"/>
+      <c r="J86" s="7" t="n"/>
     </row>
     <row r="87">
-      <c r="B87" s="6" t="inlineStr">
+      <c r="B87" s="7" t="inlineStr">
         <is>
           <t>demo.TbJingYuanTypePoolEntry</t>
         </is>
       </c>
-      <c r="C87" s="6" t="inlineStr">
+      <c r="C87" s="7" t="inlineStr">
         <is>
           <t>demo.JingYuanTypePoolEntry</t>
         </is>
       </c>
-      <c r="D87" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E87" s="6" t="inlineStr">
+      <c r="D87" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E87" s="7" t="inlineStr">
         <is>
           <t>jingyuan_type_pool@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F87" s="6" t="n"/>
-      <c r="G87" s="6" t="inlineStr">
+      <c r="F87" s="7" t="n"/>
+      <c r="G87" s="7" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="B88" s="6" t="inlineStr">
+      <c r="B88" s="7" t="inlineStr">
         <is>
           <t>demo.TbProgressionHubTab</t>
         </is>
       </c>
-      <c r="C88" s="6" t="inlineStr">
+      <c r="C88" s="7" t="inlineStr">
         <is>
           <t>demo.ProgressionHubTabDef</t>
         </is>
       </c>
-      <c r="D88" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E88" s="6" t="inlineStr">
+      <c r="D88" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
         <is>
           <t>progression_hub_tab@progression_hub_tab.xlsx</t>
         </is>
       </c>
-      <c r="F88" s="6" t="inlineStr">
+      <c r="F88" s="7" t="inlineStr">
         <is>
           <t>tab_id</t>
         </is>
       </c>
-      <c r="G88" s="6" t="inlineStr">
+      <c r="G88" s="7" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I88" s="6" t="inlineStr">
+      <c r="I88" s="7" t="inlineStr">
         <is>
           <t>养成总面板选项卡</t>
         </is>
       </c>
     </row>
     <row r="89">
-      <c r="B89" s="6" t="inlineStr">
+      <c r="B89" s="7" t="inlineStr">
         <is>
           <t>demo.TbPlayerAttachInfo</t>
         </is>
       </c>
-      <c r="C89" s="6" t="inlineStr">
+      <c r="C89" s="7" t="inlineStr">
         <is>
           <t>demo.PlayerAttachInfo</t>
         </is>
       </c>
-      <c r="D89" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="D89" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
         <is>
           <t>player_attach@player_attach.xlsx</t>
         </is>
       </c>
-      <c r="F89" s="6" t="n"/>
-      <c r="G89" s="6" t="n"/>
-      <c r="I89" s="6" t="n"/>
+      <c r="F89" s="7" t="n"/>
+      <c r="G89" s="7" t="n"/>
+      <c r="I89" s="7" t="n"/>
     </row>
     <row r="90">
-      <c r="B90" s="6" t="inlineStr">
+      <c r="B90" s="7" t="inlineStr">
         <is>
           <t>demo.TbItemDismantle</t>
         </is>
       </c>
-      <c r="C90" s="6" t="inlineStr">
+      <c r="C90" s="7" t="inlineStr">
         <is>
           <t>demo.ItemDismantle</t>
         </is>
       </c>
-      <c r="D90" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E90" s="6" t="inlineStr">
+      <c r="D90" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
         <is>
           <t>item_dismantle@item_dismantle.xlsx</t>
         </is>
       </c>
-      <c r="F90" s="6" t="inlineStr">
+      <c r="F90" s="7" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="G90" s="6" t="inlineStr">
+      <c r="G90" s="7" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I90" s="6" t="inlineStr">
+      <c r="I90" s="7" t="inlineStr">
         <is>
           <t>物品分解产物配置</t>
         </is>
       </c>
     </row>
     <row r="91">
-      <c r="B91" s="6" t="inlineStr">
+      <c r="B91" s="7" t="inlineStr">
         <is>
           <t>demo.TbItemTagInfo</t>
         </is>
       </c>
-      <c r="C91" s="6" t="inlineStr">
+      <c r="C91" s="7" t="inlineStr">
         <is>
           <t>demo.ItemTagInfo</t>
         </is>
       </c>
-      <c r="D91" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E91" s="6" t="inlineStr">
+      <c r="D91" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>item_tag@item_define.xlsx</t>
         </is>
       </c>
-      <c r="F91" s="6" t="inlineStr">
+      <c r="F91" s="7" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="G91" s="6" t="n"/>
-      <c r="H91" s="6" t="inlineStr">
+      <c r="G91" s="7" t="n"/>
+      <c r="H91" s="7" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="I91" s="6" t="inlineStr">
+      <c r="I91" s="7" t="inlineStr">
         <is>
           <t>物品标签元数据：显示字、隐藏控制、实例需求</t>
         </is>
       </c>
     </row>
     <row r="92">
-      <c r="B92" s="6" t="inlineStr">
+      <c r="B92" s="7" t="inlineStr">
         <is>
           <t>demo.TbPlayerBagDef</t>
         </is>
       </c>
-      <c r="C92" s="6" t="inlineStr">
+      <c r="C92" s="7" t="inlineStr">
         <is>
           <t>demo.PlayerBagDef</t>
         </is>
       </c>
-      <c r="D92" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E92" s="6" t="inlineStr">
+      <c r="D92" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t>player_bag@player_bag.xlsx</t>
         </is>
       </c>
-      <c r="F92" s="6" t="n"/>
-      <c r="G92" s="6" t="n"/>
-      <c r="I92" s="6" t="inlineStr">
+      <c r="F92" s="7" t="n"/>
+      <c r="G92" s="7" t="n"/>
+      <c r="I92" s="7" t="inlineStr">
         <is>
           <t>玩家背包定义</t>
         </is>
       </c>
     </row>
     <row r="93">
-      <c r="B93" s="6" t="inlineStr">
+      <c r="B93" s="7" t="inlineStr">
         <is>
           <t>demo.TbWarehouseFilter</t>
         </is>
       </c>
-      <c r="C93" s="6" t="inlineStr">
+      <c r="C93" s="7" t="inlineStr">
         <is>
           <t>demo.WarehouseFilter</t>
         </is>
       </c>
-      <c r="D93" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E93" s="6" t="inlineStr">
+      <c r="D93" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
         <is>
           <t>warehouse_filter@warehouse_filter.xlsx</t>
         </is>
       </c>
-      <c r="I93" s="6" t="inlineStr">
+      <c r="I93" s="7" t="inlineStr">
         <is>
           <t>仓库筛选定义</t>
         </is>
       </c>
     </row>
     <row r="94">
-      <c r="B94" s="6" t="inlineStr">
+      <c r="B94" s="7" t="inlineStr">
         <is>
           <t>demo.TbCharacterGiftRule</t>
         </is>
       </c>
-      <c r="C94" s="6" t="inlineStr">
+      <c r="C94" s="7" t="inlineStr">
         <is>
           <t>demo.CharacterGiftRule</t>
         </is>
       </c>
-      <c r="D94" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E94" s="6" t="inlineStr">
+      <c r="D94" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
         <is>
           <t>character_gift_rule@character.xlsx</t>
         </is>
       </c>
-      <c r="F94" s="6" t="inlineStr">
+      <c r="F94" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="G94" s="6" t="inlineStr">
+      <c r="G94" s="7" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I94" s="6" t="inlineStr">
+      <c r="I94" s="7" t="inlineStr">
         <is>
           <t>角色礼物固定覆盖规则</t>
         </is>
       </c>
     </row>
     <row r="95">
-      <c r="B95" s="6" t="inlineStr">
+      <c r="B95" s="7" t="inlineStr">
         <is>
           <t>demo.TbTalentTree</t>
         </is>
       </c>
-      <c r="C95" s="6" t="inlineStr">
+      <c r="C95" s="7" t="inlineStr">
         <is>
           <t>demo.TalentTree</t>
         </is>
       </c>
-      <c r="D95" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
+      <c r="D95" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>talent_tree@talent.xlsx</t>
         </is>
       </c>
-      <c r="F95" s="6" t="inlineStr">
+      <c r="F95" s="7" t="inlineStr">
         <is>
           <t>tree_id</t>
         </is>
       </c>
-      <c r="G95" s="6" t="inlineStr">
+      <c r="G95" s="7" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I95" s="6" t="inlineStr">
+      <c r="I95" s="7" t="inlineStr">
         <is>
           <t>天赋树定义</t>
         </is>
       </c>
     </row>
     <row r="96">
-      <c r="B96" s="6" t="inlineStr">
+      <c r="B96" s="7" t="inlineStr">
         <is>
           <t>demo.TbSecretBaseCharacterOption</t>
         </is>
       </c>
-      <c r="C96" s="6" t="inlineStr">
+      <c r="C96" s="7" t="inlineStr">
         <is>
           <t>demo.SecretBaseCharacterOption</t>
         </is>
       </c>
-      <c r="D96" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
+      <c r="D96" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
         <is>
           <t>secret_base_character_option@secret_base_character.xlsx</t>
         </is>
       </c>
-      <c r="F96" s="6" t="inlineStr">
+      <c r="F96" s="7" t="inlineStr">
         <is>
           <t>option_id</t>
         </is>
       </c>
-      <c r="G96" s="6" t="inlineStr">
+      <c r="G96" s="7" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="I96" s="6" t="inlineStr">
+      <c r="I96" s="7" t="inlineStr">
         <is>
           <t>秘密据点角色自定义选项</t>
         </is>
       </c>
     </row>
     <row r="97">
-      <c r="B97" s="6" t="inlineStr">
+      <c r="B97" s="7" t="inlineStr">
         <is>
           <t>demo.TbHumanCivilizationLevel</t>
         </is>
       </c>
-      <c r="C97" s="6" t="inlineStr">
+      <c r="C97" s="7" t="inlineStr">
         <is>
           <t>demo.HumanCivilizationLevel</t>
         </is>
       </c>
-      <c r="D97" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E97" s="6" t="inlineStr">
+      <c r="D97" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
         <is>
           <t>civilization_level@human_civilization.xlsx</t>
         </is>
       </c>
-      <c r="F97" s="6" t="inlineStr">
+      <c r="F97" s="7" t="inlineStr">
         <is>
           <t>level</t>
         </is>
       </c>
     </row>
     <row r="98">
-      <c r="B98" s="6" t="inlineStr">
+      <c r="B98" s="7" t="inlineStr">
         <is>
           <t>demo.TbHumanTechTree</t>
         </is>
       </c>
-      <c r="C98" s="6" t="inlineStr">
+      <c r="C98" s="7" t="inlineStr">
         <is>
           <t>demo.HumanTechTree</t>
         </is>
       </c>
-      <c r="D98" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E98" s="6" t="inlineStr">
+      <c r="D98" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
         <is>
           <t>human_tech_tree@human_tech.xlsx</t>
         </is>
       </c>
-      <c r="F98" s="6" t="inlineStr">
+      <c r="F98" s="7" t="inlineStr">
         <is>
           <t>tree_id</t>
         </is>
       </c>
-      <c r="G98" s="6" t="n"/>
-      <c r="I98" s="6" t="n"/>
+      <c r="G98" s="7" t="n"/>
+      <c r="I98" s="7" t="n"/>
     </row>
     <row r="99">
-      <c r="B99" s="6" t="inlineStr">
+      <c r="B99" s="7" t="inlineStr">
         <is>
           <t>demo.TbHumanTechNode</t>
         </is>
       </c>
-      <c r="C99" s="6" t="inlineStr">
+      <c r="C99" s="7" t="inlineStr">
         <is>
           <t>demo.HumanTechNode</t>
         </is>
       </c>
-      <c r="D99" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
+      <c r="D99" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
         <is>
           <t>human_tech@human_tech.xlsx</t>
         </is>
       </c>
-      <c r="F99" s="6" t="inlineStr">
+      <c r="F99" s="7" t="inlineStr">
         <is>
           <t>node_id</t>
         </is>
       </c>
-      <c r="H99" s="6" t="n"/>
-      <c r="I99" s="6" t="n"/>
+      <c r="H99" s="7" t="n"/>
+      <c r="I99" s="7" t="n"/>
     </row>
     <row r="100">
-      <c r="B100" s="6" t="inlineStr">
+      <c r="B100" s="7" t="inlineStr">
         <is>
           <t>demo.TbHumanTechNodeLevel</t>
         </is>
       </c>
-      <c r="C100" s="6" t="inlineStr">
+      <c r="C100" s="7" t="inlineStr">
         <is>
           <t>demo.HumanTechNodeLevel</t>
         </is>
       </c>
-      <c r="D100" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E100" s="6" t="inlineStr">
+      <c r="D100" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
         <is>
           <t>human_tech_level@human_tech.xlsx</t>
         </is>
       </c>
-      <c r="F100" s="6" t="inlineStr">
+      <c r="F100" s="7" t="inlineStr">
         <is>
           <t>node_id+level</t>
         </is>
       </c>
-      <c r="I100" s="6" t="n"/>
+      <c r="I100" s="7" t="n"/>
     </row>
     <row r="101">
-      <c r="B101" s="6" t="inlineStr">
+      <c r="B101" s="7" t="inlineStr">
         <is>
           <t>demo.TbQuestAcceptDialog</t>
         </is>
       </c>
-      <c r="C101" s="6" t="inlineStr">
+      <c r="C101" s="7" t="inlineStr">
         <is>
           <t>demo.QuestAcceptDialog</t>
         </is>
       </c>
-      <c r="D101" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E101" s="6" t="inlineStr">
+      <c r="D101" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
         <is>
           <t>quest_accept_dialog@dialog.xlsx</t>
         </is>
       </c>
-      <c r="I101" s="6" t="n"/>
+      <c r="I101" s="7" t="n"/>
     </row>
     <row r="102" s="2">
-      <c r="B102" s="6" t="inlineStr">
+      <c r="B102" s="7" t="inlineStr">
         <is>
           <t>demo.TbQuestRemindDialog</t>
         </is>
       </c>
-      <c r="C102" s="6" t="inlineStr">
+      <c r="C102" s="7" t="inlineStr">
         <is>
           <t>demo.QuestRemindDialog</t>
         </is>
       </c>
-      <c r="D102" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E102" s="6" t="inlineStr">
+      <c r="D102" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
         <is>
           <t>quest_remind_dialog@dialog.xlsx</t>
         </is>
       </c>
-      <c r="F102" s="6" t="n"/>
-      <c r="G102" s="6" t="n"/>
-      <c r="I102" s="6" t="n"/>
+      <c r="F102" s="7" t="n"/>
+      <c r="G102" s="7" t="n"/>
+      <c r="I102" s="7" t="n"/>
     </row>
     <row r="103" s="2">
-      <c r="B103" s="6" t="inlineStr">
+      <c r="B103" s="7" t="inlineStr">
         <is>
           <t>demo.TbQuestObjectiveDialog</t>
         </is>
       </c>
-      <c r="C103" s="6" t="inlineStr">
+      <c r="C103" s="7" t="inlineStr">
         <is>
           <t>demo.QuestObjectiveDialog</t>
         </is>
       </c>
-      <c r="D103" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E103" s="6" t="inlineStr">
+      <c r="D103" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
         <is>
           <t>quest_objective_dialog@dialog.xlsx</t>
         </is>
       </c>
-      <c r="F103" s="6" t="n"/>
-      <c r="G103" s="6" t="n"/>
-      <c r="I103" s="6" t="n"/>
+      <c r="F103" s="7" t="n"/>
+      <c r="G103" s="7" t="n"/>
+      <c r="I103" s="7" t="n"/>
     </row>
     <row r="104">
-      <c r="B104" s="6" t="inlineStr">
+      <c r="B104" s="7" t="inlineStr">
         <is>
           <t>demo.TbNpcRoutineProfile</t>
         </is>
       </c>
-      <c r="C104" s="6" t="inlineStr">
+      <c r="C104" s="7" t="inlineStr">
         <is>
           <t>demo.NpcRoutineProfile</t>
         </is>
       </c>
-      <c r="D104" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E104" s="6" t="inlineStr">
+      <c r="D104" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
         <is>
           <t>npc_routine_profile@npc_routine.xlsx</t>
         </is>
       </c>
-      <c r="F104" s="6" t="inlineStr">
+      <c r="F104" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="G104" s="6" t="n"/>
-      <c r="I104" s="6" t="n"/>
+      <c r="G104" s="7" t="n"/>
+      <c r="I104" s="7" t="n"/>
     </row>
     <row r="105">
-      <c r="B105" s="6" t="inlineStr">
+      <c r="B105" s="7" t="inlineStr">
         <is>
           <t>demo.TbNpcRoutineRule</t>
         </is>
       </c>
-      <c r="C105" s="6" t="inlineStr">
+      <c r="C105" s="7" t="inlineStr">
         <is>
           <t>demo.NpcRoutineRule</t>
         </is>
       </c>
-      <c r="D105" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E105" s="6" t="inlineStr">
+      <c r="D105" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
         <is>
           <t>npc_routine_rule@npc_routine.xlsx</t>
         </is>
       </c>
-      <c r="F105" s="6" t="inlineStr">
+      <c r="F105" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="B106" s="6" t="inlineStr">
+      <c r="B106" s="7" t="inlineStr">
         <is>
           <t>demo.TbNpcRoutineBinding</t>
         </is>
       </c>
-      <c r="C106" s="6" t="inlineStr">
+      <c r="C106" s="7" t="inlineStr">
         <is>
           <t>demo.NpcRoutineBinding</t>
         </is>
       </c>
-      <c r="D106" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E106" s="6" t="inlineStr">
+      <c r="D106" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
         <is>
           <t>npc_routine_binding@npc_routine.xlsx</t>
         </is>
       </c>
-      <c r="F106" s="6" t="inlineStr">
+      <c r="F106" s="7" t="inlineStr">
         <is>
           <t>map_variant+overlay_id+character_key</t>
         </is>
       </c>
-      <c r="G106" s="6" t="inlineStr">
+      <c r="G106" s="7" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
     </row>
     <row r="107">
-      <c r="B107" s="6" t="inlineStr">
+      <c r="B107" s="7" t="inlineStr">
         <is>
           <t>demo.TbCultTechNode</t>
         </is>
       </c>
-      <c r="C107" s="6" t="inlineStr">
+      <c r="C107" s="7" t="inlineStr">
         <is>
           <t>demo.CultTechNode</t>
         </is>
       </c>
-      <c r="D107" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E107" s="6" t="inlineStr">
+      <c r="D107" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
         <is>
           <t>cult_tech_node@cult_tech.xlsx</t>
         </is>
       </c>
-      <c r="F107" s="6" t="n"/>
+      <c r="F107" s="7" t="n"/>
     </row>
     <row r="108">
-      <c r="B108" s="6" t="inlineStr">
+      <c r="B108" s="7" t="inlineStr">
         <is>
           <t>demo.TbCultTechNodeLevel</t>
         </is>
       </c>
-      <c r="C108" s="6" t="inlineStr">
+      <c r="C108" s="7" t="inlineStr">
         <is>
           <t>demo.CultTechNodeLevel</t>
         </is>
       </c>
-      <c r="D108" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
+      <c r="D108" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
         <is>
           <t>cult_tech_node_level@cult_tech.xlsx</t>
         </is>
       </c>
-      <c r="F108" s="6" t="inlineStr">
+      <c r="F108" s="7" t="inlineStr">
         <is>
           <t>node_id+level</t>
         </is>
       </c>
     </row>
     <row r="109">
-      <c r="B109" s="6" t="inlineStr">
+      <c r="B109" s="7" t="inlineStr">
         <is>
           <t>demo.TbNpcLocomotionProfile</t>
         </is>
       </c>
-      <c r="C109" s="6" t="inlineStr">
+      <c r="C109" s="7" t="inlineStr">
         <is>
           <t>demo.NpcLocomotionProfile</t>
         </is>
       </c>
-      <c r="D109" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E109" s="6" t="inlineStr">
+      <c r="D109" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
         <is>
           <t>npc_locomotion_profile@npc_routine.xlsx</t>
         </is>
       </c>
-      <c r="F109" s="6" t="inlineStr">
+      <c r="F109" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
     </row>
     <row r="110">
-      <c r="B110" s="6" t="inlineStr">
+      <c r="B110" s="7" t="inlineStr">
         <is>
           <t>demo.TbFacilityDefinition</t>
         </is>
       </c>
-      <c r="C110" s="6" t="inlineStr">
+      <c r="C110" s="7" t="inlineStr">
         <is>
           <t>demo.FacilityDefinition</t>
         </is>
       </c>
-      <c r="D110" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E110" s="6" t="inlineStr">
+      <c r="D110" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
         <is>
           <t>facility_definition@facility_definition.xlsx</t>
         </is>
       </c>
-      <c r="F110" s="6" t="inlineStr">
+      <c r="F110" s="7" t="inlineStr">
         <is>
           <t>facility_id</t>
         </is>
       </c>
     </row>
     <row r="111">
-      <c r="B111" s="6" t="inlineStr">
+      <c r="B111" s="7" t="inlineStr">
         <is>
           <t>demo.TbFacilityDevelopmentDefinition</t>
         </is>
       </c>
-      <c r="C111" s="6" t="inlineStr">
+      <c r="C111" s="7" t="inlineStr">
         <is>
           <t>demo.FacilityDevelopmentDefinition</t>
         </is>
       </c>
-      <c r="D111" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E111" s="6" t="inlineStr">
+      <c r="D111" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
         <is>
           <t>facility_development_definition@facility_development.xlsx</t>
         </is>
       </c>
-      <c r="F111" s="6" t="inlineStr">
+      <c r="F111" s="7" t="inlineStr">
         <is>
           <t>facility_id</t>
         </is>
       </c>
-      <c r="G111" s="6" t="n"/>
+      <c r="G111" s="7" t="n"/>
     </row>
     <row r="112">
-      <c r="B112" s="6" t="inlineStr">
+      <c r="B112" s="7" t="inlineStr">
         <is>
           <t>demo.TbFacilityDevelopmentLevel</t>
         </is>
       </c>
-      <c r="C112" s="6" t="inlineStr">
+      <c r="C112" s="7" t="inlineStr">
         <is>
           <t>demo.FacilityDevelopmentLevel</t>
         </is>
       </c>
-      <c r="D112" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E112" s="6" t="inlineStr">
+      <c r="D112" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
         <is>
           <t>facility_development_level@facility_development.xlsx</t>
         </is>
       </c>
-      <c r="F112" s="6" t="inlineStr">
+      <c r="F112" s="7" t="inlineStr">
         <is>
           <t>facility_id+level</t>
         </is>
       </c>
-      <c r="G112" s="6" t="n"/>
+      <c r="G112" s="7" t="n"/>
     </row>
     <row r="113">
-      <c r="B113" s="6" t="inlineStr">
+      <c r="B113" s="7" t="inlineStr">
         <is>
           <t>demo.TbTownFacilitySite</t>
         </is>
       </c>
-      <c r="C113" s="6" t="inlineStr">
+      <c r="C113" s="7" t="inlineStr">
         <is>
           <t>demo.TownFacilitySite</t>
         </is>
       </c>
-      <c r="D113" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E113" s="6" t="inlineStr">
+      <c r="D113" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
         <is>
           <t>town_facility_site@facility_development.xlsx</t>
         </is>
       </c>
-      <c r="F113" s="6" t="inlineStr">
+      <c r="F113" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
     </row>
     <row r="114">
-      <c r="B114" s="6" t="inlineStr">
+      <c r="B114" s="7" t="inlineStr">
         <is>
           <t>demo.TbFacilityRenovation</t>
         </is>
       </c>
-      <c r="C114" s="6" t="inlineStr">
+      <c r="C114" s="7" t="inlineStr">
         <is>
           <t>demo.FacilityRenovation</t>
         </is>
       </c>
-      <c r="D114" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
+      <c r="D114" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
         <is>
           <t>facility_renovation@facility_development.xlsx</t>
         </is>
       </c>
-      <c r="F114" s="6" t="inlineStr">
+      <c r="F114" s="7" t="inlineStr">
         <is>
           <t>facility_cfg_id+renovation_id</t>
         </is>
       </c>
-      <c r="G114" s="6" t="n"/>
+      <c r="G114" s="7" t="n"/>
     </row>
     <row r="115">
-      <c r="B115" s="6" t="n"/>
-      <c r="C115" s="6" t="n"/>
-      <c r="D115" s="6" t="n"/>
-      <c r="E115" s="6" t="n"/>
+      <c r="B115" s="7" t="n"/>
+      <c r="C115" s="7" t="n"/>
+      <c r="D115" s="7" t="n"/>
+      <c r="E115" s="7" t="n"/>
     </row>
     <row r="116">
-      <c r="B116" s="6" t="n"/>
-      <c r="C116" s="6" t="n"/>
-      <c r="D116" s="6" t="n"/>
-      <c r="E116" s="6" t="n"/>
-      <c r="F116" s="6" t="n"/>
+      <c r="B116" s="7" t="n"/>
+      <c r="C116" s="7" t="n"/>
+      <c r="D116" s="7" t="n"/>
+      <c r="E116" s="7" t="n"/>
+      <c r="F116" s="7" t="n"/>
     </row>
     <row r="117">
-      <c r="B117" s="6" t="n"/>
-      <c r="C117" s="6" t="n"/>
-      <c r="D117" s="6" t="n"/>
-      <c r="E117" s="6" t="n"/>
-      <c r="F117" s="6" t="n"/>
+      <c r="B117" s="7" t="n"/>
+      <c r="C117" s="7" t="n"/>
+      <c r="D117" s="7" t="n"/>
+      <c r="E117" s="7" t="n"/>
+      <c r="F117" s="7" t="n"/>
     </row>
     <row r="118">
-      <c r="B118" s="6" t="n"/>
-      <c r="C118" s="6" t="n"/>
-      <c r="D118" s="6" t="n"/>
-      <c r="E118" s="6" t="n"/>
-      <c r="F118" s="6" t="n"/>
+      <c r="B118" s="7" t="n"/>
+      <c r="C118" s="7" t="n"/>
+      <c r="D118" s="7" t="n"/>
+      <c r="E118" s="7" t="n"/>
+      <c r="F118" s="7" t="n"/>
     </row>
     <row r="119">
-      <c r="B119" s="6" t="n"/>
-      <c r="C119" s="6" t="n"/>
-      <c r="D119" s="6" t="n"/>
-      <c r="E119" s="6" t="n"/>
-      <c r="F119" s="6" t="n"/>
+      <c r="B119" s="7" t="n"/>
+      <c r="C119" s="7" t="n"/>
+      <c r="D119" s="7" t="n"/>
+      <c r="E119" s="7" t="n"/>
+      <c r="F119" s="7" t="n"/>
     </row>
     <row r="120">
-      <c r="B120" s="6" t="n"/>
-      <c r="C120" s="6" t="n"/>
-      <c r="D120" s="6" t="n"/>
-      <c r="E120" s="6" t="n"/>
-      <c r="F120" s="6" t="n"/>
+      <c r="B120" s="7" t="n"/>
+      <c r="C120" s="7" t="n"/>
+      <c r="D120" s="7" t="n"/>
+      <c r="E120" s="7" t="n"/>
+      <c r="F120" s="7" t="n"/>
     </row>
     <row r="121">
-      <c r="B121" s="6" t="n"/>
-      <c r="C121" s="6" t="n"/>
-      <c r="D121" s="6" t="n"/>
-      <c r="E121" s="6" t="n"/>
-      <c r="F121" s="6" t="n"/>
+      <c r="B121" s="7" t="n"/>
+      <c r="C121" s="7" t="n"/>
+      <c r="D121" s="7" t="n"/>
+      <c r="E121" s="7" t="n"/>
+      <c r="F121" s="7" t="n"/>
     </row>
     <row r="122">
-      <c r="B122" s="6" t="inlineStr">
+      <c r="B122" s="7" t="inlineStr">
         <is>
           <t>demo.TbCharacterFacilitySupervisor</t>
         </is>
       </c>
-      <c r="C122" s="6" t="inlineStr">
+      <c r="C122" s="7" t="inlineStr">
         <is>
           <t>demo.CharacterFacilitySupervisor</t>
         </is>
       </c>
-      <c r="D122" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E122" s="6" t="inlineStr">
+      <c r="D122" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
         <is>
           <t>character_facility_supervisor@facility_development.xlsx</t>
         </is>
       </c>
-      <c r="F122" s="6" t="inlineStr">
+      <c r="F122" s="7" t="inlineStr">
         <is>
           <t>character_key</t>
         </is>
       </c>
     </row>
     <row r="123">
-      <c r="B123" s="6" t="inlineStr">
+      <c r="B123" s="7" t="inlineStr">
         <is>
           <t>demo.TbHumanArmar</t>
         </is>
       </c>
-      <c r="C123" s="6" t="inlineStr">
+      <c r="C123" s="7" t="inlineStr">
         <is>
           <t>demo.HumanArmar</t>
         </is>
       </c>
-      <c r="D123" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E123" s="6" t="inlineStr">
+      <c r="D123" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
         <is>
           <t>human_armar@human_armar.xlsx</t>
         </is>
       </c>
-      <c r="F123" s="6" t="inlineStr">
+      <c r="F123" s="7" t="inlineStr">
         <is>
           <t>item_id</t>
         </is>
       </c>
-      <c r="G123" s="6" t="inlineStr">
+      <c r="G123" s="7" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="H123" s="6" t="n"/>
+      <c r="H123" s="7" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="6" t="n"/>
-      <c r="B124" s="6" t="inlineStr">
+      <c r="A124" s="7" t="n"/>
+      <c r="B124" s="7" t="inlineStr">
         <is>
           <t>demo.TbNpcViewRandomization</t>
         </is>
       </c>
-      <c r="C124" s="6" t="inlineStr">
+      <c r="C124" s="7" t="inlineStr">
         <is>
           <t>demo.NpcViewRandomization</t>
         </is>
       </c>
-      <c r="D124" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E124" s="6" t="inlineStr">
+      <c r="D124" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
         <is>
           <t>npc_view_randomization@npc_view_randomization.xlsx</t>
         </is>
       </c>
-      <c r="F124" s="6" t="inlineStr">
+      <c r="F124" s="7" t="inlineStr">
         <is>
           <t>npc_id+view_prefab_name</t>
         </is>
       </c>
-      <c r="G124" s="6" t="inlineStr">
+      <c r="G124" s="7" t="inlineStr">
         <is>
           <t>list</t>
         </is>
       </c>
-      <c r="H124" s="6" t="inlineStr">
+      <c r="H124" s="7" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="I124" s="6" t="inlineStr">
+      <c r="I124" s="7" t="inlineStr">
         <is>
           <t>?? NPC ?????</t>
         </is>
       </c>
     </row>
     <row r="125">
-      <c r="B125" s="6" t="inlineStr">
+      <c r="B125" s="7" t="inlineStr">
         <is>
           <t>demo.TbCultAncientSeat</t>
         </is>
       </c>
-      <c r="C125" s="6" t="inlineStr">
+      <c r="C125" s="7" t="inlineStr">
         <is>
           <t>demo.CultAncientSeat</t>
         </is>
       </c>
-      <c r="D125" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E125" s="6" t="inlineStr">
+      <c r="D125" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
         <is>
           <t>cult_ancient_seat@cult_ancient_seat.xlsx</t>
         </is>
       </c>
-      <c r="F125" s="6" t="inlineStr">
+      <c r="F125" s="7" t="inlineStr">
         <is>
           <t>seat_id</t>
         </is>
       </c>
     </row>
     <row r="126">
-      <c r="B126" s="6" t="inlineStr">
+      <c r="B126" s="7" t="inlineStr">
         <is>
           <t>demo.TbCultSeatTechNode</t>
         </is>
       </c>
-      <c r="C126" s="6" t="inlineStr">
+      <c r="C126" s="7" t="inlineStr">
         <is>
           <t>demo.CultSeatTechNode</t>
         </is>
       </c>
-      <c r="D126" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E126" s="6" t="inlineStr">
+      <c r="D126" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
         <is>
           <t>cult_seat_tech_node@cult_ancient_seat.xlsx</t>
         </is>
       </c>
-      <c r="F126" s="6" t="inlineStr">
+      <c r="F126" s="7" t="inlineStr">
         <is>
           <t>node_id</t>
         </is>
       </c>
     </row>
     <row r="127">
-      <c r="B127" s="6" t="inlineStr">
+      <c r="B127" s="7" t="inlineStr">
         <is>
           <t>demo.TbCultSeatTechNodeLevel</t>
         </is>
       </c>
-      <c r="C127" s="6" t="inlineStr">
+      <c r="C127" s="7" t="inlineStr">
         <is>
           <t>demo.CultSeatTechNodeLevel</t>
         </is>
       </c>
-      <c r="D127" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E127" s="6" t="inlineStr">
+      <c r="D127" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
         <is>
           <t>cult_seat_tech_node_level@cult_ancient_seat.xlsx</t>
         </is>
       </c>
-      <c r="F127" s="6" t="inlineStr">
+      <c r="F127" s="7" t="inlineStr">
         <is>
           <t>node_id+level</t>
         </is>
       </c>
     </row>
     <row r="128">
-      <c r="B128" t="inlineStr">
+      <c r="B128" s="7" t="inlineStr">
         <is>
           <t>demo.TbJingYuanTypeInfo</t>
         </is>
       </c>
-      <c r="C128" t="inlineStr">
+      <c r="C128" s="7" t="inlineStr">
         <is>
           <t>demo.JingYuanTypeInfo</t>
         </is>
       </c>
-      <c r="D128" t="b">
-        <v>1</v>
-      </c>
-      <c r="E128" t="inlineStr">
+      <c r="D128" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
         <is>
           <t>jingyuan_type_info@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F128" s="7" t="inlineStr">
         <is>
           <t>type_id</t>
         </is>
       </c>
     </row>
     <row r="129">
-      <c r="B129" t="inlineStr">
+      <c r="B129" s="7" t="inlineStr">
         <is>
           <t>demo.TbJingYuanPremiumEssence</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C129" s="7" t="inlineStr">
         <is>
           <t>demo.JingYuanPremiumEssence</t>
         </is>
       </c>
-      <c r="D129" t="b">
-        <v>1</v>
-      </c>
-      <c r="E129" t="inlineStr">
+      <c r="D129" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
         <is>
           <t>jingyuan_premium_essence@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F129" s="7" t="inlineStr">
         <is>
           <t>essence_id</t>
         </is>
       </c>
     </row>
     <row r="130">
-      <c r="B130" t="inlineStr">
+      <c r="B130" s="7" t="inlineStr">
         <is>
           <t>demo.TbJingYuanPremiumEffect</t>
         </is>
       </c>
-      <c r="C130" t="inlineStr">
+      <c r="C130" s="7" t="inlineStr">
         <is>
           <t>demo.JingYuanPremiumEffect</t>
         </is>
       </c>
-      <c r="D130" t="b">
-        <v>1</v>
-      </c>
-      <c r="E130" t="inlineStr">
+      <c r="D130" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
         <is>
           <t>jingyuan_premium_effect@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F130" s="7" t="inlineStr">
         <is>
           <t>type_id+drop_level+concentration_floor</t>
         </is>
       </c>
     </row>
     <row r="131">
-      <c r="B131" t="inlineStr">
+      <c r="B131" s="7" t="inlineStr">
         <is>
           <t>demo.TbJingYuanEssenceLevelMap</t>
         </is>
       </c>
-      <c r="C131" t="inlineStr">
+      <c r="C131" s="7" t="inlineStr">
         <is>
           <t>demo.JingYuanEssenceLevelMap</t>
         </is>
       </c>
-      <c r="D131" t="b">
-        <v>1</v>
-      </c>
-      <c r="E131" t="inlineStr">
+      <c r="D131" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
         <is>
           <t>jingyuan_essence_level_map@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F131" s="7" t="inlineStr">
         <is>
           <t>map_id</t>
         </is>
       </c>
     </row>
     <row r="132">
-      <c r="B132" t="inlineStr">
+      <c r="B132" s="7" t="inlineStr">
         <is>
           <t>demo.TbJingYuanTypePoolEnum</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C132" s="7" t="inlineStr">
         <is>
           <t>demo.JingYuanTypePoolEnum</t>
         </is>
       </c>
-      <c r="D132" t="b">
-        <v>1</v>
-      </c>
-      <c r="E132" t="inlineStr">
+      <c r="D132" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
         <is>
           <t>jingyuan_type_pool_enum@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F132" s="7" t="inlineStr">
         <is>
           <t>entry_id</t>
         </is>
       </c>
     </row>
     <row r="133">
-      <c r="B133" t="inlineStr">
+      <c r="B133" s="7" t="inlineStr">
         <is>
           <t>demo.TbNamedNpcJingYuanType</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C133" s="7" t="inlineStr">
         <is>
           <t>demo.NamedNpcJingYuanType</t>
         </is>
       </c>
-      <c r="D133" t="b">
-        <v>1</v>
-      </c>
-      <c r="E133" t="inlineStr">
+      <c r="D133" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
         <is>
           <t>named_npc_jingyuan_type@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F133" s="7" t="inlineStr">
         <is>
           <t>character_key</t>
         </is>
       </c>
     </row>
     <row r="134">
-      <c r="B134" t="inlineStr">
+      <c r="B134" s="7" t="inlineStr">
         <is>
           <t>demo.TbJingYuanTuneRule</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr">
+      <c r="C134" s="7" t="inlineStr">
         <is>
           <t>demo.JingYuanTuneRule</t>
         </is>
       </c>
-      <c r="D134" t="b">
-        <v>1</v>
-      </c>
-      <c r="E134" t="inlineStr">
+      <c r="D134" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E134" s="7" t="inlineStr">
         <is>
           <t>jingyuan_tune_rule@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F134" s="7" t="inlineStr">
         <is>
           <t>rule_id</t>
         </is>
       </c>
     </row>
     <row r="135">
-      <c r="B135" t="inlineStr">
+      <c r="B135" s="7" t="inlineStr">
         <is>
           <t>demo.TbJingYuanRenewalRule</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C135" s="7" t="inlineStr">
         <is>
           <t>demo.JingYuanRenewalRule</t>
         </is>
       </c>
-      <c r="D135" t="b">
-        <v>1</v>
-      </c>
-      <c r="E135" t="inlineStr">
+      <c r="D135" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E135" s="7" t="inlineStr">
         <is>
           <t>jingyuan_renewal_rule@jingyuan_codex.xlsx</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F135" s="7" t="inlineStr">
         <is>
           <t>rule_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="B136" s="7" t="inlineStr">
+        <is>
+          <t>demo.TbAlchemyMaterial</t>
+        </is>
+      </c>
+      <c r="C136" s="7" t="inlineStr">
+        <is>
+          <t>demo.AlchemyMaterial</t>
+        </is>
+      </c>
+      <c r="D136" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E136" s="7" t="inlineStr">
+        <is>
+          <t>alchemy_material@alchemy.xlsx</t>
+        </is>
+      </c>
+      <c r="F136" s="7" t="inlineStr">
+        <is>
+          <t>item_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="B137" s="7" t="inlineStr">
+        <is>
+          <t>demo.TbAlchemyFurnace</t>
+        </is>
+      </c>
+      <c r="C137" s="7" t="inlineStr">
+        <is>
+          <t>demo.AlchemyFurnace</t>
+        </is>
+      </c>
+      <c r="D137" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E137" s="7" t="inlineStr">
+        <is>
+          <t>alchemy_furnace@alchemy.xlsx</t>
+        </is>
+      </c>
+      <c r="F137" s="7" t="inlineStr">
+        <is>
+          <t>furnace_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="B138" s="7" t="inlineStr">
+        <is>
+          <t>demo.TbAlchemyTool</t>
+        </is>
+      </c>
+      <c r="C138" s="7" t="inlineStr">
+        <is>
+          <t>demo.AlchemyTool</t>
+        </is>
+      </c>
+      <c r="D138" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E138" s="7" t="inlineStr">
+        <is>
+          <t>alchemy_tool@alchemy.xlsx</t>
+        </is>
+      </c>
+      <c r="F138" s="7" t="inlineStr">
+        <is>
+          <t>tool_id</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="B139" s="7" t="inlineStr">
+        <is>
+          <t>demo.TbAlchemyRecipe</t>
+        </is>
+      </c>
+      <c r="C139" s="7" t="inlineStr">
+        <is>
+          <t>demo.AlchemyRecipe</t>
+        </is>
+      </c>
+      <c r="D139" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>alchemy_recipe@alchemy.xlsx</t>
+        </is>
+      </c>
+      <c r="F139" s="7" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="B140" s="7" t="inlineStr">
+        <is>
+          <t>demo.TbAlchemyProgress</t>
+        </is>
+      </c>
+      <c r="C140" s="7" t="inlineStr">
+        <is>
+          <t>demo.AlchemyProgress</t>
+        </is>
+      </c>
+      <c r="D140" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>alchemy_progress@alchemy.xlsx</t>
+        </is>
+      </c>
+      <c r="F140" s="7" t="inlineStr">
+        <is>
+          <t>level</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="7" t="n"/>
+      <c r="B141" s="7" t="inlineStr">
+        <is>
+          <t>demo.TbTownWalkerPopulation</t>
+        </is>
+      </c>
+      <c r="C141" s="7" t="inlineStr">
+        <is>
+          <t>demo.TownWalkerPopulation</t>
+        </is>
+      </c>
+      <c r="D141" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E141" s="7" t="inlineStr">
+        <is>
+          <t>town_walker_population@town_walker_population.xlsx</t>
+        </is>
+      </c>
+      <c r="F141" s="7" t="inlineStr">
+        <is>
+          <t>logic_area_id+stage</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="n"/>
+      <c r="H141" s="7" t="n"/>
+      <c r="I141" s="7" t="inlineStr">
+        <is>
+          <t>城镇路人数量阶段配置，按 Prosperity 选择最高可用阶段</t>
+        </is>
+      </c>
+      <c r="J141" s="7" t="n"/>
+      <c r="K141" s="7" t="n"/>
+    </row>
+    <row r="142">
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>demo.TbAlchemyVirtueDef</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>demo.AlchemyVirtueDef</t>
+        </is>
+      </c>
+      <c r="D142" t="b">
+        <v>1</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>alchemy_virtue_def@alchemy.xlsx</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>demo.TbAlchemyAspectDef</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>demo.AlchemyAspectDef</t>
+        </is>
+      </c>
+      <c r="D143" t="b">
+        <v>1</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>alchemy_aspect_def@alchemy.xlsx</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>id</t>
         </is>
       </c>
     </row>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -3672,29 +3672,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="B140" s="7" t="inlineStr">
-        <is>
-          <t>demo.TbAlchemyProgress</t>
-        </is>
-      </c>
-      <c r="C140" s="7" t="inlineStr">
-        <is>
-          <t>demo.AlchemyProgress</t>
-        </is>
-      </c>
-      <c r="D140" s="7" t="b">
-        <v>1</v>
-      </c>
-      <c r="E140" s="7" t="inlineStr">
-        <is>
-          <t>alchemy_progress@alchemy.xlsx</t>
-        </is>
-      </c>
-      <c r="F140" s="7" t="inlineStr">
-        <is>
-          <t>level</t>
-        </is>
-      </c>
+      <c r="B140" s="7" t="n"/>
+      <c r="C140" s="7" t="n"/>
+      <c r="D140" s="7" t="n"/>
+      <c r="E140" s="7" t="n"/>
+      <c r="F140" s="7" t="n"/>
     </row>
     <row r="141">
       <c r="A141" s="7" t="n"/>
@@ -3732,50 +3714,50 @@
       <c r="K141" s="7" t="n"/>
     </row>
     <row r="142">
-      <c r="B142" t="inlineStr">
+      <c r="B142" s="7" t="inlineStr">
         <is>
           <t>demo.TbAlchemyVirtueDef</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C142" s="7" t="inlineStr">
         <is>
           <t>demo.AlchemyVirtueDef</t>
         </is>
       </c>
-      <c r="D142" t="b">
-        <v>1</v>
-      </c>
-      <c r="E142" t="inlineStr">
+      <c r="D142" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E142" s="7" t="inlineStr">
         <is>
           <t>alchemy_virtue_def@alchemy.xlsx</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F142" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
     </row>
     <row r="143">
-      <c r="B143" t="inlineStr">
+      <c r="B143" s="7" t="inlineStr">
         <is>
           <t>demo.TbAlchemyAspectDef</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C143" s="7" t="inlineStr">
         <is>
           <t>demo.AlchemyAspectDef</t>
         </is>
       </c>
-      <c r="D143" t="b">
-        <v>1</v>
-      </c>
-      <c r="E143" t="inlineStr">
+      <c r="D143" s="7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E143" s="7" t="inlineStr">
         <is>
           <t>alchemy_aspect_def@alchemy.xlsx</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F143" s="7" t="inlineStr">
         <is>
           <t>id</t>
         </is>

--- a/Config/Datas/__tables__.xlsx
+++ b/Config/Datas/__tables__.xlsx
@@ -368,7 +368,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K161"/>
+  <dimension ref="A1:K163"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col width="67.75" customWidth="1" style="2" min="2" max="2"/>
@@ -4339,37 +4339,107 @@
       </c>
     </row>
     <row r="161">
-      <c r="B161" t="inlineStr">
+      <c r="B161" s="9" t="inlineStr">
         <is>
           <t>demo.TbAbstractGroupStageReward</t>
         </is>
       </c>
-      <c r="C161" t="inlineStr">
+      <c r="C161" s="9" t="inlineStr">
         <is>
           <t>demo.AbstractGroupStageReward</t>
         </is>
       </c>
-      <c r="D161" t="b">
-        <v>1</v>
-      </c>
-      <c r="E161" t="inlineStr">
+      <c r="D161" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E161" s="9" t="inlineStr">
         <is>
           <t>abstract_group_stage_reward@abstract_group_stage_reward.xlsx</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="F161" s="9" t="inlineStr">
         <is>
           <t>group_id+stage+reward_index</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
+      <c r="H161" s="9" t="inlineStr">
         <is>
           <t>c,s</t>
         </is>
       </c>
-      <c r="I161" t="inlineStr">
+      <c r="I161" s="9" t="inlineStr">
         <is>
           <t>抽象团体阶段奖励</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="B162" s="9" t="inlineStr">
+        <is>
+          <t>demo.TbDreamPasserbyRegion</t>
+        </is>
+      </c>
+      <c r="C162" s="9" t="inlineStr">
+        <is>
+          <t>demo.DreamPasserbyRegion</t>
+        </is>
+      </c>
+      <c r="D162" s="9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E162" s="9" t="inlineStr">
+        <is>
+          <t>dream_passerby_region@dream_passerby_region.xlsx</t>
+        </is>
+      </c>
+      <c r="F162" s="9" t="inlineStr">
+        <is>
+          <t>region_id</t>
+        </is>
+      </c>
+      <c r="H162" s="9" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I162" s="9" t="inlineStr">
+        <is>
+          <t>入梦路人区域</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>demo.TbDreamPasserby</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>demo.DreamPasserby</t>
+        </is>
+      </c>
+      <c r="D163" t="b">
+        <v>1</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>dream_passerby@dream_passerby.xlsx</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>passerby_id</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>入梦抽象路人</t>
         </is>
       </c>
     </row>
